--- a/Översikt EKERÖ.xlsx
+++ b/Översikt EKERÖ.xlsx
@@ -601,7 +601,7 @@
         <v>46241</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -728,7 +728,7 @@
         <v>44872</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -848,7 +848,7 @@
         <v>44974</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -963,7 +963,7 @@
         <v>45148</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1056,7 +1056,7 @@
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A 3218-2022</t>
+          <t>A 17520-2026</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1070,10 +1070,10 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>44582</v>
+        <v>46119</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1085,8 +1085,13 @@
           <t>EKERÖ</t>
         </is>
       </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I6" t="n">
-        <v>1.2</v>
+        <v>2.2</v>
       </c>
       <c r="J6" t="n">
         <v>1</v>
@@ -1095,13 +1100,13 @@
         <v>1</v>
       </c>
       <c r="L6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M6" t="n">
         <v>1</v>
       </c>
       <c r="N6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1110,21 +1115,130 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="R6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
       </c>
       <c r="T6" t="n">
+        <v>5</v>
+      </c>
+      <c r="U6" t="n">
+        <v>1</v>
+      </c>
+      <c r="V6" s="2" t="inlineStr">
+        <is>
+          <t>Läderbagge
+Blekticka
+Ekticka
+Kandelabersvamp
+Gulgrön kantmusseron</t>
+        </is>
+      </c>
+      <c r="W6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/artfynd/A 17520-2026 artfynd.xlsx", "A 17520-2026")</f>
+        <v/>
+      </c>
+      <c r="X6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor/A 17520-2026 karta.png", "A 17520-2026")</f>
+        <v/>
+      </c>
+      <c r="Y6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor_geotiff/A 17520-2026 georefererad karta.tif", "A 17520-2026")</f>
+        <v/>
+      </c>
+      <c r="AA6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomål/A 17520-2026 FSC-klagomål.docx", "A 17520-2026")</f>
+        <v/>
+      </c>
+      <c r="AB6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomålsmail/A 17520-2026 FSC-klagomål mail.docx", "A 17520-2026")</f>
+        <v/>
+      </c>
+      <c r="AC6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsyn/A 17520-2026 tillsynsbegäran.docx", "A 17520-2026")</f>
+        <v/>
+      </c>
+      <c r="AD6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsynsmail/A 17520-2026 tillsynsbegäran mail.docx", "A 17520-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7" ht="15" customHeight="1">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>A 3218-2022</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D7" s="1" t="n">
+        <v>44582</v>
+      </c>
+      <c r="E7" s="1" t="n">
+        <v>46280</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>EKERÖ</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="J7" t="n">
+        <v>1</v>
+      </c>
+      <c r="K7" t="n">
+        <v>1</v>
+      </c>
+      <c r="L7" t="n">
+        <v>1</v>
+      </c>
+      <c r="M7" t="n">
+        <v>1</v>
+      </c>
+      <c r="N7" t="n">
+        <v>1</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>3</v>
+      </c>
+      <c r="R7" t="n">
+        <v>2</v>
+      </c>
+      <c r="S7" t="n">
+        <v>5</v>
+      </c>
+      <c r="T7" t="n">
         <v>8</v>
       </c>
-      <c r="U6" t="n">
+      <c r="U7" t="n">
         <v>6</v>
       </c>
-      <c r="V6" s="2" t="inlineStr">
+      <c r="V7" s="2" t="inlineStr">
         <is>
           <t>Bombmurkla
 Gul lammticka
@@ -1133,146 +1247,32 @@
 Blåbär</t>
         </is>
       </c>
-      <c r="W6">
+      <c r="W7">
         <f>HYPERLINK("https://klasma.github.io/Logging_0125/artfynd/A 3218-2022 artfynd.xlsx", "A 3218-2022")</f>
         <v/>
       </c>
-      <c r="X6">
+      <c r="X7">
         <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor/A 3218-2022 karta.png", "A 3218-2022")</f>
         <v/>
       </c>
-      <c r="Y6">
+      <c r="Y7">
         <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor_geotiff/A 3218-2022 georefererad karta.tif", "A 3218-2022")</f>
         <v/>
       </c>
-      <c r="AA6">
+      <c r="AA7">
         <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomål/A 3218-2022 FSC-klagomål.docx", "A 3218-2022")</f>
         <v/>
       </c>
-      <c r="AB6">
+      <c r="AB7">
         <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomålsmail/A 3218-2022 FSC-klagomål mail.docx", "A 3218-2022")</f>
         <v/>
       </c>
-      <c r="AC6">
+      <c r="AC7">
         <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsyn/A 3218-2022 tillsynsbegäran.docx", "A 3218-2022")</f>
         <v/>
       </c>
-      <c r="AD6">
+      <c r="AD7">
         <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsynsmail/A 3218-2022 tillsynsbegäran mail.docx", "A 3218-2022")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="7" ht="15" customHeight="1">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>A 17520-2026</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D7" s="1" t="n">
-        <v>46119</v>
-      </c>
-      <c r="E7" s="1" t="n">
-        <v>46279</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>EKERÖ</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
-      <c r="I7" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="J7" t="n">
-        <v>1</v>
-      </c>
-      <c r="K7" t="n">
-        <v>1</v>
-      </c>
-      <c r="L7" t="n">
-        <v>3</v>
-      </c>
-      <c r="M7" t="n">
-        <v>1</v>
-      </c>
-      <c r="N7" t="n">
-        <v>0</v>
-      </c>
-      <c r="O7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>4</v>
-      </c>
-      <c r="R7" t="n">
-        <v>1</v>
-      </c>
-      <c r="S7" t="n">
-        <v>5</v>
-      </c>
-      <c r="T7" t="n">
-        <v>5</v>
-      </c>
-      <c r="U7" t="n">
-        <v>1</v>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>Läderbagge
-Blekticka
-Ekticka
-Kandelabersvamp
-Gulgrön kantmusseron</t>
-        </is>
-      </c>
-      <c r="W7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/artfynd/A 17520-2026 artfynd.xlsx", "A 17520-2026")</f>
-        <v/>
-      </c>
-      <c r="X7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor/A 17520-2026 karta.png", "A 17520-2026")</f>
-        <v/>
-      </c>
-      <c r="Y7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor_geotiff/A 17520-2026 georefererad karta.tif", "A 17520-2026")</f>
-        <v/>
-      </c>
-      <c r="AA7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomål/A 17520-2026 FSC-klagomål.docx", "A 17520-2026")</f>
-        <v/>
-      </c>
-      <c r="AB7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomålsmail/A 17520-2026 FSC-klagomål mail.docx", "A 17520-2026")</f>
-        <v/>
-      </c>
-      <c r="AC7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsyn/A 17520-2026 tillsynsbegäran.docx", "A 17520-2026")</f>
-        <v/>
-      </c>
-      <c r="AD7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsynsmail/A 17520-2026 tillsynsbegäran mail.docx", "A 17520-2026")</f>
         <v/>
       </c>
     </row>
@@ -1296,7 +1296,7 @@
         <v>46241</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1409,7 +1409,7 @@
         <v>44634</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1499,7 +1499,7 @@
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 49131-2025</t>
+          <t>A 13237-2023</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1513,10 +1513,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>45937</v>
+        <v>45002</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1528,20 +1528,25 @@
           <t>EKERÖ</t>
         </is>
       </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I10" t="n">
-        <v>0.9</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N10" t="n">
         <v>0</v>
@@ -1553,165 +1558,160 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="R10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
         <v>3</v>
       </c>
       <c r="T10" t="n">
+        <v>7</v>
+      </c>
+      <c r="U10" t="n">
+        <v>0</v>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
+        <is>
+          <t>Tallticka
+Granbarkgnagare
+Grönpyrola</t>
+        </is>
+      </c>
+      <c r="W10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/artfynd/A 13237-2023 artfynd.xlsx", "A 13237-2023")</f>
+        <v/>
+      </c>
+      <c r="X10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor/A 13237-2023 karta.png", "A 13237-2023")</f>
+        <v/>
+      </c>
+      <c r="Y10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor_geotiff/A 13237-2023 georefererad karta.tif", "A 13237-2023")</f>
+        <v/>
+      </c>
+      <c r="AA10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomål/A 13237-2023 FSC-klagomål.docx", "A 13237-2023")</f>
+        <v/>
+      </c>
+      <c r="AB10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomålsmail/A 13237-2023 FSC-klagomål mail.docx", "A 13237-2023")</f>
+        <v/>
+      </c>
+      <c r="AC10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsyn/A 13237-2023 tillsynsbegäran.docx", "A 13237-2023")</f>
+        <v/>
+      </c>
+      <c r="AD10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsynsmail/A 13237-2023 tillsynsbegäran mail.docx", "A 13237-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11" ht="15" customHeight="1">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>A 49131-2025</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D11" s="1" t="n">
+        <v>45937</v>
+      </c>
+      <c r="E11" s="1" t="n">
+        <v>46280</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>EKERÖ</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" t="n">
+        <v>2</v>
+      </c>
+      <c r="M11" t="n">
+        <v>1</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" t="n">
         <v>3</v>
       </c>
-      <c r="U10" t="n">
+      <c r="R11" t="n">
+        <v>1</v>
+      </c>
+      <c r="S11" t="n">
         <v>3</v>
       </c>
-      <c r="V10" s="2" t="inlineStr">
+      <c r="T11" t="n">
+        <v>3</v>
+      </c>
+      <c r="U11" t="n">
+        <v>3</v>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
         <is>
           <t>Jättemusseron
 Motaggsvamp
 Svartvit taggsvamp</t>
         </is>
       </c>
-      <c r="W10">
+      <c r="W11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0125/artfynd/A 49131-2025 artfynd.xlsx", "A 49131-2025")</f>
         <v/>
       </c>
-      <c r="X10">
+      <c r="X11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor/A 49131-2025 karta.png", "A 49131-2025")</f>
         <v/>
       </c>
-      <c r="Y10">
+      <c r="Y11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor_geotiff/A 49131-2025 georefererad karta.tif", "A 49131-2025")</f>
         <v/>
       </c>
-      <c r="AA10">
+      <c r="AA11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomål/A 49131-2025 FSC-klagomål.docx", "A 49131-2025")</f>
         <v/>
       </c>
-      <c r="AB10">
+      <c r="AB11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomålsmail/A 49131-2025 FSC-klagomål mail.docx", "A 49131-2025")</f>
         <v/>
       </c>
-      <c r="AC10">
+      <c r="AC11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsyn/A 49131-2025 tillsynsbegäran.docx", "A 49131-2025")</f>
         <v/>
       </c>
-      <c r="AD10">
+      <c r="AD11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsynsmail/A 49131-2025 tillsynsbegäran mail.docx", "A 49131-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="11" ht="15" customHeight="1">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>A 13237-2023</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D11" s="1" t="n">
-        <v>45002</v>
-      </c>
-      <c r="E11" s="1" t="n">
-        <v>46279</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>EKERÖ</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
-      <c r="I11" t="n">
-        <v>9.300000000000001</v>
-      </c>
-      <c r="J11" t="n">
-        <v>0</v>
-      </c>
-      <c r="K11" t="n">
-        <v>2</v>
-      </c>
-      <c r="L11" t="n">
-        <v>1</v>
-      </c>
-      <c r="M11" t="n">
-        <v>0</v>
-      </c>
-      <c r="N11" t="n">
-        <v>0</v>
-      </c>
-      <c r="O11" t="n">
-        <v>0</v>
-      </c>
-      <c r="P11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>1</v>
-      </c>
-      <c r="R11" t="n">
-        <v>0</v>
-      </c>
-      <c r="S11" t="n">
-        <v>3</v>
-      </c>
-      <c r="T11" t="n">
-        <v>7</v>
-      </c>
-      <c r="U11" t="n">
-        <v>0</v>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
-        <is>
-          <t>Tallticka
-Granbarkgnagare
-Grönpyrola</t>
-        </is>
-      </c>
-      <c r="W11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/artfynd/A 13237-2023 artfynd.xlsx", "A 13237-2023")</f>
-        <v/>
-      </c>
-      <c r="X11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor/A 13237-2023 karta.png", "A 13237-2023")</f>
-        <v/>
-      </c>
-      <c r="Y11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor_geotiff/A 13237-2023 georefererad karta.tif", "A 13237-2023")</f>
-        <v/>
-      </c>
-      <c r="AA11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomål/A 13237-2023 FSC-klagomål.docx", "A 13237-2023")</f>
-        <v/>
-      </c>
-      <c r="AB11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomålsmail/A 13237-2023 FSC-klagomål mail.docx", "A 13237-2023")</f>
-        <v/>
-      </c>
-      <c r="AC11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsyn/A 13237-2023 tillsynsbegäran.docx", "A 13237-2023")</f>
-        <v/>
-      </c>
-      <c r="AD11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsynsmail/A 13237-2023 tillsynsbegäran mail.docx", "A 13237-2023")</f>
         <v/>
       </c>
     </row>
@@ -1735,7 +1735,7 @@
         <v>45209</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1850,7 +1850,7 @@
         <v>45170</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1956,7 +1956,7 @@
         <v>44646</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2044,7 +2044,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 2533-2026</t>
+          <t>A 3221-2022</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2058,10 +2058,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>46037</v>
+        <v>44582</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2074,13 +2074,13 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>1.4</v>
+        <v>0.5</v>
       </c>
       <c r="J15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L15" t="n">
         <v>0</v>
@@ -2110,46 +2110,46 @@
         <v>1</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/artfynd/A 2533-2026 artfynd.xlsx", "A 2533-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/artfynd/A 3221-2022 artfynd.xlsx", "A 3221-2022")</f>
         <v/>
       </c>
       <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor/A 2533-2026 karta.png", "A 2533-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor/A 3221-2022 karta.png", "A 3221-2022")</f>
         <v/>
       </c>
       <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor_geotiff/A 2533-2026 georefererad karta.tif", "A 2533-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor_geotiff/A 3221-2022 georefererad karta.tif", "A 3221-2022")</f>
         <v/>
       </c>
       <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomål/A 2533-2026 FSC-klagomål.docx", "A 2533-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomål/A 3221-2022 FSC-klagomål.docx", "A 3221-2022")</f>
         <v/>
       </c>
       <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomålsmail/A 2533-2026 FSC-klagomål mail.docx", "A 2533-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomålsmail/A 3221-2022 FSC-klagomål mail.docx", "A 3221-2022")</f>
         <v/>
       </c>
       <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsyn/A 2533-2026 tillsynsbegäran.docx", "A 2533-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsyn/A 3221-2022 tillsynsbegäran.docx", "A 3221-2022")</f>
         <v/>
       </c>
       <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsynsmail/A 2533-2026 tillsynsbegäran mail.docx", "A 2533-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsynsmail/A 3221-2022 tillsynsbegäran mail.docx", "A 3221-2022")</f>
         <v/>
       </c>
     </row>
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 3221-2022</t>
+          <t>A 13794-2023</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2163,10 +2163,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>44582</v>
+        <v>45007</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2179,16 +2179,16 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>0.5</v>
+        <v>4.8</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M16" t="n">
         <v>0</v>
@@ -2203,7 +2203,7 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R16" t="n">
         <v>0</v>
@@ -2215,46 +2215,46 @@
         <v>1</v>
       </c>
       <c r="U16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/artfynd/A 3221-2022 artfynd.xlsx", "A 3221-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/artfynd/A 13794-2023 artfynd.xlsx", "A 13794-2023")</f>
         <v/>
       </c>
       <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor/A 3221-2022 karta.png", "A 3221-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor/A 13794-2023 karta.png", "A 13794-2023")</f>
         <v/>
       </c>
       <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor_geotiff/A 3221-2022 georefererad karta.tif", "A 3221-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor_geotiff/A 13794-2023 georefererad karta.tif", "A 13794-2023")</f>
         <v/>
       </c>
       <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomål/A 3221-2022 FSC-klagomål.docx", "A 3221-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomål/A 13794-2023 FSC-klagomål.docx", "A 13794-2023")</f>
         <v/>
       </c>
       <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomålsmail/A 3221-2022 FSC-klagomål mail.docx", "A 3221-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomålsmail/A 13794-2023 FSC-klagomål mail.docx", "A 13794-2023")</f>
         <v/>
       </c>
       <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsyn/A 3221-2022 tillsynsbegäran.docx", "A 3221-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsyn/A 13794-2023 tillsynsbegäran.docx", "A 13794-2023")</f>
         <v/>
       </c>
       <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsynsmail/A 3221-2022 tillsynsbegäran mail.docx", "A 3221-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsynsmail/A 13794-2023 tillsynsbegäran mail.docx", "A 13794-2023")</f>
         <v/>
       </c>
     </row>
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 13794-2023</t>
+          <t>A 2533-2026</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2268,10 +2268,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45007</v>
+        <v>46037</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2284,16 +2284,16 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>4.8</v>
+        <v>1.4</v>
       </c>
       <c r="J17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K17" t="n">
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
         <v>0</v>
@@ -2308,7 +2308,7 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
         <v>0</v>
@@ -2324,35 +2324,35 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/artfynd/A 13794-2023 artfynd.xlsx", "A 13794-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/artfynd/A 2533-2026 artfynd.xlsx", "A 2533-2026")</f>
         <v/>
       </c>
       <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor/A 13794-2023 karta.png", "A 13794-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor/A 2533-2026 karta.png", "A 2533-2026")</f>
         <v/>
       </c>
       <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor_geotiff/A 13794-2023 georefererad karta.tif", "A 13794-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor_geotiff/A 2533-2026 georefererad karta.tif", "A 2533-2026")</f>
         <v/>
       </c>
       <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomål/A 13794-2023 FSC-klagomål.docx", "A 13794-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomål/A 2533-2026 FSC-klagomål.docx", "A 2533-2026")</f>
         <v/>
       </c>
       <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomålsmail/A 13794-2023 FSC-klagomål mail.docx", "A 13794-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomålsmail/A 2533-2026 FSC-klagomål mail.docx", "A 2533-2026")</f>
         <v/>
       </c>
       <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsyn/A 13794-2023 tillsynsbegäran.docx", "A 13794-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsyn/A 2533-2026 tillsynsbegäran.docx", "A 2533-2026")</f>
         <v/>
       </c>
       <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsynsmail/A 13794-2023 tillsynsbegäran mail.docx", "A 13794-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsynsmail/A 2533-2026 tillsynsbegäran mail.docx", "A 2533-2026")</f>
         <v/>
       </c>
     </row>
@@ -2376,7 +2376,7 @@
         <v>45671</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2481,7 +2481,7 @@
         <v>44670</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2554,7 +2554,7 @@
         <v>44802</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2610,7 +2610,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 50184-2023</t>
+          <t>A 3219-2022</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2624,10 +2624,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45208</v>
+        <v>44582</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2640,7 +2640,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>10.8</v>
+        <v>0.5</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2683,7 +2683,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 56002-2024</t>
+          <t>A 63378-2025</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2697,10 +2697,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>45623</v>
+        <v>46010</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2713,7 +2713,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>3.4</v>
+        <v>4.8</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2756,7 +2756,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 37245-2025</t>
+          <t>A 2535-2026</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2770,10 +2770,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45876</v>
+        <v>46037</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2786,7 +2786,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>1.1</v>
+        <v>1.6</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2829,7 +2829,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 61217-2024</t>
+          <t>A 50184-2023</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2843,10 +2843,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45645</v>
+        <v>45208</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2859,7 +2859,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>0.8</v>
+        <v>10.8</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2902,7 +2902,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 3222-2022</t>
+          <t>A 37245-2025</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2916,10 +2916,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>44582</v>
+        <v>45876</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2932,7 +2932,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>1.8</v>
+        <v>1.1</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2975,7 +2975,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 63378-2025</t>
+          <t>A 20399-2026</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2989,10 +2989,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>46010</v>
+        <v>46139</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3005,7 +3005,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>4.8</v>
+        <v>0.9</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -3048,7 +3048,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 2535-2026</t>
+          <t>A 20398-2026</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3062,10 +3062,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>46037</v>
+        <v>46139</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3078,7 +3078,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>1.6</v>
+        <v>2.4</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -3121,7 +3121,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 20399-2026</t>
+          <t>A 20898-2026</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3135,10 +3135,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>46139</v>
+        <v>46142</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3151,7 +3151,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>0.9</v>
+        <v>3.6</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -3194,7 +3194,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 20398-2026</t>
+          <t>A 55724-2024</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3208,10 +3208,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>46139</v>
+        <v>45622</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3224,7 +3224,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>2.4</v>
+        <v>0.5</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3267,7 +3267,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 3219-2022</t>
+          <t>A 34073-2025</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3277,14 +3277,14 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>44582</v>
+        <v>45845</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3297,7 +3297,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>0.5</v>
+        <v>2.9</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3340,7 +3340,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 20898-2026</t>
+          <t>A 33154-2026</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3354,10 +3354,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>46142</v>
+        <v>46244</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3369,8 +3369,13 @@
           <t>EKERÖ</t>
         </is>
       </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I31" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3413,7 +3418,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 60755-2024</t>
+          <t>A 35955-2023</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3427,10 +3432,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45644</v>
+        <v>45148</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3443,7 +3448,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>2.1</v>
+        <v>1.1</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3486,7 +3491,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 55724-2024</t>
+          <t>A 61217-2024</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3500,10 +3505,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45622</v>
+        <v>45645</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3516,7 +3521,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3559,7 +3564,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 35955-2023</t>
+          <t>A 56002-2024</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3573,10 +3578,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45148</v>
+        <v>45623</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3589,7 +3594,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>1.1</v>
+        <v>3.4</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3632,7 +3637,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 34073-2025</t>
+          <t>A 60728-2022</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3642,14 +3647,14 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45845</v>
+        <v>44913</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3662,7 +3667,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>2.9</v>
+        <v>1.2</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3705,7 +3710,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 33154-2026</t>
+          <t>A 3222-2022</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3719,10 +3724,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>46244</v>
+        <v>44582</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3734,13 +3739,8 @@
           <t>EKERÖ</t>
         </is>
       </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I36" t="n">
-        <v>3.5</v>
+        <v>1.8</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3783,7 +3783,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 60728-2022</t>
+          <t>A 60755-2024</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3797,10 +3797,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>44913</v>
+        <v>45644</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3813,7 +3813,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>1.2</v>
+        <v>2.1</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3873,7 +3873,7 @@
         <v>46153</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>

--- a/Översikt EKERÖ.xlsx
+++ b/Översikt EKERÖ.xlsx
@@ -601,7 +601,7 @@
         <v>46241</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -728,7 +728,7 @@
         <v>44872</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -848,7 +848,7 @@
         <v>44974</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -963,7 +963,7 @@
         <v>45148</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1073,7 +1073,7 @@
         <v>46119</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1187,7 +1187,7 @@
         <v>44582</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1296,7 +1296,7 @@
         <v>46241</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1409,7 +1409,7 @@
         <v>44634</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1499,7 +1499,7 @@
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 13237-2023</t>
+          <t>A 49131-2025</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1513,10 +1513,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>45002</v>
+        <v>45937</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1528,25 +1528,20 @@
           <t>EKERÖ</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I10" t="n">
-        <v>9.300000000000001</v>
+        <v>0.9</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
       </c>
       <c r="K10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" t="n">
         <v>2</v>
       </c>
-      <c r="L10" t="n">
-        <v>1</v>
-      </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N10" t="n">
         <v>0</v>
@@ -1558,160 +1553,165 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S10" t="n">
         <v>3</v>
       </c>
       <c r="T10" t="n">
+        <v>3</v>
+      </c>
+      <c r="U10" t="n">
+        <v>3</v>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
+        <is>
+          <t>Jättemusseron
+Motaggsvamp
+Svartvit taggsvamp</t>
+        </is>
+      </c>
+      <c r="W10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/artfynd/A 49131-2025 artfynd.xlsx", "A 49131-2025")</f>
+        <v/>
+      </c>
+      <c r="X10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor/A 49131-2025 karta.png", "A 49131-2025")</f>
+        <v/>
+      </c>
+      <c r="Y10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor_geotiff/A 49131-2025 georefererad karta.tif", "A 49131-2025")</f>
+        <v/>
+      </c>
+      <c r="AA10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomål/A 49131-2025 FSC-klagomål.docx", "A 49131-2025")</f>
+        <v/>
+      </c>
+      <c r="AB10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomålsmail/A 49131-2025 FSC-klagomål mail.docx", "A 49131-2025")</f>
+        <v/>
+      </c>
+      <c r="AC10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsyn/A 49131-2025 tillsynsbegäran.docx", "A 49131-2025")</f>
+        <v/>
+      </c>
+      <c r="AD10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsynsmail/A 49131-2025 tillsynsbegäran mail.docx", "A 49131-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11" ht="15" customHeight="1">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>A 13237-2023</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D11" s="1" t="n">
+        <v>45002</v>
+      </c>
+      <c r="E11" s="1" t="n">
+        <v>46281</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>EKERÖ</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" t="n">
+        <v>2</v>
+      </c>
+      <c r="L11" t="n">
+        <v>1</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>1</v>
+      </c>
+      <c r="R11" t="n">
+        <v>0</v>
+      </c>
+      <c r="S11" t="n">
+        <v>3</v>
+      </c>
+      <c r="T11" t="n">
         <v>7</v>
       </c>
-      <c r="U10" t="n">
-        <v>0</v>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
+      <c r="U11" t="n">
+        <v>0</v>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
         <is>
           <t>Tallticka
 Granbarkgnagare
 Grönpyrola</t>
         </is>
       </c>
-      <c r="W10">
+      <c r="W11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0125/artfynd/A 13237-2023 artfynd.xlsx", "A 13237-2023")</f>
         <v/>
       </c>
-      <c r="X10">
+      <c r="X11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor/A 13237-2023 karta.png", "A 13237-2023")</f>
         <v/>
       </c>
-      <c r="Y10">
+      <c r="Y11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor_geotiff/A 13237-2023 georefererad karta.tif", "A 13237-2023")</f>
         <v/>
       </c>
-      <c r="AA10">
+      <c r="AA11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomål/A 13237-2023 FSC-klagomål.docx", "A 13237-2023")</f>
         <v/>
       </c>
-      <c r="AB10">
+      <c r="AB11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomålsmail/A 13237-2023 FSC-klagomål mail.docx", "A 13237-2023")</f>
         <v/>
       </c>
-      <c r="AC10">
+      <c r="AC11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsyn/A 13237-2023 tillsynsbegäran.docx", "A 13237-2023")</f>
         <v/>
       </c>
-      <c r="AD10">
+      <c r="AD11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsynsmail/A 13237-2023 tillsynsbegäran mail.docx", "A 13237-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="11" ht="15" customHeight="1">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>A 49131-2025</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D11" s="1" t="n">
-        <v>45937</v>
-      </c>
-      <c r="E11" s="1" t="n">
-        <v>46280</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>EKERÖ</t>
-        </is>
-      </c>
-      <c r="I11" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="J11" t="n">
-        <v>0</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L11" t="n">
-        <v>2</v>
-      </c>
-      <c r="M11" t="n">
-        <v>1</v>
-      </c>
-      <c r="N11" t="n">
-        <v>0</v>
-      </c>
-      <c r="O11" t="n">
-        <v>0</v>
-      </c>
-      <c r="P11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>3</v>
-      </c>
-      <c r="R11" t="n">
-        <v>1</v>
-      </c>
-      <c r="S11" t="n">
-        <v>3</v>
-      </c>
-      <c r="T11" t="n">
-        <v>3</v>
-      </c>
-      <c r="U11" t="n">
-        <v>3</v>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
-        <is>
-          <t>Jättemusseron
-Motaggsvamp
-Svartvit taggsvamp</t>
-        </is>
-      </c>
-      <c r="W11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/artfynd/A 49131-2025 artfynd.xlsx", "A 49131-2025")</f>
-        <v/>
-      </c>
-      <c r="X11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor/A 49131-2025 karta.png", "A 49131-2025")</f>
-        <v/>
-      </c>
-      <c r="Y11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor_geotiff/A 49131-2025 georefererad karta.tif", "A 49131-2025")</f>
-        <v/>
-      </c>
-      <c r="AA11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomål/A 49131-2025 FSC-klagomål.docx", "A 49131-2025")</f>
-        <v/>
-      </c>
-      <c r="AB11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomålsmail/A 49131-2025 FSC-klagomål mail.docx", "A 49131-2025")</f>
-        <v/>
-      </c>
-      <c r="AC11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsyn/A 49131-2025 tillsynsbegäran.docx", "A 49131-2025")</f>
-        <v/>
-      </c>
-      <c r="AD11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsynsmail/A 49131-2025 tillsynsbegäran mail.docx", "A 49131-2025")</f>
         <v/>
       </c>
     </row>
@@ -1735,7 +1735,7 @@
         <v>45209</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1850,7 +1850,7 @@
         <v>45170</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1956,7 +1956,7 @@
         <v>44646</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2044,7 +2044,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 3221-2022</t>
+          <t>A 13794-2023</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2058,10 +2058,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>44582</v>
+        <v>45007</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2074,16 +2074,16 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>0.5</v>
+        <v>4.8</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M15" t="n">
         <v>0</v>
@@ -2098,7 +2098,7 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R15" t="n">
         <v>0</v>
@@ -2110,46 +2110,46 @@
         <v>1</v>
       </c>
       <c r="U15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/artfynd/A 3221-2022 artfynd.xlsx", "A 3221-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/artfynd/A 13794-2023 artfynd.xlsx", "A 13794-2023")</f>
         <v/>
       </c>
       <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor/A 3221-2022 karta.png", "A 3221-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor/A 13794-2023 karta.png", "A 13794-2023")</f>
         <v/>
       </c>
       <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor_geotiff/A 3221-2022 georefererad karta.tif", "A 3221-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor_geotiff/A 13794-2023 georefererad karta.tif", "A 13794-2023")</f>
         <v/>
       </c>
       <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomål/A 3221-2022 FSC-klagomål.docx", "A 3221-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomål/A 13794-2023 FSC-klagomål.docx", "A 13794-2023")</f>
         <v/>
       </c>
       <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomålsmail/A 3221-2022 FSC-klagomål mail.docx", "A 3221-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomålsmail/A 13794-2023 FSC-klagomål mail.docx", "A 13794-2023")</f>
         <v/>
       </c>
       <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsyn/A 3221-2022 tillsynsbegäran.docx", "A 3221-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsyn/A 13794-2023 tillsynsbegäran.docx", "A 13794-2023")</f>
         <v/>
       </c>
       <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsynsmail/A 3221-2022 tillsynsbegäran mail.docx", "A 3221-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsynsmail/A 13794-2023 tillsynsbegäran mail.docx", "A 13794-2023")</f>
         <v/>
       </c>
     </row>
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 13794-2023</t>
+          <t>A 2533-2026</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2163,10 +2163,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45007</v>
+        <v>46037</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2179,16 +2179,16 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>4.8</v>
+        <v>1.4</v>
       </c>
       <c r="J16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K16" t="n">
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
         <v>0</v>
@@ -2203,7 +2203,7 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
         <v>0</v>
@@ -2219,42 +2219,42 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/artfynd/A 13794-2023 artfynd.xlsx", "A 13794-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/artfynd/A 2533-2026 artfynd.xlsx", "A 2533-2026")</f>
         <v/>
       </c>
       <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor/A 13794-2023 karta.png", "A 13794-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor/A 2533-2026 karta.png", "A 2533-2026")</f>
         <v/>
       </c>
       <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor_geotiff/A 13794-2023 georefererad karta.tif", "A 13794-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor_geotiff/A 2533-2026 georefererad karta.tif", "A 2533-2026")</f>
         <v/>
       </c>
       <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomål/A 13794-2023 FSC-klagomål.docx", "A 13794-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomål/A 2533-2026 FSC-klagomål.docx", "A 2533-2026")</f>
         <v/>
       </c>
       <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomålsmail/A 13794-2023 FSC-klagomål mail.docx", "A 13794-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomålsmail/A 2533-2026 FSC-klagomål mail.docx", "A 2533-2026")</f>
         <v/>
       </c>
       <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsyn/A 13794-2023 tillsynsbegäran.docx", "A 13794-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsyn/A 2533-2026 tillsynsbegäran.docx", "A 2533-2026")</f>
         <v/>
       </c>
       <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsynsmail/A 13794-2023 tillsynsbegäran mail.docx", "A 13794-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsynsmail/A 2533-2026 tillsynsbegäran mail.docx", "A 2533-2026")</f>
         <v/>
       </c>
     </row>
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 2533-2026</t>
+          <t>A 3221-2022</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2268,10 +2268,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>46037</v>
+        <v>44582</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2284,13 +2284,13 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>1.4</v>
+        <v>0.5</v>
       </c>
       <c r="J17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L17" t="n">
         <v>0</v>
@@ -2320,39 +2320,39 @@
         <v>1</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/artfynd/A 2533-2026 artfynd.xlsx", "A 2533-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/artfynd/A 3221-2022 artfynd.xlsx", "A 3221-2022")</f>
         <v/>
       </c>
       <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor/A 2533-2026 karta.png", "A 2533-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor/A 3221-2022 karta.png", "A 3221-2022")</f>
         <v/>
       </c>
       <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor_geotiff/A 2533-2026 georefererad karta.tif", "A 2533-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor_geotiff/A 3221-2022 georefererad karta.tif", "A 3221-2022")</f>
         <v/>
       </c>
       <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomål/A 2533-2026 FSC-klagomål.docx", "A 2533-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomål/A 3221-2022 FSC-klagomål.docx", "A 3221-2022")</f>
         <v/>
       </c>
       <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomålsmail/A 2533-2026 FSC-klagomål mail.docx", "A 2533-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomålsmail/A 3221-2022 FSC-klagomål mail.docx", "A 3221-2022")</f>
         <v/>
       </c>
       <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsyn/A 2533-2026 tillsynsbegäran.docx", "A 2533-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsyn/A 3221-2022 tillsynsbegäran.docx", "A 3221-2022")</f>
         <v/>
       </c>
       <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsynsmail/A 2533-2026 tillsynsbegäran mail.docx", "A 2533-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsynsmail/A 3221-2022 tillsynsbegäran mail.docx", "A 3221-2022")</f>
         <v/>
       </c>
     </row>
@@ -2376,7 +2376,7 @@
         <v>45671</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2481,7 +2481,7 @@
         <v>44670</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2554,7 +2554,7 @@
         <v>44802</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2610,7 +2610,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 3219-2022</t>
+          <t>A 37245-2025</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2624,10 +2624,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>44582</v>
+        <v>45876</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2640,7 +2640,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>0.5</v>
+        <v>1.1</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2683,7 +2683,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 63378-2025</t>
+          <t>A 50184-2023</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2697,10 +2697,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>46010</v>
+        <v>45208</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2713,7 +2713,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>4.8</v>
+        <v>10.8</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2756,7 +2756,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 2535-2026</t>
+          <t>A 56002-2024</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2770,10 +2770,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>46037</v>
+        <v>45623</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2786,7 +2786,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>1.6</v>
+        <v>3.4</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2829,7 +2829,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 50184-2023</t>
+          <t>A 20399-2026</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2843,10 +2843,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45208</v>
+        <v>46139</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2859,7 +2859,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>10.8</v>
+        <v>0.9</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2902,7 +2902,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 37245-2025</t>
+          <t>A 20398-2026</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2916,10 +2916,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45876</v>
+        <v>46139</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2932,7 +2932,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>1.1</v>
+        <v>2.4</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2975,7 +2975,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 20399-2026</t>
+          <t>A 61217-2024</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2989,10 +2989,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>46139</v>
+        <v>45645</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3005,7 +3005,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -3048,7 +3048,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 20398-2026</t>
+          <t>A 20898-2026</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3062,10 +3062,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>46139</v>
+        <v>46142</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3078,7 +3078,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>2.4</v>
+        <v>3.6</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -3121,7 +3121,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 20898-2026</t>
+          <t>A 63378-2025</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3135,10 +3135,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>46142</v>
+        <v>46010</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3151,7 +3151,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>3.6</v>
+        <v>4.8</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -3194,7 +3194,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 55724-2024</t>
+          <t>A 3222-2022</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3208,10 +3208,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45622</v>
+        <v>44582</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3224,7 +3224,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>0.5</v>
+        <v>1.8</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3267,7 +3267,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 34073-2025</t>
+          <t>A 60728-2022</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3277,14 +3277,14 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45845</v>
+        <v>44913</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3297,7 +3297,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>2.9</v>
+        <v>1.2</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3340,7 +3340,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 33154-2026</t>
+          <t>A 34073-2025</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3350,14 +3350,14 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>46244</v>
+        <v>45845</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3369,13 +3369,8 @@
           <t>EKERÖ</t>
         </is>
       </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I31" t="n">
-        <v>3.5</v>
+        <v>2.9</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3418,7 +3413,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 35955-2023</t>
+          <t>A 2535-2026</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3432,10 +3427,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45148</v>
+        <v>46037</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3448,7 +3443,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>1.1</v>
+        <v>1.6</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3491,7 +3486,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 61217-2024</t>
+          <t>A 33154-2026</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3505,10 +3500,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45645</v>
+        <v>46244</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3520,8 +3515,13 @@
           <t>EKERÖ</t>
         </is>
       </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I33" t="n">
-        <v>0.8</v>
+        <v>3.5</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3564,7 +3564,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 56002-2024</t>
+          <t>A 3219-2022</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3578,10 +3578,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45623</v>
+        <v>44582</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3594,7 +3594,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>3.4</v>
+        <v>0.5</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3637,7 +3637,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 60728-2022</t>
+          <t>A 60755-2024</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3651,10 +3651,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>44913</v>
+        <v>45644</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3667,7 +3667,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>1.2</v>
+        <v>2.1</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3710,7 +3710,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 3222-2022</t>
+          <t>A 55724-2024</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3724,10 +3724,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>44582</v>
+        <v>45622</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3740,7 +3740,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>1.8</v>
+        <v>0.5</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3783,7 +3783,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 60755-2024</t>
+          <t>A 35955-2023</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3797,10 +3797,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45644</v>
+        <v>45148</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3813,7 +3813,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>2.1</v>
+        <v>1.1</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3873,7 +3873,7 @@
         <v>46153</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>

--- a/Översikt EKERÖ.xlsx
+++ b/Översikt EKERÖ.xlsx
@@ -601,7 +601,7 @@
         <v>46241</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -728,7 +728,7 @@
         <v>44872</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -848,7 +848,7 @@
         <v>44974</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -963,7 +963,7 @@
         <v>45148</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1073,7 +1073,7 @@
         <v>46119</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1187,7 +1187,7 @@
         <v>44582</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1296,7 +1296,7 @@
         <v>46241</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1409,7 +1409,7 @@
         <v>44634</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1499,7 +1499,7 @@
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 49131-2025</t>
+          <t>A 13237-2023</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1513,10 +1513,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>45937</v>
+        <v>45002</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1528,20 +1528,25 @@
           <t>EKERÖ</t>
         </is>
       </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I10" t="n">
-        <v>0.9</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N10" t="n">
         <v>0</v>
@@ -1553,165 +1558,160 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="R10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
         <v>3</v>
       </c>
       <c r="T10" t="n">
+        <v>7</v>
+      </c>
+      <c r="U10" t="n">
+        <v>0</v>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
+        <is>
+          <t>Tallticka
+Granbarkgnagare
+Grönpyrola</t>
+        </is>
+      </c>
+      <c r="W10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/artfynd/A 13237-2023 artfynd.xlsx", "A 13237-2023")</f>
+        <v/>
+      </c>
+      <c r="X10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor/A 13237-2023 karta.png", "A 13237-2023")</f>
+        <v/>
+      </c>
+      <c r="Y10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor_geotiff/A 13237-2023 georefererad karta.tif", "A 13237-2023")</f>
+        <v/>
+      </c>
+      <c r="AA10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomål/A 13237-2023 FSC-klagomål.docx", "A 13237-2023")</f>
+        <v/>
+      </c>
+      <c r="AB10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomålsmail/A 13237-2023 FSC-klagomål mail.docx", "A 13237-2023")</f>
+        <v/>
+      </c>
+      <c r="AC10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsyn/A 13237-2023 tillsynsbegäran.docx", "A 13237-2023")</f>
+        <v/>
+      </c>
+      <c r="AD10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsynsmail/A 13237-2023 tillsynsbegäran mail.docx", "A 13237-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11" ht="15" customHeight="1">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>A 49131-2025</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D11" s="1" t="n">
+        <v>45937</v>
+      </c>
+      <c r="E11" s="1" t="n">
+        <v>46282</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>EKERÖ</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" t="n">
+        <v>2</v>
+      </c>
+      <c r="M11" t="n">
+        <v>1</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" t="n">
         <v>3</v>
       </c>
-      <c r="U10" t="n">
+      <c r="R11" t="n">
+        <v>1</v>
+      </c>
+      <c r="S11" t="n">
         <v>3</v>
       </c>
-      <c r="V10" s="2" t="inlineStr">
+      <c r="T11" t="n">
+        <v>3</v>
+      </c>
+      <c r="U11" t="n">
+        <v>3</v>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
         <is>
           <t>Jättemusseron
 Motaggsvamp
 Svartvit taggsvamp</t>
         </is>
       </c>
-      <c r="W10">
+      <c r="W11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0125/artfynd/A 49131-2025 artfynd.xlsx", "A 49131-2025")</f>
         <v/>
       </c>
-      <c r="X10">
+      <c r="X11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor/A 49131-2025 karta.png", "A 49131-2025")</f>
         <v/>
       </c>
-      <c r="Y10">
+      <c r="Y11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor_geotiff/A 49131-2025 georefererad karta.tif", "A 49131-2025")</f>
         <v/>
       </c>
-      <c r="AA10">
+      <c r="AA11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomål/A 49131-2025 FSC-klagomål.docx", "A 49131-2025")</f>
         <v/>
       </c>
-      <c r="AB10">
+      <c r="AB11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomålsmail/A 49131-2025 FSC-klagomål mail.docx", "A 49131-2025")</f>
         <v/>
       </c>
-      <c r="AC10">
+      <c r="AC11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsyn/A 49131-2025 tillsynsbegäran.docx", "A 49131-2025")</f>
         <v/>
       </c>
-      <c r="AD10">
+      <c r="AD11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsynsmail/A 49131-2025 tillsynsbegäran mail.docx", "A 49131-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="11" ht="15" customHeight="1">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>A 13237-2023</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D11" s="1" t="n">
-        <v>45002</v>
-      </c>
-      <c r="E11" s="1" t="n">
-        <v>46281</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>EKERÖ</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
-      <c r="I11" t="n">
-        <v>9.300000000000001</v>
-      </c>
-      <c r="J11" t="n">
-        <v>0</v>
-      </c>
-      <c r="K11" t="n">
-        <v>2</v>
-      </c>
-      <c r="L11" t="n">
-        <v>1</v>
-      </c>
-      <c r="M11" t="n">
-        <v>0</v>
-      </c>
-      <c r="N11" t="n">
-        <v>0</v>
-      </c>
-      <c r="O11" t="n">
-        <v>0</v>
-      </c>
-      <c r="P11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>1</v>
-      </c>
-      <c r="R11" t="n">
-        <v>0</v>
-      </c>
-      <c r="S11" t="n">
-        <v>3</v>
-      </c>
-      <c r="T11" t="n">
-        <v>7</v>
-      </c>
-      <c r="U11" t="n">
-        <v>0</v>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
-        <is>
-          <t>Tallticka
-Granbarkgnagare
-Grönpyrola</t>
-        </is>
-      </c>
-      <c r="W11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/artfynd/A 13237-2023 artfynd.xlsx", "A 13237-2023")</f>
-        <v/>
-      </c>
-      <c r="X11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor/A 13237-2023 karta.png", "A 13237-2023")</f>
-        <v/>
-      </c>
-      <c r="Y11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor_geotiff/A 13237-2023 georefererad karta.tif", "A 13237-2023")</f>
-        <v/>
-      </c>
-      <c r="AA11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomål/A 13237-2023 FSC-klagomål.docx", "A 13237-2023")</f>
-        <v/>
-      </c>
-      <c r="AB11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomålsmail/A 13237-2023 FSC-klagomål mail.docx", "A 13237-2023")</f>
-        <v/>
-      </c>
-      <c r="AC11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsyn/A 13237-2023 tillsynsbegäran.docx", "A 13237-2023")</f>
-        <v/>
-      </c>
-      <c r="AD11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsynsmail/A 13237-2023 tillsynsbegäran mail.docx", "A 13237-2023")</f>
         <v/>
       </c>
     </row>
@@ -1735,7 +1735,7 @@
         <v>45209</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1850,7 +1850,7 @@
         <v>45170</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1956,7 +1956,7 @@
         <v>44646</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2044,7 +2044,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 13794-2023</t>
+          <t>A 3221-2022</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2058,10 +2058,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45007</v>
+        <v>44582</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2074,16 +2074,16 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>4.8</v>
+        <v>0.5</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
         <v>0</v>
@@ -2098,7 +2098,7 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
         <v>0</v>
@@ -2110,46 +2110,46 @@
         <v>1</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/artfynd/A 13794-2023 artfynd.xlsx", "A 13794-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/artfynd/A 3221-2022 artfynd.xlsx", "A 3221-2022")</f>
         <v/>
       </c>
       <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor/A 13794-2023 karta.png", "A 13794-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor/A 3221-2022 karta.png", "A 3221-2022")</f>
         <v/>
       </c>
       <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor_geotiff/A 13794-2023 georefererad karta.tif", "A 13794-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor_geotiff/A 3221-2022 georefererad karta.tif", "A 3221-2022")</f>
         <v/>
       </c>
       <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomål/A 13794-2023 FSC-klagomål.docx", "A 13794-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomål/A 3221-2022 FSC-klagomål.docx", "A 3221-2022")</f>
         <v/>
       </c>
       <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomålsmail/A 13794-2023 FSC-klagomål mail.docx", "A 13794-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomålsmail/A 3221-2022 FSC-klagomål mail.docx", "A 3221-2022")</f>
         <v/>
       </c>
       <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsyn/A 13794-2023 tillsynsbegäran.docx", "A 13794-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsyn/A 3221-2022 tillsynsbegäran.docx", "A 3221-2022")</f>
         <v/>
       </c>
       <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsynsmail/A 13794-2023 tillsynsbegäran mail.docx", "A 13794-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsynsmail/A 3221-2022 tillsynsbegäran mail.docx", "A 3221-2022")</f>
         <v/>
       </c>
     </row>
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 2533-2026</t>
+          <t>A 13794-2023</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2163,10 +2163,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>46037</v>
+        <v>45007</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2179,16 +2179,16 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>1.4</v>
+        <v>4.8</v>
       </c>
       <c r="J16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K16" t="n">
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M16" t="n">
         <v>0</v>
@@ -2203,7 +2203,7 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R16" t="n">
         <v>0</v>
@@ -2219,42 +2219,42 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/artfynd/A 2533-2026 artfynd.xlsx", "A 2533-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/artfynd/A 13794-2023 artfynd.xlsx", "A 13794-2023")</f>
         <v/>
       </c>
       <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor/A 2533-2026 karta.png", "A 2533-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor/A 13794-2023 karta.png", "A 13794-2023")</f>
         <v/>
       </c>
       <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor_geotiff/A 2533-2026 georefererad karta.tif", "A 2533-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor_geotiff/A 13794-2023 georefererad karta.tif", "A 13794-2023")</f>
         <v/>
       </c>
       <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomål/A 2533-2026 FSC-klagomål.docx", "A 2533-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomål/A 13794-2023 FSC-klagomål.docx", "A 13794-2023")</f>
         <v/>
       </c>
       <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomålsmail/A 2533-2026 FSC-klagomål mail.docx", "A 2533-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomålsmail/A 13794-2023 FSC-klagomål mail.docx", "A 13794-2023")</f>
         <v/>
       </c>
       <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsyn/A 2533-2026 tillsynsbegäran.docx", "A 2533-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsyn/A 13794-2023 tillsynsbegäran.docx", "A 13794-2023")</f>
         <v/>
       </c>
       <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsynsmail/A 2533-2026 tillsynsbegäran mail.docx", "A 2533-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsynsmail/A 13794-2023 tillsynsbegäran mail.docx", "A 13794-2023")</f>
         <v/>
       </c>
     </row>
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 3221-2022</t>
+          <t>A 2533-2026</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2268,10 +2268,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>44582</v>
+        <v>46037</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2284,13 +2284,13 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>0.5</v>
+        <v>1.4</v>
       </c>
       <c r="J17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L17" t="n">
         <v>0</v>
@@ -2320,39 +2320,39 @@
         <v>1</v>
       </c>
       <c r="U17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/artfynd/A 3221-2022 artfynd.xlsx", "A 3221-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/artfynd/A 2533-2026 artfynd.xlsx", "A 2533-2026")</f>
         <v/>
       </c>
       <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor/A 3221-2022 karta.png", "A 3221-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor/A 2533-2026 karta.png", "A 2533-2026")</f>
         <v/>
       </c>
       <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor_geotiff/A 3221-2022 georefererad karta.tif", "A 3221-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor_geotiff/A 2533-2026 georefererad karta.tif", "A 2533-2026")</f>
         <v/>
       </c>
       <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomål/A 3221-2022 FSC-klagomål.docx", "A 3221-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomål/A 2533-2026 FSC-klagomål.docx", "A 2533-2026")</f>
         <v/>
       </c>
       <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomålsmail/A 3221-2022 FSC-klagomål mail.docx", "A 3221-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomålsmail/A 2533-2026 FSC-klagomål mail.docx", "A 2533-2026")</f>
         <v/>
       </c>
       <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsyn/A 3221-2022 tillsynsbegäran.docx", "A 3221-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsyn/A 2533-2026 tillsynsbegäran.docx", "A 2533-2026")</f>
         <v/>
       </c>
       <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsynsmail/A 3221-2022 tillsynsbegäran mail.docx", "A 3221-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsynsmail/A 2533-2026 tillsynsbegäran mail.docx", "A 2533-2026")</f>
         <v/>
       </c>
     </row>
@@ -2376,7 +2376,7 @@
         <v>45671</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2481,7 +2481,7 @@
         <v>44670</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2554,7 +2554,7 @@
         <v>44802</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2610,7 +2610,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 37245-2025</t>
+          <t>A 3219-2022</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2624,10 +2624,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45876</v>
+        <v>44582</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2640,7 +2640,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>1.1</v>
+        <v>0.5</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2700,7 +2700,7 @@
         <v>45208</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2756,7 +2756,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 56002-2024</t>
+          <t>A 2535-2026</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2770,10 +2770,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45623</v>
+        <v>46037</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2786,7 +2786,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>3.4</v>
+        <v>1.6</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2829,7 +2829,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 20399-2026</t>
+          <t>A 37245-2025</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2843,10 +2843,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>46139</v>
+        <v>45876</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2859,7 +2859,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>0.9</v>
+        <v>1.1</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2902,7 +2902,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 20398-2026</t>
+          <t>A 63378-2025</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2916,10 +2916,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>46139</v>
+        <v>46010</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2932,7 +2932,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>2.4</v>
+        <v>4.8</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2975,7 +2975,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 61217-2024</t>
+          <t>A 55724-2024</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2989,10 +2989,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45645</v>
+        <v>45622</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3005,7 +3005,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -3048,7 +3048,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 20898-2026</t>
+          <t>A 35955-2023</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3062,10 +3062,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>46142</v>
+        <v>45148</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3078,7 +3078,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>3.6</v>
+        <v>1.1</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -3121,7 +3121,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 63378-2025</t>
+          <t>A 20399-2026</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3135,10 +3135,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>46010</v>
+        <v>46139</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3151,7 +3151,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>4.8</v>
+        <v>0.9</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -3194,7 +3194,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 3222-2022</t>
+          <t>A 20398-2026</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3208,10 +3208,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>44582</v>
+        <v>46139</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3224,7 +3224,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>1.8</v>
+        <v>2.4</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3267,7 +3267,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 60728-2022</t>
+          <t>A 61217-2024</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3281,10 +3281,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>44913</v>
+        <v>45645</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3297,7 +3297,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>1.2</v>
+        <v>0.8</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3340,7 +3340,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 34073-2025</t>
+          <t>A 56002-2024</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3350,14 +3350,14 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45845</v>
+        <v>45623</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3370,7 +3370,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>2.9</v>
+        <v>3.4</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3413,7 +3413,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 2535-2026</t>
+          <t>A 60728-2022</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3427,10 +3427,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>46037</v>
+        <v>44913</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3443,7 +3443,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>1.6</v>
+        <v>1.2</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3486,7 +3486,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 33154-2026</t>
+          <t>A 20898-2026</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3500,10 +3500,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>46244</v>
+        <v>46142</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3515,13 +3515,8 @@
           <t>EKERÖ</t>
         </is>
       </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I33" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3564,7 +3559,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 3219-2022</t>
+          <t>A 3222-2022</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3581,7 +3576,7 @@
         <v>44582</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3594,7 +3589,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>0.5</v>
+        <v>1.8</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3637,7 +3632,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 60755-2024</t>
+          <t>A 34073-2025</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3647,14 +3642,14 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45644</v>
+        <v>45845</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3667,7 +3662,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>2.1</v>
+        <v>2.9</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3710,7 +3705,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 55724-2024</t>
+          <t>A 33154-2026</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3724,10 +3719,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45622</v>
+        <v>46244</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3739,8 +3734,13 @@
           <t>EKERÖ</t>
         </is>
       </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I36" t="n">
-        <v>0.5</v>
+        <v>3.5</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3783,7 +3783,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 35955-2023</t>
+          <t>A 60755-2024</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3797,10 +3797,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45148</v>
+        <v>45644</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3813,7 +3813,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>1.1</v>
+        <v>2.1</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3873,7 +3873,7 @@
         <v>46153</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>

--- a/Översikt EKERÖ.xlsx
+++ b/Översikt EKERÖ.xlsx
@@ -601,7 +601,7 @@
         <v>46241</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -728,7 +728,7 @@
         <v>44872</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -848,7 +848,7 @@
         <v>44974</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -963,7 +963,7 @@
         <v>45148</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1073,7 +1073,7 @@
         <v>46119</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1187,7 +1187,7 @@
         <v>44582</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1296,7 +1296,7 @@
         <v>46241</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1409,7 +1409,7 @@
         <v>44634</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1499,7 +1499,7 @@
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 13237-2023</t>
+          <t>A 49131-2025</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1513,10 +1513,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>45002</v>
+        <v>45937</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1528,25 +1528,20 @@
           <t>EKERÖ</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I10" t="n">
-        <v>9.300000000000001</v>
+        <v>0.9</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
       </c>
       <c r="K10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" t="n">
         <v>2</v>
       </c>
-      <c r="L10" t="n">
-        <v>1</v>
-      </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N10" t="n">
         <v>0</v>
@@ -1558,160 +1553,165 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S10" t="n">
         <v>3</v>
       </c>
       <c r="T10" t="n">
+        <v>3</v>
+      </c>
+      <c r="U10" t="n">
+        <v>3</v>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
+        <is>
+          <t>Jättemusseron
+Motaggsvamp
+Svartvit taggsvamp</t>
+        </is>
+      </c>
+      <c r="W10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/artfynd/A 49131-2025 artfynd.xlsx", "A 49131-2025")</f>
+        <v/>
+      </c>
+      <c r="X10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor/A 49131-2025 karta.png", "A 49131-2025")</f>
+        <v/>
+      </c>
+      <c r="Y10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor_geotiff/A 49131-2025 georefererad karta.tif", "A 49131-2025")</f>
+        <v/>
+      </c>
+      <c r="AA10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomål/A 49131-2025 FSC-klagomål.docx", "A 49131-2025")</f>
+        <v/>
+      </c>
+      <c r="AB10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomålsmail/A 49131-2025 FSC-klagomål mail.docx", "A 49131-2025")</f>
+        <v/>
+      </c>
+      <c r="AC10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsyn/A 49131-2025 tillsynsbegäran.docx", "A 49131-2025")</f>
+        <v/>
+      </c>
+      <c r="AD10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsynsmail/A 49131-2025 tillsynsbegäran mail.docx", "A 49131-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11" ht="15" customHeight="1">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>A 13237-2023</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D11" s="1" t="n">
+        <v>45002</v>
+      </c>
+      <c r="E11" s="1" t="n">
+        <v>46283</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>EKERÖ</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" t="n">
+        <v>2</v>
+      </c>
+      <c r="L11" t="n">
+        <v>1</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>1</v>
+      </c>
+      <c r="R11" t="n">
+        <v>0</v>
+      </c>
+      <c r="S11" t="n">
+        <v>3</v>
+      </c>
+      <c r="T11" t="n">
         <v>7</v>
       </c>
-      <c r="U10" t="n">
-        <v>0</v>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
+      <c r="U11" t="n">
+        <v>0</v>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
         <is>
           <t>Tallticka
 Granbarkgnagare
 Grönpyrola</t>
         </is>
       </c>
-      <c r="W10">
+      <c r="W11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0125/artfynd/A 13237-2023 artfynd.xlsx", "A 13237-2023")</f>
         <v/>
       </c>
-      <c r="X10">
+      <c r="X11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor/A 13237-2023 karta.png", "A 13237-2023")</f>
         <v/>
       </c>
-      <c r="Y10">
+      <c r="Y11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor_geotiff/A 13237-2023 georefererad karta.tif", "A 13237-2023")</f>
         <v/>
       </c>
-      <c r="AA10">
+      <c r="AA11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomål/A 13237-2023 FSC-klagomål.docx", "A 13237-2023")</f>
         <v/>
       </c>
-      <c r="AB10">
+      <c r="AB11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomålsmail/A 13237-2023 FSC-klagomål mail.docx", "A 13237-2023")</f>
         <v/>
       </c>
-      <c r="AC10">
+      <c r="AC11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsyn/A 13237-2023 tillsynsbegäran.docx", "A 13237-2023")</f>
         <v/>
       </c>
-      <c r="AD10">
+      <c r="AD11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsynsmail/A 13237-2023 tillsynsbegäran mail.docx", "A 13237-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="11" ht="15" customHeight="1">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>A 49131-2025</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D11" s="1" t="n">
-        <v>45937</v>
-      </c>
-      <c r="E11" s="1" t="n">
-        <v>46282</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>EKERÖ</t>
-        </is>
-      </c>
-      <c r="I11" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="J11" t="n">
-        <v>0</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L11" t="n">
-        <v>2</v>
-      </c>
-      <c r="M11" t="n">
-        <v>1</v>
-      </c>
-      <c r="N11" t="n">
-        <v>0</v>
-      </c>
-      <c r="O11" t="n">
-        <v>0</v>
-      </c>
-      <c r="P11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>3</v>
-      </c>
-      <c r="R11" t="n">
-        <v>1</v>
-      </c>
-      <c r="S11" t="n">
-        <v>3</v>
-      </c>
-      <c r="T11" t="n">
-        <v>3</v>
-      </c>
-      <c r="U11" t="n">
-        <v>3</v>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
-        <is>
-          <t>Jättemusseron
-Motaggsvamp
-Svartvit taggsvamp</t>
-        </is>
-      </c>
-      <c r="W11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/artfynd/A 49131-2025 artfynd.xlsx", "A 49131-2025")</f>
-        <v/>
-      </c>
-      <c r="X11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor/A 49131-2025 karta.png", "A 49131-2025")</f>
-        <v/>
-      </c>
-      <c r="Y11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor_geotiff/A 49131-2025 georefererad karta.tif", "A 49131-2025")</f>
-        <v/>
-      </c>
-      <c r="AA11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomål/A 49131-2025 FSC-klagomål.docx", "A 49131-2025")</f>
-        <v/>
-      </c>
-      <c r="AB11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomålsmail/A 49131-2025 FSC-klagomål mail.docx", "A 49131-2025")</f>
-        <v/>
-      </c>
-      <c r="AC11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsyn/A 49131-2025 tillsynsbegäran.docx", "A 49131-2025")</f>
-        <v/>
-      </c>
-      <c r="AD11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsynsmail/A 49131-2025 tillsynsbegäran mail.docx", "A 49131-2025")</f>
         <v/>
       </c>
     </row>
@@ -1735,7 +1735,7 @@
         <v>45209</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1850,7 +1850,7 @@
         <v>45170</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1956,7 +1956,7 @@
         <v>44646</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2061,7 +2061,7 @@
         <v>44582</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2166,7 +2166,7 @@
         <v>45007</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2271,7 +2271,7 @@
         <v>46037</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2376,7 +2376,7 @@
         <v>45671</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2481,7 +2481,7 @@
         <v>44670</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2554,7 +2554,7 @@
         <v>44802</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2610,7 +2610,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 3219-2022</t>
+          <t>A 50184-2023</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2624,10 +2624,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>44582</v>
+        <v>45208</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2640,7 +2640,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>0.5</v>
+        <v>10.8</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2683,7 +2683,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 50184-2023</t>
+          <t>A 56002-2024</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2697,10 +2697,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>45208</v>
+        <v>45623</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2713,7 +2713,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>10.8</v>
+        <v>3.4</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2756,7 +2756,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 2535-2026</t>
+          <t>A 37245-2025</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2770,10 +2770,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>46037</v>
+        <v>45876</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2786,7 +2786,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>1.6</v>
+        <v>1.1</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2829,7 +2829,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 37245-2025</t>
+          <t>A 61217-2024</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2843,10 +2843,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45876</v>
+        <v>45645</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2859,7 +2859,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>1.1</v>
+        <v>0.8</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2902,7 +2902,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 63378-2025</t>
+          <t>A 20399-2026</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2916,10 +2916,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>46010</v>
+        <v>46139</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2932,7 +2932,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>4.8</v>
+        <v>0.9</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2975,7 +2975,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 55724-2024</t>
+          <t>A 20398-2026</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2989,10 +2989,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45622</v>
+        <v>46139</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3005,7 +3005,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>0.5</v>
+        <v>2.4</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -3048,7 +3048,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 35955-2023</t>
+          <t>A 3222-2022</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3062,10 +3062,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45148</v>
+        <v>44582</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3078,7 +3078,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>1.1</v>
+        <v>1.8</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -3121,7 +3121,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 20399-2026</t>
+          <t>A 20898-2026</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3135,10 +3135,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>46139</v>
+        <v>46142</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3151,7 +3151,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>0.9</v>
+        <v>3.6</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -3194,7 +3194,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 20398-2026</t>
+          <t>A 34073-2025</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3204,14 +3204,14 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>46139</v>
+        <v>45845</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3224,7 +3224,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>2.4</v>
+        <v>2.9</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3267,7 +3267,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 61217-2024</t>
+          <t>A 3219-2022</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3281,10 +3281,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45645</v>
+        <v>44582</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3297,7 +3297,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3340,7 +3340,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 56002-2024</t>
+          <t>A 60755-2024</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3354,10 +3354,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45623</v>
+        <v>45644</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3370,7 +3370,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>3.4</v>
+        <v>2.1</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3413,7 +3413,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 60728-2022</t>
+          <t>A 55724-2024</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3427,10 +3427,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>44913</v>
+        <v>45622</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3443,7 +3443,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>1.2</v>
+        <v>0.5</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3486,7 +3486,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 20898-2026</t>
+          <t>A 33154-2026</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3500,10 +3500,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>46142</v>
+        <v>46244</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3515,8 +3515,13 @@
           <t>EKERÖ</t>
         </is>
       </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I33" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3559,7 +3564,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 3222-2022</t>
+          <t>A 35955-2023</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3573,10 +3578,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>44582</v>
+        <v>45148</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3589,7 +3594,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>1.8</v>
+        <v>1.1</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3632,7 +3637,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 34073-2025</t>
+          <t>A 63378-2025</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3642,14 +3647,14 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45845</v>
+        <v>46010</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3662,7 +3667,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>2.9</v>
+        <v>4.8</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3705,7 +3710,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 33154-2026</t>
+          <t>A 60728-2022</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3719,10 +3724,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>46244</v>
+        <v>44913</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3734,13 +3739,8 @@
           <t>EKERÖ</t>
         </is>
       </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I36" t="n">
-        <v>3.5</v>
+        <v>1.2</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3783,7 +3783,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 60755-2024</t>
+          <t>A 2535-2026</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3797,10 +3797,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45644</v>
+        <v>46037</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3813,7 +3813,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>2.1</v>
+        <v>1.6</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3873,7 +3873,7 @@
         <v>46153</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>

--- a/Översikt EKERÖ.xlsx
+++ b/Översikt EKERÖ.xlsx
@@ -601,7 +601,7 @@
         <v>46241</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -728,7 +728,7 @@
         <v>44872</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -848,7 +848,7 @@
         <v>44974</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -963,7 +963,7 @@
         <v>45148</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1073,7 +1073,7 @@
         <v>46119</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1187,7 +1187,7 @@
         <v>44582</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1296,7 +1296,7 @@
         <v>46241</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1409,7 +1409,7 @@
         <v>44634</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1499,7 +1499,7 @@
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 49131-2025</t>
+          <t>A 13237-2023</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1513,10 +1513,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>45937</v>
+        <v>45002</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1528,20 +1528,25 @@
           <t>EKERÖ</t>
         </is>
       </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I10" t="n">
-        <v>0.9</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N10" t="n">
         <v>0</v>
@@ -1553,165 +1558,160 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="R10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
         <v>3</v>
       </c>
       <c r="T10" t="n">
+        <v>7</v>
+      </c>
+      <c r="U10" t="n">
+        <v>0</v>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
+        <is>
+          <t>Tallticka
+Granbarkgnagare
+Grönpyrola</t>
+        </is>
+      </c>
+      <c r="W10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/artfynd/A 13237-2023 artfynd.xlsx", "A 13237-2023")</f>
+        <v/>
+      </c>
+      <c r="X10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor/A 13237-2023 karta.png", "A 13237-2023")</f>
+        <v/>
+      </c>
+      <c r="Y10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor_geotiff/A 13237-2023 georefererad karta.tif", "A 13237-2023")</f>
+        <v/>
+      </c>
+      <c r="AA10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomål/A 13237-2023 FSC-klagomål.docx", "A 13237-2023")</f>
+        <v/>
+      </c>
+      <c r="AB10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomålsmail/A 13237-2023 FSC-klagomål mail.docx", "A 13237-2023")</f>
+        <v/>
+      </c>
+      <c r="AC10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsyn/A 13237-2023 tillsynsbegäran.docx", "A 13237-2023")</f>
+        <v/>
+      </c>
+      <c r="AD10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsynsmail/A 13237-2023 tillsynsbegäran mail.docx", "A 13237-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11" ht="15" customHeight="1">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>A 49131-2025</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D11" s="1" t="n">
+        <v>45937</v>
+      </c>
+      <c r="E11" s="1" t="n">
+        <v>46284</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>EKERÖ</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" t="n">
+        <v>2</v>
+      </c>
+      <c r="M11" t="n">
+        <v>1</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" t="n">
         <v>3</v>
       </c>
-      <c r="U10" t="n">
+      <c r="R11" t="n">
+        <v>1</v>
+      </c>
+      <c r="S11" t="n">
         <v>3</v>
       </c>
-      <c r="V10" s="2" t="inlineStr">
+      <c r="T11" t="n">
+        <v>3</v>
+      </c>
+      <c r="U11" t="n">
+        <v>3</v>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
         <is>
           <t>Jättemusseron
 Motaggsvamp
 Svartvit taggsvamp</t>
         </is>
       </c>
-      <c r="W10">
+      <c r="W11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0125/artfynd/A 49131-2025 artfynd.xlsx", "A 49131-2025")</f>
         <v/>
       </c>
-      <c r="X10">
+      <c r="X11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor/A 49131-2025 karta.png", "A 49131-2025")</f>
         <v/>
       </c>
-      <c r="Y10">
+      <c r="Y11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor_geotiff/A 49131-2025 georefererad karta.tif", "A 49131-2025")</f>
         <v/>
       </c>
-      <c r="AA10">
+      <c r="AA11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomål/A 49131-2025 FSC-klagomål.docx", "A 49131-2025")</f>
         <v/>
       </c>
-      <c r="AB10">
+      <c r="AB11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomålsmail/A 49131-2025 FSC-klagomål mail.docx", "A 49131-2025")</f>
         <v/>
       </c>
-      <c r="AC10">
+      <c r="AC11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsyn/A 49131-2025 tillsynsbegäran.docx", "A 49131-2025")</f>
         <v/>
       </c>
-      <c r="AD10">
+      <c r="AD11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsynsmail/A 49131-2025 tillsynsbegäran mail.docx", "A 49131-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="11" ht="15" customHeight="1">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>A 13237-2023</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D11" s="1" t="n">
-        <v>45002</v>
-      </c>
-      <c r="E11" s="1" t="n">
-        <v>46283</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>EKERÖ</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
-      <c r="I11" t="n">
-        <v>9.300000000000001</v>
-      </c>
-      <c r="J11" t="n">
-        <v>0</v>
-      </c>
-      <c r="K11" t="n">
-        <v>2</v>
-      </c>
-      <c r="L11" t="n">
-        <v>1</v>
-      </c>
-      <c r="M11" t="n">
-        <v>0</v>
-      </c>
-      <c r="N11" t="n">
-        <v>0</v>
-      </c>
-      <c r="O11" t="n">
-        <v>0</v>
-      </c>
-      <c r="P11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>1</v>
-      </c>
-      <c r="R11" t="n">
-        <v>0</v>
-      </c>
-      <c r="S11" t="n">
-        <v>3</v>
-      </c>
-      <c r="T11" t="n">
-        <v>7</v>
-      </c>
-      <c r="U11" t="n">
-        <v>0</v>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
-        <is>
-          <t>Tallticka
-Granbarkgnagare
-Grönpyrola</t>
-        </is>
-      </c>
-      <c r="W11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/artfynd/A 13237-2023 artfynd.xlsx", "A 13237-2023")</f>
-        <v/>
-      </c>
-      <c r="X11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor/A 13237-2023 karta.png", "A 13237-2023")</f>
-        <v/>
-      </c>
-      <c r="Y11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor_geotiff/A 13237-2023 georefererad karta.tif", "A 13237-2023")</f>
-        <v/>
-      </c>
-      <c r="AA11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomål/A 13237-2023 FSC-klagomål.docx", "A 13237-2023")</f>
-        <v/>
-      </c>
-      <c r="AB11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomålsmail/A 13237-2023 FSC-klagomål mail.docx", "A 13237-2023")</f>
-        <v/>
-      </c>
-      <c r="AC11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsyn/A 13237-2023 tillsynsbegäran.docx", "A 13237-2023")</f>
-        <v/>
-      </c>
-      <c r="AD11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsynsmail/A 13237-2023 tillsynsbegäran mail.docx", "A 13237-2023")</f>
         <v/>
       </c>
     </row>
@@ -1735,7 +1735,7 @@
         <v>45209</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1850,7 +1850,7 @@
         <v>45170</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1956,7 +1956,7 @@
         <v>44646</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2061,7 +2061,7 @@
         <v>44582</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2166,7 +2166,7 @@
         <v>45007</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2271,7 +2271,7 @@
         <v>46037</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2376,7 +2376,7 @@
         <v>45671</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2481,7 +2481,7 @@
         <v>44670</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2554,7 +2554,7 @@
         <v>44802</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2610,7 +2610,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 50184-2023</t>
+          <t>A 3219-2022</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2624,10 +2624,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45208</v>
+        <v>44582</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2640,7 +2640,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>10.8</v>
+        <v>0.5</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2683,7 +2683,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 56002-2024</t>
+          <t>A 50184-2023</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2697,10 +2697,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>45623</v>
+        <v>45208</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2713,7 +2713,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>3.4</v>
+        <v>10.8</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2756,7 +2756,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 37245-2025</t>
+          <t>A 20399-2026</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2770,10 +2770,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45876</v>
+        <v>46139</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2786,7 +2786,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>1.1</v>
+        <v>0.9</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2829,7 +2829,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 61217-2024</t>
+          <t>A 20398-2026</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2843,10 +2843,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45645</v>
+        <v>46139</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2859,7 +2859,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>0.8</v>
+        <v>2.4</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2902,7 +2902,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 20399-2026</t>
+          <t>A 20898-2026</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2916,10 +2916,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>46139</v>
+        <v>46142</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2932,7 +2932,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>0.9</v>
+        <v>3.6</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2975,7 +2975,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 20398-2026</t>
+          <t>A 55724-2024</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2989,10 +2989,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>46139</v>
+        <v>45622</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3005,7 +3005,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>2.4</v>
+        <v>0.5</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -3048,7 +3048,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 3222-2022</t>
+          <t>A 35955-2023</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3062,10 +3062,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>44582</v>
+        <v>45148</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3078,7 +3078,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>1.8</v>
+        <v>1.1</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -3121,7 +3121,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 20898-2026</t>
+          <t>A 61217-2024</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3135,10 +3135,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>46142</v>
+        <v>45645</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3151,7 +3151,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>3.6</v>
+        <v>0.8</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -3194,7 +3194,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 34073-2025</t>
+          <t>A 56002-2024</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3204,14 +3204,14 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45845</v>
+        <v>45623</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3224,7 +3224,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>2.9</v>
+        <v>3.4</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3267,7 +3267,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 3219-2022</t>
+          <t>A 60728-2022</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3281,10 +3281,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>44582</v>
+        <v>44913</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3297,7 +3297,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>0.5</v>
+        <v>1.2</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3340,7 +3340,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 60755-2024</t>
+          <t>A 63378-2025</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3354,10 +3354,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45644</v>
+        <v>46010</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3370,7 +3370,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>2.1</v>
+        <v>4.8</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3413,7 +3413,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 55724-2024</t>
+          <t>A 34073-2025</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3423,14 +3423,14 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45622</v>
+        <v>45845</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3443,7 +3443,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>0.5</v>
+        <v>2.9</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3486,7 +3486,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 33154-2026</t>
+          <t>A 3222-2022</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3500,10 +3500,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>46244</v>
+        <v>44582</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3515,13 +3515,8 @@
           <t>EKERÖ</t>
         </is>
       </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I33" t="n">
-        <v>3.5</v>
+        <v>1.8</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3564,7 +3559,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 35955-2023</t>
+          <t>A 2535-2026</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3578,10 +3573,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45148</v>
+        <v>46037</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3594,7 +3589,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>1.1</v>
+        <v>1.6</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3637,7 +3632,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 63378-2025</t>
+          <t>A 33154-2026</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3651,10 +3646,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>46010</v>
+        <v>46244</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3666,8 +3661,13 @@
           <t>EKERÖ</t>
         </is>
       </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I35" t="n">
-        <v>4.8</v>
+        <v>3.5</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3710,7 +3710,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 60728-2022</t>
+          <t>A 60755-2024</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3724,10 +3724,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>44913</v>
+        <v>45644</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3740,7 +3740,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>1.2</v>
+        <v>2.1</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3783,7 +3783,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 2535-2026</t>
+          <t>A 37245-2025</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3797,10 +3797,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>46037</v>
+        <v>45876</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3813,7 +3813,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>1.6</v>
+        <v>1.1</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3873,7 +3873,7 @@
         <v>46153</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>

--- a/Översikt EKERÖ.xlsx
+++ b/Översikt EKERÖ.xlsx
@@ -601,7 +601,7 @@
         <v>46241</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -728,7 +728,7 @@
         <v>44872</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -848,7 +848,7 @@
         <v>44974</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -963,7 +963,7 @@
         <v>45148</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1073,7 +1073,7 @@
         <v>46119</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1187,7 +1187,7 @@
         <v>44582</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1296,7 +1296,7 @@
         <v>46241</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1409,7 +1409,7 @@
         <v>44634</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1516,7 +1516,7 @@
         <v>45002</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1628,7 +1628,7 @@
         <v>45937</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1735,7 +1735,7 @@
         <v>45209</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1850,7 +1850,7 @@
         <v>45170</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1956,7 +1956,7 @@
         <v>44646</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2061,7 +2061,7 @@
         <v>44582</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2166,7 +2166,7 @@
         <v>45007</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2271,7 +2271,7 @@
         <v>46037</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2376,7 +2376,7 @@
         <v>45671</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2481,7 +2481,7 @@
         <v>44670</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2554,7 +2554,7 @@
         <v>44802</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2627,7 +2627,7 @@
         <v>44582</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2700,7 +2700,7 @@
         <v>45208</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2773,7 +2773,7 @@
         <v>46139</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2846,7 +2846,7 @@
         <v>46139</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2919,7 +2919,7 @@
         <v>46142</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2992,7 +2992,7 @@
         <v>45622</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3065,7 +3065,7 @@
         <v>45148</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3138,7 +3138,7 @@
         <v>45645</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3211,7 +3211,7 @@
         <v>45623</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3284,7 +3284,7 @@
         <v>44913</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3357,7 +3357,7 @@
         <v>46010</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3430,7 +3430,7 @@
         <v>45845</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3503,7 +3503,7 @@
         <v>44582</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3576,7 +3576,7 @@
         <v>46037</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3649,7 +3649,7 @@
         <v>46244</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3727,7 +3727,7 @@
         <v>45644</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3800,7 +3800,7 @@
         <v>45876</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3873,7 +3873,7 @@
         <v>46153</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>

--- a/Översikt EKERÖ.xlsx
+++ b/Översikt EKERÖ.xlsx
@@ -601,7 +601,7 @@
         <v>46241</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -728,7 +728,7 @@
         <v>44872</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -848,7 +848,7 @@
         <v>44974</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -963,7 +963,7 @@
         <v>45148</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1073,7 +1073,7 @@
         <v>46119</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1187,7 +1187,7 @@
         <v>44582</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1296,7 +1296,7 @@
         <v>46241</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1409,7 +1409,7 @@
         <v>44634</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1516,7 +1516,7 @@
         <v>45002</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1628,7 +1628,7 @@
         <v>45937</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1735,7 +1735,7 @@
         <v>45209</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1850,7 +1850,7 @@
         <v>45170</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1956,7 +1956,7 @@
         <v>44646</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2061,7 +2061,7 @@
         <v>44582</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2166,7 +2166,7 @@
         <v>45007</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2271,7 +2271,7 @@
         <v>46037</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2376,7 +2376,7 @@
         <v>45671</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2481,7 +2481,7 @@
         <v>44670</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2554,7 +2554,7 @@
         <v>44802</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2627,7 +2627,7 @@
         <v>44582</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2700,7 +2700,7 @@
         <v>45208</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2756,7 +2756,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 20399-2026</t>
+          <t>A 37245-2025</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2770,10 +2770,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>46139</v>
+        <v>45876</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2786,7 +2786,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>0.9</v>
+        <v>1.1</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2829,7 +2829,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 20398-2026</t>
+          <t>A 20399-2026</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2846,7 +2846,7 @@
         <v>46139</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2859,7 +2859,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>2.4</v>
+        <v>0.9</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2902,7 +2902,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 20898-2026</t>
+          <t>A 20398-2026</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2916,10 +2916,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>46142</v>
+        <v>46139</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2932,7 +2932,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>3.6</v>
+        <v>2.4</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2975,7 +2975,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 55724-2024</t>
+          <t>A 20898-2026</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2989,10 +2989,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45622</v>
+        <v>46142</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3005,7 +3005,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>0.5</v>
+        <v>3.6</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -3048,7 +3048,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 35955-2023</t>
+          <t>A 55724-2024</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3062,10 +3062,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45148</v>
+        <v>45622</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3078,7 +3078,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>1.1</v>
+        <v>0.5</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -3121,7 +3121,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 61217-2024</t>
+          <t>A 34073-2025</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3131,14 +3131,14 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45645</v>
+        <v>45845</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3151,7 +3151,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>0.8</v>
+        <v>2.9</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -3194,7 +3194,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 56002-2024</t>
+          <t>A 35955-2023</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3208,10 +3208,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45623</v>
+        <v>45148</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3224,7 +3224,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>3.4</v>
+        <v>1.1</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3267,7 +3267,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 60728-2022</t>
+          <t>A 63378-2025</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3281,10 +3281,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>44913</v>
+        <v>46010</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3297,7 +3297,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>1.2</v>
+        <v>4.8</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3340,7 +3340,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 63378-2025</t>
+          <t>A 61217-2024</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3354,10 +3354,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>46010</v>
+        <v>45645</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3370,7 +3370,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>4.8</v>
+        <v>0.8</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3413,7 +3413,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 34073-2025</t>
+          <t>A 56002-2024</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3423,14 +3423,14 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45845</v>
+        <v>45623</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3443,7 +3443,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>2.9</v>
+        <v>3.4</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3486,7 +3486,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 3222-2022</t>
+          <t>A 60728-2022</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3500,10 +3500,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>44582</v>
+        <v>44913</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3516,7 +3516,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>1.8</v>
+        <v>1.2</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3576,7 +3576,7 @@
         <v>46037</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3632,7 +3632,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 33154-2026</t>
+          <t>A 3222-2022</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3646,10 +3646,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>46244</v>
+        <v>44582</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3661,13 +3661,8 @@
           <t>EKERÖ</t>
         </is>
       </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I35" t="n">
-        <v>3.5</v>
+        <v>1.8</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3710,7 +3705,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 60755-2024</t>
+          <t>A 33154-2026</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3724,10 +3719,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45644</v>
+        <v>46244</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3739,8 +3734,13 @@
           <t>EKERÖ</t>
         </is>
       </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I36" t="n">
-        <v>2.1</v>
+        <v>3.5</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3783,7 +3783,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 37245-2025</t>
+          <t>A 60755-2024</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3797,10 +3797,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45876</v>
+        <v>45644</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3813,7 +3813,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>1.1</v>
+        <v>2.1</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3873,7 +3873,7 @@
         <v>46153</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>

--- a/Översikt EKERÖ.xlsx
+++ b/Översikt EKERÖ.xlsx
@@ -601,7 +601,7 @@
         <v>46241</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -728,7 +728,7 @@
         <v>44872</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -848,7 +848,7 @@
         <v>44974</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -963,7 +963,7 @@
         <v>45148</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1056,7 +1056,7 @@
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A 17520-2026</t>
+          <t>A 3218-2022</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1070,10 +1070,10 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>46119</v>
+        <v>44582</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1085,13 +1085,8 @@
           <t>EKERÖ</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I6" t="n">
-        <v>2.2</v>
+        <v>1.2</v>
       </c>
       <c r="J6" t="n">
         <v>1</v>
@@ -1100,36 +1095,150 @@
         <v>1</v>
       </c>
       <c r="L6" t="n">
+        <v>1</v>
+      </c>
+      <c r="M6" t="n">
+        <v>1</v>
+      </c>
+      <c r="N6" t="n">
+        <v>1</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" t="n">
         <v>3</v>
       </c>
-      <c r="M6" t="n">
-        <v>1</v>
-      </c>
-      <c r="N6" t="n">
-        <v>0</v>
-      </c>
-      <c r="O6" t="n">
-        <v>0</v>
-      </c>
-      <c r="P6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>4</v>
-      </c>
       <c r="R6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
       </c>
       <c r="T6" t="n">
+        <v>8</v>
+      </c>
+      <c r="U6" t="n">
+        <v>6</v>
+      </c>
+      <c r="V6" s="2" t="inlineStr">
+        <is>
+          <t>Bombmurkla
+Gul lammticka
+Fyrflikig jordstjärna
+Kamjordstjärna
+Blåbär</t>
+        </is>
+      </c>
+      <c r="W6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/artfynd/A 3218-2022 artfynd.xlsx", "A 3218-2022")</f>
+        <v/>
+      </c>
+      <c r="X6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor/A 3218-2022 karta.png", "A 3218-2022")</f>
+        <v/>
+      </c>
+      <c r="Y6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor_geotiff/A 3218-2022 georefererad karta.tif", "A 3218-2022")</f>
+        <v/>
+      </c>
+      <c r="AA6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomål/A 3218-2022 FSC-klagomål.docx", "A 3218-2022")</f>
+        <v/>
+      </c>
+      <c r="AB6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomålsmail/A 3218-2022 FSC-klagomål mail.docx", "A 3218-2022")</f>
+        <v/>
+      </c>
+      <c r="AC6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsyn/A 3218-2022 tillsynsbegäran.docx", "A 3218-2022")</f>
+        <v/>
+      </c>
+      <c r="AD6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsynsmail/A 3218-2022 tillsynsbegäran mail.docx", "A 3218-2022")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7" ht="15" customHeight="1">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>A 17520-2026</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D7" s="1" t="n">
+        <v>46119</v>
+      </c>
+      <c r="E7" s="1" t="n">
+        <v>46289</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>EKERÖ</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="J7" t="n">
+        <v>1</v>
+      </c>
+      <c r="K7" t="n">
+        <v>1</v>
+      </c>
+      <c r="L7" t="n">
+        <v>3</v>
+      </c>
+      <c r="M7" t="n">
+        <v>1</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>4</v>
+      </c>
+      <c r="R7" t="n">
+        <v>1</v>
+      </c>
+      <c r="S7" t="n">
         <v>5</v>
       </c>
-      <c r="U6" t="n">
-        <v>1</v>
-      </c>
-      <c r="V6" s="2" t="inlineStr">
+      <c r="T7" t="n">
+        <v>5</v>
+      </c>
+      <c r="U7" t="n">
+        <v>1</v>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
         <is>
           <t>Läderbagge
 Blekticka
@@ -1138,141 +1247,32 @@
 Gulgrön kantmusseron</t>
         </is>
       </c>
-      <c r="W6">
+      <c r="W7">
         <f>HYPERLINK("https://klasma.github.io/Logging_0125/artfynd/A 17520-2026 artfynd.xlsx", "A 17520-2026")</f>
         <v/>
       </c>
-      <c r="X6">
+      <c r="X7">
         <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor/A 17520-2026 karta.png", "A 17520-2026")</f>
         <v/>
       </c>
-      <c r="Y6">
+      <c r="Y7">
         <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor_geotiff/A 17520-2026 georefererad karta.tif", "A 17520-2026")</f>
         <v/>
       </c>
-      <c r="AA6">
+      <c r="AA7">
         <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomål/A 17520-2026 FSC-klagomål.docx", "A 17520-2026")</f>
         <v/>
       </c>
-      <c r="AB6">
+      <c r="AB7">
         <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomålsmail/A 17520-2026 FSC-klagomål mail.docx", "A 17520-2026")</f>
         <v/>
       </c>
-      <c r="AC6">
+      <c r="AC7">
         <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsyn/A 17520-2026 tillsynsbegäran.docx", "A 17520-2026")</f>
         <v/>
       </c>
-      <c r="AD6">
+      <c r="AD7">
         <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsynsmail/A 17520-2026 tillsynsbegäran mail.docx", "A 17520-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="7" ht="15" customHeight="1">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>A 3218-2022</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D7" s="1" t="n">
-        <v>44582</v>
-      </c>
-      <c r="E7" s="1" t="n">
-        <v>46288</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>EKERÖ</t>
-        </is>
-      </c>
-      <c r="I7" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="J7" t="n">
-        <v>1</v>
-      </c>
-      <c r="K7" t="n">
-        <v>1</v>
-      </c>
-      <c r="L7" t="n">
-        <v>1</v>
-      </c>
-      <c r="M7" t="n">
-        <v>1</v>
-      </c>
-      <c r="N7" t="n">
-        <v>1</v>
-      </c>
-      <c r="O7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>3</v>
-      </c>
-      <c r="R7" t="n">
-        <v>2</v>
-      </c>
-      <c r="S7" t="n">
-        <v>5</v>
-      </c>
-      <c r="T7" t="n">
-        <v>8</v>
-      </c>
-      <c r="U7" t="n">
-        <v>6</v>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>Bombmurkla
-Gul lammticka
-Fyrflikig jordstjärna
-Kamjordstjärna
-Blåbär</t>
-        </is>
-      </c>
-      <c r="W7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/artfynd/A 3218-2022 artfynd.xlsx", "A 3218-2022")</f>
-        <v/>
-      </c>
-      <c r="X7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor/A 3218-2022 karta.png", "A 3218-2022")</f>
-        <v/>
-      </c>
-      <c r="Y7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor_geotiff/A 3218-2022 georefererad karta.tif", "A 3218-2022")</f>
-        <v/>
-      </c>
-      <c r="AA7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomål/A 3218-2022 FSC-klagomål.docx", "A 3218-2022")</f>
-        <v/>
-      </c>
-      <c r="AB7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomålsmail/A 3218-2022 FSC-klagomål mail.docx", "A 3218-2022")</f>
-        <v/>
-      </c>
-      <c r="AC7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsyn/A 3218-2022 tillsynsbegäran.docx", "A 3218-2022")</f>
-        <v/>
-      </c>
-      <c r="AD7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsynsmail/A 3218-2022 tillsynsbegäran mail.docx", "A 3218-2022")</f>
         <v/>
       </c>
     </row>
@@ -1296,7 +1296,7 @@
         <v>46241</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1409,7 +1409,7 @@
         <v>44634</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1499,7 +1499,7 @@
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 13237-2023</t>
+          <t>A 49131-2025</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1513,10 +1513,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>45002</v>
+        <v>45937</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1528,25 +1528,20 @@
           <t>EKERÖ</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I10" t="n">
-        <v>9.300000000000001</v>
+        <v>0.9</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
       </c>
       <c r="K10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" t="n">
         <v>2</v>
       </c>
-      <c r="L10" t="n">
-        <v>1</v>
-      </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N10" t="n">
         <v>0</v>
@@ -1558,160 +1553,165 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S10" t="n">
         <v>3</v>
       </c>
       <c r="T10" t="n">
+        <v>3</v>
+      </c>
+      <c r="U10" t="n">
+        <v>3</v>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
+        <is>
+          <t>Jättemusseron
+Motaggsvamp
+Svartvit taggsvamp</t>
+        </is>
+      </c>
+      <c r="W10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/artfynd/A 49131-2025 artfynd.xlsx", "A 49131-2025")</f>
+        <v/>
+      </c>
+      <c r="X10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor/A 49131-2025 karta.png", "A 49131-2025")</f>
+        <v/>
+      </c>
+      <c r="Y10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor_geotiff/A 49131-2025 georefererad karta.tif", "A 49131-2025")</f>
+        <v/>
+      </c>
+      <c r="AA10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomål/A 49131-2025 FSC-klagomål.docx", "A 49131-2025")</f>
+        <v/>
+      </c>
+      <c r="AB10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomålsmail/A 49131-2025 FSC-klagomål mail.docx", "A 49131-2025")</f>
+        <v/>
+      </c>
+      <c r="AC10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsyn/A 49131-2025 tillsynsbegäran.docx", "A 49131-2025")</f>
+        <v/>
+      </c>
+      <c r="AD10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsynsmail/A 49131-2025 tillsynsbegäran mail.docx", "A 49131-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11" ht="15" customHeight="1">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>A 13237-2023</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D11" s="1" t="n">
+        <v>45002</v>
+      </c>
+      <c r="E11" s="1" t="n">
+        <v>46289</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>EKERÖ</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" t="n">
+        <v>2</v>
+      </c>
+      <c r="L11" t="n">
+        <v>1</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>1</v>
+      </c>
+      <c r="R11" t="n">
+        <v>0</v>
+      </c>
+      <c r="S11" t="n">
+        <v>3</v>
+      </c>
+      <c r="T11" t="n">
         <v>7</v>
       </c>
-      <c r="U10" t="n">
-        <v>0</v>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
+      <c r="U11" t="n">
+        <v>0</v>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
         <is>
           <t>Tallticka
 Granbarkgnagare
 Grönpyrola</t>
         </is>
       </c>
-      <c r="W10">
+      <c r="W11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0125/artfynd/A 13237-2023 artfynd.xlsx", "A 13237-2023")</f>
         <v/>
       </c>
-      <c r="X10">
+      <c r="X11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor/A 13237-2023 karta.png", "A 13237-2023")</f>
         <v/>
       </c>
-      <c r="Y10">
+      <c r="Y11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor_geotiff/A 13237-2023 georefererad karta.tif", "A 13237-2023")</f>
         <v/>
       </c>
-      <c r="AA10">
+      <c r="AA11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomål/A 13237-2023 FSC-klagomål.docx", "A 13237-2023")</f>
         <v/>
       </c>
-      <c r="AB10">
+      <c r="AB11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomålsmail/A 13237-2023 FSC-klagomål mail.docx", "A 13237-2023")</f>
         <v/>
       </c>
-      <c r="AC10">
+      <c r="AC11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsyn/A 13237-2023 tillsynsbegäran.docx", "A 13237-2023")</f>
         <v/>
       </c>
-      <c r="AD10">
+      <c r="AD11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsynsmail/A 13237-2023 tillsynsbegäran mail.docx", "A 13237-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="11" ht="15" customHeight="1">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>A 49131-2025</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D11" s="1" t="n">
-        <v>45937</v>
-      </c>
-      <c r="E11" s="1" t="n">
-        <v>46288</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>EKERÖ</t>
-        </is>
-      </c>
-      <c r="I11" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="J11" t="n">
-        <v>0</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L11" t="n">
-        <v>2</v>
-      </c>
-      <c r="M11" t="n">
-        <v>1</v>
-      </c>
-      <c r="N11" t="n">
-        <v>0</v>
-      </c>
-      <c r="O11" t="n">
-        <v>0</v>
-      </c>
-      <c r="P11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>3</v>
-      </c>
-      <c r="R11" t="n">
-        <v>1</v>
-      </c>
-      <c r="S11" t="n">
-        <v>3</v>
-      </c>
-      <c r="T11" t="n">
-        <v>3</v>
-      </c>
-      <c r="U11" t="n">
-        <v>3</v>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
-        <is>
-          <t>Jättemusseron
-Motaggsvamp
-Svartvit taggsvamp</t>
-        </is>
-      </c>
-      <c r="W11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/artfynd/A 49131-2025 artfynd.xlsx", "A 49131-2025")</f>
-        <v/>
-      </c>
-      <c r="X11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor/A 49131-2025 karta.png", "A 49131-2025")</f>
-        <v/>
-      </c>
-      <c r="Y11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor_geotiff/A 49131-2025 georefererad karta.tif", "A 49131-2025")</f>
-        <v/>
-      </c>
-      <c r="AA11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomål/A 49131-2025 FSC-klagomål.docx", "A 49131-2025")</f>
-        <v/>
-      </c>
-      <c r="AB11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomålsmail/A 49131-2025 FSC-klagomål mail.docx", "A 49131-2025")</f>
-        <v/>
-      </c>
-      <c r="AC11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsyn/A 49131-2025 tillsynsbegäran.docx", "A 49131-2025")</f>
-        <v/>
-      </c>
-      <c r="AD11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsynsmail/A 49131-2025 tillsynsbegäran mail.docx", "A 49131-2025")</f>
         <v/>
       </c>
     </row>
@@ -1735,7 +1735,7 @@
         <v>45209</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1850,7 +1850,7 @@
         <v>45170</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1956,7 +1956,7 @@
         <v>44646</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2044,7 +2044,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 3221-2022</t>
+          <t>A 1793-2025</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2058,10 +2058,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>44582</v>
+        <v>45671</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2074,13 +2074,13 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>0.5</v>
+        <v>1.7</v>
       </c>
       <c r="J15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L15" t="n">
         <v>0</v>
@@ -2107,49 +2107,49 @@
         <v>1</v>
       </c>
       <c r="T15" t="n">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="U15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Mistel</t>
         </is>
       </c>
       <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/artfynd/A 3221-2022 artfynd.xlsx", "A 3221-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/artfynd/A 1793-2025 artfynd.xlsx", "A 1793-2025")</f>
         <v/>
       </c>
       <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor/A 3221-2022 karta.png", "A 3221-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor/A 1793-2025 karta.png", "A 1793-2025")</f>
         <v/>
       </c>
       <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor_geotiff/A 3221-2022 georefererad karta.tif", "A 3221-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor_geotiff/A 1793-2025 georefererad karta.tif", "A 1793-2025")</f>
         <v/>
       </c>
       <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomål/A 3221-2022 FSC-klagomål.docx", "A 3221-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomål/A 1793-2025 FSC-klagomål.docx", "A 1793-2025")</f>
         <v/>
       </c>
       <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomålsmail/A 3221-2022 FSC-klagomål mail.docx", "A 3221-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomålsmail/A 1793-2025 FSC-klagomål mail.docx", "A 1793-2025")</f>
         <v/>
       </c>
       <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsyn/A 3221-2022 tillsynsbegäran.docx", "A 3221-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsyn/A 1793-2025 tillsynsbegäran.docx", "A 1793-2025")</f>
         <v/>
       </c>
       <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsynsmail/A 3221-2022 tillsynsbegäran mail.docx", "A 3221-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsynsmail/A 1793-2025 tillsynsbegäran mail.docx", "A 1793-2025")</f>
         <v/>
       </c>
     </row>
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 13794-2023</t>
+          <t>A 3221-2022</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2163,10 +2163,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45007</v>
+        <v>44582</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2179,16 +2179,16 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>4.8</v>
+        <v>0.5</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
         <v>0</v>
@@ -2203,7 +2203,7 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
         <v>0</v>
@@ -2215,39 +2215,39 @@
         <v>1</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/artfynd/A 13794-2023 artfynd.xlsx", "A 13794-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/artfynd/A 3221-2022 artfynd.xlsx", "A 3221-2022")</f>
         <v/>
       </c>
       <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor/A 13794-2023 karta.png", "A 13794-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor/A 3221-2022 karta.png", "A 3221-2022")</f>
         <v/>
       </c>
       <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor_geotiff/A 13794-2023 georefererad karta.tif", "A 13794-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor_geotiff/A 3221-2022 georefererad karta.tif", "A 3221-2022")</f>
         <v/>
       </c>
       <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomål/A 13794-2023 FSC-klagomål.docx", "A 13794-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomål/A 3221-2022 FSC-klagomål.docx", "A 3221-2022")</f>
         <v/>
       </c>
       <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomålsmail/A 13794-2023 FSC-klagomål mail.docx", "A 13794-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomålsmail/A 3221-2022 FSC-klagomål mail.docx", "A 3221-2022")</f>
         <v/>
       </c>
       <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsyn/A 13794-2023 tillsynsbegäran.docx", "A 13794-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsyn/A 3221-2022 tillsynsbegäran.docx", "A 3221-2022")</f>
         <v/>
       </c>
       <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsynsmail/A 13794-2023 tillsynsbegäran mail.docx", "A 13794-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsynsmail/A 3221-2022 tillsynsbegäran mail.docx", "A 3221-2022")</f>
         <v/>
       </c>
     </row>
@@ -2271,7 +2271,7 @@
         <v>46037</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2359,7 +2359,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 1793-2025</t>
+          <t>A 13794-2023</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2373,10 +2373,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45671</v>
+        <v>45007</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2389,16 +2389,16 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>1.7</v>
+        <v>4.8</v>
       </c>
       <c r="J18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K18" t="n">
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M18" t="n">
         <v>0</v>
@@ -2413,7 +2413,7 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R18" t="n">
         <v>0</v>
@@ -2422,42 +2422,42 @@
         <v>1</v>
       </c>
       <c r="T18" t="n">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="U18" t="n">
         <v>0</v>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>Mistel</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="W18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/artfynd/A 1793-2025 artfynd.xlsx", "A 1793-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/artfynd/A 13794-2023 artfynd.xlsx", "A 13794-2023")</f>
         <v/>
       </c>
       <c r="X18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor/A 1793-2025 karta.png", "A 1793-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor/A 13794-2023 karta.png", "A 13794-2023")</f>
         <v/>
       </c>
       <c r="Y18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor_geotiff/A 1793-2025 georefererad karta.tif", "A 1793-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor_geotiff/A 13794-2023 georefererad karta.tif", "A 13794-2023")</f>
         <v/>
       </c>
       <c r="AA18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomål/A 1793-2025 FSC-klagomål.docx", "A 1793-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomål/A 13794-2023 FSC-klagomål.docx", "A 13794-2023")</f>
         <v/>
       </c>
       <c r="AB18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomålsmail/A 1793-2025 FSC-klagomål mail.docx", "A 1793-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomålsmail/A 13794-2023 FSC-klagomål mail.docx", "A 13794-2023")</f>
         <v/>
       </c>
       <c r="AC18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsyn/A 1793-2025 tillsynsbegäran.docx", "A 1793-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsyn/A 13794-2023 tillsynsbegäran.docx", "A 13794-2023")</f>
         <v/>
       </c>
       <c r="AD18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsynsmail/A 1793-2025 tillsynsbegäran mail.docx", "A 1793-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsynsmail/A 13794-2023 tillsynsbegäran mail.docx", "A 13794-2023")</f>
         <v/>
       </c>
     </row>
@@ -2481,7 +2481,7 @@
         <v>44670</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2554,7 +2554,7 @@
         <v>44802</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2610,7 +2610,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 3219-2022</t>
+          <t>A 61217-2024</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2624,10 +2624,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>44582</v>
+        <v>45645</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2640,7 +2640,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2683,7 +2683,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 50184-2023</t>
+          <t>A 3222-2022</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2697,10 +2697,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>45208</v>
+        <v>44582</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2713,7 +2713,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>10.8</v>
+        <v>1.8</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2756,7 +2756,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 37245-2025</t>
+          <t>A 50184-2023</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2770,10 +2770,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45876</v>
+        <v>45208</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2786,7 +2786,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>1.1</v>
+        <v>10.8</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2829,7 +2829,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 20399-2026</t>
+          <t>A 3219-2022</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2843,10 +2843,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>46139</v>
+        <v>44582</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2859,7 +2859,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>0.9</v>
+        <v>0.5</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2902,7 +2902,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 20398-2026</t>
+          <t>A 60755-2024</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2916,10 +2916,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>46139</v>
+        <v>45644</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2932,7 +2932,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>2.4</v>
+        <v>2.1</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2975,7 +2975,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 20898-2026</t>
+          <t>A 55724-2024</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2989,10 +2989,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>46142</v>
+        <v>45622</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3005,7 +3005,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>3.6</v>
+        <v>0.5</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -3048,7 +3048,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 55724-2024</t>
+          <t>A 56002-2024</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3062,10 +3062,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45622</v>
+        <v>45623</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3078,7 +3078,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>0.5</v>
+        <v>3.4</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -3121,7 +3121,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 34073-2025</t>
+          <t>A 35955-2023</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3131,14 +3131,14 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45845</v>
+        <v>45148</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3151,7 +3151,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>2.9</v>
+        <v>1.1</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -3194,7 +3194,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 35955-2023</t>
+          <t>A 2535-2026</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3208,10 +3208,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45148</v>
+        <v>46037</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3224,7 +3224,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>1.1</v>
+        <v>1.6</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3284,7 +3284,7 @@
         <v>46010</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3340,7 +3340,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 61217-2024</t>
+          <t>A 33154-2026</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3354,10 +3354,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45645</v>
+        <v>46244</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3369,8 +3369,13 @@
           <t>EKERÖ</t>
         </is>
       </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I31" t="n">
-        <v>0.8</v>
+        <v>3.5</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3413,7 +3418,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 56002-2024</t>
+          <t>A 60728-2022</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3427,10 +3432,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45623</v>
+        <v>44913</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3443,7 +3448,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>3.4</v>
+        <v>1.2</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3486,7 +3491,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 60728-2022</t>
+          <t>A 37245-2025</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3500,10 +3505,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>44913</v>
+        <v>45876</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3516,7 +3521,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3559,7 +3564,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 2535-2026</t>
+          <t>A 20399-2026</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3573,10 +3578,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>46037</v>
+        <v>46139</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3589,7 +3594,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>1.6</v>
+        <v>0.9</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3632,7 +3637,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 3222-2022</t>
+          <t>A 20398-2026</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3646,10 +3651,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>44582</v>
+        <v>46139</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3662,7 +3667,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>1.8</v>
+        <v>2.4</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3705,7 +3710,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 33154-2026</t>
+          <t>A 20898-2026</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3719,10 +3724,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>46244</v>
+        <v>46142</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3734,13 +3739,8 @@
           <t>EKERÖ</t>
         </is>
       </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I36" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3783,7 +3783,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 60755-2024</t>
+          <t>A 34073-2025</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3793,14 +3793,14 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45644</v>
+        <v>45845</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3813,7 +3813,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>2.1</v>
+        <v>2.9</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3873,7 +3873,7 @@
         <v>46153</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>

--- a/Översikt EKERÖ.xlsx
+++ b/Översikt EKERÖ.xlsx
@@ -601,7 +601,7 @@
         <v>46241</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -728,7 +728,7 @@
         <v>44872</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -848,7 +848,7 @@
         <v>44974</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -963,7 +963,7 @@
         <v>45148</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1056,7 +1056,7 @@
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A 3218-2022</t>
+          <t>A 17520-2026</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1070,10 +1070,10 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>44582</v>
+        <v>46119</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1085,8 +1085,13 @@
           <t>EKERÖ</t>
         </is>
       </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I6" t="n">
-        <v>1.2</v>
+        <v>2.2</v>
       </c>
       <c r="J6" t="n">
         <v>1</v>
@@ -1095,13 +1100,13 @@
         <v>1</v>
       </c>
       <c r="L6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M6" t="n">
         <v>1</v>
       </c>
       <c r="N6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1110,21 +1115,130 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="R6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
       </c>
       <c r="T6" t="n">
+        <v>5</v>
+      </c>
+      <c r="U6" t="n">
+        <v>1</v>
+      </c>
+      <c r="V6" s="2" t="inlineStr">
+        <is>
+          <t>Läderbagge
+Blekticka
+Ekticka
+Kandelabersvamp
+Gulgrön kantmusseron</t>
+        </is>
+      </c>
+      <c r="W6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/artfynd/A 17520-2026 artfynd.xlsx", "A 17520-2026")</f>
+        <v/>
+      </c>
+      <c r="X6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor/A 17520-2026 karta.png", "A 17520-2026")</f>
+        <v/>
+      </c>
+      <c r="Y6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor_geotiff/A 17520-2026 georefererad karta.tif", "A 17520-2026")</f>
+        <v/>
+      </c>
+      <c r="AA6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomål/A 17520-2026 FSC-klagomål.docx", "A 17520-2026")</f>
+        <v/>
+      </c>
+      <c r="AB6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomålsmail/A 17520-2026 FSC-klagomål mail.docx", "A 17520-2026")</f>
+        <v/>
+      </c>
+      <c r="AC6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsyn/A 17520-2026 tillsynsbegäran.docx", "A 17520-2026")</f>
+        <v/>
+      </c>
+      <c r="AD6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsynsmail/A 17520-2026 tillsynsbegäran mail.docx", "A 17520-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7" ht="15" customHeight="1">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>A 3218-2022</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D7" s="1" t="n">
+        <v>44582</v>
+      </c>
+      <c r="E7" s="1" t="n">
+        <v>46290</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>EKERÖ</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="J7" t="n">
+        <v>1</v>
+      </c>
+      <c r="K7" t="n">
+        <v>1</v>
+      </c>
+      <c r="L7" t="n">
+        <v>1</v>
+      </c>
+      <c r="M7" t="n">
+        <v>1</v>
+      </c>
+      <c r="N7" t="n">
+        <v>1</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>3</v>
+      </c>
+      <c r="R7" t="n">
+        <v>2</v>
+      </c>
+      <c r="S7" t="n">
+        <v>5</v>
+      </c>
+      <c r="T7" t="n">
         <v>8</v>
       </c>
-      <c r="U6" t="n">
+      <c r="U7" t="n">
         <v>6</v>
       </c>
-      <c r="V6" s="2" t="inlineStr">
+      <c r="V7" s="2" t="inlineStr">
         <is>
           <t>Bombmurkla
 Gul lammticka
@@ -1133,146 +1247,32 @@
 Blåbär</t>
         </is>
       </c>
-      <c r="W6">
+      <c r="W7">
         <f>HYPERLINK("https://klasma.github.io/Logging_0125/artfynd/A 3218-2022 artfynd.xlsx", "A 3218-2022")</f>
         <v/>
       </c>
-      <c r="X6">
+      <c r="X7">
         <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor/A 3218-2022 karta.png", "A 3218-2022")</f>
         <v/>
       </c>
-      <c r="Y6">
+      <c r="Y7">
         <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor_geotiff/A 3218-2022 georefererad karta.tif", "A 3218-2022")</f>
         <v/>
       </c>
-      <c r="AA6">
+      <c r="AA7">
         <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomål/A 3218-2022 FSC-klagomål.docx", "A 3218-2022")</f>
         <v/>
       </c>
-      <c r="AB6">
+      <c r="AB7">
         <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomålsmail/A 3218-2022 FSC-klagomål mail.docx", "A 3218-2022")</f>
         <v/>
       </c>
-      <c r="AC6">
+      <c r="AC7">
         <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsyn/A 3218-2022 tillsynsbegäran.docx", "A 3218-2022")</f>
         <v/>
       </c>
-      <c r="AD6">
+      <c r="AD7">
         <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsynsmail/A 3218-2022 tillsynsbegäran mail.docx", "A 3218-2022")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="7" ht="15" customHeight="1">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>A 17520-2026</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D7" s="1" t="n">
-        <v>46119</v>
-      </c>
-      <c r="E7" s="1" t="n">
-        <v>46289</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>EKERÖ</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
-      <c r="I7" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="J7" t="n">
-        <v>1</v>
-      </c>
-      <c r="K7" t="n">
-        <v>1</v>
-      </c>
-      <c r="L7" t="n">
-        <v>3</v>
-      </c>
-      <c r="M7" t="n">
-        <v>1</v>
-      </c>
-      <c r="N7" t="n">
-        <v>0</v>
-      </c>
-      <c r="O7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>4</v>
-      </c>
-      <c r="R7" t="n">
-        <v>1</v>
-      </c>
-      <c r="S7" t="n">
-        <v>5</v>
-      </c>
-      <c r="T7" t="n">
-        <v>5</v>
-      </c>
-      <c r="U7" t="n">
-        <v>1</v>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>Läderbagge
-Blekticka
-Ekticka
-Kandelabersvamp
-Gulgrön kantmusseron</t>
-        </is>
-      </c>
-      <c r="W7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/artfynd/A 17520-2026 artfynd.xlsx", "A 17520-2026")</f>
-        <v/>
-      </c>
-      <c r="X7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor/A 17520-2026 karta.png", "A 17520-2026")</f>
-        <v/>
-      </c>
-      <c r="Y7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor_geotiff/A 17520-2026 georefererad karta.tif", "A 17520-2026")</f>
-        <v/>
-      </c>
-      <c r="AA7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomål/A 17520-2026 FSC-klagomål.docx", "A 17520-2026")</f>
-        <v/>
-      </c>
-      <c r="AB7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomålsmail/A 17520-2026 FSC-klagomål mail.docx", "A 17520-2026")</f>
-        <v/>
-      </c>
-      <c r="AC7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsyn/A 17520-2026 tillsynsbegäran.docx", "A 17520-2026")</f>
-        <v/>
-      </c>
-      <c r="AD7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsynsmail/A 17520-2026 tillsynsbegäran mail.docx", "A 17520-2026")</f>
         <v/>
       </c>
     </row>
@@ -1296,7 +1296,7 @@
         <v>46241</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1409,7 +1409,7 @@
         <v>44634</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1499,7 +1499,7 @@
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 49131-2025</t>
+          <t>A 13237-2023</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1513,10 +1513,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>45937</v>
+        <v>45002</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1528,20 +1528,25 @@
           <t>EKERÖ</t>
         </is>
       </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I10" t="n">
-        <v>0.9</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N10" t="n">
         <v>0</v>
@@ -1553,165 +1558,160 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="R10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
         <v>3</v>
       </c>
       <c r="T10" t="n">
+        <v>7</v>
+      </c>
+      <c r="U10" t="n">
+        <v>0</v>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
+        <is>
+          <t>Tallticka
+Granbarkgnagare
+Grönpyrola</t>
+        </is>
+      </c>
+      <c r="W10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/artfynd/A 13237-2023 artfynd.xlsx", "A 13237-2023")</f>
+        <v/>
+      </c>
+      <c r="X10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor/A 13237-2023 karta.png", "A 13237-2023")</f>
+        <v/>
+      </c>
+      <c r="Y10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor_geotiff/A 13237-2023 georefererad karta.tif", "A 13237-2023")</f>
+        <v/>
+      </c>
+      <c r="AA10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomål/A 13237-2023 FSC-klagomål.docx", "A 13237-2023")</f>
+        <v/>
+      </c>
+      <c r="AB10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomålsmail/A 13237-2023 FSC-klagomål mail.docx", "A 13237-2023")</f>
+        <v/>
+      </c>
+      <c r="AC10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsyn/A 13237-2023 tillsynsbegäran.docx", "A 13237-2023")</f>
+        <v/>
+      </c>
+      <c r="AD10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsynsmail/A 13237-2023 tillsynsbegäran mail.docx", "A 13237-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11" ht="15" customHeight="1">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>A 49131-2025</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D11" s="1" t="n">
+        <v>45937</v>
+      </c>
+      <c r="E11" s="1" t="n">
+        <v>46290</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>EKERÖ</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" t="n">
+        <v>2</v>
+      </c>
+      <c r="M11" t="n">
+        <v>1</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" t="n">
         <v>3</v>
       </c>
-      <c r="U10" t="n">
+      <c r="R11" t="n">
+        <v>1</v>
+      </c>
+      <c r="S11" t="n">
         <v>3</v>
       </c>
-      <c r="V10" s="2" t="inlineStr">
+      <c r="T11" t="n">
+        <v>3</v>
+      </c>
+      <c r="U11" t="n">
+        <v>3</v>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
         <is>
           <t>Jättemusseron
 Motaggsvamp
 Svartvit taggsvamp</t>
         </is>
       </c>
-      <c r="W10">
+      <c r="W11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0125/artfynd/A 49131-2025 artfynd.xlsx", "A 49131-2025")</f>
         <v/>
       </c>
-      <c r="X10">
+      <c r="X11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor/A 49131-2025 karta.png", "A 49131-2025")</f>
         <v/>
       </c>
-      <c r="Y10">
+      <c r="Y11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor_geotiff/A 49131-2025 georefererad karta.tif", "A 49131-2025")</f>
         <v/>
       </c>
-      <c r="AA10">
+      <c r="AA11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomål/A 49131-2025 FSC-klagomål.docx", "A 49131-2025")</f>
         <v/>
       </c>
-      <c r="AB10">
+      <c r="AB11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomålsmail/A 49131-2025 FSC-klagomål mail.docx", "A 49131-2025")</f>
         <v/>
       </c>
-      <c r="AC10">
+      <c r="AC11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsyn/A 49131-2025 tillsynsbegäran.docx", "A 49131-2025")</f>
         <v/>
       </c>
-      <c r="AD10">
+      <c r="AD11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsynsmail/A 49131-2025 tillsynsbegäran mail.docx", "A 49131-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="11" ht="15" customHeight="1">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>A 13237-2023</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D11" s="1" t="n">
-        <v>45002</v>
-      </c>
-      <c r="E11" s="1" t="n">
-        <v>46289</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>EKERÖ</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
-      <c r="I11" t="n">
-        <v>9.300000000000001</v>
-      </c>
-      <c r="J11" t="n">
-        <v>0</v>
-      </c>
-      <c r="K11" t="n">
-        <v>2</v>
-      </c>
-      <c r="L11" t="n">
-        <v>1</v>
-      </c>
-      <c r="M11" t="n">
-        <v>0</v>
-      </c>
-      <c r="N11" t="n">
-        <v>0</v>
-      </c>
-      <c r="O11" t="n">
-        <v>0</v>
-      </c>
-      <c r="P11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>1</v>
-      </c>
-      <c r="R11" t="n">
-        <v>0</v>
-      </c>
-      <c r="S11" t="n">
-        <v>3</v>
-      </c>
-      <c r="T11" t="n">
-        <v>7</v>
-      </c>
-      <c r="U11" t="n">
-        <v>0</v>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
-        <is>
-          <t>Tallticka
-Granbarkgnagare
-Grönpyrola</t>
-        </is>
-      </c>
-      <c r="W11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/artfynd/A 13237-2023 artfynd.xlsx", "A 13237-2023")</f>
-        <v/>
-      </c>
-      <c r="X11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor/A 13237-2023 karta.png", "A 13237-2023")</f>
-        <v/>
-      </c>
-      <c r="Y11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor_geotiff/A 13237-2023 georefererad karta.tif", "A 13237-2023")</f>
-        <v/>
-      </c>
-      <c r="AA11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomål/A 13237-2023 FSC-klagomål.docx", "A 13237-2023")</f>
-        <v/>
-      </c>
-      <c r="AB11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomålsmail/A 13237-2023 FSC-klagomål mail.docx", "A 13237-2023")</f>
-        <v/>
-      </c>
-      <c r="AC11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsyn/A 13237-2023 tillsynsbegäran.docx", "A 13237-2023")</f>
-        <v/>
-      </c>
-      <c r="AD11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsynsmail/A 13237-2023 tillsynsbegäran mail.docx", "A 13237-2023")</f>
         <v/>
       </c>
     </row>
@@ -1735,7 +1735,7 @@
         <v>45209</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1850,7 +1850,7 @@
         <v>45170</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1956,7 +1956,7 @@
         <v>44646</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2044,7 +2044,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 1793-2025</t>
+          <t>A 3221-2022</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2058,10 +2058,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45671</v>
+        <v>44582</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2074,13 +2074,13 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>1.7</v>
+        <v>0.5</v>
       </c>
       <c r="J15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L15" t="n">
         <v>0</v>
@@ -2107,49 +2107,49 @@
         <v>1</v>
       </c>
       <c r="T15" t="n">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>Mistel</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/artfynd/A 1793-2025 artfynd.xlsx", "A 1793-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/artfynd/A 3221-2022 artfynd.xlsx", "A 3221-2022")</f>
         <v/>
       </c>
       <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor/A 1793-2025 karta.png", "A 1793-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor/A 3221-2022 karta.png", "A 3221-2022")</f>
         <v/>
       </c>
       <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor_geotiff/A 1793-2025 georefererad karta.tif", "A 1793-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor_geotiff/A 3221-2022 georefererad karta.tif", "A 3221-2022")</f>
         <v/>
       </c>
       <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomål/A 1793-2025 FSC-klagomål.docx", "A 1793-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomål/A 3221-2022 FSC-klagomål.docx", "A 3221-2022")</f>
         <v/>
       </c>
       <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomålsmail/A 1793-2025 FSC-klagomål mail.docx", "A 1793-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomålsmail/A 3221-2022 FSC-klagomål mail.docx", "A 3221-2022")</f>
         <v/>
       </c>
       <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsyn/A 1793-2025 tillsynsbegäran.docx", "A 1793-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsyn/A 3221-2022 tillsynsbegäran.docx", "A 3221-2022")</f>
         <v/>
       </c>
       <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsynsmail/A 1793-2025 tillsynsbegäran mail.docx", "A 1793-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsynsmail/A 3221-2022 tillsynsbegäran mail.docx", "A 3221-2022")</f>
         <v/>
       </c>
     </row>
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 3221-2022</t>
+          <t>A 13794-2023</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2163,10 +2163,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>44582</v>
+        <v>45007</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2179,16 +2179,16 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>0.5</v>
+        <v>4.8</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M16" t="n">
         <v>0</v>
@@ -2203,7 +2203,7 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R16" t="n">
         <v>0</v>
@@ -2215,39 +2215,39 @@
         <v>1</v>
       </c>
       <c r="U16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/artfynd/A 3221-2022 artfynd.xlsx", "A 3221-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/artfynd/A 13794-2023 artfynd.xlsx", "A 13794-2023")</f>
         <v/>
       </c>
       <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor/A 3221-2022 karta.png", "A 3221-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor/A 13794-2023 karta.png", "A 13794-2023")</f>
         <v/>
       </c>
       <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor_geotiff/A 3221-2022 georefererad karta.tif", "A 3221-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor_geotiff/A 13794-2023 georefererad karta.tif", "A 13794-2023")</f>
         <v/>
       </c>
       <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomål/A 3221-2022 FSC-klagomål.docx", "A 3221-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomål/A 13794-2023 FSC-klagomål.docx", "A 13794-2023")</f>
         <v/>
       </c>
       <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomålsmail/A 3221-2022 FSC-klagomål mail.docx", "A 3221-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomålsmail/A 13794-2023 FSC-klagomål mail.docx", "A 13794-2023")</f>
         <v/>
       </c>
       <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsyn/A 3221-2022 tillsynsbegäran.docx", "A 3221-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsyn/A 13794-2023 tillsynsbegäran.docx", "A 13794-2023")</f>
         <v/>
       </c>
       <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsynsmail/A 3221-2022 tillsynsbegäran mail.docx", "A 3221-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsynsmail/A 13794-2023 tillsynsbegäran mail.docx", "A 13794-2023")</f>
         <v/>
       </c>
     </row>
@@ -2271,7 +2271,7 @@
         <v>46037</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2359,7 +2359,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 13794-2023</t>
+          <t>A 1793-2025</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2373,10 +2373,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45007</v>
+        <v>45671</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2389,16 +2389,16 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>4.8</v>
+        <v>1.7</v>
       </c>
       <c r="J18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K18" t="n">
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
         <v>0</v>
@@ -2413,7 +2413,7 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
         <v>0</v>
@@ -2422,42 +2422,42 @@
         <v>1</v>
       </c>
       <c r="T18" t="n">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="U18" t="n">
         <v>0</v>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Mistel</t>
         </is>
       </c>
       <c r="W18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/artfynd/A 13794-2023 artfynd.xlsx", "A 13794-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/artfynd/A 1793-2025 artfynd.xlsx", "A 1793-2025")</f>
         <v/>
       </c>
       <c r="X18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor/A 13794-2023 karta.png", "A 13794-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor/A 1793-2025 karta.png", "A 1793-2025")</f>
         <v/>
       </c>
       <c r="Y18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor_geotiff/A 13794-2023 georefererad karta.tif", "A 13794-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor_geotiff/A 1793-2025 georefererad karta.tif", "A 1793-2025")</f>
         <v/>
       </c>
       <c r="AA18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomål/A 13794-2023 FSC-klagomål.docx", "A 13794-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomål/A 1793-2025 FSC-klagomål.docx", "A 1793-2025")</f>
         <v/>
       </c>
       <c r="AB18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomålsmail/A 13794-2023 FSC-klagomål mail.docx", "A 13794-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomålsmail/A 1793-2025 FSC-klagomål mail.docx", "A 1793-2025")</f>
         <v/>
       </c>
       <c r="AC18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsyn/A 13794-2023 tillsynsbegäran.docx", "A 13794-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsyn/A 1793-2025 tillsynsbegäran.docx", "A 1793-2025")</f>
         <v/>
       </c>
       <c r="AD18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsynsmail/A 13794-2023 tillsynsbegäran mail.docx", "A 13794-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsynsmail/A 1793-2025 tillsynsbegäran mail.docx", "A 1793-2025")</f>
         <v/>
       </c>
     </row>
@@ -2481,7 +2481,7 @@
         <v>44670</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2554,7 +2554,7 @@
         <v>44802</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2610,7 +2610,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 61217-2024</t>
+          <t>A 3219-2022</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2624,10 +2624,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45645</v>
+        <v>44582</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2640,7 +2640,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2683,7 +2683,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 3222-2022</t>
+          <t>A 50184-2023</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2697,10 +2697,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>44582</v>
+        <v>45208</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2713,7 +2713,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>1.8</v>
+        <v>10.8</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2756,7 +2756,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 50184-2023</t>
+          <t>A 37245-2025</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2770,10 +2770,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45208</v>
+        <v>45876</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2786,7 +2786,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>10.8</v>
+        <v>1.1</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2829,7 +2829,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 3219-2022</t>
+          <t>A 20399-2026</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2843,10 +2843,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>44582</v>
+        <v>46139</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2859,7 +2859,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>0.5</v>
+        <v>0.9</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2902,7 +2902,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 60755-2024</t>
+          <t>A 20398-2026</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2916,10 +2916,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45644</v>
+        <v>46139</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2932,7 +2932,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>2.1</v>
+        <v>2.4</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2992,7 +2992,7 @@
         <v>45622</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3048,7 +3048,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 56002-2024</t>
+          <t>A 20898-2026</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3062,10 +3062,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45623</v>
+        <v>46142</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3078,7 +3078,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -3138,7 +3138,7 @@
         <v>45148</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3194,7 +3194,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 2535-2026</t>
+          <t>A 63378-2025</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3208,10 +3208,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>46037</v>
+        <v>46010</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3224,7 +3224,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>1.6</v>
+        <v>4.8</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3267,7 +3267,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 63378-2025</t>
+          <t>A 61217-2024</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3281,10 +3281,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>46010</v>
+        <v>45645</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3297,7 +3297,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>4.8</v>
+        <v>0.8</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3340,7 +3340,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 33154-2026</t>
+          <t>A 56002-2024</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3354,10 +3354,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>46244</v>
+        <v>45623</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3369,13 +3369,8 @@
           <t>EKERÖ</t>
         </is>
       </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I31" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3435,7 +3430,7 @@
         <v>44913</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3491,7 +3486,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 37245-2025</t>
+          <t>A 2535-2026</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3505,10 +3500,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45876</v>
+        <v>46037</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3521,7 +3516,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>1.1</v>
+        <v>1.6</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3564,7 +3559,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 20399-2026</t>
+          <t>A 34073-2025</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3574,14 +3569,14 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>46139</v>
+        <v>45845</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3594,7 +3589,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>0.9</v>
+        <v>2.9</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3637,7 +3632,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 20398-2026</t>
+          <t>A 3222-2022</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3651,10 +3646,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>46139</v>
+        <v>44582</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3667,7 +3662,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>2.4</v>
+        <v>1.8</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3710,7 +3705,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 20898-2026</t>
+          <t>A 60755-2024</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3724,10 +3719,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>46142</v>
+        <v>45644</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3740,7 +3735,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>3.6</v>
+        <v>2.1</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3783,7 +3778,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 34073-2025</t>
+          <t>A 33154-2026</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3793,14 +3788,14 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45845</v>
+        <v>46244</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3812,8 +3807,13 @@
           <t>EKERÖ</t>
         </is>
       </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I37" t="n">
-        <v>2.9</v>
+        <v>3.5</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3873,7 +3873,7 @@
         <v>46153</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>

--- a/Översikt EKERÖ.xlsx
+++ b/Översikt EKERÖ.xlsx
@@ -601,7 +601,7 @@
         <v>46241</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -728,7 +728,7 @@
         <v>44872</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -848,7 +848,7 @@
         <v>44974</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -963,7 +963,7 @@
         <v>45148</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1073,7 +1073,7 @@
         <v>46119</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1187,7 +1187,7 @@
         <v>44582</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1296,7 +1296,7 @@
         <v>46241</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1409,7 +1409,7 @@
         <v>44634</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1499,7 +1499,7 @@
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 13237-2023</t>
+          <t>A 49131-2025</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1513,10 +1513,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>45002</v>
+        <v>45937</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1528,25 +1528,20 @@
           <t>EKERÖ</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I10" t="n">
-        <v>9.300000000000001</v>
+        <v>0.9</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
       </c>
       <c r="K10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" t="n">
         <v>2</v>
       </c>
-      <c r="L10" t="n">
-        <v>1</v>
-      </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N10" t="n">
         <v>0</v>
@@ -1558,160 +1553,165 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S10" t="n">
         <v>3</v>
       </c>
       <c r="T10" t="n">
+        <v>3</v>
+      </c>
+      <c r="U10" t="n">
+        <v>3</v>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
+        <is>
+          <t>Jättemusseron
+Motaggsvamp
+Svartvit taggsvamp</t>
+        </is>
+      </c>
+      <c r="W10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/artfynd/A 49131-2025 artfynd.xlsx", "A 49131-2025")</f>
+        <v/>
+      </c>
+      <c r="X10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor/A 49131-2025 karta.png", "A 49131-2025")</f>
+        <v/>
+      </c>
+      <c r="Y10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor_geotiff/A 49131-2025 georefererad karta.tif", "A 49131-2025")</f>
+        <v/>
+      </c>
+      <c r="AA10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomål/A 49131-2025 FSC-klagomål.docx", "A 49131-2025")</f>
+        <v/>
+      </c>
+      <c r="AB10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomålsmail/A 49131-2025 FSC-klagomål mail.docx", "A 49131-2025")</f>
+        <v/>
+      </c>
+      <c r="AC10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsyn/A 49131-2025 tillsynsbegäran.docx", "A 49131-2025")</f>
+        <v/>
+      </c>
+      <c r="AD10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsynsmail/A 49131-2025 tillsynsbegäran mail.docx", "A 49131-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11" ht="15" customHeight="1">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>A 13237-2023</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D11" s="1" t="n">
+        <v>45002</v>
+      </c>
+      <c r="E11" s="1" t="n">
+        <v>46291</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>EKERÖ</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" t="n">
+        <v>2</v>
+      </c>
+      <c r="L11" t="n">
+        <v>1</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>1</v>
+      </c>
+      <c r="R11" t="n">
+        <v>0</v>
+      </c>
+      <c r="S11" t="n">
+        <v>3</v>
+      </c>
+      <c r="T11" t="n">
         <v>7</v>
       </c>
-      <c r="U10" t="n">
-        <v>0</v>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
+      <c r="U11" t="n">
+        <v>0</v>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
         <is>
           <t>Tallticka
 Granbarkgnagare
 Grönpyrola</t>
         </is>
       </c>
-      <c r="W10">
+      <c r="W11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0125/artfynd/A 13237-2023 artfynd.xlsx", "A 13237-2023")</f>
         <v/>
       </c>
-      <c r="X10">
+      <c r="X11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor/A 13237-2023 karta.png", "A 13237-2023")</f>
         <v/>
       </c>
-      <c r="Y10">
+      <c r="Y11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor_geotiff/A 13237-2023 georefererad karta.tif", "A 13237-2023")</f>
         <v/>
       </c>
-      <c r="AA10">
+      <c r="AA11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomål/A 13237-2023 FSC-klagomål.docx", "A 13237-2023")</f>
         <v/>
       </c>
-      <c r="AB10">
+      <c r="AB11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomålsmail/A 13237-2023 FSC-klagomål mail.docx", "A 13237-2023")</f>
         <v/>
       </c>
-      <c r="AC10">
+      <c r="AC11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsyn/A 13237-2023 tillsynsbegäran.docx", "A 13237-2023")</f>
         <v/>
       </c>
-      <c r="AD10">
+      <c r="AD11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsynsmail/A 13237-2023 tillsynsbegäran mail.docx", "A 13237-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="11" ht="15" customHeight="1">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>A 49131-2025</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D11" s="1" t="n">
-        <v>45937</v>
-      </c>
-      <c r="E11" s="1" t="n">
-        <v>46290</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>EKERÖ</t>
-        </is>
-      </c>
-      <c r="I11" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="J11" t="n">
-        <v>0</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L11" t="n">
-        <v>2</v>
-      </c>
-      <c r="M11" t="n">
-        <v>1</v>
-      </c>
-      <c r="N11" t="n">
-        <v>0</v>
-      </c>
-      <c r="O11" t="n">
-        <v>0</v>
-      </c>
-      <c r="P11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>3</v>
-      </c>
-      <c r="R11" t="n">
-        <v>1</v>
-      </c>
-      <c r="S11" t="n">
-        <v>3</v>
-      </c>
-      <c r="T11" t="n">
-        <v>3</v>
-      </c>
-      <c r="U11" t="n">
-        <v>3</v>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
-        <is>
-          <t>Jättemusseron
-Motaggsvamp
-Svartvit taggsvamp</t>
-        </is>
-      </c>
-      <c r="W11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/artfynd/A 49131-2025 artfynd.xlsx", "A 49131-2025")</f>
-        <v/>
-      </c>
-      <c r="X11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor/A 49131-2025 karta.png", "A 49131-2025")</f>
-        <v/>
-      </c>
-      <c r="Y11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor_geotiff/A 49131-2025 georefererad karta.tif", "A 49131-2025")</f>
-        <v/>
-      </c>
-      <c r="AA11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomål/A 49131-2025 FSC-klagomål.docx", "A 49131-2025")</f>
-        <v/>
-      </c>
-      <c r="AB11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomålsmail/A 49131-2025 FSC-klagomål mail.docx", "A 49131-2025")</f>
-        <v/>
-      </c>
-      <c r="AC11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsyn/A 49131-2025 tillsynsbegäran.docx", "A 49131-2025")</f>
-        <v/>
-      </c>
-      <c r="AD11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsynsmail/A 49131-2025 tillsynsbegäran mail.docx", "A 49131-2025")</f>
         <v/>
       </c>
     </row>
@@ -1735,7 +1735,7 @@
         <v>45209</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1850,7 +1850,7 @@
         <v>45170</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1956,7 +1956,7 @@
         <v>44646</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2044,7 +2044,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 3221-2022</t>
+          <t>A 2533-2026</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2058,10 +2058,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>44582</v>
+        <v>46037</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2074,13 +2074,13 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>0.5</v>
+        <v>1.4</v>
       </c>
       <c r="J15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L15" t="n">
         <v>0</v>
@@ -2110,46 +2110,46 @@
         <v>1</v>
       </c>
       <c r="U15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/artfynd/A 3221-2022 artfynd.xlsx", "A 3221-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/artfynd/A 2533-2026 artfynd.xlsx", "A 2533-2026")</f>
         <v/>
       </c>
       <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor/A 3221-2022 karta.png", "A 3221-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor/A 2533-2026 karta.png", "A 2533-2026")</f>
         <v/>
       </c>
       <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor_geotiff/A 3221-2022 georefererad karta.tif", "A 3221-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor_geotiff/A 2533-2026 georefererad karta.tif", "A 2533-2026")</f>
         <v/>
       </c>
       <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomål/A 3221-2022 FSC-klagomål.docx", "A 3221-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomål/A 2533-2026 FSC-klagomål.docx", "A 2533-2026")</f>
         <v/>
       </c>
       <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomålsmail/A 3221-2022 FSC-klagomål mail.docx", "A 3221-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomålsmail/A 2533-2026 FSC-klagomål mail.docx", "A 2533-2026")</f>
         <v/>
       </c>
       <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsyn/A 3221-2022 tillsynsbegäran.docx", "A 3221-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsyn/A 2533-2026 tillsynsbegäran.docx", "A 2533-2026")</f>
         <v/>
       </c>
       <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsynsmail/A 3221-2022 tillsynsbegäran mail.docx", "A 3221-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsynsmail/A 2533-2026 tillsynsbegäran mail.docx", "A 2533-2026")</f>
         <v/>
       </c>
     </row>
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 13794-2023</t>
+          <t>A 3221-2022</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2163,10 +2163,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45007</v>
+        <v>44582</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2179,16 +2179,16 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>4.8</v>
+        <v>0.5</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
         <v>0</v>
@@ -2203,7 +2203,7 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
         <v>0</v>
@@ -2215,46 +2215,46 @@
         <v>1</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/artfynd/A 13794-2023 artfynd.xlsx", "A 13794-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/artfynd/A 3221-2022 artfynd.xlsx", "A 3221-2022")</f>
         <v/>
       </c>
       <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor/A 13794-2023 karta.png", "A 13794-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor/A 3221-2022 karta.png", "A 3221-2022")</f>
         <v/>
       </c>
       <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor_geotiff/A 13794-2023 georefererad karta.tif", "A 13794-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor_geotiff/A 3221-2022 georefererad karta.tif", "A 3221-2022")</f>
         <v/>
       </c>
       <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomål/A 13794-2023 FSC-klagomål.docx", "A 13794-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomål/A 3221-2022 FSC-klagomål.docx", "A 3221-2022")</f>
         <v/>
       </c>
       <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomålsmail/A 13794-2023 FSC-klagomål mail.docx", "A 13794-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomålsmail/A 3221-2022 FSC-klagomål mail.docx", "A 3221-2022")</f>
         <v/>
       </c>
       <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsyn/A 13794-2023 tillsynsbegäran.docx", "A 13794-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsyn/A 3221-2022 tillsynsbegäran.docx", "A 3221-2022")</f>
         <v/>
       </c>
       <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsynsmail/A 13794-2023 tillsynsbegäran mail.docx", "A 13794-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsynsmail/A 3221-2022 tillsynsbegäran mail.docx", "A 3221-2022")</f>
         <v/>
       </c>
     </row>
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 2533-2026</t>
+          <t>A 13794-2023</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2268,10 +2268,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>46037</v>
+        <v>45007</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2284,16 +2284,16 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>1.4</v>
+        <v>4.8</v>
       </c>
       <c r="J17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K17" t="n">
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M17" t="n">
         <v>0</v>
@@ -2308,7 +2308,7 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R17" t="n">
         <v>0</v>
@@ -2324,35 +2324,35 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/artfynd/A 2533-2026 artfynd.xlsx", "A 2533-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/artfynd/A 13794-2023 artfynd.xlsx", "A 13794-2023")</f>
         <v/>
       </c>
       <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor/A 2533-2026 karta.png", "A 2533-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor/A 13794-2023 karta.png", "A 13794-2023")</f>
         <v/>
       </c>
       <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor_geotiff/A 2533-2026 georefererad karta.tif", "A 2533-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor_geotiff/A 13794-2023 georefererad karta.tif", "A 13794-2023")</f>
         <v/>
       </c>
       <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomål/A 2533-2026 FSC-klagomål.docx", "A 2533-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomål/A 13794-2023 FSC-klagomål.docx", "A 13794-2023")</f>
         <v/>
       </c>
       <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomålsmail/A 2533-2026 FSC-klagomål mail.docx", "A 2533-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomålsmail/A 13794-2023 FSC-klagomål mail.docx", "A 13794-2023")</f>
         <v/>
       </c>
       <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsyn/A 2533-2026 tillsynsbegäran.docx", "A 2533-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsyn/A 13794-2023 tillsynsbegäran.docx", "A 13794-2023")</f>
         <v/>
       </c>
       <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsynsmail/A 2533-2026 tillsynsbegäran mail.docx", "A 2533-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsynsmail/A 13794-2023 tillsynsbegäran mail.docx", "A 13794-2023")</f>
         <v/>
       </c>
     </row>
@@ -2376,7 +2376,7 @@
         <v>45671</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2481,7 +2481,7 @@
         <v>44670</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2554,7 +2554,7 @@
         <v>44802</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2610,7 +2610,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 3219-2022</t>
+          <t>A 63378-2025</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2624,10 +2624,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>44582</v>
+        <v>46010</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2640,7 +2640,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>0.5</v>
+        <v>4.8</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2683,7 +2683,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 50184-2023</t>
+          <t>A 2535-2026</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2697,10 +2697,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>45208</v>
+        <v>46037</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2713,7 +2713,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>10.8</v>
+        <v>1.6</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2756,7 +2756,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 37245-2025</t>
+          <t>A 50184-2023</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2770,10 +2770,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45876</v>
+        <v>45208</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2786,7 +2786,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>1.1</v>
+        <v>10.8</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2829,7 +2829,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 20399-2026</t>
+          <t>A 56002-2024</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2843,10 +2843,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>46139</v>
+        <v>45623</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2859,7 +2859,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>0.9</v>
+        <v>3.4</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2902,7 +2902,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 20398-2026</t>
+          <t>A 61217-2024</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2916,10 +2916,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>46139</v>
+        <v>45645</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2932,7 +2932,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>2.4</v>
+        <v>0.8</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2975,7 +2975,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 55724-2024</t>
+          <t>A 20399-2026</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2989,10 +2989,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45622</v>
+        <v>46139</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3005,7 +3005,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>0.5</v>
+        <v>0.9</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -3048,7 +3048,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 20898-2026</t>
+          <t>A 20398-2026</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3062,10 +3062,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>46142</v>
+        <v>46139</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3078,7 +3078,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>3.6</v>
+        <v>2.4</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -3121,7 +3121,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 35955-2023</t>
+          <t>A 3222-2022</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3135,10 +3135,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45148</v>
+        <v>44582</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3151,7 +3151,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>1.1</v>
+        <v>1.8</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -3194,7 +3194,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 63378-2025</t>
+          <t>A 20898-2026</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3208,10 +3208,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>46010</v>
+        <v>46142</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3224,7 +3224,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>4.8</v>
+        <v>3.6</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3267,7 +3267,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 61217-2024</t>
+          <t>A 34073-2025</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3277,14 +3277,14 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45645</v>
+        <v>45845</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3297,7 +3297,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>0.8</v>
+        <v>2.9</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3340,7 +3340,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 56002-2024</t>
+          <t>A 3219-2022</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3354,10 +3354,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45623</v>
+        <v>44582</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3370,7 +3370,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>3.4</v>
+        <v>0.5</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3413,7 +3413,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 60728-2022</t>
+          <t>A 37245-2025</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3427,10 +3427,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>44913</v>
+        <v>45876</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3443,7 +3443,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3486,7 +3486,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 2535-2026</t>
+          <t>A 60755-2024</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3500,10 +3500,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>46037</v>
+        <v>45644</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3516,7 +3516,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>1.6</v>
+        <v>2.1</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3559,7 +3559,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 34073-2025</t>
+          <t>A 55724-2024</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3569,14 +3569,14 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45845</v>
+        <v>45622</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3589,7 +3589,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>2.9</v>
+        <v>0.5</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3632,7 +3632,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 3222-2022</t>
+          <t>A 35955-2023</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3646,10 +3646,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>44582</v>
+        <v>45148</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3662,7 +3662,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>1.8</v>
+        <v>1.1</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3705,7 +3705,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 60755-2024</t>
+          <t>A 33154-2026</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3719,10 +3719,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45644</v>
+        <v>46244</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3734,8 +3734,13 @@
           <t>EKERÖ</t>
         </is>
       </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I36" t="n">
-        <v>2.1</v>
+        <v>3.5</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3778,7 +3783,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 33154-2026</t>
+          <t>A 60728-2022</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3792,10 +3797,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>46244</v>
+        <v>44913</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3807,13 +3812,8 @@
           <t>EKERÖ</t>
         </is>
       </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I37" t="n">
-        <v>3.5</v>
+        <v>1.2</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3873,7 +3873,7 @@
         <v>46153</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>

--- a/Översikt EKERÖ.xlsx
+++ b/Översikt EKERÖ.xlsx
@@ -601,7 +601,7 @@
         <v>46241</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -728,7 +728,7 @@
         <v>44872</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -848,7 +848,7 @@
         <v>44974</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -963,7 +963,7 @@
         <v>45148</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1073,7 +1073,7 @@
         <v>46119</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1187,7 +1187,7 @@
         <v>44582</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1296,7 +1296,7 @@
         <v>46241</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1409,7 +1409,7 @@
         <v>44634</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1516,7 +1516,7 @@
         <v>45937</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1623,7 +1623,7 @@
         <v>45002</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1735,7 +1735,7 @@
         <v>45209</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1850,7 +1850,7 @@
         <v>45170</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1956,7 +1956,7 @@
         <v>44646</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2061,7 +2061,7 @@
         <v>46037</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2166,7 +2166,7 @@
         <v>44582</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2271,7 +2271,7 @@
         <v>45007</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2376,7 +2376,7 @@
         <v>45671</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2481,7 +2481,7 @@
         <v>44670</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2554,7 +2554,7 @@
         <v>44802</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2627,7 +2627,7 @@
         <v>46010</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2700,7 +2700,7 @@
         <v>46037</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2773,7 +2773,7 @@
         <v>45208</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2846,7 +2846,7 @@
         <v>45623</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2919,7 +2919,7 @@
         <v>45645</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2992,7 +2992,7 @@
         <v>46139</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3065,7 +3065,7 @@
         <v>46139</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3138,7 +3138,7 @@
         <v>44582</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3211,7 +3211,7 @@
         <v>46142</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3284,7 +3284,7 @@
         <v>45845</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3357,7 +3357,7 @@
         <v>44582</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3430,7 +3430,7 @@
         <v>45876</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3503,7 +3503,7 @@
         <v>45644</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3576,7 +3576,7 @@
         <v>45622</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3649,7 +3649,7 @@
         <v>45148</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3722,7 +3722,7 @@
         <v>46244</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3800,7 +3800,7 @@
         <v>44913</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3873,7 +3873,7 @@
         <v>46153</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>

--- a/Översikt EKERÖ.xlsx
+++ b/Översikt EKERÖ.xlsx
@@ -601,7 +601,7 @@
         <v>46241</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -728,7 +728,7 @@
         <v>44872</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -848,7 +848,7 @@
         <v>44974</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -963,7 +963,7 @@
         <v>45148</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1073,7 +1073,7 @@
         <v>46119</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1187,7 +1187,7 @@
         <v>44582</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1296,7 +1296,7 @@
         <v>46241</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1409,7 +1409,7 @@
         <v>44634</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1516,7 +1516,7 @@
         <v>45937</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1623,7 +1623,7 @@
         <v>45002</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1735,7 +1735,7 @@
         <v>45209</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1850,7 +1850,7 @@
         <v>45170</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1956,7 +1956,7 @@
         <v>44646</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2061,7 +2061,7 @@
         <v>46037</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2166,7 +2166,7 @@
         <v>44582</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2271,7 +2271,7 @@
         <v>45007</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2376,7 +2376,7 @@
         <v>45671</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2481,7 +2481,7 @@
         <v>44670</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2554,7 +2554,7 @@
         <v>44802</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2627,7 +2627,7 @@
         <v>46010</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2700,7 +2700,7 @@
         <v>46037</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2773,7 +2773,7 @@
         <v>45208</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2846,7 +2846,7 @@
         <v>45623</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2919,7 +2919,7 @@
         <v>45645</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2992,7 +2992,7 @@
         <v>46139</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3065,7 +3065,7 @@
         <v>46139</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3138,7 +3138,7 @@
         <v>44582</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3211,7 +3211,7 @@
         <v>46142</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3284,7 +3284,7 @@
         <v>45845</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3357,7 +3357,7 @@
         <v>44582</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3430,7 +3430,7 @@
         <v>45876</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3503,7 +3503,7 @@
         <v>45644</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3576,7 +3576,7 @@
         <v>45622</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3649,7 +3649,7 @@
         <v>45148</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3722,7 +3722,7 @@
         <v>46244</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3800,7 +3800,7 @@
         <v>44913</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3873,7 +3873,7 @@
         <v>46153</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>

--- a/Översikt EKERÖ.xlsx
+++ b/Översikt EKERÖ.xlsx
@@ -601,7 +601,7 @@
         <v>46241</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -728,7 +728,7 @@
         <v>44872</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -848,7 +848,7 @@
         <v>44974</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -963,7 +963,7 @@
         <v>45148</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1073,7 +1073,7 @@
         <v>46119</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1187,7 +1187,7 @@
         <v>44582</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1296,7 +1296,7 @@
         <v>46241</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1409,7 +1409,7 @@
         <v>44634</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1499,7 +1499,7 @@
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 49131-2025</t>
+          <t>A 13237-2023</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1513,10 +1513,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>45937</v>
+        <v>45002</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1528,20 +1528,25 @@
           <t>EKERÖ</t>
         </is>
       </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I10" t="n">
-        <v>0.9</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N10" t="n">
         <v>0</v>
@@ -1553,165 +1558,160 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="R10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
         <v>3</v>
       </c>
       <c r="T10" t="n">
+        <v>7</v>
+      </c>
+      <c r="U10" t="n">
+        <v>0</v>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
+        <is>
+          <t>Tallticka
+Granbarkgnagare
+Grönpyrola</t>
+        </is>
+      </c>
+      <c r="W10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/artfynd/A 13237-2023 artfynd.xlsx", "A 13237-2023")</f>
+        <v/>
+      </c>
+      <c r="X10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor/A 13237-2023 karta.png", "A 13237-2023")</f>
+        <v/>
+      </c>
+      <c r="Y10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor_geotiff/A 13237-2023 georefererad karta.tif", "A 13237-2023")</f>
+        <v/>
+      </c>
+      <c r="AA10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomål/A 13237-2023 FSC-klagomål.docx", "A 13237-2023")</f>
+        <v/>
+      </c>
+      <c r="AB10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomålsmail/A 13237-2023 FSC-klagomål mail.docx", "A 13237-2023")</f>
+        <v/>
+      </c>
+      <c r="AC10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsyn/A 13237-2023 tillsynsbegäran.docx", "A 13237-2023")</f>
+        <v/>
+      </c>
+      <c r="AD10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsynsmail/A 13237-2023 tillsynsbegäran mail.docx", "A 13237-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11" ht="15" customHeight="1">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>A 49131-2025</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D11" s="1" t="n">
+        <v>45937</v>
+      </c>
+      <c r="E11" s="1" t="n">
+        <v>46294</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>EKERÖ</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" t="n">
+        <v>2</v>
+      </c>
+      <c r="M11" t="n">
+        <v>1</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" t="n">
         <v>3</v>
       </c>
-      <c r="U10" t="n">
+      <c r="R11" t="n">
+        <v>1</v>
+      </c>
+      <c r="S11" t="n">
         <v>3</v>
       </c>
-      <c r="V10" s="2" t="inlineStr">
+      <c r="T11" t="n">
+        <v>3</v>
+      </c>
+      <c r="U11" t="n">
+        <v>3</v>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
         <is>
           <t>Jättemusseron
 Motaggsvamp
 Svartvit taggsvamp</t>
         </is>
       </c>
-      <c r="W10">
+      <c r="W11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0125/artfynd/A 49131-2025 artfynd.xlsx", "A 49131-2025")</f>
         <v/>
       </c>
-      <c r="X10">
+      <c r="X11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor/A 49131-2025 karta.png", "A 49131-2025")</f>
         <v/>
       </c>
-      <c r="Y10">
+      <c r="Y11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor_geotiff/A 49131-2025 georefererad karta.tif", "A 49131-2025")</f>
         <v/>
       </c>
-      <c r="AA10">
+      <c r="AA11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomål/A 49131-2025 FSC-klagomål.docx", "A 49131-2025")</f>
         <v/>
       </c>
-      <c r="AB10">
+      <c r="AB11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomålsmail/A 49131-2025 FSC-klagomål mail.docx", "A 49131-2025")</f>
         <v/>
       </c>
-      <c r="AC10">
+      <c r="AC11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsyn/A 49131-2025 tillsynsbegäran.docx", "A 49131-2025")</f>
         <v/>
       </c>
-      <c r="AD10">
+      <c r="AD11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsynsmail/A 49131-2025 tillsynsbegäran mail.docx", "A 49131-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="11" ht="15" customHeight="1">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>A 13237-2023</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D11" s="1" t="n">
-        <v>45002</v>
-      </c>
-      <c r="E11" s="1" t="n">
-        <v>46293</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>EKERÖ</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
-      <c r="I11" t="n">
-        <v>9.300000000000001</v>
-      </c>
-      <c r="J11" t="n">
-        <v>0</v>
-      </c>
-      <c r="K11" t="n">
-        <v>2</v>
-      </c>
-      <c r="L11" t="n">
-        <v>1</v>
-      </c>
-      <c r="M11" t="n">
-        <v>0</v>
-      </c>
-      <c r="N11" t="n">
-        <v>0</v>
-      </c>
-      <c r="O11" t="n">
-        <v>0</v>
-      </c>
-      <c r="P11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>1</v>
-      </c>
-      <c r="R11" t="n">
-        <v>0</v>
-      </c>
-      <c r="S11" t="n">
-        <v>3</v>
-      </c>
-      <c r="T11" t="n">
-        <v>7</v>
-      </c>
-      <c r="U11" t="n">
-        <v>0</v>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
-        <is>
-          <t>Tallticka
-Granbarkgnagare
-Grönpyrola</t>
-        </is>
-      </c>
-      <c r="W11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/artfynd/A 13237-2023 artfynd.xlsx", "A 13237-2023")</f>
-        <v/>
-      </c>
-      <c r="X11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor/A 13237-2023 karta.png", "A 13237-2023")</f>
-        <v/>
-      </c>
-      <c r="Y11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor_geotiff/A 13237-2023 georefererad karta.tif", "A 13237-2023")</f>
-        <v/>
-      </c>
-      <c r="AA11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomål/A 13237-2023 FSC-klagomål.docx", "A 13237-2023")</f>
-        <v/>
-      </c>
-      <c r="AB11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomålsmail/A 13237-2023 FSC-klagomål mail.docx", "A 13237-2023")</f>
-        <v/>
-      </c>
-      <c r="AC11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsyn/A 13237-2023 tillsynsbegäran.docx", "A 13237-2023")</f>
-        <v/>
-      </c>
-      <c r="AD11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsynsmail/A 13237-2023 tillsynsbegäran mail.docx", "A 13237-2023")</f>
         <v/>
       </c>
     </row>
@@ -1735,7 +1735,7 @@
         <v>45209</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1850,7 +1850,7 @@
         <v>45170</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1956,7 +1956,7 @@
         <v>44646</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2044,7 +2044,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 2533-2026</t>
+          <t>A 3221-2022</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2058,10 +2058,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>46037</v>
+        <v>44582</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2074,13 +2074,13 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>1.4</v>
+        <v>0.5</v>
       </c>
       <c r="J15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L15" t="n">
         <v>0</v>
@@ -2110,46 +2110,46 @@
         <v>1</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/artfynd/A 2533-2026 artfynd.xlsx", "A 2533-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/artfynd/A 3221-2022 artfynd.xlsx", "A 3221-2022")</f>
         <v/>
       </c>
       <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor/A 2533-2026 karta.png", "A 2533-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor/A 3221-2022 karta.png", "A 3221-2022")</f>
         <v/>
       </c>
       <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor_geotiff/A 2533-2026 georefererad karta.tif", "A 2533-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor_geotiff/A 3221-2022 georefererad karta.tif", "A 3221-2022")</f>
         <v/>
       </c>
       <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomål/A 2533-2026 FSC-klagomål.docx", "A 2533-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomål/A 3221-2022 FSC-klagomål.docx", "A 3221-2022")</f>
         <v/>
       </c>
       <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomålsmail/A 2533-2026 FSC-klagomål mail.docx", "A 2533-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomålsmail/A 3221-2022 FSC-klagomål mail.docx", "A 3221-2022")</f>
         <v/>
       </c>
       <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsyn/A 2533-2026 tillsynsbegäran.docx", "A 2533-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsyn/A 3221-2022 tillsynsbegäran.docx", "A 3221-2022")</f>
         <v/>
       </c>
       <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsynsmail/A 2533-2026 tillsynsbegäran mail.docx", "A 2533-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsynsmail/A 3221-2022 tillsynsbegäran mail.docx", "A 3221-2022")</f>
         <v/>
       </c>
     </row>
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 3221-2022</t>
+          <t>A 1793-2025</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2163,10 +2163,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>44582</v>
+        <v>45671</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2179,13 +2179,13 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>0.5</v>
+        <v>1.7</v>
       </c>
       <c r="J16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L16" t="n">
         <v>0</v>
@@ -2212,42 +2212,42 @@
         <v>1</v>
       </c>
       <c r="T16" t="n">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="U16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Mistel</t>
         </is>
       </c>
       <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/artfynd/A 3221-2022 artfynd.xlsx", "A 3221-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/artfynd/A 1793-2025 artfynd.xlsx", "A 1793-2025")</f>
         <v/>
       </c>
       <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor/A 3221-2022 karta.png", "A 3221-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor/A 1793-2025 karta.png", "A 1793-2025")</f>
         <v/>
       </c>
       <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor_geotiff/A 3221-2022 georefererad karta.tif", "A 3221-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor_geotiff/A 1793-2025 georefererad karta.tif", "A 1793-2025")</f>
         <v/>
       </c>
       <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomål/A 3221-2022 FSC-klagomål.docx", "A 3221-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomål/A 1793-2025 FSC-klagomål.docx", "A 1793-2025")</f>
         <v/>
       </c>
       <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomålsmail/A 3221-2022 FSC-klagomål mail.docx", "A 3221-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomålsmail/A 1793-2025 FSC-klagomål mail.docx", "A 1793-2025")</f>
         <v/>
       </c>
       <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsyn/A 3221-2022 tillsynsbegäran.docx", "A 3221-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsyn/A 1793-2025 tillsynsbegäran.docx", "A 1793-2025")</f>
         <v/>
       </c>
       <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsynsmail/A 3221-2022 tillsynsbegäran mail.docx", "A 3221-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsynsmail/A 1793-2025 tillsynsbegäran mail.docx", "A 1793-2025")</f>
         <v/>
       </c>
     </row>
@@ -2271,7 +2271,7 @@
         <v>45007</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2359,7 +2359,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 1793-2025</t>
+          <t>A 2533-2026</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2373,10 +2373,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45671</v>
+        <v>46037</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2389,7 +2389,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>1.7</v>
+        <v>1.4</v>
       </c>
       <c r="J18" t="n">
         <v>1</v>
@@ -2422,42 +2422,42 @@
         <v>1</v>
       </c>
       <c r="T18" t="n">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="U18" t="n">
         <v>0</v>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>Mistel</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="W18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/artfynd/A 1793-2025 artfynd.xlsx", "A 1793-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/artfynd/A 2533-2026 artfynd.xlsx", "A 2533-2026")</f>
         <v/>
       </c>
       <c r="X18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor/A 1793-2025 karta.png", "A 1793-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor/A 2533-2026 karta.png", "A 2533-2026")</f>
         <v/>
       </c>
       <c r="Y18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor_geotiff/A 1793-2025 georefererad karta.tif", "A 1793-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor_geotiff/A 2533-2026 georefererad karta.tif", "A 2533-2026")</f>
         <v/>
       </c>
       <c r="AA18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomål/A 1793-2025 FSC-klagomål.docx", "A 1793-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomål/A 2533-2026 FSC-klagomål.docx", "A 2533-2026")</f>
         <v/>
       </c>
       <c r="AB18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomålsmail/A 1793-2025 FSC-klagomål mail.docx", "A 1793-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomålsmail/A 2533-2026 FSC-klagomål mail.docx", "A 2533-2026")</f>
         <v/>
       </c>
       <c r="AC18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsyn/A 1793-2025 tillsynsbegäran.docx", "A 1793-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsyn/A 2533-2026 tillsynsbegäran.docx", "A 2533-2026")</f>
         <v/>
       </c>
       <c r="AD18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsynsmail/A 1793-2025 tillsynsbegäran mail.docx", "A 1793-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsynsmail/A 2533-2026 tillsynsbegäran mail.docx", "A 2533-2026")</f>
         <v/>
       </c>
     </row>
@@ -2481,7 +2481,7 @@
         <v>44670</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2554,7 +2554,7 @@
         <v>44802</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2610,7 +2610,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 63378-2025</t>
+          <t>A 3219-2022</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2624,10 +2624,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>46010</v>
+        <v>44582</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2640,7 +2640,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>4.8</v>
+        <v>0.5</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2683,7 +2683,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 2535-2026</t>
+          <t>A 63378-2025</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2697,10 +2697,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>46037</v>
+        <v>46010</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2713,7 +2713,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>1.6</v>
+        <v>4.8</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2773,7 +2773,7 @@
         <v>45208</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2829,7 +2829,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 56002-2024</t>
+          <t>A 37245-2025</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2843,10 +2843,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45623</v>
+        <v>45876</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2859,7 +2859,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>3.4</v>
+        <v>1.1</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2902,7 +2902,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 61217-2024</t>
+          <t>A 2535-2026</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2916,10 +2916,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45645</v>
+        <v>46037</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2932,7 +2932,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>0.8</v>
+        <v>1.6</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2975,7 +2975,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 20399-2026</t>
+          <t>A 55724-2024</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2989,10 +2989,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>46139</v>
+        <v>45622</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3005,7 +3005,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>0.9</v>
+        <v>0.5</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -3048,7 +3048,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 20398-2026</t>
+          <t>A 20399-2026</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3065,7 +3065,7 @@
         <v>46139</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3078,7 +3078,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>2.4</v>
+        <v>0.9</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -3121,7 +3121,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 3222-2022</t>
+          <t>A 35955-2023</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3135,10 +3135,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>44582</v>
+        <v>45148</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3151,7 +3151,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>1.8</v>
+        <v>1.1</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -3194,7 +3194,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 20898-2026</t>
+          <t>A 20398-2026</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3208,10 +3208,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>46142</v>
+        <v>46139</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3224,7 +3224,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>3.6</v>
+        <v>2.4</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3267,7 +3267,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 34073-2025</t>
+          <t>A 61217-2024</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3277,14 +3277,14 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45845</v>
+        <v>45645</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3297,7 +3297,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>2.9</v>
+        <v>0.8</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3340,7 +3340,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 3219-2022</t>
+          <t>A 56002-2024</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3354,10 +3354,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>44582</v>
+        <v>45623</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3370,7 +3370,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>0.5</v>
+        <v>3.4</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3413,7 +3413,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 37245-2025</t>
+          <t>A 60728-2022</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3427,10 +3427,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45876</v>
+        <v>44913</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3443,7 +3443,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3486,7 +3486,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 60755-2024</t>
+          <t>A 20898-2026</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3500,10 +3500,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45644</v>
+        <v>46142</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3516,7 +3516,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>2.1</v>
+        <v>3.6</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3559,7 +3559,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 55724-2024</t>
+          <t>A 3222-2022</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3573,10 +3573,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45622</v>
+        <v>44582</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3589,7 +3589,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>0.5</v>
+        <v>1.8</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3632,7 +3632,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 35955-2023</t>
+          <t>A 34073-2025</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3642,14 +3642,14 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45148</v>
+        <v>45845</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3662,7 +3662,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>1.1</v>
+        <v>2.9</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3705,7 +3705,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 33154-2026</t>
+          <t>A 60755-2024</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3719,10 +3719,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>46244</v>
+        <v>45644</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3734,13 +3734,8 @@
           <t>EKERÖ</t>
         </is>
       </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I36" t="n">
-        <v>3.5</v>
+        <v>2.1</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3783,7 +3778,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 60728-2022</t>
+          <t>A 33154-2026</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3797,10 +3792,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>44913</v>
+        <v>46244</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3812,8 +3807,13 @@
           <t>EKERÖ</t>
         </is>
       </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I37" t="n">
-        <v>1.2</v>
+        <v>3.5</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3873,7 +3873,7 @@
         <v>46153</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>

--- a/Översikt EKERÖ.xlsx
+++ b/Översikt EKERÖ.xlsx
@@ -601,7 +601,7 @@
         <v>46241</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -728,7 +728,7 @@
         <v>44872</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -848,7 +848,7 @@
         <v>44974</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -963,7 +963,7 @@
         <v>45148</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1056,7 +1056,7 @@
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A 17520-2026</t>
+          <t>A 3218-2022</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1070,10 +1070,10 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>46119</v>
+        <v>44582</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1085,13 +1085,8 @@
           <t>EKERÖ</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I6" t="n">
-        <v>2.2</v>
+        <v>1.2</v>
       </c>
       <c r="J6" t="n">
         <v>1</v>
@@ -1100,36 +1095,150 @@
         <v>1</v>
       </c>
       <c r="L6" t="n">
+        <v>1</v>
+      </c>
+      <c r="M6" t="n">
+        <v>1</v>
+      </c>
+      <c r="N6" t="n">
+        <v>1</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" t="n">
         <v>3</v>
       </c>
-      <c r="M6" t="n">
-        <v>1</v>
-      </c>
-      <c r="N6" t="n">
-        <v>0</v>
-      </c>
-      <c r="O6" t="n">
-        <v>0</v>
-      </c>
-      <c r="P6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>4</v>
-      </c>
       <c r="R6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
       </c>
       <c r="T6" t="n">
+        <v>8</v>
+      </c>
+      <c r="U6" t="n">
+        <v>6</v>
+      </c>
+      <c r="V6" s="2" t="inlineStr">
+        <is>
+          <t>Bombmurkla
+Gul lammticka
+Fyrflikig jordstjärna
+Kamjordstjärna
+Blåbär</t>
+        </is>
+      </c>
+      <c r="W6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/artfynd/A 3218-2022 artfynd.xlsx", "A 3218-2022")</f>
+        <v/>
+      </c>
+      <c r="X6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor/A 3218-2022 karta.png", "A 3218-2022")</f>
+        <v/>
+      </c>
+      <c r="Y6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor_geotiff/A 3218-2022 georefererad karta.tif", "A 3218-2022")</f>
+        <v/>
+      </c>
+      <c r="AA6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomål/A 3218-2022 FSC-klagomål.docx", "A 3218-2022")</f>
+        <v/>
+      </c>
+      <c r="AB6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomålsmail/A 3218-2022 FSC-klagomål mail.docx", "A 3218-2022")</f>
+        <v/>
+      </c>
+      <c r="AC6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsyn/A 3218-2022 tillsynsbegäran.docx", "A 3218-2022")</f>
+        <v/>
+      </c>
+      <c r="AD6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsynsmail/A 3218-2022 tillsynsbegäran mail.docx", "A 3218-2022")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7" ht="15" customHeight="1">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>A 17520-2026</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D7" s="1" t="n">
+        <v>46119</v>
+      </c>
+      <c r="E7" s="1" t="n">
+        <v>46295</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>EKERÖ</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="J7" t="n">
+        <v>1</v>
+      </c>
+      <c r="K7" t="n">
+        <v>1</v>
+      </c>
+      <c r="L7" t="n">
+        <v>3</v>
+      </c>
+      <c r="M7" t="n">
+        <v>1</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>4</v>
+      </c>
+      <c r="R7" t="n">
+        <v>1</v>
+      </c>
+      <c r="S7" t="n">
         <v>5</v>
       </c>
-      <c r="U6" t="n">
-        <v>1</v>
-      </c>
-      <c r="V6" s="2" t="inlineStr">
+      <c r="T7" t="n">
+        <v>5</v>
+      </c>
+      <c r="U7" t="n">
+        <v>1</v>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
         <is>
           <t>Läderbagge
 Blekticka
@@ -1138,141 +1247,32 @@
 Gulgrön kantmusseron</t>
         </is>
       </c>
-      <c r="W6">
+      <c r="W7">
         <f>HYPERLINK("https://klasma.github.io/Logging_0125/artfynd/A 17520-2026 artfynd.xlsx", "A 17520-2026")</f>
         <v/>
       </c>
-      <c r="X6">
+      <c r="X7">
         <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor/A 17520-2026 karta.png", "A 17520-2026")</f>
         <v/>
       </c>
-      <c r="Y6">
+      <c r="Y7">
         <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor_geotiff/A 17520-2026 georefererad karta.tif", "A 17520-2026")</f>
         <v/>
       </c>
-      <c r="AA6">
+      <c r="AA7">
         <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomål/A 17520-2026 FSC-klagomål.docx", "A 17520-2026")</f>
         <v/>
       </c>
-      <c r="AB6">
+      <c r="AB7">
         <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomålsmail/A 17520-2026 FSC-klagomål mail.docx", "A 17520-2026")</f>
         <v/>
       </c>
-      <c r="AC6">
+      <c r="AC7">
         <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsyn/A 17520-2026 tillsynsbegäran.docx", "A 17520-2026")</f>
         <v/>
       </c>
-      <c r="AD6">
+      <c r="AD7">
         <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsynsmail/A 17520-2026 tillsynsbegäran mail.docx", "A 17520-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="7" ht="15" customHeight="1">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>A 3218-2022</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D7" s="1" t="n">
-        <v>44582</v>
-      </c>
-      <c r="E7" s="1" t="n">
-        <v>46294</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>EKERÖ</t>
-        </is>
-      </c>
-      <c r="I7" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="J7" t="n">
-        <v>1</v>
-      </c>
-      <c r="K7" t="n">
-        <v>1</v>
-      </c>
-      <c r="L7" t="n">
-        <v>1</v>
-      </c>
-      <c r="M7" t="n">
-        <v>1</v>
-      </c>
-      <c r="N7" t="n">
-        <v>1</v>
-      </c>
-      <c r="O7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>3</v>
-      </c>
-      <c r="R7" t="n">
-        <v>2</v>
-      </c>
-      <c r="S7" t="n">
-        <v>5</v>
-      </c>
-      <c r="T7" t="n">
-        <v>8</v>
-      </c>
-      <c r="U7" t="n">
-        <v>6</v>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>Bombmurkla
-Gul lammticka
-Fyrflikig jordstjärna
-Kamjordstjärna
-Blåbär</t>
-        </is>
-      </c>
-      <c r="W7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/artfynd/A 3218-2022 artfynd.xlsx", "A 3218-2022")</f>
-        <v/>
-      </c>
-      <c r="X7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor/A 3218-2022 karta.png", "A 3218-2022")</f>
-        <v/>
-      </c>
-      <c r="Y7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor_geotiff/A 3218-2022 georefererad karta.tif", "A 3218-2022")</f>
-        <v/>
-      </c>
-      <c r="AA7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomål/A 3218-2022 FSC-klagomål.docx", "A 3218-2022")</f>
-        <v/>
-      </c>
-      <c r="AB7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomålsmail/A 3218-2022 FSC-klagomål mail.docx", "A 3218-2022")</f>
-        <v/>
-      </c>
-      <c r="AC7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsyn/A 3218-2022 tillsynsbegäran.docx", "A 3218-2022")</f>
-        <v/>
-      </c>
-      <c r="AD7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsynsmail/A 3218-2022 tillsynsbegäran mail.docx", "A 3218-2022")</f>
         <v/>
       </c>
     </row>
@@ -1296,7 +1296,7 @@
         <v>46241</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1409,7 +1409,7 @@
         <v>44634</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1499,7 +1499,7 @@
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 13237-2023</t>
+          <t>A 49131-2025</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1513,10 +1513,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>45002</v>
+        <v>45937</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1528,25 +1528,20 @@
           <t>EKERÖ</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I10" t="n">
-        <v>9.300000000000001</v>
+        <v>0.9</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
       </c>
       <c r="K10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" t="n">
         <v>2</v>
       </c>
-      <c r="L10" t="n">
-        <v>1</v>
-      </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N10" t="n">
         <v>0</v>
@@ -1558,160 +1553,165 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S10" t="n">
         <v>3</v>
       </c>
       <c r="T10" t="n">
+        <v>3</v>
+      </c>
+      <c r="U10" t="n">
+        <v>3</v>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
+        <is>
+          <t>Jättemusseron
+Motaggsvamp
+Svartvit taggsvamp</t>
+        </is>
+      </c>
+      <c r="W10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/artfynd/A 49131-2025 artfynd.xlsx", "A 49131-2025")</f>
+        <v/>
+      </c>
+      <c r="X10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor/A 49131-2025 karta.png", "A 49131-2025")</f>
+        <v/>
+      </c>
+      <c r="Y10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor_geotiff/A 49131-2025 georefererad karta.tif", "A 49131-2025")</f>
+        <v/>
+      </c>
+      <c r="AA10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomål/A 49131-2025 FSC-klagomål.docx", "A 49131-2025")</f>
+        <v/>
+      </c>
+      <c r="AB10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomålsmail/A 49131-2025 FSC-klagomål mail.docx", "A 49131-2025")</f>
+        <v/>
+      </c>
+      <c r="AC10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsyn/A 49131-2025 tillsynsbegäran.docx", "A 49131-2025")</f>
+        <v/>
+      </c>
+      <c r="AD10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsynsmail/A 49131-2025 tillsynsbegäran mail.docx", "A 49131-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11" ht="15" customHeight="1">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>A 13237-2023</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D11" s="1" t="n">
+        <v>45002</v>
+      </c>
+      <c r="E11" s="1" t="n">
+        <v>46295</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>EKERÖ</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" t="n">
+        <v>2</v>
+      </c>
+      <c r="L11" t="n">
+        <v>1</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>1</v>
+      </c>
+      <c r="R11" t="n">
+        <v>0</v>
+      </c>
+      <c r="S11" t="n">
+        <v>3</v>
+      </c>
+      <c r="T11" t="n">
         <v>7</v>
       </c>
-      <c r="U10" t="n">
-        <v>0</v>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
+      <c r="U11" t="n">
+        <v>0</v>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
         <is>
           <t>Tallticka
 Granbarkgnagare
 Grönpyrola</t>
         </is>
       </c>
-      <c r="W10">
+      <c r="W11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0125/artfynd/A 13237-2023 artfynd.xlsx", "A 13237-2023")</f>
         <v/>
       </c>
-      <c r="X10">
+      <c r="X11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor/A 13237-2023 karta.png", "A 13237-2023")</f>
         <v/>
       </c>
-      <c r="Y10">
+      <c r="Y11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor_geotiff/A 13237-2023 georefererad karta.tif", "A 13237-2023")</f>
         <v/>
       </c>
-      <c r="AA10">
+      <c r="AA11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomål/A 13237-2023 FSC-klagomål.docx", "A 13237-2023")</f>
         <v/>
       </c>
-      <c r="AB10">
+      <c r="AB11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomålsmail/A 13237-2023 FSC-klagomål mail.docx", "A 13237-2023")</f>
         <v/>
       </c>
-      <c r="AC10">
+      <c r="AC11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsyn/A 13237-2023 tillsynsbegäran.docx", "A 13237-2023")</f>
         <v/>
       </c>
-      <c r="AD10">
+      <c r="AD11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsynsmail/A 13237-2023 tillsynsbegäran mail.docx", "A 13237-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="11" ht="15" customHeight="1">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>A 49131-2025</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D11" s="1" t="n">
-        <v>45937</v>
-      </c>
-      <c r="E11" s="1" t="n">
-        <v>46294</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>EKERÖ</t>
-        </is>
-      </c>
-      <c r="I11" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="J11" t="n">
-        <v>0</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L11" t="n">
-        <v>2</v>
-      </c>
-      <c r="M11" t="n">
-        <v>1</v>
-      </c>
-      <c r="N11" t="n">
-        <v>0</v>
-      </c>
-      <c r="O11" t="n">
-        <v>0</v>
-      </c>
-      <c r="P11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>3</v>
-      </c>
-      <c r="R11" t="n">
-        <v>1</v>
-      </c>
-      <c r="S11" t="n">
-        <v>3</v>
-      </c>
-      <c r="T11" t="n">
-        <v>3</v>
-      </c>
-      <c r="U11" t="n">
-        <v>3</v>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
-        <is>
-          <t>Jättemusseron
-Motaggsvamp
-Svartvit taggsvamp</t>
-        </is>
-      </c>
-      <c r="W11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/artfynd/A 49131-2025 artfynd.xlsx", "A 49131-2025")</f>
-        <v/>
-      </c>
-      <c r="X11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor/A 49131-2025 karta.png", "A 49131-2025")</f>
-        <v/>
-      </c>
-      <c r="Y11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor_geotiff/A 49131-2025 georefererad karta.tif", "A 49131-2025")</f>
-        <v/>
-      </c>
-      <c r="AA11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomål/A 49131-2025 FSC-klagomål.docx", "A 49131-2025")</f>
-        <v/>
-      </c>
-      <c r="AB11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomålsmail/A 49131-2025 FSC-klagomål mail.docx", "A 49131-2025")</f>
-        <v/>
-      </c>
-      <c r="AC11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsyn/A 49131-2025 tillsynsbegäran.docx", "A 49131-2025")</f>
-        <v/>
-      </c>
-      <c r="AD11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsynsmail/A 49131-2025 tillsynsbegäran mail.docx", "A 49131-2025")</f>
         <v/>
       </c>
     </row>
@@ -1735,7 +1735,7 @@
         <v>45209</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1850,7 +1850,7 @@
         <v>45170</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1956,7 +1956,7 @@
         <v>44646</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2044,7 +2044,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 3221-2022</t>
+          <t>A 2533-2026</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2058,10 +2058,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>44582</v>
+        <v>46037</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2074,13 +2074,13 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>0.5</v>
+        <v>1.4</v>
       </c>
       <c r="J15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L15" t="n">
         <v>0</v>
@@ -2110,46 +2110,46 @@
         <v>1</v>
       </c>
       <c r="U15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/artfynd/A 3221-2022 artfynd.xlsx", "A 3221-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/artfynd/A 2533-2026 artfynd.xlsx", "A 2533-2026")</f>
         <v/>
       </c>
       <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor/A 3221-2022 karta.png", "A 3221-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor/A 2533-2026 karta.png", "A 2533-2026")</f>
         <v/>
       </c>
       <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor_geotiff/A 3221-2022 georefererad karta.tif", "A 3221-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor_geotiff/A 2533-2026 georefererad karta.tif", "A 2533-2026")</f>
         <v/>
       </c>
       <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomål/A 3221-2022 FSC-klagomål.docx", "A 3221-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomål/A 2533-2026 FSC-klagomål.docx", "A 2533-2026")</f>
         <v/>
       </c>
       <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomålsmail/A 3221-2022 FSC-klagomål mail.docx", "A 3221-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomålsmail/A 2533-2026 FSC-klagomål mail.docx", "A 2533-2026")</f>
         <v/>
       </c>
       <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsyn/A 3221-2022 tillsynsbegäran.docx", "A 3221-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsyn/A 2533-2026 tillsynsbegäran.docx", "A 2533-2026")</f>
         <v/>
       </c>
       <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsynsmail/A 3221-2022 tillsynsbegäran mail.docx", "A 3221-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsynsmail/A 2533-2026 tillsynsbegäran mail.docx", "A 2533-2026")</f>
         <v/>
       </c>
     </row>
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 1793-2025</t>
+          <t>A 3221-2022</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2163,10 +2163,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45671</v>
+        <v>44582</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2179,13 +2179,13 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>1.7</v>
+        <v>0.5</v>
       </c>
       <c r="J16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L16" t="n">
         <v>0</v>
@@ -2212,42 +2212,42 @@
         <v>1</v>
       </c>
       <c r="T16" t="n">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>Mistel</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/artfynd/A 1793-2025 artfynd.xlsx", "A 1793-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/artfynd/A 3221-2022 artfynd.xlsx", "A 3221-2022")</f>
         <v/>
       </c>
       <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor/A 1793-2025 karta.png", "A 1793-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor/A 3221-2022 karta.png", "A 3221-2022")</f>
         <v/>
       </c>
       <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor_geotiff/A 1793-2025 georefererad karta.tif", "A 1793-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor_geotiff/A 3221-2022 georefererad karta.tif", "A 3221-2022")</f>
         <v/>
       </c>
       <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomål/A 1793-2025 FSC-klagomål.docx", "A 1793-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomål/A 3221-2022 FSC-klagomål.docx", "A 3221-2022")</f>
         <v/>
       </c>
       <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomålsmail/A 1793-2025 FSC-klagomål mail.docx", "A 1793-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomålsmail/A 3221-2022 FSC-klagomål mail.docx", "A 3221-2022")</f>
         <v/>
       </c>
       <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsyn/A 1793-2025 tillsynsbegäran.docx", "A 1793-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsyn/A 3221-2022 tillsynsbegäran.docx", "A 3221-2022")</f>
         <v/>
       </c>
       <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsynsmail/A 1793-2025 tillsynsbegäran mail.docx", "A 1793-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsynsmail/A 3221-2022 tillsynsbegäran mail.docx", "A 3221-2022")</f>
         <v/>
       </c>
     </row>
@@ -2271,7 +2271,7 @@
         <v>45007</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2359,7 +2359,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 2533-2026</t>
+          <t>A 1793-2025</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2373,10 +2373,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>46037</v>
+        <v>45671</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2389,7 +2389,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>1.4</v>
+        <v>1.7</v>
       </c>
       <c r="J18" t="n">
         <v>1</v>
@@ -2422,42 +2422,42 @@
         <v>1</v>
       </c>
       <c r="T18" t="n">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="U18" t="n">
         <v>0</v>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Mistel</t>
         </is>
       </c>
       <c r="W18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/artfynd/A 2533-2026 artfynd.xlsx", "A 2533-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/artfynd/A 1793-2025 artfynd.xlsx", "A 1793-2025")</f>
         <v/>
       </c>
       <c r="X18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor/A 2533-2026 karta.png", "A 2533-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor/A 1793-2025 karta.png", "A 1793-2025")</f>
         <v/>
       </c>
       <c r="Y18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor_geotiff/A 2533-2026 georefererad karta.tif", "A 2533-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor_geotiff/A 1793-2025 georefererad karta.tif", "A 1793-2025")</f>
         <v/>
       </c>
       <c r="AA18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomål/A 2533-2026 FSC-klagomål.docx", "A 2533-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomål/A 1793-2025 FSC-klagomål.docx", "A 1793-2025")</f>
         <v/>
       </c>
       <c r="AB18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomålsmail/A 2533-2026 FSC-klagomål mail.docx", "A 2533-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomålsmail/A 1793-2025 FSC-klagomål mail.docx", "A 1793-2025")</f>
         <v/>
       </c>
       <c r="AC18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsyn/A 2533-2026 tillsynsbegäran.docx", "A 2533-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsyn/A 1793-2025 tillsynsbegäran.docx", "A 1793-2025")</f>
         <v/>
       </c>
       <c r="AD18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsynsmail/A 2533-2026 tillsynsbegäran mail.docx", "A 2533-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsynsmail/A 1793-2025 tillsynsbegäran mail.docx", "A 1793-2025")</f>
         <v/>
       </c>
     </row>
@@ -2481,7 +2481,7 @@
         <v>44670</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2554,7 +2554,7 @@
         <v>44802</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2610,7 +2610,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 3219-2022</t>
+          <t>A 63378-2025</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2624,10 +2624,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>44582</v>
+        <v>46010</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2640,7 +2640,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>0.5</v>
+        <v>4.8</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2683,7 +2683,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 63378-2025</t>
+          <t>A 50184-2023</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2697,10 +2697,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>46010</v>
+        <v>45208</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2713,7 +2713,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>4.8</v>
+        <v>10.8</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2756,7 +2756,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 50184-2023</t>
+          <t>A 2535-2026</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2770,10 +2770,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45208</v>
+        <v>46037</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2786,7 +2786,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>10.8</v>
+        <v>1.6</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2829,7 +2829,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 37245-2025</t>
+          <t>A 56002-2024</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2843,10 +2843,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45876</v>
+        <v>45623</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2859,7 +2859,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>1.1</v>
+        <v>3.4</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2902,7 +2902,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 2535-2026</t>
+          <t>A 37245-2025</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2916,10 +2916,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>46037</v>
+        <v>45876</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2932,7 +2932,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>1.6</v>
+        <v>1.1</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2975,7 +2975,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 55724-2024</t>
+          <t>A 61217-2024</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2989,10 +2989,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45622</v>
+        <v>45645</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3005,7 +3005,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -3048,7 +3048,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 20399-2026</t>
+          <t>A 3222-2022</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3062,10 +3062,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>46139</v>
+        <v>44582</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3078,7 +3078,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>0.9</v>
+        <v>1.8</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -3121,7 +3121,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 35955-2023</t>
+          <t>A 20399-2026</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3135,10 +3135,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45148</v>
+        <v>46139</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3151,7 +3151,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>1.1</v>
+        <v>0.9</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -3211,7 +3211,7 @@
         <v>46139</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3267,7 +3267,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 61217-2024</t>
+          <t>A 3219-2022</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3281,10 +3281,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45645</v>
+        <v>44582</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3297,7 +3297,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3340,7 +3340,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 56002-2024</t>
+          <t>A 60755-2024</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3354,10 +3354,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45623</v>
+        <v>45644</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3370,7 +3370,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>3.4</v>
+        <v>2.1</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3413,7 +3413,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 60728-2022</t>
+          <t>A 20898-2026</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3427,10 +3427,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>44913</v>
+        <v>46142</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3443,7 +3443,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>1.2</v>
+        <v>3.6</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3486,7 +3486,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 20898-2026</t>
+          <t>A 55724-2024</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3500,10 +3500,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>46142</v>
+        <v>45622</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3516,7 +3516,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>3.6</v>
+        <v>0.5</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3559,7 +3559,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 3222-2022</t>
+          <t>A 35955-2023</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3573,10 +3573,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>44582</v>
+        <v>45148</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3589,7 +3589,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>1.8</v>
+        <v>1.1</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3649,7 +3649,7 @@
         <v>45845</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3705,7 +3705,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 60755-2024</t>
+          <t>A 60728-2022</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3719,10 +3719,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45644</v>
+        <v>44913</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3735,7 +3735,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>2.1</v>
+        <v>1.2</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3795,7 +3795,7 @@
         <v>46244</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3873,7 +3873,7 @@
         <v>46153</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>

--- a/Översikt EKERÖ.xlsx
+++ b/Översikt EKERÖ.xlsx
@@ -601,7 +601,7 @@
         <v>46241</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -728,7 +728,7 @@
         <v>44872</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -848,7 +848,7 @@
         <v>44974</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -963,7 +963,7 @@
         <v>45148</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1073,7 +1073,7 @@
         <v>44582</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1182,7 +1182,7 @@
         <v>46119</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1296,7 +1296,7 @@
         <v>46241</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1409,7 +1409,7 @@
         <v>44634</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1499,7 +1499,7 @@
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 49131-2025</t>
+          <t>A 13237-2023</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1513,10 +1513,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>45937</v>
+        <v>45002</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1528,20 +1528,25 @@
           <t>EKERÖ</t>
         </is>
       </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I10" t="n">
-        <v>0.9</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N10" t="n">
         <v>0</v>
@@ -1553,165 +1558,160 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="R10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
         <v>3</v>
       </c>
       <c r="T10" t="n">
+        <v>7</v>
+      </c>
+      <c r="U10" t="n">
+        <v>0</v>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
+        <is>
+          <t>Tallticka
+Granbarkgnagare
+Grönpyrola</t>
+        </is>
+      </c>
+      <c r="W10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/artfynd/A 13237-2023 artfynd.xlsx", "A 13237-2023")</f>
+        <v/>
+      </c>
+      <c r="X10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor/A 13237-2023 karta.png", "A 13237-2023")</f>
+        <v/>
+      </c>
+      <c r="Y10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor_geotiff/A 13237-2023 georefererad karta.tif", "A 13237-2023")</f>
+        <v/>
+      </c>
+      <c r="AA10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomål/A 13237-2023 FSC-klagomål.docx", "A 13237-2023")</f>
+        <v/>
+      </c>
+      <c r="AB10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomålsmail/A 13237-2023 FSC-klagomål mail.docx", "A 13237-2023")</f>
+        <v/>
+      </c>
+      <c r="AC10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsyn/A 13237-2023 tillsynsbegäran.docx", "A 13237-2023")</f>
+        <v/>
+      </c>
+      <c r="AD10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsynsmail/A 13237-2023 tillsynsbegäran mail.docx", "A 13237-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11" ht="15" customHeight="1">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>A 49131-2025</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D11" s="1" t="n">
+        <v>45937</v>
+      </c>
+      <c r="E11" s="1" t="n">
+        <v>46296</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>EKERÖ</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" t="n">
+        <v>2</v>
+      </c>
+      <c r="M11" t="n">
+        <v>1</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" t="n">
         <v>3</v>
       </c>
-      <c r="U10" t="n">
+      <c r="R11" t="n">
+        <v>1</v>
+      </c>
+      <c r="S11" t="n">
         <v>3</v>
       </c>
-      <c r="V10" s="2" t="inlineStr">
+      <c r="T11" t="n">
+        <v>3</v>
+      </c>
+      <c r="U11" t="n">
+        <v>3</v>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
         <is>
           <t>Jättemusseron
 Motaggsvamp
 Svartvit taggsvamp</t>
         </is>
       </c>
-      <c r="W10">
+      <c r="W11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0125/artfynd/A 49131-2025 artfynd.xlsx", "A 49131-2025")</f>
         <v/>
       </c>
-      <c r="X10">
+      <c r="X11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor/A 49131-2025 karta.png", "A 49131-2025")</f>
         <v/>
       </c>
-      <c r="Y10">
+      <c r="Y11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor_geotiff/A 49131-2025 georefererad karta.tif", "A 49131-2025")</f>
         <v/>
       </c>
-      <c r="AA10">
+      <c r="AA11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomål/A 49131-2025 FSC-klagomål.docx", "A 49131-2025")</f>
         <v/>
       </c>
-      <c r="AB10">
+      <c r="AB11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomålsmail/A 49131-2025 FSC-klagomål mail.docx", "A 49131-2025")</f>
         <v/>
       </c>
-      <c r="AC10">
+      <c r="AC11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsyn/A 49131-2025 tillsynsbegäran.docx", "A 49131-2025")</f>
         <v/>
       </c>
-      <c r="AD10">
+      <c r="AD11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsynsmail/A 49131-2025 tillsynsbegäran mail.docx", "A 49131-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="11" ht="15" customHeight="1">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>A 13237-2023</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D11" s="1" t="n">
-        <v>45002</v>
-      </c>
-      <c r="E11" s="1" t="n">
-        <v>46295</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>EKERÖ</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
-      <c r="I11" t="n">
-        <v>9.300000000000001</v>
-      </c>
-      <c r="J11" t="n">
-        <v>0</v>
-      </c>
-      <c r="K11" t="n">
-        <v>2</v>
-      </c>
-      <c r="L11" t="n">
-        <v>1</v>
-      </c>
-      <c r="M11" t="n">
-        <v>0</v>
-      </c>
-      <c r="N11" t="n">
-        <v>0</v>
-      </c>
-      <c r="O11" t="n">
-        <v>0</v>
-      </c>
-      <c r="P11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>1</v>
-      </c>
-      <c r="R11" t="n">
-        <v>0</v>
-      </c>
-      <c r="S11" t="n">
-        <v>3</v>
-      </c>
-      <c r="T11" t="n">
-        <v>7</v>
-      </c>
-      <c r="U11" t="n">
-        <v>0</v>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
-        <is>
-          <t>Tallticka
-Granbarkgnagare
-Grönpyrola</t>
-        </is>
-      </c>
-      <c r="W11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/artfynd/A 13237-2023 artfynd.xlsx", "A 13237-2023")</f>
-        <v/>
-      </c>
-      <c r="X11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor/A 13237-2023 karta.png", "A 13237-2023")</f>
-        <v/>
-      </c>
-      <c r="Y11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor_geotiff/A 13237-2023 georefererad karta.tif", "A 13237-2023")</f>
-        <v/>
-      </c>
-      <c r="AA11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomål/A 13237-2023 FSC-klagomål.docx", "A 13237-2023")</f>
-        <v/>
-      </c>
-      <c r="AB11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomålsmail/A 13237-2023 FSC-klagomål mail.docx", "A 13237-2023")</f>
-        <v/>
-      </c>
-      <c r="AC11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsyn/A 13237-2023 tillsynsbegäran.docx", "A 13237-2023")</f>
-        <v/>
-      </c>
-      <c r="AD11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsynsmail/A 13237-2023 tillsynsbegäran mail.docx", "A 13237-2023")</f>
         <v/>
       </c>
     </row>
@@ -1735,7 +1735,7 @@
         <v>45209</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1850,7 +1850,7 @@
         <v>45170</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1956,7 +1956,7 @@
         <v>44646</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2044,7 +2044,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 2533-2026</t>
+          <t>A 3221-2022</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2058,10 +2058,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>46037</v>
+        <v>44582</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2074,13 +2074,13 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>1.4</v>
+        <v>0.5</v>
       </c>
       <c r="J15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L15" t="n">
         <v>0</v>
@@ -2110,46 +2110,46 @@
         <v>1</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/artfynd/A 2533-2026 artfynd.xlsx", "A 2533-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/artfynd/A 3221-2022 artfynd.xlsx", "A 3221-2022")</f>
         <v/>
       </c>
       <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor/A 2533-2026 karta.png", "A 2533-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor/A 3221-2022 karta.png", "A 3221-2022")</f>
         <v/>
       </c>
       <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor_geotiff/A 2533-2026 georefererad karta.tif", "A 2533-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor_geotiff/A 3221-2022 georefererad karta.tif", "A 3221-2022")</f>
         <v/>
       </c>
       <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomål/A 2533-2026 FSC-klagomål.docx", "A 2533-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomål/A 3221-2022 FSC-klagomål.docx", "A 3221-2022")</f>
         <v/>
       </c>
       <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomålsmail/A 2533-2026 FSC-klagomål mail.docx", "A 2533-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomålsmail/A 3221-2022 FSC-klagomål mail.docx", "A 3221-2022")</f>
         <v/>
       </c>
       <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsyn/A 2533-2026 tillsynsbegäran.docx", "A 2533-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsyn/A 3221-2022 tillsynsbegäran.docx", "A 3221-2022")</f>
         <v/>
       </c>
       <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsynsmail/A 2533-2026 tillsynsbegäran mail.docx", "A 2533-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsynsmail/A 3221-2022 tillsynsbegäran mail.docx", "A 3221-2022")</f>
         <v/>
       </c>
     </row>
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 3221-2022</t>
+          <t>A 1793-2025</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2163,10 +2163,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>44582</v>
+        <v>45671</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2179,13 +2179,13 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>0.5</v>
+        <v>1.7</v>
       </c>
       <c r="J16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L16" t="n">
         <v>0</v>
@@ -2212,42 +2212,42 @@
         <v>1</v>
       </c>
       <c r="T16" t="n">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="U16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Mistel</t>
         </is>
       </c>
       <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/artfynd/A 3221-2022 artfynd.xlsx", "A 3221-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/artfynd/A 1793-2025 artfynd.xlsx", "A 1793-2025")</f>
         <v/>
       </c>
       <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor/A 3221-2022 karta.png", "A 3221-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor/A 1793-2025 karta.png", "A 1793-2025")</f>
         <v/>
       </c>
       <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor_geotiff/A 3221-2022 georefererad karta.tif", "A 3221-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor_geotiff/A 1793-2025 georefererad karta.tif", "A 1793-2025")</f>
         <v/>
       </c>
       <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomål/A 3221-2022 FSC-klagomål.docx", "A 3221-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomål/A 1793-2025 FSC-klagomål.docx", "A 1793-2025")</f>
         <v/>
       </c>
       <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomålsmail/A 3221-2022 FSC-klagomål mail.docx", "A 3221-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomålsmail/A 1793-2025 FSC-klagomål mail.docx", "A 1793-2025")</f>
         <v/>
       </c>
       <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsyn/A 3221-2022 tillsynsbegäran.docx", "A 3221-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsyn/A 1793-2025 tillsynsbegäran.docx", "A 1793-2025")</f>
         <v/>
       </c>
       <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsynsmail/A 3221-2022 tillsynsbegäran mail.docx", "A 3221-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsynsmail/A 1793-2025 tillsynsbegäran mail.docx", "A 1793-2025")</f>
         <v/>
       </c>
     </row>
@@ -2271,7 +2271,7 @@
         <v>45007</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2359,7 +2359,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 1793-2025</t>
+          <t>A 2533-2026</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2373,10 +2373,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45671</v>
+        <v>46037</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2389,7 +2389,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>1.7</v>
+        <v>1.4</v>
       </c>
       <c r="J18" t="n">
         <v>1</v>
@@ -2422,42 +2422,42 @@
         <v>1</v>
       </c>
       <c r="T18" t="n">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="U18" t="n">
         <v>0</v>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>Mistel</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="W18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/artfynd/A 1793-2025 artfynd.xlsx", "A 1793-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/artfynd/A 2533-2026 artfynd.xlsx", "A 2533-2026")</f>
         <v/>
       </c>
       <c r="X18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor/A 1793-2025 karta.png", "A 1793-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor/A 2533-2026 karta.png", "A 2533-2026")</f>
         <v/>
       </c>
       <c r="Y18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor_geotiff/A 1793-2025 georefererad karta.tif", "A 1793-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor_geotiff/A 2533-2026 georefererad karta.tif", "A 2533-2026")</f>
         <v/>
       </c>
       <c r="AA18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomål/A 1793-2025 FSC-klagomål.docx", "A 1793-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomål/A 2533-2026 FSC-klagomål.docx", "A 2533-2026")</f>
         <v/>
       </c>
       <c r="AB18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomålsmail/A 1793-2025 FSC-klagomål mail.docx", "A 1793-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomålsmail/A 2533-2026 FSC-klagomål mail.docx", "A 2533-2026")</f>
         <v/>
       </c>
       <c r="AC18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsyn/A 1793-2025 tillsynsbegäran.docx", "A 1793-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsyn/A 2533-2026 tillsynsbegäran.docx", "A 2533-2026")</f>
         <v/>
       </c>
       <c r="AD18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsynsmail/A 1793-2025 tillsynsbegäran mail.docx", "A 1793-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsynsmail/A 2533-2026 tillsynsbegäran mail.docx", "A 2533-2026")</f>
         <v/>
       </c>
     </row>
@@ -2481,7 +2481,7 @@
         <v>44670</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2554,7 +2554,7 @@
         <v>44802</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2610,7 +2610,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 63378-2025</t>
+          <t>A 3219-2022</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2624,10 +2624,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>46010</v>
+        <v>44582</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2640,7 +2640,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>4.8</v>
+        <v>0.5</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2683,7 +2683,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 50184-2023</t>
+          <t>A 3222-2022</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2697,10 +2697,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>45208</v>
+        <v>44582</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2713,7 +2713,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>10.8</v>
+        <v>1.8</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2756,7 +2756,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 2535-2026</t>
+          <t>A 60755-2024</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2770,10 +2770,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>46037</v>
+        <v>45644</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2786,7 +2786,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>1.6</v>
+        <v>2.1</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2829,7 +2829,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 56002-2024</t>
+          <t>A 55724-2024</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2843,10 +2843,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45623</v>
+        <v>45622</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2859,7 +2859,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>3.4</v>
+        <v>0.5</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2902,7 +2902,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 37245-2025</t>
+          <t>A 35955-2023</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2916,10 +2916,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45876</v>
+        <v>45148</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2992,7 +2992,7 @@
         <v>45645</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3048,7 +3048,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 3222-2022</t>
+          <t>A 56002-2024</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3062,10 +3062,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>44582</v>
+        <v>45623</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3078,7 +3078,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>1.8</v>
+        <v>3.4</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -3121,7 +3121,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 20399-2026</t>
+          <t>A 60728-2022</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3135,10 +3135,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>46139</v>
+        <v>44913</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3151,7 +3151,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>0.9</v>
+        <v>1.2</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -3194,7 +3194,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 20398-2026</t>
+          <t>A 50184-2023</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3208,10 +3208,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>46139</v>
+        <v>45208</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3224,7 +3224,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>2.4</v>
+        <v>10.8</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3267,7 +3267,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 3219-2022</t>
+          <t>A 37245-2025</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3281,10 +3281,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>44582</v>
+        <v>45876</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3297,7 +3297,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>0.5</v>
+        <v>1.1</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3340,7 +3340,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 60755-2024</t>
+          <t>A 63378-2025</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3354,10 +3354,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45644</v>
+        <v>46010</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3370,7 +3370,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>2.1</v>
+        <v>4.8</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3413,7 +3413,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 20898-2026</t>
+          <t>A 2535-2026</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3427,10 +3427,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>46142</v>
+        <v>46037</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3443,7 +3443,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>3.6</v>
+        <v>1.6</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3486,7 +3486,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 55724-2024</t>
+          <t>A 20399-2026</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3500,10 +3500,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45622</v>
+        <v>46139</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3516,7 +3516,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>0.5</v>
+        <v>0.9</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3559,7 +3559,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 35955-2023</t>
+          <t>A 20398-2026</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3573,10 +3573,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45148</v>
+        <v>46139</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3589,7 +3589,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>1.1</v>
+        <v>2.4</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3632,7 +3632,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 34073-2025</t>
+          <t>A 20898-2026</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3642,14 +3642,14 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45845</v>
+        <v>46142</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3662,7 +3662,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>2.9</v>
+        <v>3.6</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3705,7 +3705,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 60728-2022</t>
+          <t>A 34073-2025</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3715,14 +3715,14 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>44913</v>
+        <v>45845</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3735,7 +3735,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>1.2</v>
+        <v>2.9</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3795,7 +3795,7 @@
         <v>46244</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3873,7 +3873,7 @@
         <v>46153</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>

--- a/Översikt EKERÖ.xlsx
+++ b/Översikt EKERÖ.xlsx
@@ -601,7 +601,7 @@
         <v>46241</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -728,7 +728,7 @@
         <v>44872</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -848,7 +848,7 @@
         <v>44974</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -963,7 +963,7 @@
         <v>45148</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1056,7 +1056,7 @@
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A 3218-2022</t>
+          <t>A 17520-2026</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1070,10 +1070,10 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>44582</v>
+        <v>46119</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1085,8 +1085,13 @@
           <t>EKERÖ</t>
         </is>
       </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I6" t="n">
-        <v>1.2</v>
+        <v>2.2</v>
       </c>
       <c r="J6" t="n">
         <v>1</v>
@@ -1095,13 +1100,13 @@
         <v>1</v>
       </c>
       <c r="L6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M6" t="n">
         <v>1</v>
       </c>
       <c r="N6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1110,21 +1115,130 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="R6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
       </c>
       <c r="T6" t="n">
+        <v>5</v>
+      </c>
+      <c r="U6" t="n">
+        <v>1</v>
+      </c>
+      <c r="V6" s="2" t="inlineStr">
+        <is>
+          <t>Läderbagge
+Blekticka
+Ekticka
+Kandelabersvamp
+Gulgrön kantmusseron</t>
+        </is>
+      </c>
+      <c r="W6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/artfynd/A 17520-2026 artfynd.xlsx", "A 17520-2026")</f>
+        <v/>
+      </c>
+      <c r="X6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor/A 17520-2026 karta.png", "A 17520-2026")</f>
+        <v/>
+      </c>
+      <c r="Y6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor_geotiff/A 17520-2026 georefererad karta.tif", "A 17520-2026")</f>
+        <v/>
+      </c>
+      <c r="AA6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomål/A 17520-2026 FSC-klagomål.docx", "A 17520-2026")</f>
+        <v/>
+      </c>
+      <c r="AB6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomålsmail/A 17520-2026 FSC-klagomål mail.docx", "A 17520-2026")</f>
+        <v/>
+      </c>
+      <c r="AC6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsyn/A 17520-2026 tillsynsbegäran.docx", "A 17520-2026")</f>
+        <v/>
+      </c>
+      <c r="AD6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsynsmail/A 17520-2026 tillsynsbegäran mail.docx", "A 17520-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7" ht="15" customHeight="1">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>A 3218-2022</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D7" s="1" t="n">
+        <v>44582</v>
+      </c>
+      <c r="E7" s="1" t="n">
+        <v>46297</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>EKERÖ</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="J7" t="n">
+        <v>1</v>
+      </c>
+      <c r="K7" t="n">
+        <v>1</v>
+      </c>
+      <c r="L7" t="n">
+        <v>1</v>
+      </c>
+      <c r="M7" t="n">
+        <v>1</v>
+      </c>
+      <c r="N7" t="n">
+        <v>1</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>3</v>
+      </c>
+      <c r="R7" t="n">
+        <v>2</v>
+      </c>
+      <c r="S7" t="n">
+        <v>5</v>
+      </c>
+      <c r="T7" t="n">
         <v>8</v>
       </c>
-      <c r="U6" t="n">
+      <c r="U7" t="n">
         <v>6</v>
       </c>
-      <c r="V6" s="2" t="inlineStr">
+      <c r="V7" s="2" t="inlineStr">
         <is>
           <t>Bombmurkla
 Gul lammticka
@@ -1133,146 +1247,32 @@
 Blåbär</t>
         </is>
       </c>
-      <c r="W6">
+      <c r="W7">
         <f>HYPERLINK("https://klasma.github.io/Logging_0125/artfynd/A 3218-2022 artfynd.xlsx", "A 3218-2022")</f>
         <v/>
       </c>
-      <c r="X6">
+      <c r="X7">
         <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor/A 3218-2022 karta.png", "A 3218-2022")</f>
         <v/>
       </c>
-      <c r="Y6">
+      <c r="Y7">
         <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor_geotiff/A 3218-2022 georefererad karta.tif", "A 3218-2022")</f>
         <v/>
       </c>
-      <c r="AA6">
+      <c r="AA7">
         <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomål/A 3218-2022 FSC-klagomål.docx", "A 3218-2022")</f>
         <v/>
       </c>
-      <c r="AB6">
+      <c r="AB7">
         <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomålsmail/A 3218-2022 FSC-klagomål mail.docx", "A 3218-2022")</f>
         <v/>
       </c>
-      <c r="AC6">
+      <c r="AC7">
         <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsyn/A 3218-2022 tillsynsbegäran.docx", "A 3218-2022")</f>
         <v/>
       </c>
-      <c r="AD6">
+      <c r="AD7">
         <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsynsmail/A 3218-2022 tillsynsbegäran mail.docx", "A 3218-2022")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="7" ht="15" customHeight="1">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>A 17520-2026</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D7" s="1" t="n">
-        <v>46119</v>
-      </c>
-      <c r="E7" s="1" t="n">
-        <v>46296</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>EKERÖ</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
-      <c r="I7" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="J7" t="n">
-        <v>1</v>
-      </c>
-      <c r="K7" t="n">
-        <v>1</v>
-      </c>
-      <c r="L7" t="n">
-        <v>3</v>
-      </c>
-      <c r="M7" t="n">
-        <v>1</v>
-      </c>
-      <c r="N7" t="n">
-        <v>0</v>
-      </c>
-      <c r="O7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>4</v>
-      </c>
-      <c r="R7" t="n">
-        <v>1</v>
-      </c>
-      <c r="S7" t="n">
-        <v>5</v>
-      </c>
-      <c r="T7" t="n">
-        <v>5</v>
-      </c>
-      <c r="U7" t="n">
-        <v>1</v>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>Läderbagge
-Blekticka
-Ekticka
-Kandelabersvamp
-Gulgrön kantmusseron</t>
-        </is>
-      </c>
-      <c r="W7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/artfynd/A 17520-2026 artfynd.xlsx", "A 17520-2026")</f>
-        <v/>
-      </c>
-      <c r="X7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor/A 17520-2026 karta.png", "A 17520-2026")</f>
-        <v/>
-      </c>
-      <c r="Y7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor_geotiff/A 17520-2026 georefererad karta.tif", "A 17520-2026")</f>
-        <v/>
-      </c>
-      <c r="AA7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomål/A 17520-2026 FSC-klagomål.docx", "A 17520-2026")</f>
-        <v/>
-      </c>
-      <c r="AB7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomålsmail/A 17520-2026 FSC-klagomål mail.docx", "A 17520-2026")</f>
-        <v/>
-      </c>
-      <c r="AC7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsyn/A 17520-2026 tillsynsbegäran.docx", "A 17520-2026")</f>
-        <v/>
-      </c>
-      <c r="AD7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsynsmail/A 17520-2026 tillsynsbegäran mail.docx", "A 17520-2026")</f>
         <v/>
       </c>
     </row>
@@ -1296,7 +1296,7 @@
         <v>46241</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1409,7 +1409,7 @@
         <v>44634</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1499,7 +1499,7 @@
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 13237-2023</t>
+          <t>A 49131-2025</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1513,10 +1513,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>45002</v>
+        <v>45937</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1528,25 +1528,20 @@
           <t>EKERÖ</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I10" t="n">
-        <v>9.300000000000001</v>
+        <v>0.9</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
       </c>
       <c r="K10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" t="n">
         <v>2</v>
       </c>
-      <c r="L10" t="n">
-        <v>1</v>
-      </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N10" t="n">
         <v>0</v>
@@ -1558,160 +1553,165 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S10" t="n">
         <v>3</v>
       </c>
       <c r="T10" t="n">
+        <v>3</v>
+      </c>
+      <c r="U10" t="n">
+        <v>3</v>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
+        <is>
+          <t>Jättemusseron
+Motaggsvamp
+Svartvit taggsvamp</t>
+        </is>
+      </c>
+      <c r="W10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/artfynd/A 49131-2025 artfynd.xlsx", "A 49131-2025")</f>
+        <v/>
+      </c>
+      <c r="X10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor/A 49131-2025 karta.png", "A 49131-2025")</f>
+        <v/>
+      </c>
+      <c r="Y10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor_geotiff/A 49131-2025 georefererad karta.tif", "A 49131-2025")</f>
+        <v/>
+      </c>
+      <c r="AA10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomål/A 49131-2025 FSC-klagomål.docx", "A 49131-2025")</f>
+        <v/>
+      </c>
+      <c r="AB10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomålsmail/A 49131-2025 FSC-klagomål mail.docx", "A 49131-2025")</f>
+        <v/>
+      </c>
+      <c r="AC10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsyn/A 49131-2025 tillsynsbegäran.docx", "A 49131-2025")</f>
+        <v/>
+      </c>
+      <c r="AD10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsynsmail/A 49131-2025 tillsynsbegäran mail.docx", "A 49131-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11" ht="15" customHeight="1">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>A 13237-2023</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D11" s="1" t="n">
+        <v>45002</v>
+      </c>
+      <c r="E11" s="1" t="n">
+        <v>46297</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>EKERÖ</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" t="n">
+        <v>2</v>
+      </c>
+      <c r="L11" t="n">
+        <v>1</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>1</v>
+      </c>
+      <c r="R11" t="n">
+        <v>0</v>
+      </c>
+      <c r="S11" t="n">
+        <v>3</v>
+      </c>
+      <c r="T11" t="n">
         <v>7</v>
       </c>
-      <c r="U10" t="n">
-        <v>0</v>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
+      <c r="U11" t="n">
+        <v>0</v>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
         <is>
           <t>Tallticka
 Granbarkgnagare
 Grönpyrola</t>
         </is>
       </c>
-      <c r="W10">
+      <c r="W11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0125/artfynd/A 13237-2023 artfynd.xlsx", "A 13237-2023")</f>
         <v/>
       </c>
-      <c r="X10">
+      <c r="X11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor/A 13237-2023 karta.png", "A 13237-2023")</f>
         <v/>
       </c>
-      <c r="Y10">
+      <c r="Y11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor_geotiff/A 13237-2023 georefererad karta.tif", "A 13237-2023")</f>
         <v/>
       </c>
-      <c r="AA10">
+      <c r="AA11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomål/A 13237-2023 FSC-klagomål.docx", "A 13237-2023")</f>
         <v/>
       </c>
-      <c r="AB10">
+      <c r="AB11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomålsmail/A 13237-2023 FSC-klagomål mail.docx", "A 13237-2023")</f>
         <v/>
       </c>
-      <c r="AC10">
+      <c r="AC11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsyn/A 13237-2023 tillsynsbegäran.docx", "A 13237-2023")</f>
         <v/>
       </c>
-      <c r="AD10">
+      <c r="AD11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsynsmail/A 13237-2023 tillsynsbegäran mail.docx", "A 13237-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="11" ht="15" customHeight="1">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>A 49131-2025</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D11" s="1" t="n">
-        <v>45937</v>
-      </c>
-      <c r="E11" s="1" t="n">
-        <v>46296</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>EKERÖ</t>
-        </is>
-      </c>
-      <c r="I11" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="J11" t="n">
-        <v>0</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L11" t="n">
-        <v>2</v>
-      </c>
-      <c r="M11" t="n">
-        <v>1</v>
-      </c>
-      <c r="N11" t="n">
-        <v>0</v>
-      </c>
-      <c r="O11" t="n">
-        <v>0</v>
-      </c>
-      <c r="P11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>3</v>
-      </c>
-      <c r="R11" t="n">
-        <v>1</v>
-      </c>
-      <c r="S11" t="n">
-        <v>3</v>
-      </c>
-      <c r="T11" t="n">
-        <v>3</v>
-      </c>
-      <c r="U11" t="n">
-        <v>3</v>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
-        <is>
-          <t>Jättemusseron
-Motaggsvamp
-Svartvit taggsvamp</t>
-        </is>
-      </c>
-      <c r="W11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/artfynd/A 49131-2025 artfynd.xlsx", "A 49131-2025")</f>
-        <v/>
-      </c>
-      <c r="X11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor/A 49131-2025 karta.png", "A 49131-2025")</f>
-        <v/>
-      </c>
-      <c r="Y11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor_geotiff/A 49131-2025 georefererad karta.tif", "A 49131-2025")</f>
-        <v/>
-      </c>
-      <c r="AA11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomål/A 49131-2025 FSC-klagomål.docx", "A 49131-2025")</f>
-        <v/>
-      </c>
-      <c r="AB11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomålsmail/A 49131-2025 FSC-klagomål mail.docx", "A 49131-2025")</f>
-        <v/>
-      </c>
-      <c r="AC11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsyn/A 49131-2025 tillsynsbegäran.docx", "A 49131-2025")</f>
-        <v/>
-      </c>
-      <c r="AD11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsynsmail/A 49131-2025 tillsynsbegäran mail.docx", "A 49131-2025")</f>
         <v/>
       </c>
     </row>
@@ -1735,7 +1735,7 @@
         <v>45209</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1850,7 +1850,7 @@
         <v>45170</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1956,7 +1956,7 @@
         <v>44646</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2044,7 +2044,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 3221-2022</t>
+          <t>A 2533-2026</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2058,10 +2058,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>44582</v>
+        <v>46037</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2074,13 +2074,13 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>0.5</v>
+        <v>1.4</v>
       </c>
       <c r="J15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L15" t="n">
         <v>0</v>
@@ -2110,46 +2110,46 @@
         <v>1</v>
       </c>
       <c r="U15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/artfynd/A 3221-2022 artfynd.xlsx", "A 3221-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/artfynd/A 2533-2026 artfynd.xlsx", "A 2533-2026")</f>
         <v/>
       </c>
       <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor/A 3221-2022 karta.png", "A 3221-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor/A 2533-2026 karta.png", "A 2533-2026")</f>
         <v/>
       </c>
       <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor_geotiff/A 3221-2022 georefererad karta.tif", "A 3221-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor_geotiff/A 2533-2026 georefererad karta.tif", "A 2533-2026")</f>
         <v/>
       </c>
       <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomål/A 3221-2022 FSC-klagomål.docx", "A 3221-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomål/A 2533-2026 FSC-klagomål.docx", "A 2533-2026")</f>
         <v/>
       </c>
       <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomålsmail/A 3221-2022 FSC-klagomål mail.docx", "A 3221-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomålsmail/A 2533-2026 FSC-klagomål mail.docx", "A 2533-2026")</f>
         <v/>
       </c>
       <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsyn/A 3221-2022 tillsynsbegäran.docx", "A 3221-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsyn/A 2533-2026 tillsynsbegäran.docx", "A 2533-2026")</f>
         <v/>
       </c>
       <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsynsmail/A 3221-2022 tillsynsbegäran mail.docx", "A 3221-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsynsmail/A 2533-2026 tillsynsbegäran mail.docx", "A 2533-2026")</f>
         <v/>
       </c>
     </row>
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 1793-2025</t>
+          <t>A 3221-2022</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2163,10 +2163,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45671</v>
+        <v>44582</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2179,13 +2179,13 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>1.7</v>
+        <v>0.5</v>
       </c>
       <c r="J16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L16" t="n">
         <v>0</v>
@@ -2212,42 +2212,42 @@
         <v>1</v>
       </c>
       <c r="T16" t="n">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>Mistel</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/artfynd/A 1793-2025 artfynd.xlsx", "A 1793-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/artfynd/A 3221-2022 artfynd.xlsx", "A 3221-2022")</f>
         <v/>
       </c>
       <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor/A 1793-2025 karta.png", "A 1793-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor/A 3221-2022 karta.png", "A 3221-2022")</f>
         <v/>
       </c>
       <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor_geotiff/A 1793-2025 georefererad karta.tif", "A 1793-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor_geotiff/A 3221-2022 georefererad karta.tif", "A 3221-2022")</f>
         <v/>
       </c>
       <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomål/A 1793-2025 FSC-klagomål.docx", "A 1793-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomål/A 3221-2022 FSC-klagomål.docx", "A 3221-2022")</f>
         <v/>
       </c>
       <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomålsmail/A 1793-2025 FSC-klagomål mail.docx", "A 1793-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomålsmail/A 3221-2022 FSC-klagomål mail.docx", "A 3221-2022")</f>
         <v/>
       </c>
       <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsyn/A 1793-2025 tillsynsbegäran.docx", "A 1793-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsyn/A 3221-2022 tillsynsbegäran.docx", "A 3221-2022")</f>
         <v/>
       </c>
       <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsynsmail/A 1793-2025 tillsynsbegäran mail.docx", "A 1793-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsynsmail/A 3221-2022 tillsynsbegäran mail.docx", "A 3221-2022")</f>
         <v/>
       </c>
     </row>
@@ -2271,7 +2271,7 @@
         <v>45007</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2359,7 +2359,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 2533-2026</t>
+          <t>A 1793-2025</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2373,10 +2373,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>46037</v>
+        <v>45671</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2389,7 +2389,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>1.4</v>
+        <v>1.7</v>
       </c>
       <c r="J18" t="n">
         <v>1</v>
@@ -2422,42 +2422,42 @@
         <v>1</v>
       </c>
       <c r="T18" t="n">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="U18" t="n">
         <v>0</v>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Mistel</t>
         </is>
       </c>
       <c r="W18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/artfynd/A 2533-2026 artfynd.xlsx", "A 2533-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/artfynd/A 1793-2025 artfynd.xlsx", "A 1793-2025")</f>
         <v/>
       </c>
       <c r="X18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor/A 2533-2026 karta.png", "A 2533-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor/A 1793-2025 karta.png", "A 1793-2025")</f>
         <v/>
       </c>
       <c r="Y18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor_geotiff/A 2533-2026 georefererad karta.tif", "A 2533-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor_geotiff/A 1793-2025 georefererad karta.tif", "A 1793-2025")</f>
         <v/>
       </c>
       <c r="AA18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomål/A 2533-2026 FSC-klagomål.docx", "A 2533-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomål/A 1793-2025 FSC-klagomål.docx", "A 1793-2025")</f>
         <v/>
       </c>
       <c r="AB18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomålsmail/A 2533-2026 FSC-klagomål mail.docx", "A 2533-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomålsmail/A 1793-2025 FSC-klagomål mail.docx", "A 1793-2025")</f>
         <v/>
       </c>
       <c r="AC18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsyn/A 2533-2026 tillsynsbegäran.docx", "A 2533-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsyn/A 1793-2025 tillsynsbegäran.docx", "A 1793-2025")</f>
         <v/>
       </c>
       <c r="AD18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsynsmail/A 2533-2026 tillsynsbegäran mail.docx", "A 2533-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsynsmail/A 1793-2025 tillsynsbegäran mail.docx", "A 1793-2025")</f>
         <v/>
       </c>
     </row>
@@ -2481,7 +2481,7 @@
         <v>44670</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2554,7 +2554,7 @@
         <v>44802</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2610,7 +2610,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 3219-2022</t>
+          <t>A 63378-2025</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2624,10 +2624,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>44582</v>
+        <v>46010</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2640,7 +2640,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>0.5</v>
+        <v>4.8</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2683,7 +2683,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 3222-2022</t>
+          <t>A 2535-2026</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2697,10 +2697,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>44582</v>
+        <v>46037</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2713,7 +2713,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>1.8</v>
+        <v>1.6</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2756,7 +2756,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 60755-2024</t>
+          <t>A 50184-2023</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2770,10 +2770,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45644</v>
+        <v>45208</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2786,7 +2786,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>2.1</v>
+        <v>10.8</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2829,7 +2829,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 55724-2024</t>
+          <t>A 56002-2024</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2843,10 +2843,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45622</v>
+        <v>45623</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2859,7 +2859,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>0.5</v>
+        <v>3.4</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2902,7 +2902,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 35955-2023</t>
+          <t>A 61217-2024</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2916,10 +2916,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45148</v>
+        <v>45645</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2932,7 +2932,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>1.1</v>
+        <v>0.8</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2975,7 +2975,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 61217-2024</t>
+          <t>A 20399-2026</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2989,10 +2989,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45645</v>
+        <v>46139</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3005,7 +3005,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -3048,7 +3048,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 56002-2024</t>
+          <t>A 20398-2026</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3062,10 +3062,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45623</v>
+        <v>46139</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3078,7 +3078,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>3.4</v>
+        <v>2.4</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -3121,7 +3121,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 60728-2022</t>
+          <t>A 37245-2025</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3135,10 +3135,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>44913</v>
+        <v>45876</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3151,7 +3151,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -3194,7 +3194,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 50184-2023</t>
+          <t>A 3222-2022</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3208,10 +3208,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45208</v>
+        <v>44582</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3224,7 +3224,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>10.8</v>
+        <v>1.8</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3267,7 +3267,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 37245-2025</t>
+          <t>A 20898-2026</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3281,10 +3281,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45876</v>
+        <v>46142</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3297,7 +3297,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>1.1</v>
+        <v>3.6</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3340,7 +3340,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 63378-2025</t>
+          <t>A 34073-2025</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3350,14 +3350,14 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>46010</v>
+        <v>45845</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3370,7 +3370,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>4.8</v>
+        <v>2.9</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3413,7 +3413,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 2535-2026</t>
+          <t>A 3219-2022</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3427,10 +3427,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>46037</v>
+        <v>44582</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3443,7 +3443,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>1.6</v>
+        <v>0.5</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3486,7 +3486,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 20399-2026</t>
+          <t>A 60755-2024</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3500,10 +3500,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>46139</v>
+        <v>45644</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3516,7 +3516,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>0.9</v>
+        <v>2.1</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3559,7 +3559,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 20398-2026</t>
+          <t>A 55724-2024</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3573,10 +3573,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>46139</v>
+        <v>45622</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3589,7 +3589,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>2.4</v>
+        <v>0.5</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3632,7 +3632,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 20898-2026</t>
+          <t>A 35955-2023</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3646,10 +3646,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>46142</v>
+        <v>45148</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3662,7 +3662,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>3.6</v>
+        <v>1.1</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3705,7 +3705,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 34073-2025</t>
+          <t>A 60728-2022</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3715,14 +3715,14 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45845</v>
+        <v>44913</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3735,7 +3735,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>2.9</v>
+        <v>1.2</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3795,7 +3795,7 @@
         <v>46244</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3873,7 +3873,7 @@
         <v>46153</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>

--- a/Översikt EKERÖ.xlsx
+++ b/Översikt EKERÖ.xlsx
@@ -601,7 +601,7 @@
         <v>46241</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -728,7 +728,7 @@
         <v>44872</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -848,7 +848,7 @@
         <v>44974</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -963,7 +963,7 @@
         <v>45148</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1073,7 +1073,7 @@
         <v>46119</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1187,7 +1187,7 @@
         <v>44582</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1296,7 +1296,7 @@
         <v>46241</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1409,7 +1409,7 @@
         <v>44634</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1499,7 +1499,7 @@
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 49131-2025</t>
+          <t>A 13237-2023</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1513,10 +1513,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>45937</v>
+        <v>45002</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1528,20 +1528,25 @@
           <t>EKERÖ</t>
         </is>
       </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I10" t="n">
-        <v>0.9</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N10" t="n">
         <v>0</v>
@@ -1553,165 +1558,160 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="R10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
         <v>3</v>
       </c>
       <c r="T10" t="n">
+        <v>7</v>
+      </c>
+      <c r="U10" t="n">
+        <v>0</v>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
+        <is>
+          <t>Tallticka
+Granbarkgnagare
+Grönpyrola</t>
+        </is>
+      </c>
+      <c r="W10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/artfynd/A 13237-2023 artfynd.xlsx", "A 13237-2023")</f>
+        <v/>
+      </c>
+      <c r="X10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor/A 13237-2023 karta.png", "A 13237-2023")</f>
+        <v/>
+      </c>
+      <c r="Y10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor_geotiff/A 13237-2023 georefererad karta.tif", "A 13237-2023")</f>
+        <v/>
+      </c>
+      <c r="AA10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomål/A 13237-2023 FSC-klagomål.docx", "A 13237-2023")</f>
+        <v/>
+      </c>
+      <c r="AB10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomålsmail/A 13237-2023 FSC-klagomål mail.docx", "A 13237-2023")</f>
+        <v/>
+      </c>
+      <c r="AC10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsyn/A 13237-2023 tillsynsbegäran.docx", "A 13237-2023")</f>
+        <v/>
+      </c>
+      <c r="AD10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsynsmail/A 13237-2023 tillsynsbegäran mail.docx", "A 13237-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11" ht="15" customHeight="1">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>A 49131-2025</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D11" s="1" t="n">
+        <v>45937</v>
+      </c>
+      <c r="E11" s="1" t="n">
+        <v>46298</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>EKERÖ</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" t="n">
+        <v>2</v>
+      </c>
+      <c r="M11" t="n">
+        <v>1</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" t="n">
         <v>3</v>
       </c>
-      <c r="U10" t="n">
+      <c r="R11" t="n">
+        <v>1</v>
+      </c>
+      <c r="S11" t="n">
         <v>3</v>
       </c>
-      <c r="V10" s="2" t="inlineStr">
+      <c r="T11" t="n">
+        <v>3</v>
+      </c>
+      <c r="U11" t="n">
+        <v>3</v>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
         <is>
           <t>Jättemusseron
 Motaggsvamp
 Svartvit taggsvamp</t>
         </is>
       </c>
-      <c r="W10">
+      <c r="W11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0125/artfynd/A 49131-2025 artfynd.xlsx", "A 49131-2025")</f>
         <v/>
       </c>
-      <c r="X10">
+      <c r="X11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor/A 49131-2025 karta.png", "A 49131-2025")</f>
         <v/>
       </c>
-      <c r="Y10">
+      <c r="Y11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor_geotiff/A 49131-2025 georefererad karta.tif", "A 49131-2025")</f>
         <v/>
       </c>
-      <c r="AA10">
+      <c r="AA11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomål/A 49131-2025 FSC-klagomål.docx", "A 49131-2025")</f>
         <v/>
       </c>
-      <c r="AB10">
+      <c r="AB11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomålsmail/A 49131-2025 FSC-klagomål mail.docx", "A 49131-2025")</f>
         <v/>
       </c>
-      <c r="AC10">
+      <c r="AC11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsyn/A 49131-2025 tillsynsbegäran.docx", "A 49131-2025")</f>
         <v/>
       </c>
-      <c r="AD10">
+      <c r="AD11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsynsmail/A 49131-2025 tillsynsbegäran mail.docx", "A 49131-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="11" ht="15" customHeight="1">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>A 13237-2023</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D11" s="1" t="n">
-        <v>45002</v>
-      </c>
-      <c r="E11" s="1" t="n">
-        <v>46297</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>EKERÖ</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
-      <c r="I11" t="n">
-        <v>9.300000000000001</v>
-      </c>
-      <c r="J11" t="n">
-        <v>0</v>
-      </c>
-      <c r="K11" t="n">
-        <v>2</v>
-      </c>
-      <c r="L11" t="n">
-        <v>1</v>
-      </c>
-      <c r="M11" t="n">
-        <v>0</v>
-      </c>
-      <c r="N11" t="n">
-        <v>0</v>
-      </c>
-      <c r="O11" t="n">
-        <v>0</v>
-      </c>
-      <c r="P11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>1</v>
-      </c>
-      <c r="R11" t="n">
-        <v>0</v>
-      </c>
-      <c r="S11" t="n">
-        <v>3</v>
-      </c>
-      <c r="T11" t="n">
-        <v>7</v>
-      </c>
-      <c r="U11" t="n">
-        <v>0</v>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
-        <is>
-          <t>Tallticka
-Granbarkgnagare
-Grönpyrola</t>
-        </is>
-      </c>
-      <c r="W11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/artfynd/A 13237-2023 artfynd.xlsx", "A 13237-2023")</f>
-        <v/>
-      </c>
-      <c r="X11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor/A 13237-2023 karta.png", "A 13237-2023")</f>
-        <v/>
-      </c>
-      <c r="Y11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor_geotiff/A 13237-2023 georefererad karta.tif", "A 13237-2023")</f>
-        <v/>
-      </c>
-      <c r="AA11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomål/A 13237-2023 FSC-klagomål.docx", "A 13237-2023")</f>
-        <v/>
-      </c>
-      <c r="AB11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomålsmail/A 13237-2023 FSC-klagomål mail.docx", "A 13237-2023")</f>
-        <v/>
-      </c>
-      <c r="AC11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsyn/A 13237-2023 tillsynsbegäran.docx", "A 13237-2023")</f>
-        <v/>
-      </c>
-      <c r="AD11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsynsmail/A 13237-2023 tillsynsbegäran mail.docx", "A 13237-2023")</f>
         <v/>
       </c>
     </row>
@@ -1735,7 +1735,7 @@
         <v>45209</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1850,7 +1850,7 @@
         <v>45170</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1956,7 +1956,7 @@
         <v>44646</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2044,7 +2044,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 2533-2026</t>
+          <t>A 3221-2022</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2058,10 +2058,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>46037</v>
+        <v>44582</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2074,13 +2074,13 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>1.4</v>
+        <v>0.5</v>
       </c>
       <c r="J15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L15" t="n">
         <v>0</v>
@@ -2110,46 +2110,46 @@
         <v>1</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/artfynd/A 2533-2026 artfynd.xlsx", "A 2533-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/artfynd/A 3221-2022 artfynd.xlsx", "A 3221-2022")</f>
         <v/>
       </c>
       <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor/A 2533-2026 karta.png", "A 2533-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor/A 3221-2022 karta.png", "A 3221-2022")</f>
         <v/>
       </c>
       <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor_geotiff/A 2533-2026 georefererad karta.tif", "A 2533-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor_geotiff/A 3221-2022 georefererad karta.tif", "A 3221-2022")</f>
         <v/>
       </c>
       <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomål/A 2533-2026 FSC-klagomål.docx", "A 2533-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomål/A 3221-2022 FSC-klagomål.docx", "A 3221-2022")</f>
         <v/>
       </c>
       <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomålsmail/A 2533-2026 FSC-klagomål mail.docx", "A 2533-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomålsmail/A 3221-2022 FSC-klagomål mail.docx", "A 3221-2022")</f>
         <v/>
       </c>
       <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsyn/A 2533-2026 tillsynsbegäran.docx", "A 2533-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsyn/A 3221-2022 tillsynsbegäran.docx", "A 3221-2022")</f>
         <v/>
       </c>
       <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsynsmail/A 2533-2026 tillsynsbegäran mail.docx", "A 2533-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsynsmail/A 3221-2022 tillsynsbegäran mail.docx", "A 3221-2022")</f>
         <v/>
       </c>
     </row>
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 3221-2022</t>
+          <t>A 1793-2025</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2163,10 +2163,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>44582</v>
+        <v>45671</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2179,13 +2179,13 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>0.5</v>
+        <v>1.7</v>
       </c>
       <c r="J16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L16" t="n">
         <v>0</v>
@@ -2212,42 +2212,42 @@
         <v>1</v>
       </c>
       <c r="T16" t="n">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="U16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Mistel</t>
         </is>
       </c>
       <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/artfynd/A 3221-2022 artfynd.xlsx", "A 3221-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/artfynd/A 1793-2025 artfynd.xlsx", "A 1793-2025")</f>
         <v/>
       </c>
       <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor/A 3221-2022 karta.png", "A 3221-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor/A 1793-2025 karta.png", "A 1793-2025")</f>
         <v/>
       </c>
       <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor_geotiff/A 3221-2022 georefererad karta.tif", "A 3221-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor_geotiff/A 1793-2025 georefererad karta.tif", "A 1793-2025")</f>
         <v/>
       </c>
       <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomål/A 3221-2022 FSC-klagomål.docx", "A 3221-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomål/A 1793-2025 FSC-klagomål.docx", "A 1793-2025")</f>
         <v/>
       </c>
       <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomålsmail/A 3221-2022 FSC-klagomål mail.docx", "A 3221-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomålsmail/A 1793-2025 FSC-klagomål mail.docx", "A 1793-2025")</f>
         <v/>
       </c>
       <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsyn/A 3221-2022 tillsynsbegäran.docx", "A 3221-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsyn/A 1793-2025 tillsynsbegäran.docx", "A 1793-2025")</f>
         <v/>
       </c>
       <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsynsmail/A 3221-2022 tillsynsbegäran mail.docx", "A 3221-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsynsmail/A 1793-2025 tillsynsbegäran mail.docx", "A 1793-2025")</f>
         <v/>
       </c>
     </row>
@@ -2271,7 +2271,7 @@
         <v>45007</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2359,7 +2359,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 1793-2025</t>
+          <t>A 2533-2026</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2373,10 +2373,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45671</v>
+        <v>46037</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2389,7 +2389,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>1.7</v>
+        <v>1.4</v>
       </c>
       <c r="J18" t="n">
         <v>1</v>
@@ -2422,42 +2422,42 @@
         <v>1</v>
       </c>
       <c r="T18" t="n">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="U18" t="n">
         <v>0</v>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>Mistel</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="W18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/artfynd/A 1793-2025 artfynd.xlsx", "A 1793-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/artfynd/A 2533-2026 artfynd.xlsx", "A 2533-2026")</f>
         <v/>
       </c>
       <c r="X18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor/A 1793-2025 karta.png", "A 1793-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor/A 2533-2026 karta.png", "A 2533-2026")</f>
         <v/>
       </c>
       <c r="Y18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor_geotiff/A 1793-2025 georefererad karta.tif", "A 1793-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor_geotiff/A 2533-2026 georefererad karta.tif", "A 2533-2026")</f>
         <v/>
       </c>
       <c r="AA18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomål/A 1793-2025 FSC-klagomål.docx", "A 1793-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomål/A 2533-2026 FSC-klagomål.docx", "A 2533-2026")</f>
         <v/>
       </c>
       <c r="AB18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomålsmail/A 1793-2025 FSC-klagomål mail.docx", "A 1793-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomålsmail/A 2533-2026 FSC-klagomål mail.docx", "A 2533-2026")</f>
         <v/>
       </c>
       <c r="AC18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsyn/A 1793-2025 tillsynsbegäran.docx", "A 1793-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsyn/A 2533-2026 tillsynsbegäran.docx", "A 2533-2026")</f>
         <v/>
       </c>
       <c r="AD18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsynsmail/A 1793-2025 tillsynsbegäran mail.docx", "A 1793-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsynsmail/A 2533-2026 tillsynsbegäran mail.docx", "A 2533-2026")</f>
         <v/>
       </c>
     </row>
@@ -2481,7 +2481,7 @@
         <v>44670</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2554,7 +2554,7 @@
         <v>44802</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2610,7 +2610,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 63378-2025</t>
+          <t>A 3219-2022</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2624,10 +2624,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>46010</v>
+        <v>44582</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2640,7 +2640,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>4.8</v>
+        <v>0.5</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2683,7 +2683,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 2535-2026</t>
+          <t>A 63378-2025</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2697,10 +2697,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>46037</v>
+        <v>46010</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2713,7 +2713,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>1.6</v>
+        <v>4.8</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2756,7 +2756,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 50184-2023</t>
+          <t>A 2535-2026</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2770,10 +2770,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45208</v>
+        <v>46037</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2786,7 +2786,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>10.8</v>
+        <v>1.6</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2829,7 +2829,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 56002-2024</t>
+          <t>A 50184-2023</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2843,10 +2843,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45623</v>
+        <v>45208</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2859,7 +2859,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>3.4</v>
+        <v>10.8</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2902,7 +2902,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 61217-2024</t>
+          <t>A 20399-2026</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2916,10 +2916,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45645</v>
+        <v>46139</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2932,7 +2932,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2975,7 +2975,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 20399-2026</t>
+          <t>A 20398-2026</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2992,7 +2992,7 @@
         <v>46139</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3005,7 +3005,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>0.9</v>
+        <v>2.4</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -3048,7 +3048,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 20398-2026</t>
+          <t>A 55724-2024</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3062,10 +3062,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>46139</v>
+        <v>45622</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3078,7 +3078,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>2.4</v>
+        <v>0.5</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -3121,7 +3121,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 37245-2025</t>
+          <t>A 20898-2026</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3135,10 +3135,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45876</v>
+        <v>46142</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3151,7 +3151,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>1.1</v>
+        <v>3.6</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -3194,7 +3194,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 3222-2022</t>
+          <t>A 35955-2023</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3208,10 +3208,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>44582</v>
+        <v>45148</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3224,7 +3224,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>1.8</v>
+        <v>1.1</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3267,7 +3267,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 20898-2026</t>
+          <t>A 37245-2025</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3281,10 +3281,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>46142</v>
+        <v>45876</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3297,7 +3297,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>3.6</v>
+        <v>1.1</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3340,7 +3340,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 34073-2025</t>
+          <t>A 61217-2024</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3350,14 +3350,14 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45845</v>
+        <v>45645</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3370,7 +3370,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>2.9</v>
+        <v>0.8</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3413,7 +3413,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 3219-2022</t>
+          <t>A 56002-2024</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3427,10 +3427,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>44582</v>
+        <v>45623</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3443,7 +3443,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>0.5</v>
+        <v>3.4</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3486,7 +3486,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 60755-2024</t>
+          <t>A 34073-2025</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3496,14 +3496,14 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45644</v>
+        <v>45845</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3516,7 +3516,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>2.1</v>
+        <v>2.9</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3559,7 +3559,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 55724-2024</t>
+          <t>A 60728-2022</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3573,10 +3573,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45622</v>
+        <v>44913</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3589,7 +3589,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>0.5</v>
+        <v>1.2</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3632,7 +3632,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 35955-2023</t>
+          <t>A 3222-2022</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3646,10 +3646,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45148</v>
+        <v>44582</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3662,7 +3662,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>1.1</v>
+        <v>1.8</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3705,7 +3705,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 60728-2022</t>
+          <t>A 33154-2026</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3719,10 +3719,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>44913</v>
+        <v>46244</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3734,8 +3734,13 @@
           <t>EKERÖ</t>
         </is>
       </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I36" t="n">
-        <v>1.2</v>
+        <v>3.5</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3778,7 +3783,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 33154-2026</t>
+          <t>A 60755-2024</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3792,10 +3797,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>46244</v>
+        <v>45644</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3807,13 +3812,8 @@
           <t>EKERÖ</t>
         </is>
       </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I37" t="n">
-        <v>3.5</v>
+        <v>2.1</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3873,7 +3873,7 @@
         <v>46153</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>

--- a/Översikt EKERÖ.xlsx
+++ b/Översikt EKERÖ.xlsx
@@ -601,7 +601,7 @@
         <v>46241</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -728,7 +728,7 @@
         <v>44872</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -848,7 +848,7 @@
         <v>44974</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -963,7 +963,7 @@
         <v>45148</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1073,7 +1073,7 @@
         <v>46119</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1187,7 +1187,7 @@
         <v>44582</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1296,7 +1296,7 @@
         <v>46241</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1409,7 +1409,7 @@
         <v>44634</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1516,7 +1516,7 @@
         <v>45002</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1628,7 +1628,7 @@
         <v>45937</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1735,7 +1735,7 @@
         <v>45209</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1850,7 +1850,7 @@
         <v>45170</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1956,7 +1956,7 @@
         <v>44646</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2061,7 +2061,7 @@
         <v>44582</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2166,7 +2166,7 @@
         <v>45671</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2271,7 +2271,7 @@
         <v>45007</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2376,7 +2376,7 @@
         <v>46037</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2481,7 +2481,7 @@
         <v>44670</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2554,7 +2554,7 @@
         <v>44802</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2627,7 +2627,7 @@
         <v>44582</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2700,7 +2700,7 @@
         <v>46010</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2773,7 +2773,7 @@
         <v>46037</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2846,7 +2846,7 @@
         <v>45208</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2919,7 +2919,7 @@
         <v>46139</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2992,7 +2992,7 @@
         <v>46139</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3065,7 +3065,7 @@
         <v>45622</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3138,7 +3138,7 @@
         <v>46142</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3211,7 +3211,7 @@
         <v>45148</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3284,7 +3284,7 @@
         <v>45876</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3357,7 +3357,7 @@
         <v>45645</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3430,7 +3430,7 @@
         <v>45623</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3503,7 +3503,7 @@
         <v>45845</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3576,7 +3576,7 @@
         <v>44913</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3649,7 +3649,7 @@
         <v>44582</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3722,7 +3722,7 @@
         <v>46244</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3800,7 +3800,7 @@
         <v>45644</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3873,7 +3873,7 @@
         <v>46153</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>

--- a/Översikt EKERÖ.xlsx
+++ b/Översikt EKERÖ.xlsx
@@ -601,7 +601,7 @@
         <v>46241</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -728,7 +728,7 @@
         <v>44872</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -848,7 +848,7 @@
         <v>44974</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -963,7 +963,7 @@
         <v>45148</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1073,7 +1073,7 @@
         <v>46119</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1187,7 +1187,7 @@
         <v>44582</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1296,7 +1296,7 @@
         <v>46241</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1409,7 +1409,7 @@
         <v>44634</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1516,7 +1516,7 @@
         <v>45002</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1628,7 +1628,7 @@
         <v>45937</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1735,7 +1735,7 @@
         <v>45209</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1850,7 +1850,7 @@
         <v>45170</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1956,7 +1956,7 @@
         <v>44646</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2061,7 +2061,7 @@
         <v>44582</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2166,7 +2166,7 @@
         <v>45671</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2271,7 +2271,7 @@
         <v>45007</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2376,7 +2376,7 @@
         <v>46037</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2481,7 +2481,7 @@
         <v>44670</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2554,7 +2554,7 @@
         <v>44802</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2627,7 +2627,7 @@
         <v>44582</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2700,7 +2700,7 @@
         <v>46010</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2773,7 +2773,7 @@
         <v>46037</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2846,7 +2846,7 @@
         <v>45208</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2919,7 +2919,7 @@
         <v>46139</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2992,7 +2992,7 @@
         <v>46139</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3065,7 +3065,7 @@
         <v>45622</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3138,7 +3138,7 @@
         <v>46142</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3211,7 +3211,7 @@
         <v>45148</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3284,7 +3284,7 @@
         <v>45876</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3357,7 +3357,7 @@
         <v>45645</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3430,7 +3430,7 @@
         <v>45623</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3503,7 +3503,7 @@
         <v>45845</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3576,7 +3576,7 @@
         <v>44913</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3649,7 +3649,7 @@
         <v>44582</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3722,7 +3722,7 @@
         <v>46244</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3800,7 +3800,7 @@
         <v>45644</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3873,7 +3873,7 @@
         <v>46153</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>

--- a/Översikt EKERÖ.xlsx
+++ b/Översikt EKERÖ.xlsx
@@ -601,7 +601,7 @@
         <v>46241</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -728,7 +728,7 @@
         <v>44872</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -848,7 +848,7 @@
         <v>44974</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -963,7 +963,7 @@
         <v>45148</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1056,7 +1056,7 @@
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A 17520-2026</t>
+          <t>A 3218-2022</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1070,10 +1070,10 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>46119</v>
+        <v>44582</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1085,13 +1085,8 @@
           <t>EKERÖ</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I6" t="n">
-        <v>2.2</v>
+        <v>1.2</v>
       </c>
       <c r="J6" t="n">
         <v>1</v>
@@ -1100,36 +1095,150 @@
         <v>1</v>
       </c>
       <c r="L6" t="n">
+        <v>1</v>
+      </c>
+      <c r="M6" t="n">
+        <v>1</v>
+      </c>
+      <c r="N6" t="n">
+        <v>1</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" t="n">
         <v>3</v>
       </c>
-      <c r="M6" t="n">
-        <v>1</v>
-      </c>
-      <c r="N6" t="n">
-        <v>0</v>
-      </c>
-      <c r="O6" t="n">
-        <v>0</v>
-      </c>
-      <c r="P6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>4</v>
-      </c>
       <c r="R6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
       </c>
       <c r="T6" t="n">
+        <v>8</v>
+      </c>
+      <c r="U6" t="n">
+        <v>6</v>
+      </c>
+      <c r="V6" s="2" t="inlineStr">
+        <is>
+          <t>Bombmurkla
+Gul lammticka
+Fyrflikig jordstjärna
+Kamjordstjärna
+Blåbär</t>
+        </is>
+      </c>
+      <c r="W6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/artfynd/A 3218-2022 artfynd.xlsx", "A 3218-2022")</f>
+        <v/>
+      </c>
+      <c r="X6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor/A 3218-2022 karta.png", "A 3218-2022")</f>
+        <v/>
+      </c>
+      <c r="Y6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor_geotiff/A 3218-2022 georefererad karta.tif", "A 3218-2022")</f>
+        <v/>
+      </c>
+      <c r="AA6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomål/A 3218-2022 FSC-klagomål.docx", "A 3218-2022")</f>
+        <v/>
+      </c>
+      <c r="AB6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomålsmail/A 3218-2022 FSC-klagomål mail.docx", "A 3218-2022")</f>
+        <v/>
+      </c>
+      <c r="AC6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsyn/A 3218-2022 tillsynsbegäran.docx", "A 3218-2022")</f>
+        <v/>
+      </c>
+      <c r="AD6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsynsmail/A 3218-2022 tillsynsbegäran mail.docx", "A 3218-2022")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7" ht="15" customHeight="1">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>A 17520-2026</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D7" s="1" t="n">
+        <v>46119</v>
+      </c>
+      <c r="E7" s="1" t="n">
+        <v>46301</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>EKERÖ</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="J7" t="n">
+        <v>1</v>
+      </c>
+      <c r="K7" t="n">
+        <v>1</v>
+      </c>
+      <c r="L7" t="n">
+        <v>3</v>
+      </c>
+      <c r="M7" t="n">
+        <v>1</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>4</v>
+      </c>
+      <c r="R7" t="n">
+        <v>1</v>
+      </c>
+      <c r="S7" t="n">
         <v>5</v>
       </c>
-      <c r="U6" t="n">
-        <v>1</v>
-      </c>
-      <c r="V6" s="2" t="inlineStr">
+      <c r="T7" t="n">
+        <v>5</v>
+      </c>
+      <c r="U7" t="n">
+        <v>1</v>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
         <is>
           <t>Läderbagge
 Blekticka
@@ -1138,141 +1247,32 @@
 Gulgrön kantmusseron</t>
         </is>
       </c>
-      <c r="W6">
+      <c r="W7">
         <f>HYPERLINK("https://klasma.github.io/Logging_0125/artfynd/A 17520-2026 artfynd.xlsx", "A 17520-2026")</f>
         <v/>
       </c>
-      <c r="X6">
+      <c r="X7">
         <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor/A 17520-2026 karta.png", "A 17520-2026")</f>
         <v/>
       </c>
-      <c r="Y6">
+      <c r="Y7">
         <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor_geotiff/A 17520-2026 georefererad karta.tif", "A 17520-2026")</f>
         <v/>
       </c>
-      <c r="AA6">
+      <c r="AA7">
         <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomål/A 17520-2026 FSC-klagomål.docx", "A 17520-2026")</f>
         <v/>
       </c>
-      <c r="AB6">
+      <c r="AB7">
         <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomålsmail/A 17520-2026 FSC-klagomål mail.docx", "A 17520-2026")</f>
         <v/>
       </c>
-      <c r="AC6">
+      <c r="AC7">
         <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsyn/A 17520-2026 tillsynsbegäran.docx", "A 17520-2026")</f>
         <v/>
       </c>
-      <c r="AD6">
+      <c r="AD7">
         <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsynsmail/A 17520-2026 tillsynsbegäran mail.docx", "A 17520-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="7" ht="15" customHeight="1">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>A 3218-2022</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D7" s="1" t="n">
-        <v>44582</v>
-      </c>
-      <c r="E7" s="1" t="n">
-        <v>46300</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>EKERÖ</t>
-        </is>
-      </c>
-      <c r="I7" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="J7" t="n">
-        <v>1</v>
-      </c>
-      <c r="K7" t="n">
-        <v>1</v>
-      </c>
-      <c r="L7" t="n">
-        <v>1</v>
-      </c>
-      <c r="M7" t="n">
-        <v>1</v>
-      </c>
-      <c r="N7" t="n">
-        <v>1</v>
-      </c>
-      <c r="O7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>3</v>
-      </c>
-      <c r="R7" t="n">
-        <v>2</v>
-      </c>
-      <c r="S7" t="n">
-        <v>5</v>
-      </c>
-      <c r="T7" t="n">
-        <v>8</v>
-      </c>
-      <c r="U7" t="n">
-        <v>6</v>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>Bombmurkla
-Gul lammticka
-Fyrflikig jordstjärna
-Kamjordstjärna
-Blåbär</t>
-        </is>
-      </c>
-      <c r="W7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/artfynd/A 3218-2022 artfynd.xlsx", "A 3218-2022")</f>
-        <v/>
-      </c>
-      <c r="X7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor/A 3218-2022 karta.png", "A 3218-2022")</f>
-        <v/>
-      </c>
-      <c r="Y7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor_geotiff/A 3218-2022 georefererad karta.tif", "A 3218-2022")</f>
-        <v/>
-      </c>
-      <c r="AA7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomål/A 3218-2022 FSC-klagomål.docx", "A 3218-2022")</f>
-        <v/>
-      </c>
-      <c r="AB7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomålsmail/A 3218-2022 FSC-klagomål mail.docx", "A 3218-2022")</f>
-        <v/>
-      </c>
-      <c r="AC7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsyn/A 3218-2022 tillsynsbegäran.docx", "A 3218-2022")</f>
-        <v/>
-      </c>
-      <c r="AD7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsynsmail/A 3218-2022 tillsynsbegäran mail.docx", "A 3218-2022")</f>
         <v/>
       </c>
     </row>
@@ -1296,7 +1296,7 @@
         <v>46241</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1409,7 +1409,7 @@
         <v>44634</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1499,7 +1499,7 @@
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 13237-2023</t>
+          <t>A 49131-2025</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1513,10 +1513,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>45002</v>
+        <v>45937</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1528,25 +1528,20 @@
           <t>EKERÖ</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I10" t="n">
-        <v>9.300000000000001</v>
+        <v>0.9</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
       </c>
       <c r="K10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" t="n">
         <v>2</v>
       </c>
-      <c r="L10" t="n">
-        <v>1</v>
-      </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N10" t="n">
         <v>0</v>
@@ -1558,160 +1553,165 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S10" t="n">
         <v>3</v>
       </c>
       <c r="T10" t="n">
+        <v>3</v>
+      </c>
+      <c r="U10" t="n">
+        <v>3</v>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
+        <is>
+          <t>Jättemusseron
+Motaggsvamp
+Svartvit taggsvamp</t>
+        </is>
+      </c>
+      <c r="W10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/artfynd/A 49131-2025 artfynd.xlsx", "A 49131-2025")</f>
+        <v/>
+      </c>
+      <c r="X10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor/A 49131-2025 karta.png", "A 49131-2025")</f>
+        <v/>
+      </c>
+      <c r="Y10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor_geotiff/A 49131-2025 georefererad karta.tif", "A 49131-2025")</f>
+        <v/>
+      </c>
+      <c r="AA10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomål/A 49131-2025 FSC-klagomål.docx", "A 49131-2025")</f>
+        <v/>
+      </c>
+      <c r="AB10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomålsmail/A 49131-2025 FSC-klagomål mail.docx", "A 49131-2025")</f>
+        <v/>
+      </c>
+      <c r="AC10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsyn/A 49131-2025 tillsynsbegäran.docx", "A 49131-2025")</f>
+        <v/>
+      </c>
+      <c r="AD10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsynsmail/A 49131-2025 tillsynsbegäran mail.docx", "A 49131-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11" ht="15" customHeight="1">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>A 13237-2023</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D11" s="1" t="n">
+        <v>45002</v>
+      </c>
+      <c r="E11" s="1" t="n">
+        <v>46301</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>EKERÖ</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" t="n">
+        <v>2</v>
+      </c>
+      <c r="L11" t="n">
+        <v>1</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>1</v>
+      </c>
+      <c r="R11" t="n">
+        <v>0</v>
+      </c>
+      <c r="S11" t="n">
+        <v>3</v>
+      </c>
+      <c r="T11" t="n">
         <v>7</v>
       </c>
-      <c r="U10" t="n">
-        <v>0</v>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
+      <c r="U11" t="n">
+        <v>0</v>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
         <is>
           <t>Tallticka
 Granbarkgnagare
 Grönpyrola</t>
         </is>
       </c>
-      <c r="W10">
+      <c r="W11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0125/artfynd/A 13237-2023 artfynd.xlsx", "A 13237-2023")</f>
         <v/>
       </c>
-      <c r="X10">
+      <c r="X11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor/A 13237-2023 karta.png", "A 13237-2023")</f>
         <v/>
       </c>
-      <c r="Y10">
+      <c r="Y11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor_geotiff/A 13237-2023 georefererad karta.tif", "A 13237-2023")</f>
         <v/>
       </c>
-      <c r="AA10">
+      <c r="AA11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomål/A 13237-2023 FSC-klagomål.docx", "A 13237-2023")</f>
         <v/>
       </c>
-      <c r="AB10">
+      <c r="AB11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomålsmail/A 13237-2023 FSC-klagomål mail.docx", "A 13237-2023")</f>
         <v/>
       </c>
-      <c r="AC10">
+      <c r="AC11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsyn/A 13237-2023 tillsynsbegäran.docx", "A 13237-2023")</f>
         <v/>
       </c>
-      <c r="AD10">
+      <c r="AD11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsynsmail/A 13237-2023 tillsynsbegäran mail.docx", "A 13237-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="11" ht="15" customHeight="1">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>A 49131-2025</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D11" s="1" t="n">
-        <v>45937</v>
-      </c>
-      <c r="E11" s="1" t="n">
-        <v>46300</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>EKERÖ</t>
-        </is>
-      </c>
-      <c r="I11" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="J11" t="n">
-        <v>0</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L11" t="n">
-        <v>2</v>
-      </c>
-      <c r="M11" t="n">
-        <v>1</v>
-      </c>
-      <c r="N11" t="n">
-        <v>0</v>
-      </c>
-      <c r="O11" t="n">
-        <v>0</v>
-      </c>
-      <c r="P11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>3</v>
-      </c>
-      <c r="R11" t="n">
-        <v>1</v>
-      </c>
-      <c r="S11" t="n">
-        <v>3</v>
-      </c>
-      <c r="T11" t="n">
-        <v>3</v>
-      </c>
-      <c r="U11" t="n">
-        <v>3</v>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
-        <is>
-          <t>Jättemusseron
-Motaggsvamp
-Svartvit taggsvamp</t>
-        </is>
-      </c>
-      <c r="W11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/artfynd/A 49131-2025 artfynd.xlsx", "A 49131-2025")</f>
-        <v/>
-      </c>
-      <c r="X11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor/A 49131-2025 karta.png", "A 49131-2025")</f>
-        <v/>
-      </c>
-      <c r="Y11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor_geotiff/A 49131-2025 georefererad karta.tif", "A 49131-2025")</f>
-        <v/>
-      </c>
-      <c r="AA11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomål/A 49131-2025 FSC-klagomål.docx", "A 49131-2025")</f>
-        <v/>
-      </c>
-      <c r="AB11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomålsmail/A 49131-2025 FSC-klagomål mail.docx", "A 49131-2025")</f>
-        <v/>
-      </c>
-      <c r="AC11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsyn/A 49131-2025 tillsynsbegäran.docx", "A 49131-2025")</f>
-        <v/>
-      </c>
-      <c r="AD11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsynsmail/A 49131-2025 tillsynsbegäran mail.docx", "A 49131-2025")</f>
         <v/>
       </c>
     </row>
@@ -1735,7 +1735,7 @@
         <v>45209</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1850,7 +1850,7 @@
         <v>45170</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1956,7 +1956,7 @@
         <v>44646</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2044,7 +2044,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 3221-2022</t>
+          <t>A 2533-2026</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2058,10 +2058,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>44582</v>
+        <v>46037</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2074,13 +2074,13 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>0.5</v>
+        <v>1.4</v>
       </c>
       <c r="J15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L15" t="n">
         <v>0</v>
@@ -2110,46 +2110,46 @@
         <v>1</v>
       </c>
       <c r="U15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/artfynd/A 3221-2022 artfynd.xlsx", "A 3221-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/artfynd/A 2533-2026 artfynd.xlsx", "A 2533-2026")</f>
         <v/>
       </c>
       <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor/A 3221-2022 karta.png", "A 3221-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor/A 2533-2026 karta.png", "A 2533-2026")</f>
         <v/>
       </c>
       <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor_geotiff/A 3221-2022 georefererad karta.tif", "A 3221-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor_geotiff/A 2533-2026 georefererad karta.tif", "A 2533-2026")</f>
         <v/>
       </c>
       <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomål/A 3221-2022 FSC-klagomål.docx", "A 3221-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomål/A 2533-2026 FSC-klagomål.docx", "A 2533-2026")</f>
         <v/>
       </c>
       <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomålsmail/A 3221-2022 FSC-klagomål mail.docx", "A 3221-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomålsmail/A 2533-2026 FSC-klagomål mail.docx", "A 2533-2026")</f>
         <v/>
       </c>
       <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsyn/A 3221-2022 tillsynsbegäran.docx", "A 3221-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsyn/A 2533-2026 tillsynsbegäran.docx", "A 2533-2026")</f>
         <v/>
       </c>
       <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsynsmail/A 3221-2022 tillsynsbegäran mail.docx", "A 3221-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsynsmail/A 2533-2026 tillsynsbegäran mail.docx", "A 2533-2026")</f>
         <v/>
       </c>
     </row>
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 1793-2025</t>
+          <t>A 3221-2022</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2163,10 +2163,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45671</v>
+        <v>44582</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2179,13 +2179,13 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>1.7</v>
+        <v>0.5</v>
       </c>
       <c r="J16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L16" t="n">
         <v>0</v>
@@ -2212,42 +2212,42 @@
         <v>1</v>
       </c>
       <c r="T16" t="n">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>Mistel</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/artfynd/A 1793-2025 artfynd.xlsx", "A 1793-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/artfynd/A 3221-2022 artfynd.xlsx", "A 3221-2022")</f>
         <v/>
       </c>
       <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor/A 1793-2025 karta.png", "A 1793-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor/A 3221-2022 karta.png", "A 3221-2022")</f>
         <v/>
       </c>
       <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor_geotiff/A 1793-2025 georefererad karta.tif", "A 1793-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor_geotiff/A 3221-2022 georefererad karta.tif", "A 3221-2022")</f>
         <v/>
       </c>
       <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomål/A 1793-2025 FSC-klagomål.docx", "A 1793-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomål/A 3221-2022 FSC-klagomål.docx", "A 3221-2022")</f>
         <v/>
       </c>
       <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomålsmail/A 1793-2025 FSC-klagomål mail.docx", "A 1793-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomålsmail/A 3221-2022 FSC-klagomål mail.docx", "A 3221-2022")</f>
         <v/>
       </c>
       <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsyn/A 1793-2025 tillsynsbegäran.docx", "A 1793-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsyn/A 3221-2022 tillsynsbegäran.docx", "A 3221-2022")</f>
         <v/>
       </c>
       <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsynsmail/A 1793-2025 tillsynsbegäran mail.docx", "A 1793-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsynsmail/A 3221-2022 tillsynsbegäran mail.docx", "A 3221-2022")</f>
         <v/>
       </c>
     </row>
@@ -2271,7 +2271,7 @@
         <v>45007</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2359,7 +2359,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 2533-2026</t>
+          <t>A 1793-2025</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2373,10 +2373,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>46037</v>
+        <v>45671</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2389,7 +2389,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>1.4</v>
+        <v>1.7</v>
       </c>
       <c r="J18" t="n">
         <v>1</v>
@@ -2422,42 +2422,42 @@
         <v>1</v>
       </c>
       <c r="T18" t="n">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="U18" t="n">
         <v>0</v>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Mistel</t>
         </is>
       </c>
       <c r="W18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/artfynd/A 2533-2026 artfynd.xlsx", "A 2533-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/artfynd/A 1793-2025 artfynd.xlsx", "A 1793-2025")</f>
         <v/>
       </c>
       <c r="X18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor/A 2533-2026 karta.png", "A 2533-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor/A 1793-2025 karta.png", "A 1793-2025")</f>
         <v/>
       </c>
       <c r="Y18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor_geotiff/A 2533-2026 georefererad karta.tif", "A 2533-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor_geotiff/A 1793-2025 georefererad karta.tif", "A 1793-2025")</f>
         <v/>
       </c>
       <c r="AA18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomål/A 2533-2026 FSC-klagomål.docx", "A 2533-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomål/A 1793-2025 FSC-klagomål.docx", "A 1793-2025")</f>
         <v/>
       </c>
       <c r="AB18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomålsmail/A 2533-2026 FSC-klagomål mail.docx", "A 2533-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomålsmail/A 1793-2025 FSC-klagomål mail.docx", "A 1793-2025")</f>
         <v/>
       </c>
       <c r="AC18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsyn/A 2533-2026 tillsynsbegäran.docx", "A 2533-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsyn/A 1793-2025 tillsynsbegäran.docx", "A 1793-2025")</f>
         <v/>
       </c>
       <c r="AD18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsynsmail/A 2533-2026 tillsynsbegäran mail.docx", "A 2533-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsynsmail/A 1793-2025 tillsynsbegäran mail.docx", "A 1793-2025")</f>
         <v/>
       </c>
     </row>
@@ -2481,7 +2481,7 @@
         <v>44670</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2554,7 +2554,7 @@
         <v>44802</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2610,7 +2610,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 3219-2022</t>
+          <t>A 50184-2023</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2624,10 +2624,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>44582</v>
+        <v>45208</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2640,7 +2640,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>0.5</v>
+        <v>10.8</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2683,7 +2683,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 63378-2025</t>
+          <t>A 2535-2026</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2697,10 +2697,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>46010</v>
+        <v>46037</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2713,7 +2713,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>4.8</v>
+        <v>1.6</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2756,7 +2756,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 2535-2026</t>
+          <t>A 56002-2024</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2770,10 +2770,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>46037</v>
+        <v>45623</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2786,7 +2786,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>1.6</v>
+        <v>3.4</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2829,7 +2829,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 50184-2023</t>
+          <t>A 37245-2025</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2843,10 +2843,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45208</v>
+        <v>45876</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2859,7 +2859,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>10.8</v>
+        <v>1.1</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2902,7 +2902,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 20399-2026</t>
+          <t>A 61217-2024</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2916,10 +2916,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>46139</v>
+        <v>45645</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2932,7 +2932,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2975,7 +2975,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 20398-2026</t>
+          <t>A 3222-2022</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2989,10 +2989,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>46139</v>
+        <v>44582</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3005,7 +3005,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>2.4</v>
+        <v>1.8</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -3048,7 +3048,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 55724-2024</t>
+          <t>A 63378-2025</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3062,10 +3062,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45622</v>
+        <v>46010</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3078,7 +3078,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>0.5</v>
+        <v>4.8</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -3121,7 +3121,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 20898-2026</t>
+          <t>A 20399-2026</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3135,10 +3135,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>46142</v>
+        <v>46139</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3151,7 +3151,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>3.6</v>
+        <v>0.9</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -3194,7 +3194,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 35955-2023</t>
+          <t>A 20398-2026</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3208,10 +3208,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45148</v>
+        <v>46139</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3224,7 +3224,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>1.1</v>
+        <v>2.4</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3267,7 +3267,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 37245-2025</t>
+          <t>A 20898-2026</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3281,10 +3281,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45876</v>
+        <v>46142</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3297,7 +3297,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>1.1</v>
+        <v>3.6</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3340,7 +3340,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 61217-2024</t>
+          <t>A 3219-2022</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3354,10 +3354,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45645</v>
+        <v>44582</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3370,7 +3370,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3413,7 +3413,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 56002-2024</t>
+          <t>A 60755-2024</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3427,10 +3427,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45623</v>
+        <v>45644</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3443,7 +3443,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>3.4</v>
+        <v>2.1</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3486,7 +3486,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 34073-2025</t>
+          <t>A 55724-2024</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3496,14 +3496,14 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45845</v>
+        <v>45622</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3516,7 +3516,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>2.9</v>
+        <v>0.5</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3559,7 +3559,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 60728-2022</t>
+          <t>A 34073-2025</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3569,14 +3569,14 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>44913</v>
+        <v>45845</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3589,7 +3589,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>1.2</v>
+        <v>2.9</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3632,7 +3632,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 3222-2022</t>
+          <t>A 35955-2023</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3646,10 +3646,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>44582</v>
+        <v>45148</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3662,7 +3662,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>1.8</v>
+        <v>1.1</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3705,7 +3705,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 33154-2026</t>
+          <t>A 60728-2022</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3719,10 +3719,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>46244</v>
+        <v>44913</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3734,13 +3734,8 @@
           <t>EKERÖ</t>
         </is>
       </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I36" t="n">
-        <v>3.5</v>
+        <v>1.2</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3783,7 +3778,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 60755-2024</t>
+          <t>A 33154-2026</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3797,10 +3792,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45644</v>
+        <v>46244</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3812,8 +3807,13 @@
           <t>EKERÖ</t>
         </is>
       </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I37" t="n">
-        <v>2.1</v>
+        <v>3.5</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3873,7 +3873,7 @@
         <v>46153</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>

--- a/Översikt EKERÖ.xlsx
+++ b/Översikt EKERÖ.xlsx
@@ -601,7 +601,7 @@
         <v>46241</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -728,7 +728,7 @@
         <v>44872</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -848,7 +848,7 @@
         <v>44974</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -963,7 +963,7 @@
         <v>45148</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1056,7 +1056,7 @@
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A 3218-2022</t>
+          <t>A 17520-2026</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1070,10 +1070,10 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>44582</v>
+        <v>46119</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1085,8 +1085,13 @@
           <t>EKERÖ</t>
         </is>
       </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I6" t="n">
-        <v>1.2</v>
+        <v>2.2</v>
       </c>
       <c r="J6" t="n">
         <v>1</v>
@@ -1095,13 +1100,13 @@
         <v>1</v>
       </c>
       <c r="L6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M6" t="n">
         <v>1</v>
       </c>
       <c r="N6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1110,21 +1115,130 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="R6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
       </c>
       <c r="T6" t="n">
+        <v>5</v>
+      </c>
+      <c r="U6" t="n">
+        <v>1</v>
+      </c>
+      <c r="V6" s="2" t="inlineStr">
+        <is>
+          <t>Läderbagge
+Blekticka
+Ekticka
+Kandelabersvamp
+Gulgrön kantmusseron</t>
+        </is>
+      </c>
+      <c r="W6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/artfynd/A 17520-2026 artfynd.xlsx", "A 17520-2026")</f>
+        <v/>
+      </c>
+      <c r="X6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor/A 17520-2026 karta.png", "A 17520-2026")</f>
+        <v/>
+      </c>
+      <c r="Y6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor_geotiff/A 17520-2026 georefererad karta.tif", "A 17520-2026")</f>
+        <v/>
+      </c>
+      <c r="AA6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomål/A 17520-2026 FSC-klagomål.docx", "A 17520-2026")</f>
+        <v/>
+      </c>
+      <c r="AB6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomålsmail/A 17520-2026 FSC-klagomål mail.docx", "A 17520-2026")</f>
+        <v/>
+      </c>
+      <c r="AC6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsyn/A 17520-2026 tillsynsbegäran.docx", "A 17520-2026")</f>
+        <v/>
+      </c>
+      <c r="AD6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsynsmail/A 17520-2026 tillsynsbegäran mail.docx", "A 17520-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7" ht="15" customHeight="1">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>A 3218-2022</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D7" s="1" t="n">
+        <v>44582</v>
+      </c>
+      <c r="E7" s="1" t="n">
+        <v>46302</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>EKERÖ</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="J7" t="n">
+        <v>1</v>
+      </c>
+      <c r="K7" t="n">
+        <v>1</v>
+      </c>
+      <c r="L7" t="n">
+        <v>1</v>
+      </c>
+      <c r="M7" t="n">
+        <v>1</v>
+      </c>
+      <c r="N7" t="n">
+        <v>1</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>3</v>
+      </c>
+      <c r="R7" t="n">
+        <v>2</v>
+      </c>
+      <c r="S7" t="n">
+        <v>5</v>
+      </c>
+      <c r="T7" t="n">
         <v>8</v>
       </c>
-      <c r="U6" t="n">
+      <c r="U7" t="n">
         <v>6</v>
       </c>
-      <c r="V6" s="2" t="inlineStr">
+      <c r="V7" s="2" t="inlineStr">
         <is>
           <t>Bombmurkla
 Gul lammticka
@@ -1133,146 +1247,32 @@
 Blåbär</t>
         </is>
       </c>
-      <c r="W6">
+      <c r="W7">
         <f>HYPERLINK("https://klasma.github.io/Logging_0125/artfynd/A 3218-2022 artfynd.xlsx", "A 3218-2022")</f>
         <v/>
       </c>
-      <c r="X6">
+      <c r="X7">
         <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor/A 3218-2022 karta.png", "A 3218-2022")</f>
         <v/>
       </c>
-      <c r="Y6">
+      <c r="Y7">
         <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor_geotiff/A 3218-2022 georefererad karta.tif", "A 3218-2022")</f>
         <v/>
       </c>
-      <c r="AA6">
+      <c r="AA7">
         <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomål/A 3218-2022 FSC-klagomål.docx", "A 3218-2022")</f>
         <v/>
       </c>
-      <c r="AB6">
+      <c r="AB7">
         <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomålsmail/A 3218-2022 FSC-klagomål mail.docx", "A 3218-2022")</f>
         <v/>
       </c>
-      <c r="AC6">
+      <c r="AC7">
         <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsyn/A 3218-2022 tillsynsbegäran.docx", "A 3218-2022")</f>
         <v/>
       </c>
-      <c r="AD6">
+      <c r="AD7">
         <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsynsmail/A 3218-2022 tillsynsbegäran mail.docx", "A 3218-2022")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="7" ht="15" customHeight="1">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>A 17520-2026</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D7" s="1" t="n">
-        <v>46119</v>
-      </c>
-      <c r="E7" s="1" t="n">
-        <v>46301</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>EKERÖ</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
-      <c r="I7" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="J7" t="n">
-        <v>1</v>
-      </c>
-      <c r="K7" t="n">
-        <v>1</v>
-      </c>
-      <c r="L7" t="n">
-        <v>3</v>
-      </c>
-      <c r="M7" t="n">
-        <v>1</v>
-      </c>
-      <c r="N7" t="n">
-        <v>0</v>
-      </c>
-      <c r="O7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>4</v>
-      </c>
-      <c r="R7" t="n">
-        <v>1</v>
-      </c>
-      <c r="S7" t="n">
-        <v>5</v>
-      </c>
-      <c r="T7" t="n">
-        <v>5</v>
-      </c>
-      <c r="U7" t="n">
-        <v>1</v>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>Läderbagge
-Blekticka
-Ekticka
-Kandelabersvamp
-Gulgrön kantmusseron</t>
-        </is>
-      </c>
-      <c r="W7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/artfynd/A 17520-2026 artfynd.xlsx", "A 17520-2026")</f>
-        <v/>
-      </c>
-      <c r="X7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor/A 17520-2026 karta.png", "A 17520-2026")</f>
-        <v/>
-      </c>
-      <c r="Y7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor_geotiff/A 17520-2026 georefererad karta.tif", "A 17520-2026")</f>
-        <v/>
-      </c>
-      <c r="AA7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomål/A 17520-2026 FSC-klagomål.docx", "A 17520-2026")</f>
-        <v/>
-      </c>
-      <c r="AB7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomålsmail/A 17520-2026 FSC-klagomål mail.docx", "A 17520-2026")</f>
-        <v/>
-      </c>
-      <c r="AC7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsyn/A 17520-2026 tillsynsbegäran.docx", "A 17520-2026")</f>
-        <v/>
-      </c>
-      <c r="AD7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsynsmail/A 17520-2026 tillsynsbegäran mail.docx", "A 17520-2026")</f>
         <v/>
       </c>
     </row>
@@ -1296,7 +1296,7 @@
         <v>46241</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1409,7 +1409,7 @@
         <v>44634</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1499,7 +1499,7 @@
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 49131-2025</t>
+          <t>A 13237-2023</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1513,10 +1513,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>45937</v>
+        <v>45002</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1528,20 +1528,25 @@
           <t>EKERÖ</t>
         </is>
       </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I10" t="n">
-        <v>0.9</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N10" t="n">
         <v>0</v>
@@ -1553,165 +1558,160 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="R10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
         <v>3</v>
       </c>
       <c r="T10" t="n">
+        <v>7</v>
+      </c>
+      <c r="U10" t="n">
+        <v>0</v>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
+        <is>
+          <t>Tallticka
+Granbarkgnagare
+Grönpyrola</t>
+        </is>
+      </c>
+      <c r="W10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/artfynd/A 13237-2023 artfynd.xlsx", "A 13237-2023")</f>
+        <v/>
+      </c>
+      <c r="X10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor/A 13237-2023 karta.png", "A 13237-2023")</f>
+        <v/>
+      </c>
+      <c r="Y10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor_geotiff/A 13237-2023 georefererad karta.tif", "A 13237-2023")</f>
+        <v/>
+      </c>
+      <c r="AA10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomål/A 13237-2023 FSC-klagomål.docx", "A 13237-2023")</f>
+        <v/>
+      </c>
+      <c r="AB10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomålsmail/A 13237-2023 FSC-klagomål mail.docx", "A 13237-2023")</f>
+        <v/>
+      </c>
+      <c r="AC10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsyn/A 13237-2023 tillsynsbegäran.docx", "A 13237-2023")</f>
+        <v/>
+      </c>
+      <c r="AD10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsynsmail/A 13237-2023 tillsynsbegäran mail.docx", "A 13237-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11" ht="15" customHeight="1">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>A 49131-2025</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D11" s="1" t="n">
+        <v>45937</v>
+      </c>
+      <c r="E11" s="1" t="n">
+        <v>46302</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>EKERÖ</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" t="n">
+        <v>2</v>
+      </c>
+      <c r="M11" t="n">
+        <v>1</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" t="n">
         <v>3</v>
       </c>
-      <c r="U10" t="n">
+      <c r="R11" t="n">
+        <v>1</v>
+      </c>
+      <c r="S11" t="n">
         <v>3</v>
       </c>
-      <c r="V10" s="2" t="inlineStr">
+      <c r="T11" t="n">
+        <v>3</v>
+      </c>
+      <c r="U11" t="n">
+        <v>3</v>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
         <is>
           <t>Jättemusseron
 Motaggsvamp
 Svartvit taggsvamp</t>
         </is>
       </c>
-      <c r="W10">
+      <c r="W11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0125/artfynd/A 49131-2025 artfynd.xlsx", "A 49131-2025")</f>
         <v/>
       </c>
-      <c r="X10">
+      <c r="X11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor/A 49131-2025 karta.png", "A 49131-2025")</f>
         <v/>
       </c>
-      <c r="Y10">
+      <c r="Y11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor_geotiff/A 49131-2025 georefererad karta.tif", "A 49131-2025")</f>
         <v/>
       </c>
-      <c r="AA10">
+      <c r="AA11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomål/A 49131-2025 FSC-klagomål.docx", "A 49131-2025")</f>
         <v/>
       </c>
-      <c r="AB10">
+      <c r="AB11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomålsmail/A 49131-2025 FSC-klagomål mail.docx", "A 49131-2025")</f>
         <v/>
       </c>
-      <c r="AC10">
+      <c r="AC11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsyn/A 49131-2025 tillsynsbegäran.docx", "A 49131-2025")</f>
         <v/>
       </c>
-      <c r="AD10">
+      <c r="AD11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsynsmail/A 49131-2025 tillsynsbegäran mail.docx", "A 49131-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="11" ht="15" customHeight="1">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>A 13237-2023</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D11" s="1" t="n">
-        <v>45002</v>
-      </c>
-      <c r="E11" s="1" t="n">
-        <v>46301</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>EKERÖ</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
-      <c r="I11" t="n">
-        <v>9.300000000000001</v>
-      </c>
-      <c r="J11" t="n">
-        <v>0</v>
-      </c>
-      <c r="K11" t="n">
-        <v>2</v>
-      </c>
-      <c r="L11" t="n">
-        <v>1</v>
-      </c>
-      <c r="M11" t="n">
-        <v>0</v>
-      </c>
-      <c r="N11" t="n">
-        <v>0</v>
-      </c>
-      <c r="O11" t="n">
-        <v>0</v>
-      </c>
-      <c r="P11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>1</v>
-      </c>
-      <c r="R11" t="n">
-        <v>0</v>
-      </c>
-      <c r="S11" t="n">
-        <v>3</v>
-      </c>
-      <c r="T11" t="n">
-        <v>7</v>
-      </c>
-      <c r="U11" t="n">
-        <v>0</v>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
-        <is>
-          <t>Tallticka
-Granbarkgnagare
-Grönpyrola</t>
-        </is>
-      </c>
-      <c r="W11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/artfynd/A 13237-2023 artfynd.xlsx", "A 13237-2023")</f>
-        <v/>
-      </c>
-      <c r="X11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor/A 13237-2023 karta.png", "A 13237-2023")</f>
-        <v/>
-      </c>
-      <c r="Y11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor_geotiff/A 13237-2023 georefererad karta.tif", "A 13237-2023")</f>
-        <v/>
-      </c>
-      <c r="AA11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomål/A 13237-2023 FSC-klagomål.docx", "A 13237-2023")</f>
-        <v/>
-      </c>
-      <c r="AB11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomålsmail/A 13237-2023 FSC-klagomål mail.docx", "A 13237-2023")</f>
-        <v/>
-      </c>
-      <c r="AC11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsyn/A 13237-2023 tillsynsbegäran.docx", "A 13237-2023")</f>
-        <v/>
-      </c>
-      <c r="AD11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsynsmail/A 13237-2023 tillsynsbegäran mail.docx", "A 13237-2023")</f>
         <v/>
       </c>
     </row>
@@ -1735,7 +1735,7 @@
         <v>45209</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1850,7 +1850,7 @@
         <v>45170</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1956,7 +1956,7 @@
         <v>44646</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2044,7 +2044,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 2533-2026</t>
+          <t>A 3221-2022</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2058,10 +2058,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>46037</v>
+        <v>44582</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2074,13 +2074,13 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>1.4</v>
+        <v>0.5</v>
       </c>
       <c r="J15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L15" t="n">
         <v>0</v>
@@ -2110,46 +2110,46 @@
         <v>1</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/artfynd/A 2533-2026 artfynd.xlsx", "A 2533-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/artfynd/A 3221-2022 artfynd.xlsx", "A 3221-2022")</f>
         <v/>
       </c>
       <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor/A 2533-2026 karta.png", "A 2533-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor/A 3221-2022 karta.png", "A 3221-2022")</f>
         <v/>
       </c>
       <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor_geotiff/A 2533-2026 georefererad karta.tif", "A 2533-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor_geotiff/A 3221-2022 georefererad karta.tif", "A 3221-2022")</f>
         <v/>
       </c>
       <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomål/A 2533-2026 FSC-klagomål.docx", "A 2533-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomål/A 3221-2022 FSC-klagomål.docx", "A 3221-2022")</f>
         <v/>
       </c>
       <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomålsmail/A 2533-2026 FSC-klagomål mail.docx", "A 2533-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomålsmail/A 3221-2022 FSC-klagomål mail.docx", "A 3221-2022")</f>
         <v/>
       </c>
       <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsyn/A 2533-2026 tillsynsbegäran.docx", "A 2533-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsyn/A 3221-2022 tillsynsbegäran.docx", "A 3221-2022")</f>
         <v/>
       </c>
       <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsynsmail/A 2533-2026 tillsynsbegäran mail.docx", "A 2533-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsynsmail/A 3221-2022 tillsynsbegäran mail.docx", "A 3221-2022")</f>
         <v/>
       </c>
     </row>
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 3221-2022</t>
+          <t>A 13794-2023</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2163,10 +2163,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>44582</v>
+        <v>45007</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2179,16 +2179,16 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>0.5</v>
+        <v>4.8</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M16" t="n">
         <v>0</v>
@@ -2203,7 +2203,7 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R16" t="n">
         <v>0</v>
@@ -2215,46 +2215,46 @@
         <v>1</v>
       </c>
       <c r="U16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/artfynd/A 3221-2022 artfynd.xlsx", "A 3221-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/artfynd/A 13794-2023 artfynd.xlsx", "A 13794-2023")</f>
         <v/>
       </c>
       <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor/A 3221-2022 karta.png", "A 3221-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor/A 13794-2023 karta.png", "A 13794-2023")</f>
         <v/>
       </c>
       <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor_geotiff/A 3221-2022 georefererad karta.tif", "A 3221-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor_geotiff/A 13794-2023 georefererad karta.tif", "A 13794-2023")</f>
         <v/>
       </c>
       <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomål/A 3221-2022 FSC-klagomål.docx", "A 3221-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomål/A 13794-2023 FSC-klagomål.docx", "A 13794-2023")</f>
         <v/>
       </c>
       <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomålsmail/A 3221-2022 FSC-klagomål mail.docx", "A 3221-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomålsmail/A 13794-2023 FSC-klagomål mail.docx", "A 13794-2023")</f>
         <v/>
       </c>
       <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsyn/A 3221-2022 tillsynsbegäran.docx", "A 3221-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsyn/A 13794-2023 tillsynsbegäran.docx", "A 13794-2023")</f>
         <v/>
       </c>
       <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsynsmail/A 3221-2022 tillsynsbegäran mail.docx", "A 3221-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsynsmail/A 13794-2023 tillsynsbegäran mail.docx", "A 13794-2023")</f>
         <v/>
       </c>
     </row>
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 13794-2023</t>
+          <t>A 2533-2026</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2268,10 +2268,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45007</v>
+        <v>46037</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2284,16 +2284,16 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>4.8</v>
+        <v>1.4</v>
       </c>
       <c r="J17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K17" t="n">
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
         <v>0</v>
@@ -2308,7 +2308,7 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
         <v>0</v>
@@ -2324,35 +2324,35 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/artfynd/A 13794-2023 artfynd.xlsx", "A 13794-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/artfynd/A 2533-2026 artfynd.xlsx", "A 2533-2026")</f>
         <v/>
       </c>
       <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor/A 13794-2023 karta.png", "A 13794-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor/A 2533-2026 karta.png", "A 2533-2026")</f>
         <v/>
       </c>
       <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor_geotiff/A 13794-2023 georefererad karta.tif", "A 13794-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor_geotiff/A 2533-2026 georefererad karta.tif", "A 2533-2026")</f>
         <v/>
       </c>
       <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomål/A 13794-2023 FSC-klagomål.docx", "A 13794-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomål/A 2533-2026 FSC-klagomål.docx", "A 2533-2026")</f>
         <v/>
       </c>
       <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomålsmail/A 13794-2023 FSC-klagomål mail.docx", "A 13794-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomålsmail/A 2533-2026 FSC-klagomål mail.docx", "A 2533-2026")</f>
         <v/>
       </c>
       <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsyn/A 13794-2023 tillsynsbegäran.docx", "A 13794-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsyn/A 2533-2026 tillsynsbegäran.docx", "A 2533-2026")</f>
         <v/>
       </c>
       <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsynsmail/A 13794-2023 tillsynsbegäran mail.docx", "A 13794-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsynsmail/A 2533-2026 tillsynsbegäran mail.docx", "A 2533-2026")</f>
         <v/>
       </c>
     </row>
@@ -2376,7 +2376,7 @@
         <v>45671</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2481,7 +2481,7 @@
         <v>44670</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2554,7 +2554,7 @@
         <v>44802</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2610,7 +2610,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 50184-2023</t>
+          <t>A 3219-2022</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2624,10 +2624,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45208</v>
+        <v>44582</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2640,7 +2640,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>10.8</v>
+        <v>0.5</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2700,7 +2700,7 @@
         <v>46037</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2756,7 +2756,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 56002-2024</t>
+          <t>A 50184-2023</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2770,10 +2770,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45623</v>
+        <v>45208</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2786,7 +2786,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>3.4</v>
+        <v>10.8</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2846,7 +2846,7 @@
         <v>45876</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2902,7 +2902,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 61217-2024</t>
+          <t>A 20399-2026</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2916,10 +2916,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45645</v>
+        <v>46139</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2932,7 +2932,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2975,7 +2975,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 3222-2022</t>
+          <t>A 20398-2026</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2989,10 +2989,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>44582</v>
+        <v>46139</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3005,7 +3005,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>1.8</v>
+        <v>2.4</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -3065,7 +3065,7 @@
         <v>46010</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3121,7 +3121,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 20399-2026</t>
+          <t>A 20898-2026</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3135,10 +3135,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>46139</v>
+        <v>46142</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3151,7 +3151,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>0.9</v>
+        <v>3.6</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -3194,7 +3194,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 20398-2026</t>
+          <t>A 34073-2025</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3204,14 +3204,14 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>46139</v>
+        <v>45845</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3224,7 +3224,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>2.4</v>
+        <v>2.9</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3267,7 +3267,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 20898-2026</t>
+          <t>A 55724-2024</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3281,10 +3281,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>46142</v>
+        <v>45622</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3297,7 +3297,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>3.6</v>
+        <v>0.5</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3340,7 +3340,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 3219-2022</t>
+          <t>A 35955-2023</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3354,10 +3354,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>44582</v>
+        <v>45148</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3370,7 +3370,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>0.5</v>
+        <v>1.1</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3413,7 +3413,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 60755-2024</t>
+          <t>A 61217-2024</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3427,10 +3427,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45644</v>
+        <v>45645</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3443,7 +3443,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>2.1</v>
+        <v>0.8</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3486,7 +3486,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 55724-2024</t>
+          <t>A 56002-2024</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3500,10 +3500,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45622</v>
+        <v>45623</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3516,7 +3516,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>0.5</v>
+        <v>3.4</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3559,7 +3559,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 34073-2025</t>
+          <t>A 60728-2022</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3569,14 +3569,14 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45845</v>
+        <v>44913</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3589,7 +3589,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>2.9</v>
+        <v>1.2</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3632,7 +3632,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 35955-2023</t>
+          <t>A 3222-2022</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3646,10 +3646,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45148</v>
+        <v>44582</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3662,7 +3662,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>1.1</v>
+        <v>1.8</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3705,7 +3705,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 60728-2022</t>
+          <t>A 33154-2026</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3719,10 +3719,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>44913</v>
+        <v>46244</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3734,8 +3734,13 @@
           <t>EKERÖ</t>
         </is>
       </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I36" t="n">
-        <v>1.2</v>
+        <v>3.5</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3778,7 +3783,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 33154-2026</t>
+          <t>A 60755-2024</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3792,10 +3797,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>46244</v>
+        <v>45644</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3807,13 +3812,8 @@
           <t>EKERÖ</t>
         </is>
       </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I37" t="n">
-        <v>3.5</v>
+        <v>2.1</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3873,7 +3873,7 @@
         <v>46153</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>

--- a/Översikt EKERÖ.xlsx
+++ b/Översikt EKERÖ.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE38"/>
+  <dimension ref="A1:AE39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="0" ht="15" customHeight="1"/>
@@ -601,7 +601,7 @@
         <v>46241</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -728,7 +728,7 @@
         <v>44872</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -848,7 +848,7 @@
         <v>44974</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -963,7 +963,7 @@
         <v>45148</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1056,7 +1056,7 @@
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A 17520-2026</t>
+          <t>A 3218-2022</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1070,10 +1070,10 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>46119</v>
+        <v>44582</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1085,13 +1085,8 @@
           <t>EKERÖ</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I6" t="n">
-        <v>2.2</v>
+        <v>1.2</v>
       </c>
       <c r="J6" t="n">
         <v>1</v>
@@ -1100,36 +1095,150 @@
         <v>1</v>
       </c>
       <c r="L6" t="n">
+        <v>1</v>
+      </c>
+      <c r="M6" t="n">
+        <v>1</v>
+      </c>
+      <c r="N6" t="n">
+        <v>1</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" t="n">
         <v>3</v>
       </c>
-      <c r="M6" t="n">
-        <v>1</v>
-      </c>
-      <c r="N6" t="n">
-        <v>0</v>
-      </c>
-      <c r="O6" t="n">
-        <v>0</v>
-      </c>
-      <c r="P6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>4</v>
-      </c>
       <c r="R6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
       </c>
       <c r="T6" t="n">
+        <v>8</v>
+      </c>
+      <c r="U6" t="n">
+        <v>6</v>
+      </c>
+      <c r="V6" s="2" t="inlineStr">
+        <is>
+          <t>Bombmurkla
+Gul lammticka
+Fyrflikig jordstjärna
+Kamjordstjärna
+Blåbär</t>
+        </is>
+      </c>
+      <c r="W6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/artfynd/A 3218-2022 artfynd.xlsx", "A 3218-2022")</f>
+        <v/>
+      </c>
+      <c r="X6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor/A 3218-2022 karta.png", "A 3218-2022")</f>
+        <v/>
+      </c>
+      <c r="Y6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor_geotiff/A 3218-2022 georefererad karta.tif", "A 3218-2022")</f>
+        <v/>
+      </c>
+      <c r="AA6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomål/A 3218-2022 FSC-klagomål.docx", "A 3218-2022")</f>
+        <v/>
+      </c>
+      <c r="AB6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomålsmail/A 3218-2022 FSC-klagomål mail.docx", "A 3218-2022")</f>
+        <v/>
+      </c>
+      <c r="AC6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsyn/A 3218-2022 tillsynsbegäran.docx", "A 3218-2022")</f>
+        <v/>
+      </c>
+      <c r="AD6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsynsmail/A 3218-2022 tillsynsbegäran mail.docx", "A 3218-2022")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7" ht="15" customHeight="1">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>A 17520-2026</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D7" s="1" t="n">
+        <v>46119</v>
+      </c>
+      <c r="E7" s="1" t="n">
+        <v>46303</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>EKERÖ</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="J7" t="n">
+        <v>1</v>
+      </c>
+      <c r="K7" t="n">
+        <v>1</v>
+      </c>
+      <c r="L7" t="n">
+        <v>3</v>
+      </c>
+      <c r="M7" t="n">
+        <v>1</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>4</v>
+      </c>
+      <c r="R7" t="n">
+        <v>1</v>
+      </c>
+      <c r="S7" t="n">
         <v>5</v>
       </c>
-      <c r="U6" t="n">
-        <v>1</v>
-      </c>
-      <c r="V6" s="2" t="inlineStr">
+      <c r="T7" t="n">
+        <v>5</v>
+      </c>
+      <c r="U7" t="n">
+        <v>1</v>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
         <is>
           <t>Läderbagge
 Blekticka
@@ -1138,141 +1247,32 @@
 Gulgrön kantmusseron</t>
         </is>
       </c>
-      <c r="W6">
+      <c r="W7">
         <f>HYPERLINK("https://klasma.github.io/Logging_0125/artfynd/A 17520-2026 artfynd.xlsx", "A 17520-2026")</f>
         <v/>
       </c>
-      <c r="X6">
+      <c r="X7">
         <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor/A 17520-2026 karta.png", "A 17520-2026")</f>
         <v/>
       </c>
-      <c r="Y6">
+      <c r="Y7">
         <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor_geotiff/A 17520-2026 georefererad karta.tif", "A 17520-2026")</f>
         <v/>
       </c>
-      <c r="AA6">
+      <c r="AA7">
         <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomål/A 17520-2026 FSC-klagomål.docx", "A 17520-2026")</f>
         <v/>
       </c>
-      <c r="AB6">
+      <c r="AB7">
         <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomålsmail/A 17520-2026 FSC-klagomål mail.docx", "A 17520-2026")</f>
         <v/>
       </c>
-      <c r="AC6">
+      <c r="AC7">
         <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsyn/A 17520-2026 tillsynsbegäran.docx", "A 17520-2026")</f>
         <v/>
       </c>
-      <c r="AD6">
+      <c r="AD7">
         <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsynsmail/A 17520-2026 tillsynsbegäran mail.docx", "A 17520-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="7" ht="15" customHeight="1">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>A 3218-2022</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D7" s="1" t="n">
-        <v>44582</v>
-      </c>
-      <c r="E7" s="1" t="n">
-        <v>46302</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>EKERÖ</t>
-        </is>
-      </c>
-      <c r="I7" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="J7" t="n">
-        <v>1</v>
-      </c>
-      <c r="K7" t="n">
-        <v>1</v>
-      </c>
-      <c r="L7" t="n">
-        <v>1</v>
-      </c>
-      <c r="M7" t="n">
-        <v>1</v>
-      </c>
-      <c r="N7" t="n">
-        <v>1</v>
-      </c>
-      <c r="O7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>3</v>
-      </c>
-      <c r="R7" t="n">
-        <v>2</v>
-      </c>
-      <c r="S7" t="n">
-        <v>5</v>
-      </c>
-      <c r="T7" t="n">
-        <v>8</v>
-      </c>
-      <c r="U7" t="n">
-        <v>6</v>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>Bombmurkla
-Gul lammticka
-Fyrflikig jordstjärna
-Kamjordstjärna
-Blåbär</t>
-        </is>
-      </c>
-      <c r="W7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/artfynd/A 3218-2022 artfynd.xlsx", "A 3218-2022")</f>
-        <v/>
-      </c>
-      <c r="X7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor/A 3218-2022 karta.png", "A 3218-2022")</f>
-        <v/>
-      </c>
-      <c r="Y7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor_geotiff/A 3218-2022 georefererad karta.tif", "A 3218-2022")</f>
-        <v/>
-      </c>
-      <c r="AA7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomål/A 3218-2022 FSC-klagomål.docx", "A 3218-2022")</f>
-        <v/>
-      </c>
-      <c r="AB7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomålsmail/A 3218-2022 FSC-klagomål mail.docx", "A 3218-2022")</f>
-        <v/>
-      </c>
-      <c r="AC7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsyn/A 3218-2022 tillsynsbegäran.docx", "A 3218-2022")</f>
-        <v/>
-      </c>
-      <c r="AD7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsynsmail/A 3218-2022 tillsynsbegäran mail.docx", "A 3218-2022")</f>
         <v/>
       </c>
     </row>
@@ -1296,7 +1296,7 @@
         <v>46241</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1409,7 +1409,7 @@
         <v>44634</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1499,7 +1499,7 @@
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 13237-2023</t>
+          <t>A 49131-2025</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1513,10 +1513,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>45002</v>
+        <v>45937</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1528,25 +1528,20 @@
           <t>EKERÖ</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I10" t="n">
-        <v>9.300000000000001</v>
+        <v>0.9</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
       </c>
       <c r="K10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" t="n">
         <v>2</v>
       </c>
-      <c r="L10" t="n">
-        <v>1</v>
-      </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N10" t="n">
         <v>0</v>
@@ -1558,160 +1553,165 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S10" t="n">
         <v>3</v>
       </c>
       <c r="T10" t="n">
+        <v>3</v>
+      </c>
+      <c r="U10" t="n">
+        <v>3</v>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
+        <is>
+          <t>Jättemusseron
+Motaggsvamp
+Svartvit taggsvamp</t>
+        </is>
+      </c>
+      <c r="W10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/artfynd/A 49131-2025 artfynd.xlsx", "A 49131-2025")</f>
+        <v/>
+      </c>
+      <c r="X10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor/A 49131-2025 karta.png", "A 49131-2025")</f>
+        <v/>
+      </c>
+      <c r="Y10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor_geotiff/A 49131-2025 georefererad karta.tif", "A 49131-2025")</f>
+        <v/>
+      </c>
+      <c r="AA10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomål/A 49131-2025 FSC-klagomål.docx", "A 49131-2025")</f>
+        <v/>
+      </c>
+      <c r="AB10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomålsmail/A 49131-2025 FSC-klagomål mail.docx", "A 49131-2025")</f>
+        <v/>
+      </c>
+      <c r="AC10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsyn/A 49131-2025 tillsynsbegäran.docx", "A 49131-2025")</f>
+        <v/>
+      </c>
+      <c r="AD10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsynsmail/A 49131-2025 tillsynsbegäran mail.docx", "A 49131-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11" ht="15" customHeight="1">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>A 13237-2023</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D11" s="1" t="n">
+        <v>45002</v>
+      </c>
+      <c r="E11" s="1" t="n">
+        <v>46303</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>EKERÖ</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" t="n">
+        <v>2</v>
+      </c>
+      <c r="L11" t="n">
+        <v>1</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>1</v>
+      </c>
+      <c r="R11" t="n">
+        <v>0</v>
+      </c>
+      <c r="S11" t="n">
+        <v>3</v>
+      </c>
+      <c r="T11" t="n">
         <v>7</v>
       </c>
-      <c r="U10" t="n">
-        <v>0</v>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
+      <c r="U11" t="n">
+        <v>0</v>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
         <is>
           <t>Tallticka
 Granbarkgnagare
 Grönpyrola</t>
         </is>
       </c>
-      <c r="W10">
+      <c r="W11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0125/artfynd/A 13237-2023 artfynd.xlsx", "A 13237-2023")</f>
         <v/>
       </c>
-      <c r="X10">
+      <c r="X11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor/A 13237-2023 karta.png", "A 13237-2023")</f>
         <v/>
       </c>
-      <c r="Y10">
+      <c r="Y11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor_geotiff/A 13237-2023 georefererad karta.tif", "A 13237-2023")</f>
         <v/>
       </c>
-      <c r="AA10">
+      <c r="AA11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomål/A 13237-2023 FSC-klagomål.docx", "A 13237-2023")</f>
         <v/>
       </c>
-      <c r="AB10">
+      <c r="AB11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomålsmail/A 13237-2023 FSC-klagomål mail.docx", "A 13237-2023")</f>
         <v/>
       </c>
-      <c r="AC10">
+      <c r="AC11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsyn/A 13237-2023 tillsynsbegäran.docx", "A 13237-2023")</f>
         <v/>
       </c>
-      <c r="AD10">
+      <c r="AD11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsynsmail/A 13237-2023 tillsynsbegäran mail.docx", "A 13237-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="11" ht="15" customHeight="1">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>A 49131-2025</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D11" s="1" t="n">
-        <v>45937</v>
-      </c>
-      <c r="E11" s="1" t="n">
-        <v>46302</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>EKERÖ</t>
-        </is>
-      </c>
-      <c r="I11" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="J11" t="n">
-        <v>0</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L11" t="n">
-        <v>2</v>
-      </c>
-      <c r="M11" t="n">
-        <v>1</v>
-      </c>
-      <c r="N11" t="n">
-        <v>0</v>
-      </c>
-      <c r="O11" t="n">
-        <v>0</v>
-      </c>
-      <c r="P11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>3</v>
-      </c>
-      <c r="R11" t="n">
-        <v>1</v>
-      </c>
-      <c r="S11" t="n">
-        <v>3</v>
-      </c>
-      <c r="T11" t="n">
-        <v>3</v>
-      </c>
-      <c r="U11" t="n">
-        <v>3</v>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
-        <is>
-          <t>Jättemusseron
-Motaggsvamp
-Svartvit taggsvamp</t>
-        </is>
-      </c>
-      <c r="W11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/artfynd/A 49131-2025 artfynd.xlsx", "A 49131-2025")</f>
-        <v/>
-      </c>
-      <c r="X11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor/A 49131-2025 karta.png", "A 49131-2025")</f>
-        <v/>
-      </c>
-      <c r="Y11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor_geotiff/A 49131-2025 georefererad karta.tif", "A 49131-2025")</f>
-        <v/>
-      </c>
-      <c r="AA11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomål/A 49131-2025 FSC-klagomål.docx", "A 49131-2025")</f>
-        <v/>
-      </c>
-      <c r="AB11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomålsmail/A 49131-2025 FSC-klagomål mail.docx", "A 49131-2025")</f>
-        <v/>
-      </c>
-      <c r="AC11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsyn/A 49131-2025 tillsynsbegäran.docx", "A 49131-2025")</f>
-        <v/>
-      </c>
-      <c r="AD11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsynsmail/A 49131-2025 tillsynsbegäran mail.docx", "A 49131-2025")</f>
         <v/>
       </c>
     </row>
@@ -1735,7 +1735,7 @@
         <v>45209</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1850,7 +1850,7 @@
         <v>45170</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1956,7 +1956,7 @@
         <v>44646</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2044,7 +2044,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 3221-2022</t>
+          <t>A 1793-2025</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2058,10 +2058,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>44582</v>
+        <v>45671</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2074,13 +2074,13 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>0.5</v>
+        <v>1.7</v>
       </c>
       <c r="J15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L15" t="n">
         <v>0</v>
@@ -2107,49 +2107,49 @@
         <v>1</v>
       </c>
       <c r="T15" t="n">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="U15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Mistel</t>
         </is>
       </c>
       <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/artfynd/A 3221-2022 artfynd.xlsx", "A 3221-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/artfynd/A 1793-2025 artfynd.xlsx", "A 1793-2025")</f>
         <v/>
       </c>
       <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor/A 3221-2022 karta.png", "A 3221-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor/A 1793-2025 karta.png", "A 1793-2025")</f>
         <v/>
       </c>
       <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor_geotiff/A 3221-2022 georefererad karta.tif", "A 3221-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor_geotiff/A 1793-2025 georefererad karta.tif", "A 1793-2025")</f>
         <v/>
       </c>
       <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomål/A 3221-2022 FSC-klagomål.docx", "A 3221-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomål/A 1793-2025 FSC-klagomål.docx", "A 1793-2025")</f>
         <v/>
       </c>
       <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomålsmail/A 3221-2022 FSC-klagomål mail.docx", "A 3221-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomålsmail/A 1793-2025 FSC-klagomål mail.docx", "A 1793-2025")</f>
         <v/>
       </c>
       <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsyn/A 3221-2022 tillsynsbegäran.docx", "A 3221-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsyn/A 1793-2025 tillsynsbegäran.docx", "A 1793-2025")</f>
         <v/>
       </c>
       <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsynsmail/A 3221-2022 tillsynsbegäran mail.docx", "A 3221-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsynsmail/A 1793-2025 tillsynsbegäran mail.docx", "A 1793-2025")</f>
         <v/>
       </c>
     </row>
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 13794-2023</t>
+          <t>A 3221-2022</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2163,10 +2163,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45007</v>
+        <v>44582</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2179,16 +2179,16 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>4.8</v>
+        <v>0.5</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
         <v>0</v>
@@ -2203,7 +2203,7 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
         <v>0</v>
@@ -2215,39 +2215,39 @@
         <v>1</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/artfynd/A 13794-2023 artfynd.xlsx", "A 13794-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/artfynd/A 3221-2022 artfynd.xlsx", "A 3221-2022")</f>
         <v/>
       </c>
       <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor/A 13794-2023 karta.png", "A 13794-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor/A 3221-2022 karta.png", "A 3221-2022")</f>
         <v/>
       </c>
       <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor_geotiff/A 13794-2023 georefererad karta.tif", "A 13794-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor_geotiff/A 3221-2022 georefererad karta.tif", "A 3221-2022")</f>
         <v/>
       </c>
       <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomål/A 13794-2023 FSC-klagomål.docx", "A 13794-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomål/A 3221-2022 FSC-klagomål.docx", "A 3221-2022")</f>
         <v/>
       </c>
       <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomålsmail/A 13794-2023 FSC-klagomål mail.docx", "A 13794-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomålsmail/A 3221-2022 FSC-klagomål mail.docx", "A 3221-2022")</f>
         <v/>
       </c>
       <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsyn/A 13794-2023 tillsynsbegäran.docx", "A 13794-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsyn/A 3221-2022 tillsynsbegäran.docx", "A 3221-2022")</f>
         <v/>
       </c>
       <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsynsmail/A 13794-2023 tillsynsbegäran mail.docx", "A 13794-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsynsmail/A 3221-2022 tillsynsbegäran mail.docx", "A 3221-2022")</f>
         <v/>
       </c>
     </row>
@@ -2271,7 +2271,7 @@
         <v>46037</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2359,7 +2359,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 1793-2025</t>
+          <t>A 13794-2023</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2373,10 +2373,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45671</v>
+        <v>45007</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2389,16 +2389,16 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>1.7</v>
+        <v>4.8</v>
       </c>
       <c r="J18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K18" t="n">
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M18" t="n">
         <v>0</v>
@@ -2413,7 +2413,7 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R18" t="n">
         <v>0</v>
@@ -2422,42 +2422,42 @@
         <v>1</v>
       </c>
       <c r="T18" t="n">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="U18" t="n">
         <v>0</v>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>Mistel</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="W18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/artfynd/A 1793-2025 artfynd.xlsx", "A 1793-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/artfynd/A 13794-2023 artfynd.xlsx", "A 13794-2023")</f>
         <v/>
       </c>
       <c r="X18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor/A 1793-2025 karta.png", "A 1793-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor/A 13794-2023 karta.png", "A 13794-2023")</f>
         <v/>
       </c>
       <c r="Y18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor_geotiff/A 1793-2025 georefererad karta.tif", "A 1793-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor_geotiff/A 13794-2023 georefererad karta.tif", "A 13794-2023")</f>
         <v/>
       </c>
       <c r="AA18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomål/A 1793-2025 FSC-klagomål.docx", "A 1793-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomål/A 13794-2023 FSC-klagomål.docx", "A 13794-2023")</f>
         <v/>
       </c>
       <c r="AB18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomålsmail/A 1793-2025 FSC-klagomål mail.docx", "A 1793-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomålsmail/A 13794-2023 FSC-klagomål mail.docx", "A 13794-2023")</f>
         <v/>
       </c>
       <c r="AC18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsyn/A 1793-2025 tillsynsbegäran.docx", "A 1793-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsyn/A 13794-2023 tillsynsbegäran.docx", "A 13794-2023")</f>
         <v/>
       </c>
       <c r="AD18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsynsmail/A 1793-2025 tillsynsbegäran mail.docx", "A 1793-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsynsmail/A 13794-2023 tillsynsbegäran mail.docx", "A 13794-2023")</f>
         <v/>
       </c>
     </row>
@@ -2481,7 +2481,7 @@
         <v>44670</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2554,7 +2554,7 @@
         <v>44802</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2610,7 +2610,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 3219-2022</t>
+          <t>A 3222-2022</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2627,7 +2627,7 @@
         <v>44582</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2640,7 +2640,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>0.5</v>
+        <v>1.8</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2683,7 +2683,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 2535-2026</t>
+          <t>A 3219-2022</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2697,10 +2697,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>46037</v>
+        <v>44582</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2713,7 +2713,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>1.6</v>
+        <v>0.5</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2773,7 +2773,7 @@
         <v>45208</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2829,7 +2829,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 37245-2025</t>
+          <t>A 60755-2024</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2843,10 +2843,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45876</v>
+        <v>45644</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2859,7 +2859,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>1.1</v>
+        <v>2.1</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2902,7 +2902,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 20399-2026</t>
+          <t>A 55724-2024</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2916,10 +2916,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>46139</v>
+        <v>45622</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2932,7 +2932,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>0.9</v>
+        <v>0.5</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2975,7 +2975,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 20398-2026</t>
+          <t>A 37245-2025</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2989,10 +2989,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>46139</v>
+        <v>45876</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3005,7 +3005,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>2.4</v>
+        <v>1.1</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -3048,7 +3048,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 63378-2025</t>
+          <t>A 20399-2026</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3062,10 +3062,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>46010</v>
+        <v>46139</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3078,7 +3078,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>4.8</v>
+        <v>0.9</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -3121,7 +3121,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 20898-2026</t>
+          <t>A 56002-2024</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3135,10 +3135,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>46142</v>
+        <v>45623</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3151,7 +3151,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -3194,7 +3194,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 34073-2025</t>
+          <t>A 20398-2026</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3204,14 +3204,14 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45845</v>
+        <v>46139</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3224,7 +3224,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>2.9</v>
+        <v>2.4</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3267,7 +3267,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 55724-2024</t>
+          <t>A 20898-2026</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3281,10 +3281,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45622</v>
+        <v>46142</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3297,7 +3297,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>0.5</v>
+        <v>3.6</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3357,7 +3357,7 @@
         <v>45148</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3413,7 +3413,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 61217-2024</t>
+          <t>A 63378-2025</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3427,10 +3427,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45645</v>
+        <v>46010</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3443,7 +3443,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>0.8</v>
+        <v>4.8</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3486,7 +3486,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 56002-2024</t>
+          <t>A 34073-2025</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3496,14 +3496,14 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45623</v>
+        <v>45845</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3516,7 +3516,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>3.4</v>
+        <v>2.9</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3559,7 +3559,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 60728-2022</t>
+          <t>A 61217-2024</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3573,10 +3573,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>44913</v>
+        <v>45645</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3589,7 +3589,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>1.2</v>
+        <v>0.8</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3632,7 +3632,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 3222-2022</t>
+          <t>A 2535-2026</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3646,10 +3646,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>44582</v>
+        <v>46037</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3662,7 +3662,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>1.8</v>
+        <v>1.6</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3705,7 +3705,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 33154-2026</t>
+          <t>A 60728-2022</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3719,10 +3719,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>46244</v>
+        <v>44913</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3734,13 +3734,8 @@
           <t>EKERÖ</t>
         </is>
       </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I36" t="n">
-        <v>3.5</v>
+        <v>1.2</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3783,7 +3778,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 60755-2024</t>
+          <t>A 33154-2026</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3797,10 +3792,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45644</v>
+        <v>46244</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3812,8 +3807,13 @@
           <t>EKERÖ</t>
         </is>
       </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I37" t="n">
-        <v>2.1</v>
+        <v>3.5</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3853,78 +3853,156 @@
       </c>
       <c r="V37" s="2" t="inlineStr"/>
     </row>
-    <row r="38">
+    <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
+          <t>A 41699-2026</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D38" s="1" t="n">
+        <v>46301</v>
+      </c>
+      <c r="E38" s="1" t="n">
+        <v>46303</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>EKERÖ</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
+      <c r="I38" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="J38" t="n">
+        <v>0</v>
+      </c>
+      <c r="K38" t="n">
+        <v>0</v>
+      </c>
+      <c r="L38" t="n">
+        <v>0</v>
+      </c>
+      <c r="M38" t="n">
+        <v>0</v>
+      </c>
+      <c r="N38" t="n">
+        <v>0</v>
+      </c>
+      <c r="O38" t="n">
+        <v>0</v>
+      </c>
+      <c r="P38" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>0</v>
+      </c>
+      <c r="R38" t="n">
+        <v>0</v>
+      </c>
+      <c r="S38" t="n">
+        <v>0</v>
+      </c>
+      <c r="T38" t="n">
+        <v>0</v>
+      </c>
+      <c r="U38" t="n">
+        <v>0</v>
+      </c>
+      <c r="V38" s="2" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
           <t>S 1390-2026</t>
         </is>
       </c>
-      <c r="B38" t="inlineStr">
+      <c r="B39" t="inlineStr">
         <is>
           <t>samrådsanmälan</t>
         </is>
       </c>
-      <c r="C38" t="inlineStr">
+      <c r="C39" t="inlineStr">
         <is>
           <t>Annan skogsbruksåtgärd</t>
         </is>
       </c>
-      <c r="D38" s="1" t="n">
+      <c r="D39" s="1" t="n">
         <v>46153</v>
       </c>
-      <c r="E38" s="1" t="n">
-        <v>46302</v>
-      </c>
-      <c r="F38" t="inlineStr">
+      <c r="E39" s="1" t="n">
+        <v>46303</v>
+      </c>
+      <c r="F39" t="inlineStr">
         <is>
           <t>STOCKHOLMS LÄN</t>
         </is>
       </c>
-      <c r="G38" t="inlineStr">
+      <c r="G39" t="inlineStr">
         <is>
           <t>EKERÖ</t>
         </is>
       </c>
-      <c r="I38" t="n">
+      <c r="I39" t="n">
         <v>0.7</v>
       </c>
-      <c r="J38" t="n">
-        <v>0</v>
-      </c>
-      <c r="K38" t="n">
-        <v>0</v>
-      </c>
-      <c r="L38" t="n">
-        <v>0</v>
-      </c>
-      <c r="M38" t="n">
-        <v>0</v>
-      </c>
-      <c r="N38" t="n">
-        <v>0</v>
-      </c>
-      <c r="O38" t="n">
-        <v>0</v>
-      </c>
-      <c r="P38" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q38" t="n">
-        <v>0</v>
-      </c>
-      <c r="R38" t="n">
-        <v>0</v>
-      </c>
-      <c r="S38" t="n">
-        <v>0</v>
-      </c>
-      <c r="T38" t="n">
-        <v>0</v>
-      </c>
-      <c r="U38" t="n">
-        <v>0</v>
-      </c>
-      <c r="V38" s="2" t="inlineStr"/>
+      <c r="J39" t="n">
+        <v>0</v>
+      </c>
+      <c r="K39" t="n">
+        <v>0</v>
+      </c>
+      <c r="L39" t="n">
+        <v>0</v>
+      </c>
+      <c r="M39" t="n">
+        <v>0</v>
+      </c>
+      <c r="N39" t="n">
+        <v>0</v>
+      </c>
+      <c r="O39" t="n">
+        <v>0</v>
+      </c>
+      <c r="P39" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q39" t="n">
+        <v>0</v>
+      </c>
+      <c r="R39" t="n">
+        <v>0</v>
+      </c>
+      <c r="S39" t="n">
+        <v>0</v>
+      </c>
+      <c r="T39" t="n">
+        <v>0</v>
+      </c>
+      <c r="U39" t="n">
+        <v>0</v>
+      </c>
+      <c r="V39" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Översikt EKERÖ.xlsx
+++ b/Översikt EKERÖ.xlsx
@@ -601,7 +601,7 @@
         <v>46241</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -728,7 +728,7 @@
         <v>44872</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -848,7 +848,7 @@
         <v>44974</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -963,7 +963,7 @@
         <v>45148</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1073,7 +1073,7 @@
         <v>44582</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1182,7 +1182,7 @@
         <v>46119</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1296,7 +1296,7 @@
         <v>46241</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1409,7 +1409,7 @@
         <v>44634</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1499,7 +1499,7 @@
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 49131-2025</t>
+          <t>A 13237-2023</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1513,10 +1513,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>45937</v>
+        <v>45002</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1528,20 +1528,25 @@
           <t>EKERÖ</t>
         </is>
       </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I10" t="n">
-        <v>0.9</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N10" t="n">
         <v>0</v>
@@ -1553,165 +1558,160 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="R10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
         <v>3</v>
       </c>
       <c r="T10" t="n">
+        <v>7</v>
+      </c>
+      <c r="U10" t="n">
+        <v>0</v>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
+        <is>
+          <t>Tallticka
+Granbarkgnagare
+Grönpyrola</t>
+        </is>
+      </c>
+      <c r="W10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/artfynd/A 13237-2023 artfynd.xlsx", "A 13237-2023")</f>
+        <v/>
+      </c>
+      <c r="X10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor/A 13237-2023 karta.png", "A 13237-2023")</f>
+        <v/>
+      </c>
+      <c r="Y10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor_geotiff/A 13237-2023 georefererad karta.tif", "A 13237-2023")</f>
+        <v/>
+      </c>
+      <c r="AA10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomål/A 13237-2023 FSC-klagomål.docx", "A 13237-2023")</f>
+        <v/>
+      </c>
+      <c r="AB10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomålsmail/A 13237-2023 FSC-klagomål mail.docx", "A 13237-2023")</f>
+        <v/>
+      </c>
+      <c r="AC10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsyn/A 13237-2023 tillsynsbegäran.docx", "A 13237-2023")</f>
+        <v/>
+      </c>
+      <c r="AD10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsynsmail/A 13237-2023 tillsynsbegäran mail.docx", "A 13237-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11" ht="15" customHeight="1">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>A 49131-2025</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D11" s="1" t="n">
+        <v>45937</v>
+      </c>
+      <c r="E11" s="1" t="n">
+        <v>46304</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>EKERÖ</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" t="n">
+        <v>2</v>
+      </c>
+      <c r="M11" t="n">
+        <v>1</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" t="n">
         <v>3</v>
       </c>
-      <c r="U10" t="n">
+      <c r="R11" t="n">
+        <v>1</v>
+      </c>
+      <c r="S11" t="n">
         <v>3</v>
       </c>
-      <c r="V10" s="2" t="inlineStr">
+      <c r="T11" t="n">
+        <v>3</v>
+      </c>
+      <c r="U11" t="n">
+        <v>3</v>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
         <is>
           <t>Jättemusseron
 Motaggsvamp
 Svartvit taggsvamp</t>
         </is>
       </c>
-      <c r="W10">
+      <c r="W11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0125/artfynd/A 49131-2025 artfynd.xlsx", "A 49131-2025")</f>
         <v/>
       </c>
-      <c r="X10">
+      <c r="X11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor/A 49131-2025 karta.png", "A 49131-2025")</f>
         <v/>
       </c>
-      <c r="Y10">
+      <c r="Y11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor_geotiff/A 49131-2025 georefererad karta.tif", "A 49131-2025")</f>
         <v/>
       </c>
-      <c r="AA10">
+      <c r="AA11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomål/A 49131-2025 FSC-klagomål.docx", "A 49131-2025")</f>
         <v/>
       </c>
-      <c r="AB10">
+      <c r="AB11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomålsmail/A 49131-2025 FSC-klagomål mail.docx", "A 49131-2025")</f>
         <v/>
       </c>
-      <c r="AC10">
+      <c r="AC11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsyn/A 49131-2025 tillsynsbegäran.docx", "A 49131-2025")</f>
         <v/>
       </c>
-      <c r="AD10">
+      <c r="AD11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsynsmail/A 49131-2025 tillsynsbegäran mail.docx", "A 49131-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="11" ht="15" customHeight="1">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>A 13237-2023</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D11" s="1" t="n">
-        <v>45002</v>
-      </c>
-      <c r="E11" s="1" t="n">
-        <v>46303</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>EKERÖ</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
-      <c r="I11" t="n">
-        <v>9.300000000000001</v>
-      </c>
-      <c r="J11" t="n">
-        <v>0</v>
-      </c>
-      <c r="K11" t="n">
-        <v>2</v>
-      </c>
-      <c r="L11" t="n">
-        <v>1</v>
-      </c>
-      <c r="M11" t="n">
-        <v>0</v>
-      </c>
-      <c r="N11" t="n">
-        <v>0</v>
-      </c>
-      <c r="O11" t="n">
-        <v>0</v>
-      </c>
-      <c r="P11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>1</v>
-      </c>
-      <c r="R11" t="n">
-        <v>0</v>
-      </c>
-      <c r="S11" t="n">
-        <v>3</v>
-      </c>
-      <c r="T11" t="n">
-        <v>7</v>
-      </c>
-      <c r="U11" t="n">
-        <v>0</v>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
-        <is>
-          <t>Tallticka
-Granbarkgnagare
-Grönpyrola</t>
-        </is>
-      </c>
-      <c r="W11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/artfynd/A 13237-2023 artfynd.xlsx", "A 13237-2023")</f>
-        <v/>
-      </c>
-      <c r="X11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor/A 13237-2023 karta.png", "A 13237-2023")</f>
-        <v/>
-      </c>
-      <c r="Y11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor_geotiff/A 13237-2023 georefererad karta.tif", "A 13237-2023")</f>
-        <v/>
-      </c>
-      <c r="AA11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomål/A 13237-2023 FSC-klagomål.docx", "A 13237-2023")</f>
-        <v/>
-      </c>
-      <c r="AB11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomålsmail/A 13237-2023 FSC-klagomål mail.docx", "A 13237-2023")</f>
-        <v/>
-      </c>
-      <c r="AC11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsyn/A 13237-2023 tillsynsbegäran.docx", "A 13237-2023")</f>
-        <v/>
-      </c>
-      <c r="AD11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsynsmail/A 13237-2023 tillsynsbegäran mail.docx", "A 13237-2023")</f>
         <v/>
       </c>
     </row>
@@ -1735,7 +1735,7 @@
         <v>45209</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1850,7 +1850,7 @@
         <v>45170</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1956,7 +1956,7 @@
         <v>44646</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2044,7 +2044,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 1793-2025</t>
+          <t>A 3221-2022</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2058,10 +2058,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45671</v>
+        <v>44582</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2074,13 +2074,13 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>1.7</v>
+        <v>0.5</v>
       </c>
       <c r="J15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L15" t="n">
         <v>0</v>
@@ -2107,49 +2107,49 @@
         <v>1</v>
       </c>
       <c r="T15" t="n">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>Mistel</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/artfynd/A 1793-2025 artfynd.xlsx", "A 1793-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/artfynd/A 3221-2022 artfynd.xlsx", "A 3221-2022")</f>
         <v/>
       </c>
       <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor/A 1793-2025 karta.png", "A 1793-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor/A 3221-2022 karta.png", "A 3221-2022")</f>
         <v/>
       </c>
       <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor_geotiff/A 1793-2025 georefererad karta.tif", "A 1793-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor_geotiff/A 3221-2022 georefererad karta.tif", "A 3221-2022")</f>
         <v/>
       </c>
       <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomål/A 1793-2025 FSC-klagomål.docx", "A 1793-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomål/A 3221-2022 FSC-klagomål.docx", "A 3221-2022")</f>
         <v/>
       </c>
       <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomålsmail/A 1793-2025 FSC-klagomål mail.docx", "A 1793-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomålsmail/A 3221-2022 FSC-klagomål mail.docx", "A 3221-2022")</f>
         <v/>
       </c>
       <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsyn/A 1793-2025 tillsynsbegäran.docx", "A 1793-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsyn/A 3221-2022 tillsynsbegäran.docx", "A 3221-2022")</f>
         <v/>
       </c>
       <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsynsmail/A 1793-2025 tillsynsbegäran mail.docx", "A 1793-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsynsmail/A 3221-2022 tillsynsbegäran mail.docx", "A 3221-2022")</f>
         <v/>
       </c>
     </row>
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 3221-2022</t>
+          <t>A 13794-2023</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2163,10 +2163,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>44582</v>
+        <v>45007</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2179,16 +2179,16 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>0.5</v>
+        <v>4.8</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M16" t="n">
         <v>0</v>
@@ -2203,7 +2203,7 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R16" t="n">
         <v>0</v>
@@ -2215,39 +2215,39 @@
         <v>1</v>
       </c>
       <c r="U16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/artfynd/A 3221-2022 artfynd.xlsx", "A 3221-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/artfynd/A 13794-2023 artfynd.xlsx", "A 13794-2023")</f>
         <v/>
       </c>
       <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor/A 3221-2022 karta.png", "A 3221-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor/A 13794-2023 karta.png", "A 13794-2023")</f>
         <v/>
       </c>
       <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor_geotiff/A 3221-2022 georefererad karta.tif", "A 3221-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor_geotiff/A 13794-2023 georefererad karta.tif", "A 13794-2023")</f>
         <v/>
       </c>
       <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomål/A 3221-2022 FSC-klagomål.docx", "A 3221-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomål/A 13794-2023 FSC-klagomål.docx", "A 13794-2023")</f>
         <v/>
       </c>
       <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomålsmail/A 3221-2022 FSC-klagomål mail.docx", "A 3221-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomålsmail/A 13794-2023 FSC-klagomål mail.docx", "A 13794-2023")</f>
         <v/>
       </c>
       <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsyn/A 3221-2022 tillsynsbegäran.docx", "A 3221-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsyn/A 13794-2023 tillsynsbegäran.docx", "A 13794-2023")</f>
         <v/>
       </c>
       <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsynsmail/A 3221-2022 tillsynsbegäran mail.docx", "A 3221-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsynsmail/A 13794-2023 tillsynsbegäran mail.docx", "A 13794-2023")</f>
         <v/>
       </c>
     </row>
@@ -2271,7 +2271,7 @@
         <v>46037</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2359,7 +2359,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 13794-2023</t>
+          <t>A 1793-2025</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2373,10 +2373,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45007</v>
+        <v>45671</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2389,16 +2389,16 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>4.8</v>
+        <v>1.7</v>
       </c>
       <c r="J18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K18" t="n">
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
         <v>0</v>
@@ -2413,7 +2413,7 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
         <v>0</v>
@@ -2422,42 +2422,42 @@
         <v>1</v>
       </c>
       <c r="T18" t="n">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="U18" t="n">
         <v>0</v>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Mistel</t>
         </is>
       </c>
       <c r="W18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/artfynd/A 13794-2023 artfynd.xlsx", "A 13794-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/artfynd/A 1793-2025 artfynd.xlsx", "A 1793-2025")</f>
         <v/>
       </c>
       <c r="X18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor/A 13794-2023 karta.png", "A 13794-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor/A 1793-2025 karta.png", "A 1793-2025")</f>
         <v/>
       </c>
       <c r="Y18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor_geotiff/A 13794-2023 georefererad karta.tif", "A 13794-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor_geotiff/A 1793-2025 georefererad karta.tif", "A 1793-2025")</f>
         <v/>
       </c>
       <c r="AA18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomål/A 13794-2023 FSC-klagomål.docx", "A 13794-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomål/A 1793-2025 FSC-klagomål.docx", "A 1793-2025")</f>
         <v/>
       </c>
       <c r="AB18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomålsmail/A 13794-2023 FSC-klagomål mail.docx", "A 13794-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomålsmail/A 1793-2025 FSC-klagomål mail.docx", "A 1793-2025")</f>
         <v/>
       </c>
       <c r="AC18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsyn/A 13794-2023 tillsynsbegäran.docx", "A 13794-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsyn/A 1793-2025 tillsynsbegäran.docx", "A 1793-2025")</f>
         <v/>
       </c>
       <c r="AD18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsynsmail/A 13794-2023 tillsynsbegäran mail.docx", "A 13794-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsynsmail/A 1793-2025 tillsynsbegäran mail.docx", "A 1793-2025")</f>
         <v/>
       </c>
     </row>
@@ -2481,7 +2481,7 @@
         <v>44670</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2554,7 +2554,7 @@
         <v>44802</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2610,7 +2610,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 3222-2022</t>
+          <t>A 3219-2022</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2627,7 +2627,7 @@
         <v>44582</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2640,7 +2640,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>1.8</v>
+        <v>0.5</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2683,7 +2683,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 3219-2022</t>
+          <t>A 50184-2023</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2697,10 +2697,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>44582</v>
+        <v>45208</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2713,7 +2713,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>0.5</v>
+        <v>10.8</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2756,7 +2756,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 50184-2023</t>
+          <t>A 37245-2025</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2770,10 +2770,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45208</v>
+        <v>45876</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2786,7 +2786,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>10.8</v>
+        <v>1.1</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2829,7 +2829,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 60755-2024</t>
+          <t>A 55724-2024</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2843,10 +2843,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45644</v>
+        <v>45622</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2859,7 +2859,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>2.1</v>
+        <v>0.5</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2902,7 +2902,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 55724-2024</t>
+          <t>A 20399-2026</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2916,10 +2916,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45622</v>
+        <v>46139</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2932,7 +2932,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>0.5</v>
+        <v>0.9</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2975,7 +2975,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 37245-2025</t>
+          <t>A 35955-2023</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2989,10 +2989,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45876</v>
+        <v>45148</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3048,7 +3048,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 20399-2026</t>
+          <t>A 63378-2025</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3062,10 +3062,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>46139</v>
+        <v>46010</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3078,7 +3078,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>0.9</v>
+        <v>4.8</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -3121,7 +3121,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 56002-2024</t>
+          <t>A 20398-2026</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3135,10 +3135,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45623</v>
+        <v>46139</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3151,7 +3151,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>3.4</v>
+        <v>2.4</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -3194,7 +3194,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 20398-2026</t>
+          <t>A 61217-2024</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3208,10 +3208,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>46139</v>
+        <v>45645</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3224,7 +3224,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>2.4</v>
+        <v>0.8</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3267,7 +3267,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 20898-2026</t>
+          <t>A 56002-2024</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3281,10 +3281,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>46142</v>
+        <v>45623</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3297,7 +3297,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3340,7 +3340,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 35955-2023</t>
+          <t>A 60728-2022</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3354,10 +3354,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45148</v>
+        <v>44913</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3370,7 +3370,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3413,7 +3413,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 63378-2025</t>
+          <t>A 2535-2026</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3427,10 +3427,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>46010</v>
+        <v>46037</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3443,7 +3443,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>4.8</v>
+        <v>1.6</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3486,7 +3486,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 34073-2025</t>
+          <t>A 20898-2026</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3496,14 +3496,14 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45845</v>
+        <v>46142</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3516,7 +3516,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>2.9</v>
+        <v>3.6</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3559,7 +3559,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 61217-2024</t>
+          <t>A 3222-2022</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3573,10 +3573,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45645</v>
+        <v>44582</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3589,7 +3589,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>0.8</v>
+        <v>1.8</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3632,7 +3632,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 2535-2026</t>
+          <t>A 34073-2025</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3642,14 +3642,14 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>46037</v>
+        <v>45845</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3662,7 +3662,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>1.6</v>
+        <v>2.9</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3705,7 +3705,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 60728-2022</t>
+          <t>A 60755-2024</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3719,10 +3719,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>44913</v>
+        <v>45644</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3735,7 +3735,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>1.2</v>
+        <v>2.1</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3795,7 +3795,7 @@
         <v>46244</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3873,7 +3873,7 @@
         <v>46301</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3951,7 +3951,7 @@
         <v>46153</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>

--- a/Översikt EKERÖ.xlsx
+++ b/Översikt EKERÖ.xlsx
@@ -601,7 +601,7 @@
         <v>46241</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -728,7 +728,7 @@
         <v>44872</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -848,7 +848,7 @@
         <v>44974</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -963,7 +963,7 @@
         <v>45148</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1073,7 +1073,7 @@
         <v>44582</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1182,7 +1182,7 @@
         <v>46119</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1296,7 +1296,7 @@
         <v>46241</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1409,7 +1409,7 @@
         <v>44634</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1516,7 +1516,7 @@
         <v>45002</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1628,7 +1628,7 @@
         <v>45937</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1735,7 +1735,7 @@
         <v>45209</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1850,7 +1850,7 @@
         <v>45170</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1956,7 +1956,7 @@
         <v>44646</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2061,7 +2061,7 @@
         <v>44582</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2149,7 +2149,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 13794-2023</t>
+          <t>A 1793-2025</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2163,10 +2163,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45007</v>
+        <v>45671</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2179,16 +2179,16 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>4.8</v>
+        <v>1.7</v>
       </c>
       <c r="J16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K16" t="n">
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
         <v>0</v>
@@ -2203,7 +2203,7 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
         <v>0</v>
@@ -2212,49 +2212,49 @@
         <v>1</v>
       </c>
       <c r="T16" t="n">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="U16" t="n">
         <v>0</v>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Mistel</t>
         </is>
       </c>
       <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/artfynd/A 13794-2023 artfynd.xlsx", "A 13794-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/artfynd/A 1793-2025 artfynd.xlsx", "A 1793-2025")</f>
         <v/>
       </c>
       <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor/A 13794-2023 karta.png", "A 13794-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor/A 1793-2025 karta.png", "A 1793-2025")</f>
         <v/>
       </c>
       <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor_geotiff/A 13794-2023 georefererad karta.tif", "A 13794-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor_geotiff/A 1793-2025 georefererad karta.tif", "A 1793-2025")</f>
         <v/>
       </c>
       <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomål/A 13794-2023 FSC-klagomål.docx", "A 13794-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomål/A 1793-2025 FSC-klagomål.docx", "A 1793-2025")</f>
         <v/>
       </c>
       <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomålsmail/A 13794-2023 FSC-klagomål mail.docx", "A 13794-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomålsmail/A 1793-2025 FSC-klagomål mail.docx", "A 1793-2025")</f>
         <v/>
       </c>
       <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsyn/A 13794-2023 tillsynsbegäran.docx", "A 13794-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsyn/A 1793-2025 tillsynsbegäran.docx", "A 1793-2025")</f>
         <v/>
       </c>
       <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsynsmail/A 13794-2023 tillsynsbegäran mail.docx", "A 13794-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsynsmail/A 1793-2025 tillsynsbegäran mail.docx", "A 1793-2025")</f>
         <v/>
       </c>
     </row>
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 2533-2026</t>
+          <t>A 13794-2023</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2268,10 +2268,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>46037</v>
+        <v>45007</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2284,16 +2284,16 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>1.4</v>
+        <v>4.8</v>
       </c>
       <c r="J17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K17" t="n">
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M17" t="n">
         <v>0</v>
@@ -2308,7 +2308,7 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R17" t="n">
         <v>0</v>
@@ -2324,42 +2324,42 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/artfynd/A 2533-2026 artfynd.xlsx", "A 2533-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/artfynd/A 13794-2023 artfynd.xlsx", "A 13794-2023")</f>
         <v/>
       </c>
       <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor/A 2533-2026 karta.png", "A 2533-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor/A 13794-2023 karta.png", "A 13794-2023")</f>
         <v/>
       </c>
       <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor_geotiff/A 2533-2026 georefererad karta.tif", "A 2533-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor_geotiff/A 13794-2023 georefererad karta.tif", "A 13794-2023")</f>
         <v/>
       </c>
       <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomål/A 2533-2026 FSC-klagomål.docx", "A 2533-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomål/A 13794-2023 FSC-klagomål.docx", "A 13794-2023")</f>
         <v/>
       </c>
       <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomålsmail/A 2533-2026 FSC-klagomål mail.docx", "A 2533-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomålsmail/A 13794-2023 FSC-klagomål mail.docx", "A 13794-2023")</f>
         <v/>
       </c>
       <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsyn/A 2533-2026 tillsynsbegäran.docx", "A 2533-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsyn/A 13794-2023 tillsynsbegäran.docx", "A 13794-2023")</f>
         <v/>
       </c>
       <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsynsmail/A 2533-2026 tillsynsbegäran mail.docx", "A 2533-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsynsmail/A 13794-2023 tillsynsbegäran mail.docx", "A 13794-2023")</f>
         <v/>
       </c>
     </row>
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 1793-2025</t>
+          <t>A 2533-2026</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2373,10 +2373,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45671</v>
+        <v>46037</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2389,7 +2389,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>1.7</v>
+        <v>1.4</v>
       </c>
       <c r="J18" t="n">
         <v>1</v>
@@ -2422,42 +2422,42 @@
         <v>1</v>
       </c>
       <c r="T18" t="n">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="U18" t="n">
         <v>0</v>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>Mistel</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="W18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/artfynd/A 1793-2025 artfynd.xlsx", "A 1793-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/artfynd/A 2533-2026 artfynd.xlsx", "A 2533-2026")</f>
         <v/>
       </c>
       <c r="X18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor/A 1793-2025 karta.png", "A 1793-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor/A 2533-2026 karta.png", "A 2533-2026")</f>
         <v/>
       </c>
       <c r="Y18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor_geotiff/A 1793-2025 georefererad karta.tif", "A 1793-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor_geotiff/A 2533-2026 georefererad karta.tif", "A 2533-2026")</f>
         <v/>
       </c>
       <c r="AA18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomål/A 1793-2025 FSC-klagomål.docx", "A 1793-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomål/A 2533-2026 FSC-klagomål.docx", "A 2533-2026")</f>
         <v/>
       </c>
       <c r="AB18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomålsmail/A 1793-2025 FSC-klagomål mail.docx", "A 1793-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomålsmail/A 2533-2026 FSC-klagomål mail.docx", "A 2533-2026")</f>
         <v/>
       </c>
       <c r="AC18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsyn/A 1793-2025 tillsynsbegäran.docx", "A 1793-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsyn/A 2533-2026 tillsynsbegäran.docx", "A 2533-2026")</f>
         <v/>
       </c>
       <c r="AD18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsynsmail/A 1793-2025 tillsynsbegäran mail.docx", "A 1793-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsynsmail/A 2533-2026 tillsynsbegäran mail.docx", "A 2533-2026")</f>
         <v/>
       </c>
     </row>
@@ -2481,7 +2481,7 @@
         <v>44670</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2554,7 +2554,7 @@
         <v>44802</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2610,7 +2610,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 3219-2022</t>
+          <t>A 50184-2023</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2624,10 +2624,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>44582</v>
+        <v>45208</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2640,7 +2640,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>0.5</v>
+        <v>10.8</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2683,7 +2683,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 50184-2023</t>
+          <t>A 3219-2022</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2697,10 +2697,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>45208</v>
+        <v>44582</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2713,7 +2713,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>10.8</v>
+        <v>0.5</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2756,7 +2756,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 37245-2025</t>
+          <t>A 60755-2024</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2770,10 +2770,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45876</v>
+        <v>45644</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2786,7 +2786,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>1.1</v>
+        <v>2.1</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2846,7 +2846,7 @@
         <v>45622</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2902,7 +2902,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 20399-2026</t>
+          <t>A 56002-2024</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2916,10 +2916,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>46139</v>
+        <v>45623</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2932,7 +2932,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>0.9</v>
+        <v>3.4</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2992,7 +2992,7 @@
         <v>45148</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3048,7 +3048,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 63378-2025</t>
+          <t>A 61217-2024</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3062,10 +3062,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>46010</v>
+        <v>45645</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3078,7 +3078,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>4.8</v>
+        <v>0.8</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -3121,7 +3121,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 20398-2026</t>
+          <t>A 37245-2025</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3135,10 +3135,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>46139</v>
+        <v>45876</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3151,7 +3151,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>2.4</v>
+        <v>1.1</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -3194,7 +3194,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 61217-2024</t>
+          <t>A 3222-2022</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3208,10 +3208,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45645</v>
+        <v>44582</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3224,7 +3224,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>0.8</v>
+        <v>1.8</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3267,7 +3267,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 56002-2024</t>
+          <t>A 63378-2025</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3281,10 +3281,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45623</v>
+        <v>46010</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3297,7 +3297,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>3.4</v>
+        <v>4.8</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3357,7 +3357,7 @@
         <v>44913</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3430,7 +3430,7 @@
         <v>46037</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3486,7 +3486,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 20898-2026</t>
+          <t>A 20399-2026</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3500,10 +3500,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>46142</v>
+        <v>46139</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3516,7 +3516,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>3.6</v>
+        <v>0.9</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3559,7 +3559,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 3222-2022</t>
+          <t>A 20398-2026</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3573,10 +3573,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>44582</v>
+        <v>46139</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3589,7 +3589,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>1.8</v>
+        <v>2.4</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3632,7 +3632,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 34073-2025</t>
+          <t>A 20898-2026</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3642,14 +3642,14 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45845</v>
+        <v>46142</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3662,7 +3662,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>2.9</v>
+        <v>3.6</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3705,7 +3705,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 60755-2024</t>
+          <t>A 34073-2025</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3715,14 +3715,14 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45644</v>
+        <v>45845</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3735,7 +3735,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>2.1</v>
+        <v>2.9</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3795,7 +3795,7 @@
         <v>46244</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3873,7 +3873,7 @@
         <v>46301</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3951,7 +3951,7 @@
         <v>46153</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>

--- a/Översikt EKERÖ.xlsx
+++ b/Översikt EKERÖ.xlsx
@@ -601,7 +601,7 @@
         <v>46241</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -728,7 +728,7 @@
         <v>44872</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -848,7 +848,7 @@
         <v>44974</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -963,7 +963,7 @@
         <v>45148</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1073,7 +1073,7 @@
         <v>44582</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1182,7 +1182,7 @@
         <v>46119</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1296,7 +1296,7 @@
         <v>46241</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1409,7 +1409,7 @@
         <v>44634</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1516,7 +1516,7 @@
         <v>45002</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1628,7 +1628,7 @@
         <v>45937</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1735,7 +1735,7 @@
         <v>45209</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1850,7 +1850,7 @@
         <v>45170</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1956,7 +1956,7 @@
         <v>44646</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2061,7 +2061,7 @@
         <v>44582</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2166,7 +2166,7 @@
         <v>45671</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2271,7 +2271,7 @@
         <v>45007</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2376,7 +2376,7 @@
         <v>46037</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2481,7 +2481,7 @@
         <v>44670</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2554,7 +2554,7 @@
         <v>44802</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2627,7 +2627,7 @@
         <v>45208</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2700,7 +2700,7 @@
         <v>44582</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2773,7 +2773,7 @@
         <v>45644</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2846,7 +2846,7 @@
         <v>45622</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2919,7 +2919,7 @@
         <v>45623</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2992,7 +2992,7 @@
         <v>45148</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3065,7 +3065,7 @@
         <v>45645</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3138,7 +3138,7 @@
         <v>45876</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3211,7 +3211,7 @@
         <v>44582</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3284,7 +3284,7 @@
         <v>46010</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3357,7 +3357,7 @@
         <v>44913</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3430,7 +3430,7 @@
         <v>46037</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3503,7 +3503,7 @@
         <v>46139</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3576,7 +3576,7 @@
         <v>46139</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3649,7 +3649,7 @@
         <v>46142</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3722,7 +3722,7 @@
         <v>45845</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3795,7 +3795,7 @@
         <v>46244</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3873,7 +3873,7 @@
         <v>46301</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3951,7 +3951,7 @@
         <v>46153</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>

--- a/Översikt EKERÖ.xlsx
+++ b/Översikt EKERÖ.xlsx
@@ -601,7 +601,7 @@
         <v>46241</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -728,7 +728,7 @@
         <v>44872</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -848,7 +848,7 @@
         <v>44974</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -963,7 +963,7 @@
         <v>45148</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1073,7 +1073,7 @@
         <v>44582</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1182,7 +1182,7 @@
         <v>46119</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1296,7 +1296,7 @@
         <v>46241</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1409,7 +1409,7 @@
         <v>44634</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1516,7 +1516,7 @@
         <v>45002</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1628,7 +1628,7 @@
         <v>45937</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1735,7 +1735,7 @@
         <v>45209</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1850,7 +1850,7 @@
         <v>45170</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1956,7 +1956,7 @@
         <v>44646</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2061,7 +2061,7 @@
         <v>44582</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2166,7 +2166,7 @@
         <v>45671</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2271,7 +2271,7 @@
         <v>45007</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2376,7 +2376,7 @@
         <v>46037</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2481,7 +2481,7 @@
         <v>44670</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2554,7 +2554,7 @@
         <v>44802</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2627,7 +2627,7 @@
         <v>45208</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2700,7 +2700,7 @@
         <v>44582</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2773,7 +2773,7 @@
         <v>45644</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2846,7 +2846,7 @@
         <v>45622</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2919,7 +2919,7 @@
         <v>45623</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2992,7 +2992,7 @@
         <v>45148</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3065,7 +3065,7 @@
         <v>45645</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3138,7 +3138,7 @@
         <v>45876</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3211,7 +3211,7 @@
         <v>44582</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3284,7 +3284,7 @@
         <v>46010</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3357,7 +3357,7 @@
         <v>44913</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3430,7 +3430,7 @@
         <v>46037</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3503,7 +3503,7 @@
         <v>46139</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3576,7 +3576,7 @@
         <v>46139</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3649,7 +3649,7 @@
         <v>46142</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3722,7 +3722,7 @@
         <v>45845</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3795,7 +3795,7 @@
         <v>46244</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3873,7 +3873,7 @@
         <v>46301</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3951,7 +3951,7 @@
         <v>46153</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>

--- a/Översikt EKERÖ.xlsx
+++ b/Översikt EKERÖ.xlsx
@@ -601,7 +601,7 @@
         <v>46241</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -728,7 +728,7 @@
         <v>44872</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -848,7 +848,7 @@
         <v>44974</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -963,7 +963,7 @@
         <v>45148</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1056,7 +1056,7 @@
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A 3218-2022</t>
+          <t>A 17520-2026</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1070,10 +1070,10 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>44582</v>
+        <v>46119</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1085,8 +1085,13 @@
           <t>EKERÖ</t>
         </is>
       </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I6" t="n">
-        <v>1.2</v>
+        <v>2.2</v>
       </c>
       <c r="J6" t="n">
         <v>1</v>
@@ -1095,13 +1100,13 @@
         <v>1</v>
       </c>
       <c r="L6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M6" t="n">
         <v>1</v>
       </c>
       <c r="N6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1110,21 +1115,130 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="R6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
       </c>
       <c r="T6" t="n">
+        <v>5</v>
+      </c>
+      <c r="U6" t="n">
+        <v>1</v>
+      </c>
+      <c r="V6" s="2" t="inlineStr">
+        <is>
+          <t>Läderbagge
+Blekticka
+Ekticka
+Kandelabersvamp
+Gulgrön kantmusseron</t>
+        </is>
+      </c>
+      <c r="W6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/artfynd/A 17520-2026 artfynd.xlsx", "A 17520-2026")</f>
+        <v/>
+      </c>
+      <c r="X6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor/A 17520-2026 karta.png", "A 17520-2026")</f>
+        <v/>
+      </c>
+      <c r="Y6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor_geotiff/A 17520-2026 georefererad karta.tif", "A 17520-2026")</f>
+        <v/>
+      </c>
+      <c r="AA6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomål/A 17520-2026 FSC-klagomål.docx", "A 17520-2026")</f>
+        <v/>
+      </c>
+      <c r="AB6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomålsmail/A 17520-2026 FSC-klagomål mail.docx", "A 17520-2026")</f>
+        <v/>
+      </c>
+      <c r="AC6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsyn/A 17520-2026 tillsynsbegäran.docx", "A 17520-2026")</f>
+        <v/>
+      </c>
+      <c r="AD6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsynsmail/A 17520-2026 tillsynsbegäran mail.docx", "A 17520-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7" ht="15" customHeight="1">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>A 3218-2022</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D7" s="1" t="n">
+        <v>44582</v>
+      </c>
+      <c r="E7" s="1" t="n">
+        <v>46308</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>EKERÖ</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="J7" t="n">
+        <v>1</v>
+      </c>
+      <c r="K7" t="n">
+        <v>1</v>
+      </c>
+      <c r="L7" t="n">
+        <v>1</v>
+      </c>
+      <c r="M7" t="n">
+        <v>1</v>
+      </c>
+      <c r="N7" t="n">
+        <v>1</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>3</v>
+      </c>
+      <c r="R7" t="n">
+        <v>2</v>
+      </c>
+      <c r="S7" t="n">
+        <v>5</v>
+      </c>
+      <c r="T7" t="n">
         <v>8</v>
       </c>
-      <c r="U6" t="n">
+      <c r="U7" t="n">
         <v>6</v>
       </c>
-      <c r="V6" s="2" t="inlineStr">
+      <c r="V7" s="2" t="inlineStr">
         <is>
           <t>Bombmurkla
 Gul lammticka
@@ -1133,146 +1247,32 @@
 Blåbär</t>
         </is>
       </c>
-      <c r="W6">
+      <c r="W7">
         <f>HYPERLINK("https://klasma.github.io/Logging_0125/artfynd/A 3218-2022 artfynd.xlsx", "A 3218-2022")</f>
         <v/>
       </c>
-      <c r="X6">
+      <c r="X7">
         <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor/A 3218-2022 karta.png", "A 3218-2022")</f>
         <v/>
       </c>
-      <c r="Y6">
+      <c r="Y7">
         <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor_geotiff/A 3218-2022 georefererad karta.tif", "A 3218-2022")</f>
         <v/>
       </c>
-      <c r="AA6">
+      <c r="AA7">
         <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomål/A 3218-2022 FSC-klagomål.docx", "A 3218-2022")</f>
         <v/>
       </c>
-      <c r="AB6">
+      <c r="AB7">
         <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomålsmail/A 3218-2022 FSC-klagomål mail.docx", "A 3218-2022")</f>
         <v/>
       </c>
-      <c r="AC6">
+      <c r="AC7">
         <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsyn/A 3218-2022 tillsynsbegäran.docx", "A 3218-2022")</f>
         <v/>
       </c>
-      <c r="AD6">
+      <c r="AD7">
         <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsynsmail/A 3218-2022 tillsynsbegäran mail.docx", "A 3218-2022")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="7" ht="15" customHeight="1">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>A 17520-2026</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D7" s="1" t="n">
-        <v>46119</v>
-      </c>
-      <c r="E7" s="1" t="n">
-        <v>46307</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>EKERÖ</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
-      <c r="I7" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="J7" t="n">
-        <v>1</v>
-      </c>
-      <c r="K7" t="n">
-        <v>1</v>
-      </c>
-      <c r="L7" t="n">
-        <v>3</v>
-      </c>
-      <c r="M7" t="n">
-        <v>1</v>
-      </c>
-      <c r="N7" t="n">
-        <v>0</v>
-      </c>
-      <c r="O7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>4</v>
-      </c>
-      <c r="R7" t="n">
-        <v>1</v>
-      </c>
-      <c r="S7" t="n">
-        <v>5</v>
-      </c>
-      <c r="T7" t="n">
-        <v>5</v>
-      </c>
-      <c r="U7" t="n">
-        <v>1</v>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>Läderbagge
-Blekticka
-Ekticka
-Kandelabersvamp
-Gulgrön kantmusseron</t>
-        </is>
-      </c>
-      <c r="W7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/artfynd/A 17520-2026 artfynd.xlsx", "A 17520-2026")</f>
-        <v/>
-      </c>
-      <c r="X7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor/A 17520-2026 karta.png", "A 17520-2026")</f>
-        <v/>
-      </c>
-      <c r="Y7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor_geotiff/A 17520-2026 georefererad karta.tif", "A 17520-2026")</f>
-        <v/>
-      </c>
-      <c r="AA7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomål/A 17520-2026 FSC-klagomål.docx", "A 17520-2026")</f>
-        <v/>
-      </c>
-      <c r="AB7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomålsmail/A 17520-2026 FSC-klagomål mail.docx", "A 17520-2026")</f>
-        <v/>
-      </c>
-      <c r="AC7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsyn/A 17520-2026 tillsynsbegäran.docx", "A 17520-2026")</f>
-        <v/>
-      </c>
-      <c r="AD7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsynsmail/A 17520-2026 tillsynsbegäran mail.docx", "A 17520-2026")</f>
         <v/>
       </c>
     </row>
@@ -1296,7 +1296,7 @@
         <v>46241</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1409,7 +1409,7 @@
         <v>44634</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1516,7 +1516,7 @@
         <v>45002</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1628,7 +1628,7 @@
         <v>45937</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1735,7 +1735,7 @@
         <v>45209</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1850,7 +1850,7 @@
         <v>45170</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1956,7 +1956,7 @@
         <v>44646</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2061,7 +2061,7 @@
         <v>44582</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2166,7 +2166,7 @@
         <v>45671</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2254,7 +2254,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 13794-2023</t>
+          <t>A 2533-2026</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2268,10 +2268,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45007</v>
+        <v>46037</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2284,16 +2284,16 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>4.8</v>
+        <v>1.4</v>
       </c>
       <c r="J17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K17" t="n">
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
         <v>0</v>
@@ -2308,7 +2308,7 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
         <v>0</v>
@@ -2324,42 +2324,42 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/artfynd/A 13794-2023 artfynd.xlsx", "A 13794-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/artfynd/A 2533-2026 artfynd.xlsx", "A 2533-2026")</f>
         <v/>
       </c>
       <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor/A 13794-2023 karta.png", "A 13794-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor/A 2533-2026 karta.png", "A 2533-2026")</f>
         <v/>
       </c>
       <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor_geotiff/A 13794-2023 georefererad karta.tif", "A 13794-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor_geotiff/A 2533-2026 georefererad karta.tif", "A 2533-2026")</f>
         <v/>
       </c>
       <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomål/A 13794-2023 FSC-klagomål.docx", "A 13794-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomål/A 2533-2026 FSC-klagomål.docx", "A 2533-2026")</f>
         <v/>
       </c>
       <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomålsmail/A 13794-2023 FSC-klagomål mail.docx", "A 13794-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomålsmail/A 2533-2026 FSC-klagomål mail.docx", "A 2533-2026")</f>
         <v/>
       </c>
       <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsyn/A 13794-2023 tillsynsbegäran.docx", "A 13794-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsyn/A 2533-2026 tillsynsbegäran.docx", "A 2533-2026")</f>
         <v/>
       </c>
       <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsynsmail/A 13794-2023 tillsynsbegäran mail.docx", "A 13794-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsynsmail/A 2533-2026 tillsynsbegäran mail.docx", "A 2533-2026")</f>
         <v/>
       </c>
     </row>
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 2533-2026</t>
+          <t>A 13794-2023</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2373,10 +2373,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>46037</v>
+        <v>45007</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2389,16 +2389,16 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>1.4</v>
+        <v>4.8</v>
       </c>
       <c r="J18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K18" t="n">
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M18" t="n">
         <v>0</v>
@@ -2413,7 +2413,7 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R18" t="n">
         <v>0</v>
@@ -2429,35 +2429,35 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="W18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/artfynd/A 2533-2026 artfynd.xlsx", "A 2533-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/artfynd/A 13794-2023 artfynd.xlsx", "A 13794-2023")</f>
         <v/>
       </c>
       <c r="X18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor/A 2533-2026 karta.png", "A 2533-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor/A 13794-2023 karta.png", "A 13794-2023")</f>
         <v/>
       </c>
       <c r="Y18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor_geotiff/A 2533-2026 georefererad karta.tif", "A 2533-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor_geotiff/A 13794-2023 georefererad karta.tif", "A 13794-2023")</f>
         <v/>
       </c>
       <c r="AA18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomål/A 2533-2026 FSC-klagomål.docx", "A 2533-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomål/A 13794-2023 FSC-klagomål.docx", "A 13794-2023")</f>
         <v/>
       </c>
       <c r="AB18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomålsmail/A 2533-2026 FSC-klagomål mail.docx", "A 2533-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomålsmail/A 13794-2023 FSC-klagomål mail.docx", "A 13794-2023")</f>
         <v/>
       </c>
       <c r="AC18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsyn/A 2533-2026 tillsynsbegäran.docx", "A 2533-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsyn/A 13794-2023 tillsynsbegäran.docx", "A 13794-2023")</f>
         <v/>
       </c>
       <c r="AD18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsynsmail/A 2533-2026 tillsynsbegäran mail.docx", "A 2533-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsynsmail/A 13794-2023 tillsynsbegäran mail.docx", "A 13794-2023")</f>
         <v/>
       </c>
     </row>
@@ -2481,7 +2481,7 @@
         <v>44670</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2554,7 +2554,7 @@
         <v>44802</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2610,7 +2610,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 50184-2023</t>
+          <t>A 60755-2024</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2624,10 +2624,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45208</v>
+        <v>45644</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2640,7 +2640,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>10.8</v>
+        <v>2.1</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2700,7 +2700,7 @@
         <v>44582</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2756,7 +2756,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 60755-2024</t>
+          <t>A 63378-2025</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2770,10 +2770,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45644</v>
+        <v>46010</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2786,7 +2786,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>2.1</v>
+        <v>4.8</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2829,7 +2829,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 55724-2024</t>
+          <t>A 2535-2026</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2843,10 +2843,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45622</v>
+        <v>46037</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2859,7 +2859,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>0.5</v>
+        <v>1.6</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2902,7 +2902,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 56002-2024</t>
+          <t>A 33154-2026</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2916,10 +2916,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45623</v>
+        <v>46244</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2931,8 +2931,13 @@
           <t>EKERÖ</t>
         </is>
       </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I25" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2975,7 +2980,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 35955-2023</t>
+          <t>A 37245-2025</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2989,10 +2994,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45148</v>
+        <v>45876</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3048,7 +3053,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 61217-2024</t>
+          <t>A 41699-2026</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3062,10 +3067,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45645</v>
+        <v>46301</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3077,8 +3082,13 @@
           <t>EKERÖ</t>
         </is>
       </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I27" t="n">
-        <v>0.8</v>
+        <v>1.6</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -3121,7 +3131,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 37245-2025</t>
+          <t>A 20399-2026</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3135,10 +3145,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45876</v>
+        <v>46139</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3151,7 +3161,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>1.1</v>
+        <v>0.9</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -3194,7 +3204,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 3222-2022</t>
+          <t>A 20398-2026</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3208,10 +3218,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>44582</v>
+        <v>46139</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3224,7 +3234,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>1.8</v>
+        <v>2.4</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3267,7 +3277,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 63378-2025</t>
+          <t>A 50184-2023</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3281,10 +3291,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>46010</v>
+        <v>45208</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3297,7 +3307,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>4.8</v>
+        <v>10.8</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3340,7 +3350,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 60728-2022</t>
+          <t>A 20898-2026</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3354,10 +3364,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>44913</v>
+        <v>46142</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3370,7 +3380,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>1.2</v>
+        <v>3.6</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3413,7 +3423,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 2535-2026</t>
+          <t>A 34073-2025</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3423,14 +3433,14 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>46037</v>
+        <v>45845</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3443,7 +3453,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>1.6</v>
+        <v>2.9</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3486,7 +3496,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 20399-2026</t>
+          <t>A 55724-2024</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3500,10 +3510,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>46139</v>
+        <v>45622</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3516,7 +3526,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>0.9</v>
+        <v>0.5</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3559,7 +3569,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 20398-2026</t>
+          <t>A 35955-2023</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3573,10 +3583,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>46139</v>
+        <v>45148</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3589,7 +3599,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>2.4</v>
+        <v>1.1</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3632,7 +3642,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 20898-2026</t>
+          <t>A 61217-2024</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3646,10 +3656,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>46142</v>
+        <v>45645</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3662,7 +3672,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>3.6</v>
+        <v>0.8</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3705,7 +3715,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 34073-2025</t>
+          <t>A 56002-2024</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3715,14 +3725,14 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45845</v>
+        <v>45623</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3735,7 +3745,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>2.9</v>
+        <v>3.4</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3778,7 +3788,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 33154-2026</t>
+          <t>A 60728-2022</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3792,10 +3802,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>46244</v>
+        <v>44913</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3807,13 +3817,8 @@
           <t>EKERÖ</t>
         </is>
       </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I37" t="n">
-        <v>3.5</v>
+        <v>1.2</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3856,7 +3861,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 41699-2026</t>
+          <t>A 3222-2022</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3870,10 +3875,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>46301</v>
+        <v>44582</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3885,13 +3890,8 @@
           <t>EKERÖ</t>
         </is>
       </c>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I38" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3951,7 +3951,7 @@
         <v>46153</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>

--- a/Översikt EKERÖ.xlsx
+++ b/Översikt EKERÖ.xlsx
@@ -601,7 +601,7 @@
         <v>46241</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -728,7 +728,7 @@
         <v>44872</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -848,7 +848,7 @@
         <v>44974</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -963,7 +963,7 @@
         <v>45148</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1056,7 +1056,7 @@
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A 17520-2026</t>
+          <t>A 3218-2022</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1070,10 +1070,10 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>46119</v>
+        <v>44582</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1085,13 +1085,8 @@
           <t>EKERÖ</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I6" t="n">
-        <v>2.2</v>
+        <v>1.2</v>
       </c>
       <c r="J6" t="n">
         <v>1</v>
@@ -1100,36 +1095,150 @@
         <v>1</v>
       </c>
       <c r="L6" t="n">
+        <v>1</v>
+      </c>
+      <c r="M6" t="n">
+        <v>1</v>
+      </c>
+      <c r="N6" t="n">
+        <v>1</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" t="n">
         <v>3</v>
       </c>
-      <c r="M6" t="n">
-        <v>1</v>
-      </c>
-      <c r="N6" t="n">
-        <v>0</v>
-      </c>
-      <c r="O6" t="n">
-        <v>0</v>
-      </c>
-      <c r="P6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>4</v>
-      </c>
       <c r="R6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
       </c>
       <c r="T6" t="n">
+        <v>8</v>
+      </c>
+      <c r="U6" t="n">
+        <v>6</v>
+      </c>
+      <c r="V6" s="2" t="inlineStr">
+        <is>
+          <t>Bombmurkla
+Gul lammticka
+Fyrflikig jordstjärna
+Kamjordstjärna
+Blåbär</t>
+        </is>
+      </c>
+      <c r="W6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/artfynd/A 3218-2022 artfynd.xlsx", "A 3218-2022")</f>
+        <v/>
+      </c>
+      <c r="X6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor/A 3218-2022 karta.png", "A 3218-2022")</f>
+        <v/>
+      </c>
+      <c r="Y6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor_geotiff/A 3218-2022 georefererad karta.tif", "A 3218-2022")</f>
+        <v/>
+      </c>
+      <c r="AA6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomål/A 3218-2022 FSC-klagomål.docx", "A 3218-2022")</f>
+        <v/>
+      </c>
+      <c r="AB6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomålsmail/A 3218-2022 FSC-klagomål mail.docx", "A 3218-2022")</f>
+        <v/>
+      </c>
+      <c r="AC6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsyn/A 3218-2022 tillsynsbegäran.docx", "A 3218-2022")</f>
+        <v/>
+      </c>
+      <c r="AD6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsynsmail/A 3218-2022 tillsynsbegäran mail.docx", "A 3218-2022")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7" ht="15" customHeight="1">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>A 17520-2026</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D7" s="1" t="n">
+        <v>46119</v>
+      </c>
+      <c r="E7" s="1" t="n">
+        <v>46309</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>EKERÖ</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="J7" t="n">
+        <v>1</v>
+      </c>
+      <c r="K7" t="n">
+        <v>1</v>
+      </c>
+      <c r="L7" t="n">
+        <v>3</v>
+      </c>
+      <c r="M7" t="n">
+        <v>1</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>4</v>
+      </c>
+      <c r="R7" t="n">
+        <v>1</v>
+      </c>
+      <c r="S7" t="n">
         <v>5</v>
       </c>
-      <c r="U6" t="n">
-        <v>1</v>
-      </c>
-      <c r="V6" s="2" t="inlineStr">
+      <c r="T7" t="n">
+        <v>5</v>
+      </c>
+      <c r="U7" t="n">
+        <v>1</v>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
         <is>
           <t>Läderbagge
 Blekticka
@@ -1138,141 +1247,32 @@
 Gulgrön kantmusseron</t>
         </is>
       </c>
-      <c r="W6">
+      <c r="W7">
         <f>HYPERLINK("https://klasma.github.io/Logging_0125/artfynd/A 17520-2026 artfynd.xlsx", "A 17520-2026")</f>
         <v/>
       </c>
-      <c r="X6">
+      <c r="X7">
         <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor/A 17520-2026 karta.png", "A 17520-2026")</f>
         <v/>
       </c>
-      <c r="Y6">
+      <c r="Y7">
         <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor_geotiff/A 17520-2026 georefererad karta.tif", "A 17520-2026")</f>
         <v/>
       </c>
-      <c r="AA6">
+      <c r="AA7">
         <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomål/A 17520-2026 FSC-klagomål.docx", "A 17520-2026")</f>
         <v/>
       </c>
-      <c r="AB6">
+      <c r="AB7">
         <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomålsmail/A 17520-2026 FSC-klagomål mail.docx", "A 17520-2026")</f>
         <v/>
       </c>
-      <c r="AC6">
+      <c r="AC7">
         <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsyn/A 17520-2026 tillsynsbegäran.docx", "A 17520-2026")</f>
         <v/>
       </c>
-      <c r="AD6">
+      <c r="AD7">
         <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsynsmail/A 17520-2026 tillsynsbegäran mail.docx", "A 17520-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="7" ht="15" customHeight="1">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>A 3218-2022</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D7" s="1" t="n">
-        <v>44582</v>
-      </c>
-      <c r="E7" s="1" t="n">
-        <v>46308</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>EKERÖ</t>
-        </is>
-      </c>
-      <c r="I7" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="J7" t="n">
-        <v>1</v>
-      </c>
-      <c r="K7" t="n">
-        <v>1</v>
-      </c>
-      <c r="L7" t="n">
-        <v>1</v>
-      </c>
-      <c r="M7" t="n">
-        <v>1</v>
-      </c>
-      <c r="N7" t="n">
-        <v>1</v>
-      </c>
-      <c r="O7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>3</v>
-      </c>
-      <c r="R7" t="n">
-        <v>2</v>
-      </c>
-      <c r="S7" t="n">
-        <v>5</v>
-      </c>
-      <c r="T7" t="n">
-        <v>8</v>
-      </c>
-      <c r="U7" t="n">
-        <v>6</v>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>Bombmurkla
-Gul lammticka
-Fyrflikig jordstjärna
-Kamjordstjärna
-Blåbär</t>
-        </is>
-      </c>
-      <c r="W7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/artfynd/A 3218-2022 artfynd.xlsx", "A 3218-2022")</f>
-        <v/>
-      </c>
-      <c r="X7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor/A 3218-2022 karta.png", "A 3218-2022")</f>
-        <v/>
-      </c>
-      <c r="Y7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor_geotiff/A 3218-2022 georefererad karta.tif", "A 3218-2022")</f>
-        <v/>
-      </c>
-      <c r="AA7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomål/A 3218-2022 FSC-klagomål.docx", "A 3218-2022")</f>
-        <v/>
-      </c>
-      <c r="AB7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomålsmail/A 3218-2022 FSC-klagomål mail.docx", "A 3218-2022")</f>
-        <v/>
-      </c>
-      <c r="AC7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsyn/A 3218-2022 tillsynsbegäran.docx", "A 3218-2022")</f>
-        <v/>
-      </c>
-      <c r="AD7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsynsmail/A 3218-2022 tillsynsbegäran mail.docx", "A 3218-2022")</f>
         <v/>
       </c>
     </row>
@@ -1296,7 +1296,7 @@
         <v>46241</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1409,7 +1409,7 @@
         <v>44634</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1499,7 +1499,7 @@
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 13237-2023</t>
+          <t>A 49131-2025</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1513,10 +1513,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>45002</v>
+        <v>45937</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1528,25 +1528,20 @@
           <t>EKERÖ</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I10" t="n">
-        <v>9.300000000000001</v>
+        <v>0.9</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
       </c>
       <c r="K10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" t="n">
         <v>2</v>
       </c>
-      <c r="L10" t="n">
-        <v>1</v>
-      </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N10" t="n">
         <v>0</v>
@@ -1558,160 +1553,165 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S10" t="n">
         <v>3</v>
       </c>
       <c r="T10" t="n">
+        <v>3</v>
+      </c>
+      <c r="U10" t="n">
+        <v>3</v>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
+        <is>
+          <t>Jättemusseron
+Motaggsvamp
+Svartvit taggsvamp</t>
+        </is>
+      </c>
+      <c r="W10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/artfynd/A 49131-2025 artfynd.xlsx", "A 49131-2025")</f>
+        <v/>
+      </c>
+      <c r="X10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor/A 49131-2025 karta.png", "A 49131-2025")</f>
+        <v/>
+      </c>
+      <c r="Y10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor_geotiff/A 49131-2025 georefererad karta.tif", "A 49131-2025")</f>
+        <v/>
+      </c>
+      <c r="AA10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomål/A 49131-2025 FSC-klagomål.docx", "A 49131-2025")</f>
+        <v/>
+      </c>
+      <c r="AB10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomålsmail/A 49131-2025 FSC-klagomål mail.docx", "A 49131-2025")</f>
+        <v/>
+      </c>
+      <c r="AC10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsyn/A 49131-2025 tillsynsbegäran.docx", "A 49131-2025")</f>
+        <v/>
+      </c>
+      <c r="AD10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsynsmail/A 49131-2025 tillsynsbegäran mail.docx", "A 49131-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11" ht="15" customHeight="1">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>A 13237-2023</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D11" s="1" t="n">
+        <v>45002</v>
+      </c>
+      <c r="E11" s="1" t="n">
+        <v>46309</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>EKERÖ</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" t="n">
+        <v>2</v>
+      </c>
+      <c r="L11" t="n">
+        <v>1</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>1</v>
+      </c>
+      <c r="R11" t="n">
+        <v>0</v>
+      </c>
+      <c r="S11" t="n">
+        <v>3</v>
+      </c>
+      <c r="T11" t="n">
         <v>7</v>
       </c>
-      <c r="U10" t="n">
-        <v>0</v>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
+      <c r="U11" t="n">
+        <v>0</v>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
         <is>
           <t>Tallticka
 Granbarkgnagare
 Grönpyrola</t>
         </is>
       </c>
-      <c r="W10">
+      <c r="W11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0125/artfynd/A 13237-2023 artfynd.xlsx", "A 13237-2023")</f>
         <v/>
       </c>
-      <c r="X10">
+      <c r="X11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor/A 13237-2023 karta.png", "A 13237-2023")</f>
         <v/>
       </c>
-      <c r="Y10">
+      <c r="Y11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor_geotiff/A 13237-2023 georefererad karta.tif", "A 13237-2023")</f>
         <v/>
       </c>
-      <c r="AA10">
+      <c r="AA11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomål/A 13237-2023 FSC-klagomål.docx", "A 13237-2023")</f>
         <v/>
       </c>
-      <c r="AB10">
+      <c r="AB11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomålsmail/A 13237-2023 FSC-klagomål mail.docx", "A 13237-2023")</f>
         <v/>
       </c>
-      <c r="AC10">
+      <c r="AC11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsyn/A 13237-2023 tillsynsbegäran.docx", "A 13237-2023")</f>
         <v/>
       </c>
-      <c r="AD10">
+      <c r="AD11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsynsmail/A 13237-2023 tillsynsbegäran mail.docx", "A 13237-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="11" ht="15" customHeight="1">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>A 49131-2025</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D11" s="1" t="n">
-        <v>45937</v>
-      </c>
-      <c r="E11" s="1" t="n">
-        <v>46308</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>EKERÖ</t>
-        </is>
-      </c>
-      <c r="I11" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="J11" t="n">
-        <v>0</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L11" t="n">
-        <v>2</v>
-      </c>
-      <c r="M11" t="n">
-        <v>1</v>
-      </c>
-      <c r="N11" t="n">
-        <v>0</v>
-      </c>
-      <c r="O11" t="n">
-        <v>0</v>
-      </c>
-      <c r="P11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>3</v>
-      </c>
-      <c r="R11" t="n">
-        <v>1</v>
-      </c>
-      <c r="S11" t="n">
-        <v>3</v>
-      </c>
-      <c r="T11" t="n">
-        <v>3</v>
-      </c>
-      <c r="U11" t="n">
-        <v>3</v>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
-        <is>
-          <t>Jättemusseron
-Motaggsvamp
-Svartvit taggsvamp</t>
-        </is>
-      </c>
-      <c r="W11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/artfynd/A 49131-2025 artfynd.xlsx", "A 49131-2025")</f>
-        <v/>
-      </c>
-      <c r="X11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor/A 49131-2025 karta.png", "A 49131-2025")</f>
-        <v/>
-      </c>
-      <c r="Y11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor_geotiff/A 49131-2025 georefererad karta.tif", "A 49131-2025")</f>
-        <v/>
-      </c>
-      <c r="AA11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomål/A 49131-2025 FSC-klagomål.docx", "A 49131-2025")</f>
-        <v/>
-      </c>
-      <c r="AB11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomålsmail/A 49131-2025 FSC-klagomål mail.docx", "A 49131-2025")</f>
-        <v/>
-      </c>
-      <c r="AC11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsyn/A 49131-2025 tillsynsbegäran.docx", "A 49131-2025")</f>
-        <v/>
-      </c>
-      <c r="AD11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsynsmail/A 49131-2025 tillsynsbegäran mail.docx", "A 49131-2025")</f>
         <v/>
       </c>
     </row>
@@ -1735,7 +1735,7 @@
         <v>45209</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1850,7 +1850,7 @@
         <v>45170</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1956,7 +1956,7 @@
         <v>44646</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2044,7 +2044,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 3221-2022</t>
+          <t>A 2533-2026</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2058,10 +2058,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>44582</v>
+        <v>46037</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2074,13 +2074,13 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>0.5</v>
+        <v>1.4</v>
       </c>
       <c r="J15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L15" t="n">
         <v>0</v>
@@ -2110,46 +2110,46 @@
         <v>1</v>
       </c>
       <c r="U15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/artfynd/A 3221-2022 artfynd.xlsx", "A 3221-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/artfynd/A 2533-2026 artfynd.xlsx", "A 2533-2026")</f>
         <v/>
       </c>
       <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor/A 3221-2022 karta.png", "A 3221-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor/A 2533-2026 karta.png", "A 2533-2026")</f>
         <v/>
       </c>
       <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor_geotiff/A 3221-2022 georefererad karta.tif", "A 3221-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor_geotiff/A 2533-2026 georefererad karta.tif", "A 2533-2026")</f>
         <v/>
       </c>
       <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomål/A 3221-2022 FSC-klagomål.docx", "A 3221-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomål/A 2533-2026 FSC-klagomål.docx", "A 2533-2026")</f>
         <v/>
       </c>
       <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomålsmail/A 3221-2022 FSC-klagomål mail.docx", "A 3221-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomålsmail/A 2533-2026 FSC-klagomål mail.docx", "A 2533-2026")</f>
         <v/>
       </c>
       <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsyn/A 3221-2022 tillsynsbegäran.docx", "A 3221-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsyn/A 2533-2026 tillsynsbegäran.docx", "A 2533-2026")</f>
         <v/>
       </c>
       <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsynsmail/A 3221-2022 tillsynsbegäran mail.docx", "A 3221-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsynsmail/A 2533-2026 tillsynsbegäran mail.docx", "A 2533-2026")</f>
         <v/>
       </c>
     </row>
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 1793-2025</t>
+          <t>A 3221-2022</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2163,10 +2163,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45671</v>
+        <v>44582</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2179,13 +2179,13 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>1.7</v>
+        <v>0.5</v>
       </c>
       <c r="J16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L16" t="n">
         <v>0</v>
@@ -2212,49 +2212,49 @@
         <v>1</v>
       </c>
       <c r="T16" t="n">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>Mistel</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/artfynd/A 1793-2025 artfynd.xlsx", "A 1793-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/artfynd/A 3221-2022 artfynd.xlsx", "A 3221-2022")</f>
         <v/>
       </c>
       <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor/A 1793-2025 karta.png", "A 1793-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor/A 3221-2022 karta.png", "A 3221-2022")</f>
         <v/>
       </c>
       <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor_geotiff/A 1793-2025 georefererad karta.tif", "A 1793-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor_geotiff/A 3221-2022 georefererad karta.tif", "A 3221-2022")</f>
         <v/>
       </c>
       <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomål/A 1793-2025 FSC-klagomål.docx", "A 1793-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomål/A 3221-2022 FSC-klagomål.docx", "A 3221-2022")</f>
         <v/>
       </c>
       <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomålsmail/A 1793-2025 FSC-klagomål mail.docx", "A 1793-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomålsmail/A 3221-2022 FSC-klagomål mail.docx", "A 3221-2022")</f>
         <v/>
       </c>
       <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsyn/A 1793-2025 tillsynsbegäran.docx", "A 1793-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsyn/A 3221-2022 tillsynsbegäran.docx", "A 3221-2022")</f>
         <v/>
       </c>
       <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsynsmail/A 1793-2025 tillsynsbegäran mail.docx", "A 1793-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsynsmail/A 3221-2022 tillsynsbegäran mail.docx", "A 3221-2022")</f>
         <v/>
       </c>
     </row>
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 2533-2026</t>
+          <t>A 13794-2023</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2268,10 +2268,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>46037</v>
+        <v>45007</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2284,16 +2284,16 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>1.4</v>
+        <v>4.8</v>
       </c>
       <c r="J17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K17" t="n">
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M17" t="n">
         <v>0</v>
@@ -2308,7 +2308,7 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R17" t="n">
         <v>0</v>
@@ -2324,42 +2324,42 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/artfynd/A 2533-2026 artfynd.xlsx", "A 2533-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/artfynd/A 13794-2023 artfynd.xlsx", "A 13794-2023")</f>
         <v/>
       </c>
       <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor/A 2533-2026 karta.png", "A 2533-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor/A 13794-2023 karta.png", "A 13794-2023")</f>
         <v/>
       </c>
       <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor_geotiff/A 2533-2026 georefererad karta.tif", "A 2533-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor_geotiff/A 13794-2023 georefererad karta.tif", "A 13794-2023")</f>
         <v/>
       </c>
       <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomål/A 2533-2026 FSC-klagomål.docx", "A 2533-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomål/A 13794-2023 FSC-klagomål.docx", "A 13794-2023")</f>
         <v/>
       </c>
       <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomålsmail/A 2533-2026 FSC-klagomål mail.docx", "A 2533-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomålsmail/A 13794-2023 FSC-klagomål mail.docx", "A 13794-2023")</f>
         <v/>
       </c>
       <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsyn/A 2533-2026 tillsynsbegäran.docx", "A 2533-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsyn/A 13794-2023 tillsynsbegäran.docx", "A 13794-2023")</f>
         <v/>
       </c>
       <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsynsmail/A 2533-2026 tillsynsbegäran mail.docx", "A 2533-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsynsmail/A 13794-2023 tillsynsbegäran mail.docx", "A 13794-2023")</f>
         <v/>
       </c>
     </row>
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 13794-2023</t>
+          <t>A 1793-2025</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2373,10 +2373,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45007</v>
+        <v>45671</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2389,16 +2389,16 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>4.8</v>
+        <v>1.7</v>
       </c>
       <c r="J18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K18" t="n">
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
         <v>0</v>
@@ -2413,7 +2413,7 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
         <v>0</v>
@@ -2422,42 +2422,42 @@
         <v>1</v>
       </c>
       <c r="T18" t="n">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="U18" t="n">
         <v>0</v>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Mistel</t>
         </is>
       </c>
       <c r="W18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/artfynd/A 13794-2023 artfynd.xlsx", "A 13794-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/artfynd/A 1793-2025 artfynd.xlsx", "A 1793-2025")</f>
         <v/>
       </c>
       <c r="X18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor/A 13794-2023 karta.png", "A 13794-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor/A 1793-2025 karta.png", "A 1793-2025")</f>
         <v/>
       </c>
       <c r="Y18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor_geotiff/A 13794-2023 georefererad karta.tif", "A 13794-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor_geotiff/A 1793-2025 georefererad karta.tif", "A 1793-2025")</f>
         <v/>
       </c>
       <c r="AA18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomål/A 13794-2023 FSC-klagomål.docx", "A 13794-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomål/A 1793-2025 FSC-klagomål.docx", "A 1793-2025")</f>
         <v/>
       </c>
       <c r="AB18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomålsmail/A 13794-2023 FSC-klagomål mail.docx", "A 13794-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomålsmail/A 1793-2025 FSC-klagomål mail.docx", "A 1793-2025")</f>
         <v/>
       </c>
       <c r="AC18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsyn/A 13794-2023 tillsynsbegäran.docx", "A 13794-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsyn/A 1793-2025 tillsynsbegäran.docx", "A 1793-2025")</f>
         <v/>
       </c>
       <c r="AD18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsynsmail/A 13794-2023 tillsynsbegäran mail.docx", "A 13794-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsynsmail/A 1793-2025 tillsynsbegäran mail.docx", "A 1793-2025")</f>
         <v/>
       </c>
     </row>
@@ -2481,7 +2481,7 @@
         <v>44670</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2554,7 +2554,7 @@
         <v>44802</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2610,7 +2610,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 60755-2024</t>
+          <t>A 63378-2025</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2624,10 +2624,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45644</v>
+        <v>46010</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2640,7 +2640,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>2.1</v>
+        <v>4.8</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2683,7 +2683,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 3219-2022</t>
+          <t>A 50184-2023</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2697,10 +2697,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>44582</v>
+        <v>45208</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2713,7 +2713,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>0.5</v>
+        <v>10.8</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2756,7 +2756,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 63378-2025</t>
+          <t>A 2535-2026</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2770,10 +2770,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>46010</v>
+        <v>46037</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2786,7 +2786,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>4.8</v>
+        <v>1.6</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2829,7 +2829,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 2535-2026</t>
+          <t>A 37245-2025</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2843,10 +2843,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>46037</v>
+        <v>45876</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2859,7 +2859,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>1.6</v>
+        <v>1.1</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2902,7 +2902,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 33154-2026</t>
+          <t>A 56002-2024</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2916,10 +2916,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>46244</v>
+        <v>45623</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2931,13 +2931,8 @@
           <t>EKERÖ</t>
         </is>
       </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I25" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2980,7 +2975,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 37245-2025</t>
+          <t>A 61217-2024</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2994,10 +2989,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45876</v>
+        <v>45645</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3010,7 +3005,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>1.1</v>
+        <v>0.8</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -3053,7 +3048,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 41699-2026</t>
+          <t>A 3222-2022</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3067,10 +3062,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>46301</v>
+        <v>44582</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3082,13 +3077,8 @@
           <t>EKERÖ</t>
         </is>
       </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I27" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -3148,7 +3138,7 @@
         <v>46139</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3221,7 +3211,7 @@
         <v>46139</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3277,7 +3267,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 50184-2023</t>
+          <t>A 3219-2022</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3291,10 +3281,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45208</v>
+        <v>44582</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3307,7 +3297,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>10.8</v>
+        <v>0.5</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3367,7 +3357,7 @@
         <v>46142</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3423,7 +3413,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 34073-2025</t>
+          <t>A 60755-2024</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3433,14 +3423,14 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45845</v>
+        <v>45644</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3453,7 +3443,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>2.9</v>
+        <v>2.1</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3513,7 +3503,7 @@
         <v>45622</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3569,7 +3559,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 35955-2023</t>
+          <t>A 34073-2025</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3579,14 +3569,14 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45148</v>
+        <v>45845</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3599,7 +3589,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>1.1</v>
+        <v>2.9</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3642,7 +3632,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 61217-2024</t>
+          <t>A 35955-2023</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3656,10 +3646,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45645</v>
+        <v>45148</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3672,7 +3662,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>0.8</v>
+        <v>1.1</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3715,7 +3705,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 56002-2024</t>
+          <t>A 60728-2022</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3729,10 +3719,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45623</v>
+        <v>44913</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3745,7 +3735,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>3.4</v>
+        <v>1.2</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3788,7 +3778,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 60728-2022</t>
+          <t>A 33154-2026</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3802,10 +3792,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>44913</v>
+        <v>46244</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3817,8 +3807,13 @@
           <t>EKERÖ</t>
         </is>
       </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I37" t="n">
-        <v>1.2</v>
+        <v>3.5</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3861,7 +3856,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 3222-2022</t>
+          <t>A 41699-2026</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3875,10 +3870,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>44582</v>
+        <v>46301</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3890,8 +3885,13 @@
           <t>EKERÖ</t>
         </is>
       </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I38" t="n">
-        <v>1.8</v>
+        <v>1.6</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3951,7 +3951,7 @@
         <v>46153</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>

--- a/Översikt EKERÖ.xlsx
+++ b/Översikt EKERÖ.xlsx
@@ -601,7 +601,7 @@
         <v>46241</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -728,7 +728,7 @@
         <v>44872</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -848,7 +848,7 @@
         <v>44974</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -963,7 +963,7 @@
         <v>45148</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1056,7 +1056,7 @@
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A 3218-2022</t>
+          <t>A 17520-2026</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1070,10 +1070,10 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>44582</v>
+        <v>46119</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1085,8 +1085,13 @@
           <t>EKERÖ</t>
         </is>
       </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I6" t="n">
-        <v>1.2</v>
+        <v>2.2</v>
       </c>
       <c r="J6" t="n">
         <v>1</v>
@@ -1095,13 +1100,13 @@
         <v>1</v>
       </c>
       <c r="L6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M6" t="n">
         <v>1</v>
       </c>
       <c r="N6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1110,21 +1115,130 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="R6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
       </c>
       <c r="T6" t="n">
+        <v>5</v>
+      </c>
+      <c r="U6" t="n">
+        <v>1</v>
+      </c>
+      <c r="V6" s="2" t="inlineStr">
+        <is>
+          <t>Läderbagge
+Blekticka
+Ekticka
+Kandelabersvamp
+Gulgrön kantmusseron</t>
+        </is>
+      </c>
+      <c r="W6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/artfynd/A 17520-2026 artfynd.xlsx", "A 17520-2026")</f>
+        <v/>
+      </c>
+      <c r="X6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor/A 17520-2026 karta.png", "A 17520-2026")</f>
+        <v/>
+      </c>
+      <c r="Y6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor_geotiff/A 17520-2026 georefererad karta.tif", "A 17520-2026")</f>
+        <v/>
+      </c>
+      <c r="AA6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomål/A 17520-2026 FSC-klagomål.docx", "A 17520-2026")</f>
+        <v/>
+      </c>
+      <c r="AB6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomålsmail/A 17520-2026 FSC-klagomål mail.docx", "A 17520-2026")</f>
+        <v/>
+      </c>
+      <c r="AC6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsyn/A 17520-2026 tillsynsbegäran.docx", "A 17520-2026")</f>
+        <v/>
+      </c>
+      <c r="AD6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsynsmail/A 17520-2026 tillsynsbegäran mail.docx", "A 17520-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7" ht="15" customHeight="1">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>A 3218-2022</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D7" s="1" t="n">
+        <v>44582</v>
+      </c>
+      <c r="E7" s="1" t="n">
+        <v>46310</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>EKERÖ</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="J7" t="n">
+        <v>1</v>
+      </c>
+      <c r="K7" t="n">
+        <v>1</v>
+      </c>
+      <c r="L7" t="n">
+        <v>1</v>
+      </c>
+      <c r="M7" t="n">
+        <v>1</v>
+      </c>
+      <c r="N7" t="n">
+        <v>1</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>3</v>
+      </c>
+      <c r="R7" t="n">
+        <v>2</v>
+      </c>
+      <c r="S7" t="n">
+        <v>5</v>
+      </c>
+      <c r="T7" t="n">
         <v>8</v>
       </c>
-      <c r="U6" t="n">
+      <c r="U7" t="n">
         <v>6</v>
       </c>
-      <c r="V6" s="2" t="inlineStr">
+      <c r="V7" s="2" t="inlineStr">
         <is>
           <t>Bombmurkla
 Gul lammticka
@@ -1133,146 +1247,32 @@
 Blåbär</t>
         </is>
       </c>
-      <c r="W6">
+      <c r="W7">
         <f>HYPERLINK("https://klasma.github.io/Logging_0125/artfynd/A 3218-2022 artfynd.xlsx", "A 3218-2022")</f>
         <v/>
       </c>
-      <c r="X6">
+      <c r="X7">
         <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor/A 3218-2022 karta.png", "A 3218-2022")</f>
         <v/>
       </c>
-      <c r="Y6">
+      <c r="Y7">
         <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor_geotiff/A 3218-2022 georefererad karta.tif", "A 3218-2022")</f>
         <v/>
       </c>
-      <c r="AA6">
+      <c r="AA7">
         <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomål/A 3218-2022 FSC-klagomål.docx", "A 3218-2022")</f>
         <v/>
       </c>
-      <c r="AB6">
+      <c r="AB7">
         <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomålsmail/A 3218-2022 FSC-klagomål mail.docx", "A 3218-2022")</f>
         <v/>
       </c>
-      <c r="AC6">
+      <c r="AC7">
         <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsyn/A 3218-2022 tillsynsbegäran.docx", "A 3218-2022")</f>
         <v/>
       </c>
-      <c r="AD6">
+      <c r="AD7">
         <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsynsmail/A 3218-2022 tillsynsbegäran mail.docx", "A 3218-2022")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="7" ht="15" customHeight="1">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>A 17520-2026</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D7" s="1" t="n">
-        <v>46119</v>
-      </c>
-      <c r="E7" s="1" t="n">
-        <v>46309</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>EKERÖ</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
-      <c r="I7" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="J7" t="n">
-        <v>1</v>
-      </c>
-      <c r="K7" t="n">
-        <v>1</v>
-      </c>
-      <c r="L7" t="n">
-        <v>3</v>
-      </c>
-      <c r="M7" t="n">
-        <v>1</v>
-      </c>
-      <c r="N7" t="n">
-        <v>0</v>
-      </c>
-      <c r="O7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>4</v>
-      </c>
-      <c r="R7" t="n">
-        <v>1</v>
-      </c>
-      <c r="S7" t="n">
-        <v>5</v>
-      </c>
-      <c r="T7" t="n">
-        <v>5</v>
-      </c>
-      <c r="U7" t="n">
-        <v>1</v>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>Läderbagge
-Blekticka
-Ekticka
-Kandelabersvamp
-Gulgrön kantmusseron</t>
-        </is>
-      </c>
-      <c r="W7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/artfynd/A 17520-2026 artfynd.xlsx", "A 17520-2026")</f>
-        <v/>
-      </c>
-      <c r="X7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor/A 17520-2026 karta.png", "A 17520-2026")</f>
-        <v/>
-      </c>
-      <c r="Y7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor_geotiff/A 17520-2026 georefererad karta.tif", "A 17520-2026")</f>
-        <v/>
-      </c>
-      <c r="AA7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomål/A 17520-2026 FSC-klagomål.docx", "A 17520-2026")</f>
-        <v/>
-      </c>
-      <c r="AB7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomålsmail/A 17520-2026 FSC-klagomål mail.docx", "A 17520-2026")</f>
-        <v/>
-      </c>
-      <c r="AC7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsyn/A 17520-2026 tillsynsbegäran.docx", "A 17520-2026")</f>
-        <v/>
-      </c>
-      <c r="AD7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsynsmail/A 17520-2026 tillsynsbegäran mail.docx", "A 17520-2026")</f>
         <v/>
       </c>
     </row>
@@ -1296,7 +1296,7 @@
         <v>46241</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1409,7 +1409,7 @@
         <v>44634</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1499,7 +1499,7 @@
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 49131-2025</t>
+          <t>A 13237-2023</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1513,10 +1513,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>45937</v>
+        <v>45002</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1528,20 +1528,25 @@
           <t>EKERÖ</t>
         </is>
       </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I10" t="n">
-        <v>0.9</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N10" t="n">
         <v>0</v>
@@ -1553,165 +1558,160 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="R10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
         <v>3</v>
       </c>
       <c r="T10" t="n">
+        <v>7</v>
+      </c>
+      <c r="U10" t="n">
+        <v>0</v>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
+        <is>
+          <t>Tallticka
+Granbarkgnagare
+Grönpyrola</t>
+        </is>
+      </c>
+      <c r="W10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/artfynd/A 13237-2023 artfynd.xlsx", "A 13237-2023")</f>
+        <v/>
+      </c>
+      <c r="X10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor/A 13237-2023 karta.png", "A 13237-2023")</f>
+        <v/>
+      </c>
+      <c r="Y10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor_geotiff/A 13237-2023 georefererad karta.tif", "A 13237-2023")</f>
+        <v/>
+      </c>
+      <c r="AA10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomål/A 13237-2023 FSC-klagomål.docx", "A 13237-2023")</f>
+        <v/>
+      </c>
+      <c r="AB10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomålsmail/A 13237-2023 FSC-klagomål mail.docx", "A 13237-2023")</f>
+        <v/>
+      </c>
+      <c r="AC10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsyn/A 13237-2023 tillsynsbegäran.docx", "A 13237-2023")</f>
+        <v/>
+      </c>
+      <c r="AD10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsynsmail/A 13237-2023 tillsynsbegäran mail.docx", "A 13237-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11" ht="15" customHeight="1">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>A 49131-2025</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D11" s="1" t="n">
+        <v>45937</v>
+      </c>
+      <c r="E11" s="1" t="n">
+        <v>46310</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>EKERÖ</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" t="n">
+        <v>2</v>
+      </c>
+      <c r="M11" t="n">
+        <v>1</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" t="n">
         <v>3</v>
       </c>
-      <c r="U10" t="n">
+      <c r="R11" t="n">
+        <v>1</v>
+      </c>
+      <c r="S11" t="n">
         <v>3</v>
       </c>
-      <c r="V10" s="2" t="inlineStr">
+      <c r="T11" t="n">
+        <v>3</v>
+      </c>
+      <c r="U11" t="n">
+        <v>3</v>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
         <is>
           <t>Jättemusseron
 Motaggsvamp
 Svartvit taggsvamp</t>
         </is>
       </c>
-      <c r="W10">
+      <c r="W11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0125/artfynd/A 49131-2025 artfynd.xlsx", "A 49131-2025")</f>
         <v/>
       </c>
-      <c r="X10">
+      <c r="X11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor/A 49131-2025 karta.png", "A 49131-2025")</f>
         <v/>
       </c>
-      <c r="Y10">
+      <c r="Y11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor_geotiff/A 49131-2025 georefererad karta.tif", "A 49131-2025")</f>
         <v/>
       </c>
-      <c r="AA10">
+      <c r="AA11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomål/A 49131-2025 FSC-klagomål.docx", "A 49131-2025")</f>
         <v/>
       </c>
-      <c r="AB10">
+      <c r="AB11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomålsmail/A 49131-2025 FSC-klagomål mail.docx", "A 49131-2025")</f>
         <v/>
       </c>
-      <c r="AC10">
+      <c r="AC11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsyn/A 49131-2025 tillsynsbegäran.docx", "A 49131-2025")</f>
         <v/>
       </c>
-      <c r="AD10">
+      <c r="AD11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsynsmail/A 49131-2025 tillsynsbegäran mail.docx", "A 49131-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="11" ht="15" customHeight="1">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>A 13237-2023</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D11" s="1" t="n">
-        <v>45002</v>
-      </c>
-      <c r="E11" s="1" t="n">
-        <v>46309</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>EKERÖ</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
-      <c r="I11" t="n">
-        <v>9.300000000000001</v>
-      </c>
-      <c r="J11" t="n">
-        <v>0</v>
-      </c>
-      <c r="K11" t="n">
-        <v>2</v>
-      </c>
-      <c r="L11" t="n">
-        <v>1</v>
-      </c>
-      <c r="M11" t="n">
-        <v>0</v>
-      </c>
-      <c r="N11" t="n">
-        <v>0</v>
-      </c>
-      <c r="O11" t="n">
-        <v>0</v>
-      </c>
-      <c r="P11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>1</v>
-      </c>
-      <c r="R11" t="n">
-        <v>0</v>
-      </c>
-      <c r="S11" t="n">
-        <v>3</v>
-      </c>
-      <c r="T11" t="n">
-        <v>7</v>
-      </c>
-      <c r="U11" t="n">
-        <v>0</v>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
-        <is>
-          <t>Tallticka
-Granbarkgnagare
-Grönpyrola</t>
-        </is>
-      </c>
-      <c r="W11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/artfynd/A 13237-2023 artfynd.xlsx", "A 13237-2023")</f>
-        <v/>
-      </c>
-      <c r="X11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor/A 13237-2023 karta.png", "A 13237-2023")</f>
-        <v/>
-      </c>
-      <c r="Y11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor_geotiff/A 13237-2023 georefererad karta.tif", "A 13237-2023")</f>
-        <v/>
-      </c>
-      <c r="AA11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomål/A 13237-2023 FSC-klagomål.docx", "A 13237-2023")</f>
-        <v/>
-      </c>
-      <c r="AB11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomålsmail/A 13237-2023 FSC-klagomål mail.docx", "A 13237-2023")</f>
-        <v/>
-      </c>
-      <c r="AC11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsyn/A 13237-2023 tillsynsbegäran.docx", "A 13237-2023")</f>
-        <v/>
-      </c>
-      <c r="AD11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsynsmail/A 13237-2023 tillsynsbegäran mail.docx", "A 13237-2023")</f>
         <v/>
       </c>
     </row>
@@ -1735,7 +1735,7 @@
         <v>45209</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1850,7 +1850,7 @@
         <v>45170</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1956,7 +1956,7 @@
         <v>44646</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2044,7 +2044,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 2533-2026</t>
+          <t>A 3221-2022</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2058,10 +2058,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>46037</v>
+        <v>44582</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2074,13 +2074,13 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>1.4</v>
+        <v>0.5</v>
       </c>
       <c r="J15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L15" t="n">
         <v>0</v>
@@ -2110,46 +2110,46 @@
         <v>1</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/artfynd/A 2533-2026 artfynd.xlsx", "A 2533-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/artfynd/A 3221-2022 artfynd.xlsx", "A 3221-2022")</f>
         <v/>
       </c>
       <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor/A 2533-2026 karta.png", "A 2533-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor/A 3221-2022 karta.png", "A 3221-2022")</f>
         <v/>
       </c>
       <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor_geotiff/A 2533-2026 georefererad karta.tif", "A 2533-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor_geotiff/A 3221-2022 georefererad karta.tif", "A 3221-2022")</f>
         <v/>
       </c>
       <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomål/A 2533-2026 FSC-klagomål.docx", "A 2533-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomål/A 3221-2022 FSC-klagomål.docx", "A 3221-2022")</f>
         <v/>
       </c>
       <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomålsmail/A 2533-2026 FSC-klagomål mail.docx", "A 2533-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomålsmail/A 3221-2022 FSC-klagomål mail.docx", "A 3221-2022")</f>
         <v/>
       </c>
       <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsyn/A 2533-2026 tillsynsbegäran.docx", "A 2533-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsyn/A 3221-2022 tillsynsbegäran.docx", "A 3221-2022")</f>
         <v/>
       </c>
       <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsynsmail/A 2533-2026 tillsynsbegäran mail.docx", "A 2533-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsynsmail/A 3221-2022 tillsynsbegäran mail.docx", "A 3221-2022")</f>
         <v/>
       </c>
     </row>
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 3221-2022</t>
+          <t>A 13794-2023</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2163,10 +2163,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>44582</v>
+        <v>45007</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2179,16 +2179,16 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>0.5</v>
+        <v>4.8</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M16" t="n">
         <v>0</v>
@@ -2203,7 +2203,7 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R16" t="n">
         <v>0</v>
@@ -2215,46 +2215,46 @@
         <v>1</v>
       </c>
       <c r="U16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/artfynd/A 3221-2022 artfynd.xlsx", "A 3221-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/artfynd/A 13794-2023 artfynd.xlsx", "A 13794-2023")</f>
         <v/>
       </c>
       <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor/A 3221-2022 karta.png", "A 3221-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor/A 13794-2023 karta.png", "A 13794-2023")</f>
         <v/>
       </c>
       <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor_geotiff/A 3221-2022 georefererad karta.tif", "A 3221-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor_geotiff/A 13794-2023 georefererad karta.tif", "A 13794-2023")</f>
         <v/>
       </c>
       <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomål/A 3221-2022 FSC-klagomål.docx", "A 3221-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomål/A 13794-2023 FSC-klagomål.docx", "A 13794-2023")</f>
         <v/>
       </c>
       <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomålsmail/A 3221-2022 FSC-klagomål mail.docx", "A 3221-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomålsmail/A 13794-2023 FSC-klagomål mail.docx", "A 13794-2023")</f>
         <v/>
       </c>
       <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsyn/A 3221-2022 tillsynsbegäran.docx", "A 3221-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsyn/A 13794-2023 tillsynsbegäran.docx", "A 13794-2023")</f>
         <v/>
       </c>
       <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsynsmail/A 3221-2022 tillsynsbegäran mail.docx", "A 3221-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsynsmail/A 13794-2023 tillsynsbegäran mail.docx", "A 13794-2023")</f>
         <v/>
       </c>
     </row>
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 13794-2023</t>
+          <t>A 2533-2026</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2268,10 +2268,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45007</v>
+        <v>46037</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2284,16 +2284,16 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>4.8</v>
+        <v>1.4</v>
       </c>
       <c r="J17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K17" t="n">
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
         <v>0</v>
@@ -2308,7 +2308,7 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
         <v>0</v>
@@ -2324,35 +2324,35 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/artfynd/A 13794-2023 artfynd.xlsx", "A 13794-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/artfynd/A 2533-2026 artfynd.xlsx", "A 2533-2026")</f>
         <v/>
       </c>
       <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor/A 13794-2023 karta.png", "A 13794-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor/A 2533-2026 karta.png", "A 2533-2026")</f>
         <v/>
       </c>
       <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor_geotiff/A 13794-2023 georefererad karta.tif", "A 13794-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor_geotiff/A 2533-2026 georefererad karta.tif", "A 2533-2026")</f>
         <v/>
       </c>
       <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomål/A 13794-2023 FSC-klagomål.docx", "A 13794-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomål/A 2533-2026 FSC-klagomål.docx", "A 2533-2026")</f>
         <v/>
       </c>
       <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomålsmail/A 13794-2023 FSC-klagomål mail.docx", "A 13794-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomålsmail/A 2533-2026 FSC-klagomål mail.docx", "A 2533-2026")</f>
         <v/>
       </c>
       <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsyn/A 13794-2023 tillsynsbegäran.docx", "A 13794-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsyn/A 2533-2026 tillsynsbegäran.docx", "A 2533-2026")</f>
         <v/>
       </c>
       <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsynsmail/A 13794-2023 tillsynsbegäran mail.docx", "A 13794-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsynsmail/A 2533-2026 tillsynsbegäran mail.docx", "A 2533-2026")</f>
         <v/>
       </c>
     </row>
@@ -2376,7 +2376,7 @@
         <v>45671</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2481,7 +2481,7 @@
         <v>44670</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2554,7 +2554,7 @@
         <v>44802</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2610,7 +2610,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 63378-2025</t>
+          <t>A 3219-2022</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2624,10 +2624,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>46010</v>
+        <v>44582</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2640,7 +2640,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>4.8</v>
+        <v>0.5</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2683,7 +2683,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 50184-2023</t>
+          <t>A 55724-2024</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2697,10 +2697,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>45208</v>
+        <v>45622</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2713,7 +2713,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>10.8</v>
+        <v>0.5</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2756,7 +2756,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 2535-2026</t>
+          <t>A 37245-2025</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2770,10 +2770,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>46037</v>
+        <v>45876</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2786,7 +2786,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>1.6</v>
+        <v>1.1</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2829,7 +2829,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 37245-2025</t>
+          <t>A 50184-2023</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2843,10 +2843,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45876</v>
+        <v>45208</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2859,7 +2859,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>1.1</v>
+        <v>10.8</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2902,7 +2902,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 56002-2024</t>
+          <t>A 35955-2023</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2916,10 +2916,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45623</v>
+        <v>45148</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2932,7 +2932,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>3.4</v>
+        <v>1.1</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2975,7 +2975,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 61217-2024</t>
+          <t>A 63378-2025</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2989,10 +2989,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45645</v>
+        <v>46010</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3005,7 +3005,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>0.8</v>
+        <v>4.8</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -3048,7 +3048,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 3222-2022</t>
+          <t>A 20399-2026</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3062,10 +3062,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>44582</v>
+        <v>46139</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3078,7 +3078,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>1.8</v>
+        <v>0.9</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -3121,7 +3121,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 20399-2026</t>
+          <t>A 20398-2026</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3138,7 +3138,7 @@
         <v>46139</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3151,7 +3151,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>0.9</v>
+        <v>2.4</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -3194,7 +3194,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 20398-2026</t>
+          <t>A 2535-2026</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3208,10 +3208,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>46139</v>
+        <v>46037</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3224,7 +3224,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>2.4</v>
+        <v>1.6</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3267,7 +3267,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 3219-2022</t>
+          <t>A 20898-2026</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3281,10 +3281,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>44582</v>
+        <v>46142</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3297,7 +3297,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>0.5</v>
+        <v>3.6</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3340,7 +3340,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 20898-2026</t>
+          <t>A 61217-2024</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3354,10 +3354,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>46142</v>
+        <v>45645</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3370,7 +3370,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>3.6</v>
+        <v>0.8</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3413,7 +3413,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 60755-2024</t>
+          <t>A 56002-2024</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3427,10 +3427,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45644</v>
+        <v>45623</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3443,7 +3443,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>2.1</v>
+        <v>3.4</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3486,7 +3486,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 55724-2024</t>
+          <t>A 60728-2022</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3500,10 +3500,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45622</v>
+        <v>44913</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3516,7 +3516,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>0.5</v>
+        <v>1.2</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3576,7 +3576,7 @@
         <v>45845</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3632,7 +3632,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 35955-2023</t>
+          <t>A 3222-2022</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3646,10 +3646,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45148</v>
+        <v>44582</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3662,7 +3662,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>1.1</v>
+        <v>1.8</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3705,7 +3705,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 60728-2022</t>
+          <t>A 33154-2026</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3719,10 +3719,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>44913</v>
+        <v>46244</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3734,8 +3734,13 @@
           <t>EKERÖ</t>
         </is>
       </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I36" t="n">
-        <v>1.2</v>
+        <v>3.5</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3778,7 +3783,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 33154-2026</t>
+          <t>A 60755-2024</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3792,10 +3797,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>46244</v>
+        <v>45644</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3807,13 +3812,8 @@
           <t>EKERÖ</t>
         </is>
       </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I37" t="n">
-        <v>3.5</v>
+        <v>2.1</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3873,7 +3873,7 @@
         <v>46301</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3951,7 +3951,7 @@
         <v>46153</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>

--- a/Översikt EKERÖ.xlsx
+++ b/Översikt EKERÖ.xlsx
@@ -601,7 +601,7 @@
         <v>46241</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -728,7 +728,7 @@
         <v>44872</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -848,7 +848,7 @@
         <v>44974</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -963,7 +963,7 @@
         <v>45148</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1056,7 +1056,7 @@
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A 17520-2026</t>
+          <t>A 3218-2022</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1070,10 +1070,10 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>46119</v>
+        <v>44582</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1085,13 +1085,8 @@
           <t>EKERÖ</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I6" t="n">
-        <v>2.2</v>
+        <v>1.2</v>
       </c>
       <c r="J6" t="n">
         <v>1</v>
@@ -1100,36 +1095,150 @@
         <v>1</v>
       </c>
       <c r="L6" t="n">
+        <v>1</v>
+      </c>
+      <c r="M6" t="n">
+        <v>1</v>
+      </c>
+      <c r="N6" t="n">
+        <v>1</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" t="n">
         <v>3</v>
       </c>
-      <c r="M6" t="n">
-        <v>1</v>
-      </c>
-      <c r="N6" t="n">
-        <v>0</v>
-      </c>
-      <c r="O6" t="n">
-        <v>0</v>
-      </c>
-      <c r="P6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>4</v>
-      </c>
       <c r="R6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
       </c>
       <c r="T6" t="n">
+        <v>8</v>
+      </c>
+      <c r="U6" t="n">
+        <v>6</v>
+      </c>
+      <c r="V6" s="2" t="inlineStr">
+        <is>
+          <t>Bombmurkla
+Gul lammticka
+Fyrflikig jordstjärna
+Kamjordstjärna
+Blåbär</t>
+        </is>
+      </c>
+      <c r="W6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/artfynd/A 3218-2022 artfynd.xlsx", "A 3218-2022")</f>
+        <v/>
+      </c>
+      <c r="X6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor/A 3218-2022 karta.png", "A 3218-2022")</f>
+        <v/>
+      </c>
+      <c r="Y6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor_geotiff/A 3218-2022 georefererad karta.tif", "A 3218-2022")</f>
+        <v/>
+      </c>
+      <c r="AA6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomål/A 3218-2022 FSC-klagomål.docx", "A 3218-2022")</f>
+        <v/>
+      </c>
+      <c r="AB6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomålsmail/A 3218-2022 FSC-klagomål mail.docx", "A 3218-2022")</f>
+        <v/>
+      </c>
+      <c r="AC6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsyn/A 3218-2022 tillsynsbegäran.docx", "A 3218-2022")</f>
+        <v/>
+      </c>
+      <c r="AD6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsynsmail/A 3218-2022 tillsynsbegäran mail.docx", "A 3218-2022")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7" ht="15" customHeight="1">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>A 17520-2026</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D7" s="1" t="n">
+        <v>46119</v>
+      </c>
+      <c r="E7" s="1" t="n">
+        <v>46311</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>EKERÖ</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="J7" t="n">
+        <v>1</v>
+      </c>
+      <c r="K7" t="n">
+        <v>1</v>
+      </c>
+      <c r="L7" t="n">
+        <v>3</v>
+      </c>
+      <c r="M7" t="n">
+        <v>1</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>4</v>
+      </c>
+      <c r="R7" t="n">
+        <v>1</v>
+      </c>
+      <c r="S7" t="n">
         <v>5</v>
       </c>
-      <c r="U6" t="n">
-        <v>1</v>
-      </c>
-      <c r="V6" s="2" t="inlineStr">
+      <c r="T7" t="n">
+        <v>5</v>
+      </c>
+      <c r="U7" t="n">
+        <v>1</v>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
         <is>
           <t>Läderbagge
 Blekticka
@@ -1138,141 +1247,32 @@
 Gulgrön kantmusseron</t>
         </is>
       </c>
-      <c r="W6">
+      <c r="W7">
         <f>HYPERLINK("https://klasma.github.io/Logging_0125/artfynd/A 17520-2026 artfynd.xlsx", "A 17520-2026")</f>
         <v/>
       </c>
-      <c r="X6">
+      <c r="X7">
         <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor/A 17520-2026 karta.png", "A 17520-2026")</f>
         <v/>
       </c>
-      <c r="Y6">
+      <c r="Y7">
         <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor_geotiff/A 17520-2026 georefererad karta.tif", "A 17520-2026")</f>
         <v/>
       </c>
-      <c r="AA6">
+      <c r="AA7">
         <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomål/A 17520-2026 FSC-klagomål.docx", "A 17520-2026")</f>
         <v/>
       </c>
-      <c r="AB6">
+      <c r="AB7">
         <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomålsmail/A 17520-2026 FSC-klagomål mail.docx", "A 17520-2026")</f>
         <v/>
       </c>
-      <c r="AC6">
+      <c r="AC7">
         <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsyn/A 17520-2026 tillsynsbegäran.docx", "A 17520-2026")</f>
         <v/>
       </c>
-      <c r="AD6">
+      <c r="AD7">
         <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsynsmail/A 17520-2026 tillsynsbegäran mail.docx", "A 17520-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="7" ht="15" customHeight="1">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>A 3218-2022</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D7" s="1" t="n">
-        <v>44582</v>
-      </c>
-      <c r="E7" s="1" t="n">
-        <v>46310</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>EKERÖ</t>
-        </is>
-      </c>
-      <c r="I7" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="J7" t="n">
-        <v>1</v>
-      </c>
-      <c r="K7" t="n">
-        <v>1</v>
-      </c>
-      <c r="L7" t="n">
-        <v>1</v>
-      </c>
-      <c r="M7" t="n">
-        <v>1</v>
-      </c>
-      <c r="N7" t="n">
-        <v>1</v>
-      </c>
-      <c r="O7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>3</v>
-      </c>
-      <c r="R7" t="n">
-        <v>2</v>
-      </c>
-      <c r="S7" t="n">
-        <v>5</v>
-      </c>
-      <c r="T7" t="n">
-        <v>8</v>
-      </c>
-      <c r="U7" t="n">
-        <v>6</v>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>Bombmurkla
-Gul lammticka
-Fyrflikig jordstjärna
-Kamjordstjärna
-Blåbär</t>
-        </is>
-      </c>
-      <c r="W7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/artfynd/A 3218-2022 artfynd.xlsx", "A 3218-2022")</f>
-        <v/>
-      </c>
-      <c r="X7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor/A 3218-2022 karta.png", "A 3218-2022")</f>
-        <v/>
-      </c>
-      <c r="Y7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor_geotiff/A 3218-2022 georefererad karta.tif", "A 3218-2022")</f>
-        <v/>
-      </c>
-      <c r="AA7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomål/A 3218-2022 FSC-klagomål.docx", "A 3218-2022")</f>
-        <v/>
-      </c>
-      <c r="AB7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomålsmail/A 3218-2022 FSC-klagomål mail.docx", "A 3218-2022")</f>
-        <v/>
-      </c>
-      <c r="AC7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsyn/A 3218-2022 tillsynsbegäran.docx", "A 3218-2022")</f>
-        <v/>
-      </c>
-      <c r="AD7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsynsmail/A 3218-2022 tillsynsbegäran mail.docx", "A 3218-2022")</f>
         <v/>
       </c>
     </row>
@@ -1296,7 +1296,7 @@
         <v>46241</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1409,7 +1409,7 @@
         <v>44634</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1499,7 +1499,7 @@
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 13237-2023</t>
+          <t>A 49131-2025</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1513,10 +1513,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>45002</v>
+        <v>45937</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1528,25 +1528,20 @@
           <t>EKERÖ</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I10" t="n">
-        <v>9.300000000000001</v>
+        <v>0.9</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
       </c>
       <c r="K10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" t="n">
         <v>2</v>
       </c>
-      <c r="L10" t="n">
-        <v>1</v>
-      </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N10" t="n">
         <v>0</v>
@@ -1558,160 +1553,165 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S10" t="n">
         <v>3</v>
       </c>
       <c r="T10" t="n">
+        <v>3</v>
+      </c>
+      <c r="U10" t="n">
+        <v>3</v>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
+        <is>
+          <t>Jättemusseron
+Motaggsvamp
+Svartvit taggsvamp</t>
+        </is>
+      </c>
+      <c r="W10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/artfynd/A 49131-2025 artfynd.xlsx", "A 49131-2025")</f>
+        <v/>
+      </c>
+      <c r="X10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor/A 49131-2025 karta.png", "A 49131-2025")</f>
+        <v/>
+      </c>
+      <c r="Y10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor_geotiff/A 49131-2025 georefererad karta.tif", "A 49131-2025")</f>
+        <v/>
+      </c>
+      <c r="AA10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomål/A 49131-2025 FSC-klagomål.docx", "A 49131-2025")</f>
+        <v/>
+      </c>
+      <c r="AB10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomålsmail/A 49131-2025 FSC-klagomål mail.docx", "A 49131-2025")</f>
+        <v/>
+      </c>
+      <c r="AC10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsyn/A 49131-2025 tillsynsbegäran.docx", "A 49131-2025")</f>
+        <v/>
+      </c>
+      <c r="AD10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsynsmail/A 49131-2025 tillsynsbegäran mail.docx", "A 49131-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11" ht="15" customHeight="1">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>A 13237-2023</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D11" s="1" t="n">
+        <v>45002</v>
+      </c>
+      <c r="E11" s="1" t="n">
+        <v>46311</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>EKERÖ</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" t="n">
+        <v>2</v>
+      </c>
+      <c r="L11" t="n">
+        <v>1</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>1</v>
+      </c>
+      <c r="R11" t="n">
+        <v>0</v>
+      </c>
+      <c r="S11" t="n">
+        <v>3</v>
+      </c>
+      <c r="T11" t="n">
         <v>7</v>
       </c>
-      <c r="U10" t="n">
-        <v>0</v>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
+      <c r="U11" t="n">
+        <v>0</v>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
         <is>
           <t>Tallticka
 Granbarkgnagare
 Grönpyrola</t>
         </is>
       </c>
-      <c r="W10">
+      <c r="W11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0125/artfynd/A 13237-2023 artfynd.xlsx", "A 13237-2023")</f>
         <v/>
       </c>
-      <c r="X10">
+      <c r="X11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor/A 13237-2023 karta.png", "A 13237-2023")</f>
         <v/>
       </c>
-      <c r="Y10">
+      <c r="Y11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor_geotiff/A 13237-2023 georefererad karta.tif", "A 13237-2023")</f>
         <v/>
       </c>
-      <c r="AA10">
+      <c r="AA11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomål/A 13237-2023 FSC-klagomål.docx", "A 13237-2023")</f>
         <v/>
       </c>
-      <c r="AB10">
+      <c r="AB11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomålsmail/A 13237-2023 FSC-klagomål mail.docx", "A 13237-2023")</f>
         <v/>
       </c>
-      <c r="AC10">
+      <c r="AC11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsyn/A 13237-2023 tillsynsbegäran.docx", "A 13237-2023")</f>
         <v/>
       </c>
-      <c r="AD10">
+      <c r="AD11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsynsmail/A 13237-2023 tillsynsbegäran mail.docx", "A 13237-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="11" ht="15" customHeight="1">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>A 49131-2025</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D11" s="1" t="n">
-        <v>45937</v>
-      </c>
-      <c r="E11" s="1" t="n">
-        <v>46310</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>EKERÖ</t>
-        </is>
-      </c>
-      <c r="I11" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="J11" t="n">
-        <v>0</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L11" t="n">
-        <v>2</v>
-      </c>
-      <c r="M11" t="n">
-        <v>1</v>
-      </c>
-      <c r="N11" t="n">
-        <v>0</v>
-      </c>
-      <c r="O11" t="n">
-        <v>0</v>
-      </c>
-      <c r="P11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>3</v>
-      </c>
-      <c r="R11" t="n">
-        <v>1</v>
-      </c>
-      <c r="S11" t="n">
-        <v>3</v>
-      </c>
-      <c r="T11" t="n">
-        <v>3</v>
-      </c>
-      <c r="U11" t="n">
-        <v>3</v>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
-        <is>
-          <t>Jättemusseron
-Motaggsvamp
-Svartvit taggsvamp</t>
-        </is>
-      </c>
-      <c r="W11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/artfynd/A 49131-2025 artfynd.xlsx", "A 49131-2025")</f>
-        <v/>
-      </c>
-      <c r="X11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor/A 49131-2025 karta.png", "A 49131-2025")</f>
-        <v/>
-      </c>
-      <c r="Y11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor_geotiff/A 49131-2025 georefererad karta.tif", "A 49131-2025")</f>
-        <v/>
-      </c>
-      <c r="AA11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomål/A 49131-2025 FSC-klagomål.docx", "A 49131-2025")</f>
-        <v/>
-      </c>
-      <c r="AB11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomålsmail/A 49131-2025 FSC-klagomål mail.docx", "A 49131-2025")</f>
-        <v/>
-      </c>
-      <c r="AC11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsyn/A 49131-2025 tillsynsbegäran.docx", "A 49131-2025")</f>
-        <v/>
-      </c>
-      <c r="AD11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsynsmail/A 49131-2025 tillsynsbegäran mail.docx", "A 49131-2025")</f>
         <v/>
       </c>
     </row>
@@ -1735,7 +1735,7 @@
         <v>45209</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1850,7 +1850,7 @@
         <v>45170</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1956,7 +1956,7 @@
         <v>44646</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2061,7 +2061,7 @@
         <v>44582</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2166,7 +2166,7 @@
         <v>45007</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2254,7 +2254,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 2533-2026</t>
+          <t>A 1793-2025</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2268,10 +2268,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>46037</v>
+        <v>45671</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2284,7 +2284,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>1.4</v>
+        <v>1.7</v>
       </c>
       <c r="J17" t="n">
         <v>1</v>
@@ -2317,49 +2317,49 @@
         <v>1</v>
       </c>
       <c r="T17" t="n">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="U17" t="n">
         <v>0</v>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Mistel</t>
         </is>
       </c>
       <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/artfynd/A 2533-2026 artfynd.xlsx", "A 2533-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/artfynd/A 1793-2025 artfynd.xlsx", "A 1793-2025")</f>
         <v/>
       </c>
       <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor/A 2533-2026 karta.png", "A 2533-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor/A 1793-2025 karta.png", "A 1793-2025")</f>
         <v/>
       </c>
       <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor_geotiff/A 2533-2026 georefererad karta.tif", "A 2533-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor_geotiff/A 1793-2025 georefererad karta.tif", "A 1793-2025")</f>
         <v/>
       </c>
       <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomål/A 2533-2026 FSC-klagomål.docx", "A 2533-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomål/A 1793-2025 FSC-klagomål.docx", "A 1793-2025")</f>
         <v/>
       </c>
       <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomålsmail/A 2533-2026 FSC-klagomål mail.docx", "A 2533-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomålsmail/A 1793-2025 FSC-klagomål mail.docx", "A 1793-2025")</f>
         <v/>
       </c>
       <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsyn/A 2533-2026 tillsynsbegäran.docx", "A 2533-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsyn/A 1793-2025 tillsynsbegäran.docx", "A 1793-2025")</f>
         <v/>
       </c>
       <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsynsmail/A 2533-2026 tillsynsbegäran mail.docx", "A 2533-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsynsmail/A 1793-2025 tillsynsbegäran mail.docx", "A 1793-2025")</f>
         <v/>
       </c>
     </row>
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 1793-2025</t>
+          <t>A 2533-2026</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2373,10 +2373,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45671</v>
+        <v>46037</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2389,7 +2389,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>1.7</v>
+        <v>1.4</v>
       </c>
       <c r="J18" t="n">
         <v>1</v>
@@ -2422,42 +2422,42 @@
         <v>1</v>
       </c>
       <c r="T18" t="n">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="U18" t="n">
         <v>0</v>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>Mistel</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="W18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/artfynd/A 1793-2025 artfynd.xlsx", "A 1793-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/artfynd/A 2533-2026 artfynd.xlsx", "A 2533-2026")</f>
         <v/>
       </c>
       <c r="X18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor/A 1793-2025 karta.png", "A 1793-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor/A 2533-2026 karta.png", "A 2533-2026")</f>
         <v/>
       </c>
       <c r="Y18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor_geotiff/A 1793-2025 georefererad karta.tif", "A 1793-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor_geotiff/A 2533-2026 georefererad karta.tif", "A 2533-2026")</f>
         <v/>
       </c>
       <c r="AA18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomål/A 1793-2025 FSC-klagomål.docx", "A 1793-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomål/A 2533-2026 FSC-klagomål.docx", "A 2533-2026")</f>
         <v/>
       </c>
       <c r="AB18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomålsmail/A 1793-2025 FSC-klagomål mail.docx", "A 1793-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomålsmail/A 2533-2026 FSC-klagomål mail.docx", "A 2533-2026")</f>
         <v/>
       </c>
       <c r="AC18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsyn/A 1793-2025 tillsynsbegäran.docx", "A 1793-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsyn/A 2533-2026 tillsynsbegäran.docx", "A 2533-2026")</f>
         <v/>
       </c>
       <c r="AD18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsynsmail/A 1793-2025 tillsynsbegäran mail.docx", "A 1793-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsynsmail/A 2533-2026 tillsynsbegäran mail.docx", "A 2533-2026")</f>
         <v/>
       </c>
     </row>
@@ -2481,7 +2481,7 @@
         <v>44670</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2554,7 +2554,7 @@
         <v>44802</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2610,7 +2610,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 3219-2022</t>
+          <t>A 3222-2022</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2627,7 +2627,7 @@
         <v>44582</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2640,7 +2640,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>0.5</v>
+        <v>1.8</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2683,7 +2683,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 55724-2024</t>
+          <t>A 37245-2025</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2697,10 +2697,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>45622</v>
+        <v>45876</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2713,7 +2713,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>0.5</v>
+        <v>1.1</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2756,7 +2756,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 37245-2025</t>
+          <t>A 50184-2023</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2770,10 +2770,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45876</v>
+        <v>45208</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2786,7 +2786,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>1.1</v>
+        <v>10.8</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2829,7 +2829,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 50184-2023</t>
+          <t>A 3219-2022</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2843,10 +2843,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45208</v>
+        <v>44582</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2859,7 +2859,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>10.8</v>
+        <v>0.5</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2902,7 +2902,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 35955-2023</t>
+          <t>A 60755-2024</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2916,10 +2916,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45148</v>
+        <v>45644</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2932,7 +2932,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>1.1</v>
+        <v>2.1</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2975,7 +2975,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 63378-2025</t>
+          <t>A 55724-2024</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2989,10 +2989,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>46010</v>
+        <v>45622</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3005,7 +3005,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>4.8</v>
+        <v>0.5</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -3048,7 +3048,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 20399-2026</t>
+          <t>A 56002-2024</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3062,10 +3062,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>46139</v>
+        <v>45623</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3078,7 +3078,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>0.9</v>
+        <v>3.4</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -3121,7 +3121,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 20398-2026</t>
+          <t>A 35955-2023</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3135,10 +3135,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>46139</v>
+        <v>45148</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3151,7 +3151,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>2.4</v>
+        <v>1.1</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -3194,7 +3194,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 2535-2026</t>
+          <t>A 20399-2026</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3208,10 +3208,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>46037</v>
+        <v>46139</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3224,7 +3224,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>1.6</v>
+        <v>0.9</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3267,7 +3267,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 20898-2026</t>
+          <t>A 20398-2026</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3281,10 +3281,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>46142</v>
+        <v>46139</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3297,7 +3297,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>3.6</v>
+        <v>2.4</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3357,7 +3357,7 @@
         <v>45645</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3413,7 +3413,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 56002-2024</t>
+          <t>A 20898-2026</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3427,10 +3427,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45623</v>
+        <v>46142</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3443,7 +3443,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3486,7 +3486,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 60728-2022</t>
+          <t>A 34073-2025</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3496,14 +3496,14 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>44913</v>
+        <v>45845</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3516,7 +3516,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>1.2</v>
+        <v>2.9</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3559,7 +3559,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 34073-2025</t>
+          <t>A 60728-2022</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3569,14 +3569,14 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45845</v>
+        <v>44913</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3589,7 +3589,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>2.9</v>
+        <v>1.2</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3632,7 +3632,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 3222-2022</t>
+          <t>A 33154-2026</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3646,10 +3646,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>44582</v>
+        <v>46244</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3661,8 +3661,13 @@
           <t>EKERÖ</t>
         </is>
       </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I35" t="n">
-        <v>1.8</v>
+        <v>3.5</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3705,7 +3710,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 33154-2026</t>
+          <t>A 63378-2025</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3719,10 +3724,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>46244</v>
+        <v>46010</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3734,13 +3739,8 @@
           <t>EKERÖ</t>
         </is>
       </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I36" t="n">
-        <v>3.5</v>
+        <v>4.8</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3783,7 +3783,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 60755-2024</t>
+          <t>A 41699-2026</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3797,10 +3797,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45644</v>
+        <v>46301</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3812,8 +3812,13 @@
           <t>EKERÖ</t>
         </is>
       </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I37" t="n">
-        <v>2.1</v>
+        <v>1.6</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3856,7 +3861,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 41699-2026</t>
+          <t>A 2535-2026</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3870,10 +3875,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>46301</v>
+        <v>46037</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3883,11 +3888,6 @@
       <c r="G38" t="inlineStr">
         <is>
           <t>EKERÖ</t>
-        </is>
-      </c>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
         </is>
       </c>
       <c r="I38" t="n">
@@ -3951,7 +3951,7 @@
         <v>46153</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>

--- a/Översikt EKERÖ.xlsx
+++ b/Översikt EKERÖ.xlsx
@@ -601,7 +601,7 @@
         <v>46241</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -728,7 +728,7 @@
         <v>44872</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -848,7 +848,7 @@
         <v>44974</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -963,7 +963,7 @@
         <v>45148</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1056,7 +1056,7 @@
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A 3218-2022</t>
+          <t>A 17520-2026</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1070,10 +1070,10 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>44582</v>
+        <v>46119</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1085,8 +1085,13 @@
           <t>EKERÖ</t>
         </is>
       </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I6" t="n">
-        <v>1.2</v>
+        <v>2.2</v>
       </c>
       <c r="J6" t="n">
         <v>1</v>
@@ -1095,13 +1100,13 @@
         <v>1</v>
       </c>
       <c r="L6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M6" t="n">
         <v>1</v>
       </c>
       <c r="N6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1110,21 +1115,130 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="R6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
       </c>
       <c r="T6" t="n">
+        <v>5</v>
+      </c>
+      <c r="U6" t="n">
+        <v>1</v>
+      </c>
+      <c r="V6" s="2" t="inlineStr">
+        <is>
+          <t>Läderbagge
+Blekticka
+Ekticka
+Kandelabersvamp
+Gulgrön kantmusseron</t>
+        </is>
+      </c>
+      <c r="W6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/artfynd/A 17520-2026 artfynd.xlsx", "A 17520-2026")</f>
+        <v/>
+      </c>
+      <c r="X6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor/A 17520-2026 karta.png", "A 17520-2026")</f>
+        <v/>
+      </c>
+      <c r="Y6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor_geotiff/A 17520-2026 georefererad karta.tif", "A 17520-2026")</f>
+        <v/>
+      </c>
+      <c r="AA6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomål/A 17520-2026 FSC-klagomål.docx", "A 17520-2026")</f>
+        <v/>
+      </c>
+      <c r="AB6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomålsmail/A 17520-2026 FSC-klagomål mail.docx", "A 17520-2026")</f>
+        <v/>
+      </c>
+      <c r="AC6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsyn/A 17520-2026 tillsynsbegäran.docx", "A 17520-2026")</f>
+        <v/>
+      </c>
+      <c r="AD6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsynsmail/A 17520-2026 tillsynsbegäran mail.docx", "A 17520-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7" ht="15" customHeight="1">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>A 3218-2022</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D7" s="1" t="n">
+        <v>44582</v>
+      </c>
+      <c r="E7" s="1" t="n">
+        <v>46312</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>EKERÖ</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="J7" t="n">
+        <v>1</v>
+      </c>
+      <c r="K7" t="n">
+        <v>1</v>
+      </c>
+      <c r="L7" t="n">
+        <v>1</v>
+      </c>
+      <c r="M7" t="n">
+        <v>1</v>
+      </c>
+      <c r="N7" t="n">
+        <v>1</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>3</v>
+      </c>
+      <c r="R7" t="n">
+        <v>2</v>
+      </c>
+      <c r="S7" t="n">
+        <v>5</v>
+      </c>
+      <c r="T7" t="n">
         <v>8</v>
       </c>
-      <c r="U6" t="n">
+      <c r="U7" t="n">
         <v>6</v>
       </c>
-      <c r="V6" s="2" t="inlineStr">
+      <c r="V7" s="2" t="inlineStr">
         <is>
           <t>Bombmurkla
 Gul lammticka
@@ -1133,146 +1247,32 @@
 Blåbär</t>
         </is>
       </c>
-      <c r="W6">
+      <c r="W7">
         <f>HYPERLINK("https://klasma.github.io/Logging_0125/artfynd/A 3218-2022 artfynd.xlsx", "A 3218-2022")</f>
         <v/>
       </c>
-      <c r="X6">
+      <c r="X7">
         <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor/A 3218-2022 karta.png", "A 3218-2022")</f>
         <v/>
       </c>
-      <c r="Y6">
+      <c r="Y7">
         <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor_geotiff/A 3218-2022 georefererad karta.tif", "A 3218-2022")</f>
         <v/>
       </c>
-      <c r="AA6">
+      <c r="AA7">
         <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomål/A 3218-2022 FSC-klagomål.docx", "A 3218-2022")</f>
         <v/>
       </c>
-      <c r="AB6">
+      <c r="AB7">
         <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomålsmail/A 3218-2022 FSC-klagomål mail.docx", "A 3218-2022")</f>
         <v/>
       </c>
-      <c r="AC6">
+      <c r="AC7">
         <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsyn/A 3218-2022 tillsynsbegäran.docx", "A 3218-2022")</f>
         <v/>
       </c>
-      <c r="AD6">
+      <c r="AD7">
         <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsynsmail/A 3218-2022 tillsynsbegäran mail.docx", "A 3218-2022")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="7" ht="15" customHeight="1">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>A 17520-2026</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D7" s="1" t="n">
-        <v>46119</v>
-      </c>
-      <c r="E7" s="1" t="n">
-        <v>46311</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>EKERÖ</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
-      <c r="I7" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="J7" t="n">
-        <v>1</v>
-      </c>
-      <c r="K7" t="n">
-        <v>1</v>
-      </c>
-      <c r="L7" t="n">
-        <v>3</v>
-      </c>
-      <c r="M7" t="n">
-        <v>1</v>
-      </c>
-      <c r="N7" t="n">
-        <v>0</v>
-      </c>
-      <c r="O7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>4</v>
-      </c>
-      <c r="R7" t="n">
-        <v>1</v>
-      </c>
-      <c r="S7" t="n">
-        <v>5</v>
-      </c>
-      <c r="T7" t="n">
-        <v>5</v>
-      </c>
-      <c r="U7" t="n">
-        <v>1</v>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>Läderbagge
-Blekticka
-Ekticka
-Kandelabersvamp
-Gulgrön kantmusseron</t>
-        </is>
-      </c>
-      <c r="W7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/artfynd/A 17520-2026 artfynd.xlsx", "A 17520-2026")</f>
-        <v/>
-      </c>
-      <c r="X7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor/A 17520-2026 karta.png", "A 17520-2026")</f>
-        <v/>
-      </c>
-      <c r="Y7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor_geotiff/A 17520-2026 georefererad karta.tif", "A 17520-2026")</f>
-        <v/>
-      </c>
-      <c r="AA7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomål/A 17520-2026 FSC-klagomål.docx", "A 17520-2026")</f>
-        <v/>
-      </c>
-      <c r="AB7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomålsmail/A 17520-2026 FSC-klagomål mail.docx", "A 17520-2026")</f>
-        <v/>
-      </c>
-      <c r="AC7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsyn/A 17520-2026 tillsynsbegäran.docx", "A 17520-2026")</f>
-        <v/>
-      </c>
-      <c r="AD7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsynsmail/A 17520-2026 tillsynsbegäran mail.docx", "A 17520-2026")</f>
         <v/>
       </c>
     </row>
@@ -1296,7 +1296,7 @@
         <v>46241</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1409,7 +1409,7 @@
         <v>44634</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1499,7 +1499,7 @@
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 49131-2025</t>
+          <t>A 13237-2023</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1513,10 +1513,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>45937</v>
+        <v>45002</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1528,20 +1528,25 @@
           <t>EKERÖ</t>
         </is>
       </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I10" t="n">
-        <v>0.9</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N10" t="n">
         <v>0</v>
@@ -1553,165 +1558,160 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="R10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
         <v>3</v>
       </c>
       <c r="T10" t="n">
+        <v>7</v>
+      </c>
+      <c r="U10" t="n">
+        <v>0</v>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
+        <is>
+          <t>Tallticka
+Granbarkgnagare
+Grönpyrola</t>
+        </is>
+      </c>
+      <c r="W10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/artfynd/A 13237-2023 artfynd.xlsx", "A 13237-2023")</f>
+        <v/>
+      </c>
+      <c r="X10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor/A 13237-2023 karta.png", "A 13237-2023")</f>
+        <v/>
+      </c>
+      <c r="Y10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor_geotiff/A 13237-2023 georefererad karta.tif", "A 13237-2023")</f>
+        <v/>
+      </c>
+      <c r="AA10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomål/A 13237-2023 FSC-klagomål.docx", "A 13237-2023")</f>
+        <v/>
+      </c>
+      <c r="AB10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomålsmail/A 13237-2023 FSC-klagomål mail.docx", "A 13237-2023")</f>
+        <v/>
+      </c>
+      <c r="AC10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsyn/A 13237-2023 tillsynsbegäran.docx", "A 13237-2023")</f>
+        <v/>
+      </c>
+      <c r="AD10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsynsmail/A 13237-2023 tillsynsbegäran mail.docx", "A 13237-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11" ht="15" customHeight="1">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>A 49131-2025</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D11" s="1" t="n">
+        <v>45937</v>
+      </c>
+      <c r="E11" s="1" t="n">
+        <v>46312</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>EKERÖ</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" t="n">
+        <v>2</v>
+      </c>
+      <c r="M11" t="n">
+        <v>1</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" t="n">
         <v>3</v>
       </c>
-      <c r="U10" t="n">
+      <c r="R11" t="n">
+        <v>1</v>
+      </c>
+      <c r="S11" t="n">
         <v>3</v>
       </c>
-      <c r="V10" s="2" t="inlineStr">
+      <c r="T11" t="n">
+        <v>3</v>
+      </c>
+      <c r="U11" t="n">
+        <v>3</v>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
         <is>
           <t>Jättemusseron
 Motaggsvamp
 Svartvit taggsvamp</t>
         </is>
       </c>
-      <c r="W10">
+      <c r="W11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0125/artfynd/A 49131-2025 artfynd.xlsx", "A 49131-2025")</f>
         <v/>
       </c>
-      <c r="X10">
+      <c r="X11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor/A 49131-2025 karta.png", "A 49131-2025")</f>
         <v/>
       </c>
-      <c r="Y10">
+      <c r="Y11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor_geotiff/A 49131-2025 georefererad karta.tif", "A 49131-2025")</f>
         <v/>
       </c>
-      <c r="AA10">
+      <c r="AA11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomål/A 49131-2025 FSC-klagomål.docx", "A 49131-2025")</f>
         <v/>
       </c>
-      <c r="AB10">
+      <c r="AB11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomålsmail/A 49131-2025 FSC-klagomål mail.docx", "A 49131-2025")</f>
         <v/>
       </c>
-      <c r="AC10">
+      <c r="AC11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsyn/A 49131-2025 tillsynsbegäran.docx", "A 49131-2025")</f>
         <v/>
       </c>
-      <c r="AD10">
+      <c r="AD11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsynsmail/A 49131-2025 tillsynsbegäran mail.docx", "A 49131-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="11" ht="15" customHeight="1">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>A 13237-2023</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D11" s="1" t="n">
-        <v>45002</v>
-      </c>
-      <c r="E11" s="1" t="n">
-        <v>46311</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>EKERÖ</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
-      <c r="I11" t="n">
-        <v>9.300000000000001</v>
-      </c>
-      <c r="J11" t="n">
-        <v>0</v>
-      </c>
-      <c r="K11" t="n">
-        <v>2</v>
-      </c>
-      <c r="L11" t="n">
-        <v>1</v>
-      </c>
-      <c r="M11" t="n">
-        <v>0</v>
-      </c>
-      <c r="N11" t="n">
-        <v>0</v>
-      </c>
-      <c r="O11" t="n">
-        <v>0</v>
-      </c>
-      <c r="P11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>1</v>
-      </c>
-      <c r="R11" t="n">
-        <v>0</v>
-      </c>
-      <c r="S11" t="n">
-        <v>3</v>
-      </c>
-      <c r="T11" t="n">
-        <v>7</v>
-      </c>
-      <c r="U11" t="n">
-        <v>0</v>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
-        <is>
-          <t>Tallticka
-Granbarkgnagare
-Grönpyrola</t>
-        </is>
-      </c>
-      <c r="W11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/artfynd/A 13237-2023 artfynd.xlsx", "A 13237-2023")</f>
-        <v/>
-      </c>
-      <c r="X11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor/A 13237-2023 karta.png", "A 13237-2023")</f>
-        <v/>
-      </c>
-      <c r="Y11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor_geotiff/A 13237-2023 georefererad karta.tif", "A 13237-2023")</f>
-        <v/>
-      </c>
-      <c r="AA11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomål/A 13237-2023 FSC-klagomål.docx", "A 13237-2023")</f>
-        <v/>
-      </c>
-      <c r="AB11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomålsmail/A 13237-2023 FSC-klagomål mail.docx", "A 13237-2023")</f>
-        <v/>
-      </c>
-      <c r="AC11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsyn/A 13237-2023 tillsynsbegäran.docx", "A 13237-2023")</f>
-        <v/>
-      </c>
-      <c r="AD11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsynsmail/A 13237-2023 tillsynsbegäran mail.docx", "A 13237-2023")</f>
         <v/>
       </c>
     </row>
@@ -1735,7 +1735,7 @@
         <v>45209</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1850,7 +1850,7 @@
         <v>45170</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1956,7 +1956,7 @@
         <v>44646</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2061,7 +2061,7 @@
         <v>44582</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2166,7 +2166,7 @@
         <v>45007</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2254,7 +2254,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 1793-2025</t>
+          <t>A 2533-2026</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2268,10 +2268,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45671</v>
+        <v>46037</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2284,7 +2284,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>1.7</v>
+        <v>1.4</v>
       </c>
       <c r="J17" t="n">
         <v>1</v>
@@ -2317,49 +2317,49 @@
         <v>1</v>
       </c>
       <c r="T17" t="n">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="U17" t="n">
         <v>0</v>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>Mistel</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/artfynd/A 1793-2025 artfynd.xlsx", "A 1793-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/artfynd/A 2533-2026 artfynd.xlsx", "A 2533-2026")</f>
         <v/>
       </c>
       <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor/A 1793-2025 karta.png", "A 1793-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor/A 2533-2026 karta.png", "A 2533-2026")</f>
         <v/>
       </c>
       <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor_geotiff/A 1793-2025 georefererad karta.tif", "A 1793-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor_geotiff/A 2533-2026 georefererad karta.tif", "A 2533-2026")</f>
         <v/>
       </c>
       <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomål/A 1793-2025 FSC-klagomål.docx", "A 1793-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomål/A 2533-2026 FSC-klagomål.docx", "A 2533-2026")</f>
         <v/>
       </c>
       <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomålsmail/A 1793-2025 FSC-klagomål mail.docx", "A 1793-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomålsmail/A 2533-2026 FSC-klagomål mail.docx", "A 2533-2026")</f>
         <v/>
       </c>
       <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsyn/A 1793-2025 tillsynsbegäran.docx", "A 1793-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsyn/A 2533-2026 tillsynsbegäran.docx", "A 2533-2026")</f>
         <v/>
       </c>
       <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsynsmail/A 1793-2025 tillsynsbegäran mail.docx", "A 1793-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsynsmail/A 2533-2026 tillsynsbegäran mail.docx", "A 2533-2026")</f>
         <v/>
       </c>
     </row>
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 2533-2026</t>
+          <t>A 1793-2025</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2373,10 +2373,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>46037</v>
+        <v>45671</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2389,7 +2389,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>1.4</v>
+        <v>1.7</v>
       </c>
       <c r="J18" t="n">
         <v>1</v>
@@ -2422,42 +2422,42 @@
         <v>1</v>
       </c>
       <c r="T18" t="n">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="U18" t="n">
         <v>0</v>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Mistel</t>
         </is>
       </c>
       <c r="W18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/artfynd/A 2533-2026 artfynd.xlsx", "A 2533-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/artfynd/A 1793-2025 artfynd.xlsx", "A 1793-2025")</f>
         <v/>
       </c>
       <c r="X18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor/A 2533-2026 karta.png", "A 2533-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor/A 1793-2025 karta.png", "A 1793-2025")</f>
         <v/>
       </c>
       <c r="Y18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor_geotiff/A 2533-2026 georefererad karta.tif", "A 2533-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor_geotiff/A 1793-2025 georefererad karta.tif", "A 1793-2025")</f>
         <v/>
       </c>
       <c r="AA18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomål/A 2533-2026 FSC-klagomål.docx", "A 2533-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomål/A 1793-2025 FSC-klagomål.docx", "A 1793-2025")</f>
         <v/>
       </c>
       <c r="AB18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomålsmail/A 2533-2026 FSC-klagomål mail.docx", "A 2533-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomålsmail/A 1793-2025 FSC-klagomål mail.docx", "A 1793-2025")</f>
         <v/>
       </c>
       <c r="AC18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsyn/A 2533-2026 tillsynsbegäran.docx", "A 2533-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsyn/A 1793-2025 tillsynsbegäran.docx", "A 1793-2025")</f>
         <v/>
       </c>
       <c r="AD18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsynsmail/A 2533-2026 tillsynsbegäran mail.docx", "A 2533-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsynsmail/A 1793-2025 tillsynsbegäran mail.docx", "A 1793-2025")</f>
         <v/>
       </c>
     </row>
@@ -2481,7 +2481,7 @@
         <v>44670</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2554,7 +2554,7 @@
         <v>44802</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2610,7 +2610,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 3222-2022</t>
+          <t>A 3219-2022</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2627,7 +2627,7 @@
         <v>44582</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2640,7 +2640,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>1.8</v>
+        <v>0.5</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2683,7 +2683,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 37245-2025</t>
+          <t>A 50184-2023</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2697,10 +2697,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>45876</v>
+        <v>45208</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2713,7 +2713,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>1.1</v>
+        <v>10.8</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2756,7 +2756,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 50184-2023</t>
+          <t>A 20399-2026</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2770,10 +2770,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45208</v>
+        <v>46139</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2786,7 +2786,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>10.8</v>
+        <v>0.9</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2829,7 +2829,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 3219-2022</t>
+          <t>A 20398-2026</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2843,10 +2843,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>44582</v>
+        <v>46139</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2859,7 +2859,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>0.5</v>
+        <v>2.4</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2902,7 +2902,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 60755-2024</t>
+          <t>A 20898-2026</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2916,10 +2916,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45644</v>
+        <v>46142</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2932,7 +2932,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>2.1</v>
+        <v>3.6</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2992,7 +2992,7 @@
         <v>45622</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3048,7 +3048,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 56002-2024</t>
+          <t>A 35955-2023</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3062,10 +3062,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45623</v>
+        <v>45148</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3078,7 +3078,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>3.4</v>
+        <v>1.1</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -3121,7 +3121,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 35955-2023</t>
+          <t>A 34073-2025</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3131,14 +3131,14 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45148</v>
+        <v>45845</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3151,7 +3151,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>1.1</v>
+        <v>2.9</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -3194,7 +3194,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 20399-2026</t>
+          <t>A 61217-2024</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3208,10 +3208,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>46139</v>
+        <v>45645</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3224,7 +3224,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3267,7 +3267,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 20398-2026</t>
+          <t>A 56002-2024</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3281,10 +3281,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>46139</v>
+        <v>45623</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3297,7 +3297,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>2.4</v>
+        <v>3.4</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3340,7 +3340,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 61217-2024</t>
+          <t>A 60728-2022</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3354,10 +3354,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45645</v>
+        <v>44913</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3370,7 +3370,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>0.8</v>
+        <v>1.2</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3413,7 +3413,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 20898-2026</t>
+          <t>A 63378-2025</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3427,10 +3427,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>46142</v>
+        <v>46010</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3443,7 +3443,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>3.6</v>
+        <v>4.8</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3486,7 +3486,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 34073-2025</t>
+          <t>A 2535-2026</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3496,14 +3496,14 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45845</v>
+        <v>46037</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3516,7 +3516,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>2.9</v>
+        <v>1.6</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3559,7 +3559,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 60728-2022</t>
+          <t>A 3222-2022</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3573,10 +3573,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>44913</v>
+        <v>44582</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3589,7 +3589,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>1.2</v>
+        <v>1.8</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3649,7 +3649,7 @@
         <v>46244</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3710,7 +3710,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 63378-2025</t>
+          <t>A 60755-2024</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3724,10 +3724,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>46010</v>
+        <v>45644</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3740,7 +3740,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>4.8</v>
+        <v>2.1</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3800,7 +3800,7 @@
         <v>46301</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3861,7 +3861,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 2535-2026</t>
+          <t>A 37245-2025</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3875,10 +3875,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>46037</v>
+        <v>45876</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3891,7 +3891,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>1.6</v>
+        <v>1.1</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3951,7 +3951,7 @@
         <v>46153</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>

--- a/Översikt EKERÖ.xlsx
+++ b/Översikt EKERÖ.xlsx
@@ -601,7 +601,7 @@
         <v>46241</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -728,7 +728,7 @@
         <v>44872</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -848,7 +848,7 @@
         <v>44974</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -963,7 +963,7 @@
         <v>45148</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1073,7 +1073,7 @@
         <v>46119</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1187,7 +1187,7 @@
         <v>44582</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1296,7 +1296,7 @@
         <v>46241</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1409,7 +1409,7 @@
         <v>44634</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1516,7 +1516,7 @@
         <v>45002</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1628,7 +1628,7 @@
         <v>45937</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1735,7 +1735,7 @@
         <v>45209</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1850,7 +1850,7 @@
         <v>45170</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1956,7 +1956,7 @@
         <v>44646</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2061,7 +2061,7 @@
         <v>44582</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2166,7 +2166,7 @@
         <v>45007</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2271,7 +2271,7 @@
         <v>46037</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2376,7 +2376,7 @@
         <v>45671</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2481,7 +2481,7 @@
         <v>44670</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2554,7 +2554,7 @@
         <v>44802</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2627,7 +2627,7 @@
         <v>44582</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2700,7 +2700,7 @@
         <v>45208</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2773,7 +2773,7 @@
         <v>46139</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2846,7 +2846,7 @@
         <v>46139</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2919,7 +2919,7 @@
         <v>46142</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2992,7 +2992,7 @@
         <v>45622</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3065,7 +3065,7 @@
         <v>45148</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3138,7 +3138,7 @@
         <v>45845</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3211,7 +3211,7 @@
         <v>45645</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3284,7 +3284,7 @@
         <v>45623</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3357,7 +3357,7 @@
         <v>44913</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3430,7 +3430,7 @@
         <v>46010</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3503,7 +3503,7 @@
         <v>46037</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3576,7 +3576,7 @@
         <v>44582</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3649,7 +3649,7 @@
         <v>46244</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3727,7 +3727,7 @@
         <v>45644</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3800,7 +3800,7 @@
         <v>46301</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3878,7 +3878,7 @@
         <v>45876</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3951,7 +3951,7 @@
         <v>46153</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>

--- a/Översikt EKERÖ.xlsx
+++ b/Översikt EKERÖ.xlsx
@@ -601,7 +601,7 @@
         <v>46241</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -728,7 +728,7 @@
         <v>44872</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -848,7 +848,7 @@
         <v>44974</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -963,7 +963,7 @@
         <v>45148</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1073,7 +1073,7 @@
         <v>46119</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1187,7 +1187,7 @@
         <v>44582</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1296,7 +1296,7 @@
         <v>46241</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1409,7 +1409,7 @@
         <v>44634</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1516,7 +1516,7 @@
         <v>45002</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1628,7 +1628,7 @@
         <v>45937</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1735,7 +1735,7 @@
         <v>45209</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1850,7 +1850,7 @@
         <v>45170</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1956,7 +1956,7 @@
         <v>44646</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2061,7 +2061,7 @@
         <v>44582</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2166,7 +2166,7 @@
         <v>45007</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2271,7 +2271,7 @@
         <v>46037</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2376,7 +2376,7 @@
         <v>45671</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2481,7 +2481,7 @@
         <v>44670</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2554,7 +2554,7 @@
         <v>44802</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2627,7 +2627,7 @@
         <v>44582</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2700,7 +2700,7 @@
         <v>45208</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2773,7 +2773,7 @@
         <v>46139</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2846,7 +2846,7 @@
         <v>46139</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2919,7 +2919,7 @@
         <v>46142</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2992,7 +2992,7 @@
         <v>45622</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3065,7 +3065,7 @@
         <v>45148</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3138,7 +3138,7 @@
         <v>45845</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3211,7 +3211,7 @@
         <v>45645</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3284,7 +3284,7 @@
         <v>45623</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3357,7 +3357,7 @@
         <v>44913</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3430,7 +3430,7 @@
         <v>46010</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3503,7 +3503,7 @@
         <v>46037</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3576,7 +3576,7 @@
         <v>44582</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3649,7 +3649,7 @@
         <v>46244</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3727,7 +3727,7 @@
         <v>45644</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3800,7 +3800,7 @@
         <v>46301</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3878,7 +3878,7 @@
         <v>45876</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3951,7 +3951,7 @@
         <v>46153</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>

--- a/Översikt EKERÖ.xlsx
+++ b/Översikt EKERÖ.xlsx
@@ -601,7 +601,7 @@
         <v>46241</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -728,7 +728,7 @@
         <v>44872</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -848,7 +848,7 @@
         <v>44974</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -963,7 +963,7 @@
         <v>45148</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1073,7 +1073,7 @@
         <v>46119</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1187,7 +1187,7 @@
         <v>44582</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1296,7 +1296,7 @@
         <v>46241</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1409,7 +1409,7 @@
         <v>44634</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1499,7 +1499,7 @@
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 13237-2023</t>
+          <t>A 49131-2025</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1513,10 +1513,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>45002</v>
+        <v>45937</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1528,25 +1528,20 @@
           <t>EKERÖ</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I10" t="n">
-        <v>9.300000000000001</v>
+        <v>0.9</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
       </c>
       <c r="K10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" t="n">
         <v>2</v>
       </c>
-      <c r="L10" t="n">
-        <v>1</v>
-      </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N10" t="n">
         <v>0</v>
@@ -1558,160 +1553,165 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S10" t="n">
         <v>3</v>
       </c>
       <c r="T10" t="n">
+        <v>3</v>
+      </c>
+      <c r="U10" t="n">
+        <v>3</v>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
+        <is>
+          <t>Jättemusseron
+Motaggsvamp
+Svartvit taggsvamp</t>
+        </is>
+      </c>
+      <c r="W10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/artfynd/A 49131-2025 artfynd.xlsx", "A 49131-2025")</f>
+        <v/>
+      </c>
+      <c r="X10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor/A 49131-2025 karta.png", "A 49131-2025")</f>
+        <v/>
+      </c>
+      <c r="Y10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor_geotiff/A 49131-2025 georefererad karta.tif", "A 49131-2025")</f>
+        <v/>
+      </c>
+      <c r="AA10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomål/A 49131-2025 FSC-klagomål.docx", "A 49131-2025")</f>
+        <v/>
+      </c>
+      <c r="AB10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomålsmail/A 49131-2025 FSC-klagomål mail.docx", "A 49131-2025")</f>
+        <v/>
+      </c>
+      <c r="AC10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsyn/A 49131-2025 tillsynsbegäran.docx", "A 49131-2025")</f>
+        <v/>
+      </c>
+      <c r="AD10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsynsmail/A 49131-2025 tillsynsbegäran mail.docx", "A 49131-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11" ht="15" customHeight="1">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>A 13237-2023</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D11" s="1" t="n">
+        <v>45002</v>
+      </c>
+      <c r="E11" s="1" t="n">
+        <v>46315</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>EKERÖ</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" t="n">
+        <v>2</v>
+      </c>
+      <c r="L11" t="n">
+        <v>1</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>1</v>
+      </c>
+      <c r="R11" t="n">
+        <v>0</v>
+      </c>
+      <c r="S11" t="n">
+        <v>3</v>
+      </c>
+      <c r="T11" t="n">
         <v>7</v>
       </c>
-      <c r="U10" t="n">
-        <v>0</v>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
+      <c r="U11" t="n">
+        <v>0</v>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
         <is>
           <t>Tallticka
 Granbarkgnagare
 Grönpyrola</t>
         </is>
       </c>
-      <c r="W10">
+      <c r="W11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0125/artfynd/A 13237-2023 artfynd.xlsx", "A 13237-2023")</f>
         <v/>
       </c>
-      <c r="X10">
+      <c r="X11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor/A 13237-2023 karta.png", "A 13237-2023")</f>
         <v/>
       </c>
-      <c r="Y10">
+      <c r="Y11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor_geotiff/A 13237-2023 georefererad karta.tif", "A 13237-2023")</f>
         <v/>
       </c>
-      <c r="AA10">
+      <c r="AA11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomål/A 13237-2023 FSC-klagomål.docx", "A 13237-2023")</f>
         <v/>
       </c>
-      <c r="AB10">
+      <c r="AB11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomålsmail/A 13237-2023 FSC-klagomål mail.docx", "A 13237-2023")</f>
         <v/>
       </c>
-      <c r="AC10">
+      <c r="AC11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsyn/A 13237-2023 tillsynsbegäran.docx", "A 13237-2023")</f>
         <v/>
       </c>
-      <c r="AD10">
+      <c r="AD11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsynsmail/A 13237-2023 tillsynsbegäran mail.docx", "A 13237-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="11" ht="15" customHeight="1">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>A 49131-2025</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D11" s="1" t="n">
-        <v>45937</v>
-      </c>
-      <c r="E11" s="1" t="n">
-        <v>46314</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>EKERÖ</t>
-        </is>
-      </c>
-      <c r="I11" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="J11" t="n">
-        <v>0</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L11" t="n">
-        <v>2</v>
-      </c>
-      <c r="M11" t="n">
-        <v>1</v>
-      </c>
-      <c r="N11" t="n">
-        <v>0</v>
-      </c>
-      <c r="O11" t="n">
-        <v>0</v>
-      </c>
-      <c r="P11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>3</v>
-      </c>
-      <c r="R11" t="n">
-        <v>1</v>
-      </c>
-      <c r="S11" t="n">
-        <v>3</v>
-      </c>
-      <c r="T11" t="n">
-        <v>3</v>
-      </c>
-      <c r="U11" t="n">
-        <v>3</v>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
-        <is>
-          <t>Jättemusseron
-Motaggsvamp
-Svartvit taggsvamp</t>
-        </is>
-      </c>
-      <c r="W11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/artfynd/A 49131-2025 artfynd.xlsx", "A 49131-2025")</f>
-        <v/>
-      </c>
-      <c r="X11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor/A 49131-2025 karta.png", "A 49131-2025")</f>
-        <v/>
-      </c>
-      <c r="Y11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor_geotiff/A 49131-2025 georefererad karta.tif", "A 49131-2025")</f>
-        <v/>
-      </c>
-      <c r="AA11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomål/A 49131-2025 FSC-klagomål.docx", "A 49131-2025")</f>
-        <v/>
-      </c>
-      <c r="AB11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomålsmail/A 49131-2025 FSC-klagomål mail.docx", "A 49131-2025")</f>
-        <v/>
-      </c>
-      <c r="AC11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsyn/A 49131-2025 tillsynsbegäran.docx", "A 49131-2025")</f>
-        <v/>
-      </c>
-      <c r="AD11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsynsmail/A 49131-2025 tillsynsbegäran mail.docx", "A 49131-2025")</f>
         <v/>
       </c>
     </row>
@@ -1735,7 +1735,7 @@
         <v>45209</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1850,7 +1850,7 @@
         <v>45170</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1956,7 +1956,7 @@
         <v>44646</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2061,7 +2061,7 @@
         <v>44582</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2149,7 +2149,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 13794-2023</t>
+          <t>A 2533-2026</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2163,10 +2163,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45007</v>
+        <v>46037</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2179,16 +2179,16 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>4.8</v>
+        <v>1.4</v>
       </c>
       <c r="J16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K16" t="n">
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
         <v>0</v>
@@ -2203,7 +2203,7 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
         <v>0</v>
@@ -2219,42 +2219,42 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/artfynd/A 13794-2023 artfynd.xlsx", "A 13794-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/artfynd/A 2533-2026 artfynd.xlsx", "A 2533-2026")</f>
         <v/>
       </c>
       <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor/A 13794-2023 karta.png", "A 13794-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor/A 2533-2026 karta.png", "A 2533-2026")</f>
         <v/>
       </c>
       <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor_geotiff/A 13794-2023 georefererad karta.tif", "A 13794-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor_geotiff/A 2533-2026 georefererad karta.tif", "A 2533-2026")</f>
         <v/>
       </c>
       <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomål/A 13794-2023 FSC-klagomål.docx", "A 13794-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomål/A 2533-2026 FSC-klagomål.docx", "A 2533-2026")</f>
         <v/>
       </c>
       <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomålsmail/A 13794-2023 FSC-klagomål mail.docx", "A 13794-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomålsmail/A 2533-2026 FSC-klagomål mail.docx", "A 2533-2026")</f>
         <v/>
       </c>
       <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsyn/A 13794-2023 tillsynsbegäran.docx", "A 13794-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsyn/A 2533-2026 tillsynsbegäran.docx", "A 2533-2026")</f>
         <v/>
       </c>
       <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsynsmail/A 13794-2023 tillsynsbegäran mail.docx", "A 13794-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsynsmail/A 2533-2026 tillsynsbegäran mail.docx", "A 2533-2026")</f>
         <v/>
       </c>
     </row>
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 2533-2026</t>
+          <t>A 13794-2023</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2268,10 +2268,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>46037</v>
+        <v>45007</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2284,16 +2284,16 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>1.4</v>
+        <v>4.8</v>
       </c>
       <c r="J17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K17" t="n">
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M17" t="n">
         <v>0</v>
@@ -2308,7 +2308,7 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R17" t="n">
         <v>0</v>
@@ -2324,35 +2324,35 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/artfynd/A 2533-2026 artfynd.xlsx", "A 2533-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/artfynd/A 13794-2023 artfynd.xlsx", "A 13794-2023")</f>
         <v/>
       </c>
       <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor/A 2533-2026 karta.png", "A 2533-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor/A 13794-2023 karta.png", "A 13794-2023")</f>
         <v/>
       </c>
       <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor_geotiff/A 2533-2026 georefererad karta.tif", "A 2533-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor_geotiff/A 13794-2023 georefererad karta.tif", "A 13794-2023")</f>
         <v/>
       </c>
       <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomål/A 2533-2026 FSC-klagomål.docx", "A 2533-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomål/A 13794-2023 FSC-klagomål.docx", "A 13794-2023")</f>
         <v/>
       </c>
       <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomålsmail/A 2533-2026 FSC-klagomål mail.docx", "A 2533-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomålsmail/A 13794-2023 FSC-klagomål mail.docx", "A 13794-2023")</f>
         <v/>
       </c>
       <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsyn/A 2533-2026 tillsynsbegäran.docx", "A 2533-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsyn/A 13794-2023 tillsynsbegäran.docx", "A 13794-2023")</f>
         <v/>
       </c>
       <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsynsmail/A 2533-2026 tillsynsbegäran mail.docx", "A 2533-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsynsmail/A 13794-2023 tillsynsbegäran mail.docx", "A 13794-2023")</f>
         <v/>
       </c>
     </row>
@@ -2376,7 +2376,7 @@
         <v>45671</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2481,7 +2481,7 @@
         <v>44670</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2554,7 +2554,7 @@
         <v>44802</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2610,7 +2610,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 3219-2022</t>
+          <t>A 50184-2023</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2624,10 +2624,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>44582</v>
+        <v>45208</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2640,7 +2640,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>0.5</v>
+        <v>10.8</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2683,7 +2683,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 50184-2023</t>
+          <t>A 56002-2024</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2697,10 +2697,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>45208</v>
+        <v>45623</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2713,7 +2713,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>10.8</v>
+        <v>3.4</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2756,7 +2756,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 20399-2026</t>
+          <t>A 61217-2024</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2770,10 +2770,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>46139</v>
+        <v>45645</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2786,7 +2786,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2829,7 +2829,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 20398-2026</t>
+          <t>A 20399-2026</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2846,7 +2846,7 @@
         <v>46139</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2859,7 +2859,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>2.4</v>
+        <v>0.9</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2902,7 +2902,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 20898-2026</t>
+          <t>A 20398-2026</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2916,10 +2916,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>46142</v>
+        <v>46139</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2932,7 +2932,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>3.6</v>
+        <v>2.4</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2975,7 +2975,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 55724-2024</t>
+          <t>A 3222-2022</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2989,10 +2989,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45622</v>
+        <v>44582</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3005,7 +3005,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>0.5</v>
+        <v>1.8</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -3048,7 +3048,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 35955-2023</t>
+          <t>A 20898-2026</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3062,10 +3062,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45148</v>
+        <v>46142</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3078,7 +3078,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>1.1</v>
+        <v>3.6</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -3121,7 +3121,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 34073-2025</t>
+          <t>A 3219-2022</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3131,14 +3131,14 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45845</v>
+        <v>44582</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3151,7 +3151,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>2.9</v>
+        <v>0.5</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -3194,7 +3194,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 61217-2024</t>
+          <t>A 63378-2025</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3208,10 +3208,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45645</v>
+        <v>46010</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3224,7 +3224,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>0.8</v>
+        <v>4.8</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3267,7 +3267,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 56002-2024</t>
+          <t>A 34073-2025</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3277,14 +3277,14 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45623</v>
+        <v>45845</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3297,7 +3297,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>3.4</v>
+        <v>2.9</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3340,7 +3340,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 60728-2022</t>
+          <t>A 60755-2024</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3354,10 +3354,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>44913</v>
+        <v>45644</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3370,7 +3370,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>1.2</v>
+        <v>2.1</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3413,7 +3413,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 63378-2025</t>
+          <t>A 55724-2024</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3427,10 +3427,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>46010</v>
+        <v>45622</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3443,7 +3443,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>4.8</v>
+        <v>0.5</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3503,7 +3503,7 @@
         <v>46037</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3559,7 +3559,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 3222-2022</t>
+          <t>A 35955-2023</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3573,10 +3573,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>44582</v>
+        <v>45148</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3589,7 +3589,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>1.8</v>
+        <v>1.1</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3632,7 +3632,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 33154-2026</t>
+          <t>A 60728-2022</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3646,10 +3646,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>46244</v>
+        <v>44913</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3661,13 +3661,8 @@
           <t>EKERÖ</t>
         </is>
       </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I35" t="n">
-        <v>3.5</v>
+        <v>1.2</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3710,7 +3705,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 60755-2024</t>
+          <t>A 33154-2026</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3724,10 +3719,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45644</v>
+        <v>46244</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3739,8 +3734,13 @@
           <t>EKERÖ</t>
         </is>
       </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I36" t="n">
-        <v>2.1</v>
+        <v>3.5</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3800,7 +3800,7 @@
         <v>46301</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3878,7 +3878,7 @@
         <v>45876</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3951,7 +3951,7 @@
         <v>46153</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>

--- a/Översikt EKERÖ.xlsx
+++ b/Översikt EKERÖ.xlsx
@@ -601,7 +601,7 @@
         <v>46241</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -728,7 +728,7 @@
         <v>44872</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -848,7 +848,7 @@
         <v>44974</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -963,7 +963,7 @@
         <v>45148</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1073,7 +1073,7 @@
         <v>46119</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1187,7 +1187,7 @@
         <v>44582</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1296,7 +1296,7 @@
         <v>46241</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1409,7 +1409,7 @@
         <v>44634</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1499,7 +1499,7 @@
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 49131-2025</t>
+          <t>A 13237-2023</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1513,10 +1513,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>45937</v>
+        <v>45002</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1528,20 +1528,25 @@
           <t>EKERÖ</t>
         </is>
       </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I10" t="n">
-        <v>0.9</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N10" t="n">
         <v>0</v>
@@ -1553,165 +1558,160 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="R10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
         <v>3</v>
       </c>
       <c r="T10" t="n">
+        <v>7</v>
+      </c>
+      <c r="U10" t="n">
+        <v>0</v>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
+        <is>
+          <t>Tallticka
+Granbarkgnagare
+Grönpyrola</t>
+        </is>
+      </c>
+      <c r="W10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/artfynd/A 13237-2023 artfynd.xlsx", "A 13237-2023")</f>
+        <v/>
+      </c>
+      <c r="X10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor/A 13237-2023 karta.png", "A 13237-2023")</f>
+        <v/>
+      </c>
+      <c r="Y10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor_geotiff/A 13237-2023 georefererad karta.tif", "A 13237-2023")</f>
+        <v/>
+      </c>
+      <c r="AA10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomål/A 13237-2023 FSC-klagomål.docx", "A 13237-2023")</f>
+        <v/>
+      </c>
+      <c r="AB10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomålsmail/A 13237-2023 FSC-klagomål mail.docx", "A 13237-2023")</f>
+        <v/>
+      </c>
+      <c r="AC10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsyn/A 13237-2023 tillsynsbegäran.docx", "A 13237-2023")</f>
+        <v/>
+      </c>
+      <c r="AD10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsynsmail/A 13237-2023 tillsynsbegäran mail.docx", "A 13237-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11" ht="15" customHeight="1">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>A 49131-2025</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D11" s="1" t="n">
+        <v>45937</v>
+      </c>
+      <c r="E11" s="1" t="n">
+        <v>46316</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>EKERÖ</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" t="n">
+        <v>2</v>
+      </c>
+      <c r="M11" t="n">
+        <v>1</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" t="n">
         <v>3</v>
       </c>
-      <c r="U10" t="n">
+      <c r="R11" t="n">
+        <v>1</v>
+      </c>
+      <c r="S11" t="n">
         <v>3</v>
       </c>
-      <c r="V10" s="2" t="inlineStr">
+      <c r="T11" t="n">
+        <v>3</v>
+      </c>
+      <c r="U11" t="n">
+        <v>3</v>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
         <is>
           <t>Jättemusseron
 Motaggsvamp
 Svartvit taggsvamp</t>
         </is>
       </c>
-      <c r="W10">
+      <c r="W11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0125/artfynd/A 49131-2025 artfynd.xlsx", "A 49131-2025")</f>
         <v/>
       </c>
-      <c r="X10">
+      <c r="X11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor/A 49131-2025 karta.png", "A 49131-2025")</f>
         <v/>
       </c>
-      <c r="Y10">
+      <c r="Y11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor_geotiff/A 49131-2025 georefererad karta.tif", "A 49131-2025")</f>
         <v/>
       </c>
-      <c r="AA10">
+      <c r="AA11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomål/A 49131-2025 FSC-klagomål.docx", "A 49131-2025")</f>
         <v/>
       </c>
-      <c r="AB10">
+      <c r="AB11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomålsmail/A 49131-2025 FSC-klagomål mail.docx", "A 49131-2025")</f>
         <v/>
       </c>
-      <c r="AC10">
+      <c r="AC11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsyn/A 49131-2025 tillsynsbegäran.docx", "A 49131-2025")</f>
         <v/>
       </c>
-      <c r="AD10">
+      <c r="AD11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsynsmail/A 49131-2025 tillsynsbegäran mail.docx", "A 49131-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="11" ht="15" customHeight="1">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>A 13237-2023</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D11" s="1" t="n">
-        <v>45002</v>
-      </c>
-      <c r="E11" s="1" t="n">
-        <v>46315</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>EKERÖ</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
-      <c r="I11" t="n">
-        <v>9.300000000000001</v>
-      </c>
-      <c r="J11" t="n">
-        <v>0</v>
-      </c>
-      <c r="K11" t="n">
-        <v>2</v>
-      </c>
-      <c r="L11" t="n">
-        <v>1</v>
-      </c>
-      <c r="M11" t="n">
-        <v>0</v>
-      </c>
-      <c r="N11" t="n">
-        <v>0</v>
-      </c>
-      <c r="O11" t="n">
-        <v>0</v>
-      </c>
-      <c r="P11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>1</v>
-      </c>
-      <c r="R11" t="n">
-        <v>0</v>
-      </c>
-      <c r="S11" t="n">
-        <v>3</v>
-      </c>
-      <c r="T11" t="n">
-        <v>7</v>
-      </c>
-      <c r="U11" t="n">
-        <v>0</v>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
-        <is>
-          <t>Tallticka
-Granbarkgnagare
-Grönpyrola</t>
-        </is>
-      </c>
-      <c r="W11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/artfynd/A 13237-2023 artfynd.xlsx", "A 13237-2023")</f>
-        <v/>
-      </c>
-      <c r="X11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor/A 13237-2023 karta.png", "A 13237-2023")</f>
-        <v/>
-      </c>
-      <c r="Y11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor_geotiff/A 13237-2023 georefererad karta.tif", "A 13237-2023")</f>
-        <v/>
-      </c>
-      <c r="AA11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomål/A 13237-2023 FSC-klagomål.docx", "A 13237-2023")</f>
-        <v/>
-      </c>
-      <c r="AB11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomålsmail/A 13237-2023 FSC-klagomål mail.docx", "A 13237-2023")</f>
-        <v/>
-      </c>
-      <c r="AC11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsyn/A 13237-2023 tillsynsbegäran.docx", "A 13237-2023")</f>
-        <v/>
-      </c>
-      <c r="AD11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsynsmail/A 13237-2023 tillsynsbegäran mail.docx", "A 13237-2023")</f>
         <v/>
       </c>
     </row>
@@ -1735,7 +1735,7 @@
         <v>45209</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1850,7 +1850,7 @@
         <v>45170</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1956,7 +1956,7 @@
         <v>44646</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2061,7 +2061,7 @@
         <v>44582</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2149,7 +2149,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 2533-2026</t>
+          <t>A 13794-2023</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2163,10 +2163,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>46037</v>
+        <v>45007</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2179,16 +2179,16 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>1.4</v>
+        <v>4.8</v>
       </c>
       <c r="J16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K16" t="n">
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M16" t="n">
         <v>0</v>
@@ -2203,7 +2203,7 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R16" t="n">
         <v>0</v>
@@ -2219,42 +2219,42 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/artfynd/A 2533-2026 artfynd.xlsx", "A 2533-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/artfynd/A 13794-2023 artfynd.xlsx", "A 13794-2023")</f>
         <v/>
       </c>
       <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor/A 2533-2026 karta.png", "A 2533-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor/A 13794-2023 karta.png", "A 13794-2023")</f>
         <v/>
       </c>
       <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor_geotiff/A 2533-2026 georefererad karta.tif", "A 2533-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor_geotiff/A 13794-2023 georefererad karta.tif", "A 13794-2023")</f>
         <v/>
       </c>
       <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomål/A 2533-2026 FSC-klagomål.docx", "A 2533-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomål/A 13794-2023 FSC-klagomål.docx", "A 13794-2023")</f>
         <v/>
       </c>
       <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomålsmail/A 2533-2026 FSC-klagomål mail.docx", "A 2533-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomålsmail/A 13794-2023 FSC-klagomål mail.docx", "A 13794-2023")</f>
         <v/>
       </c>
       <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsyn/A 2533-2026 tillsynsbegäran.docx", "A 2533-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsyn/A 13794-2023 tillsynsbegäran.docx", "A 13794-2023")</f>
         <v/>
       </c>
       <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsynsmail/A 2533-2026 tillsynsbegäran mail.docx", "A 2533-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsynsmail/A 13794-2023 tillsynsbegäran mail.docx", "A 13794-2023")</f>
         <v/>
       </c>
     </row>
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 13794-2023</t>
+          <t>A 2533-2026</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2268,10 +2268,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45007</v>
+        <v>46037</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2284,16 +2284,16 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>4.8</v>
+        <v>1.4</v>
       </c>
       <c r="J17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K17" t="n">
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
         <v>0</v>
@@ -2308,7 +2308,7 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
         <v>0</v>
@@ -2324,35 +2324,35 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/artfynd/A 13794-2023 artfynd.xlsx", "A 13794-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/artfynd/A 2533-2026 artfynd.xlsx", "A 2533-2026")</f>
         <v/>
       </c>
       <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor/A 13794-2023 karta.png", "A 13794-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor/A 2533-2026 karta.png", "A 2533-2026")</f>
         <v/>
       </c>
       <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor_geotiff/A 13794-2023 georefererad karta.tif", "A 13794-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor_geotiff/A 2533-2026 georefererad karta.tif", "A 2533-2026")</f>
         <v/>
       </c>
       <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomål/A 13794-2023 FSC-klagomål.docx", "A 13794-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomål/A 2533-2026 FSC-klagomål.docx", "A 2533-2026")</f>
         <v/>
       </c>
       <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomålsmail/A 13794-2023 FSC-klagomål mail.docx", "A 13794-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomålsmail/A 2533-2026 FSC-klagomål mail.docx", "A 2533-2026")</f>
         <v/>
       </c>
       <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsyn/A 13794-2023 tillsynsbegäran.docx", "A 13794-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsyn/A 2533-2026 tillsynsbegäran.docx", "A 2533-2026")</f>
         <v/>
       </c>
       <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsynsmail/A 13794-2023 tillsynsbegäran mail.docx", "A 13794-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsynsmail/A 2533-2026 tillsynsbegäran mail.docx", "A 2533-2026")</f>
         <v/>
       </c>
     </row>
@@ -2376,7 +2376,7 @@
         <v>45671</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2481,7 +2481,7 @@
         <v>44670</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2554,7 +2554,7 @@
         <v>44802</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2610,7 +2610,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 50184-2023</t>
+          <t>A 3219-2022</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2624,10 +2624,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45208</v>
+        <v>44582</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2640,7 +2640,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>10.8</v>
+        <v>0.5</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2683,7 +2683,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 56002-2024</t>
+          <t>A 63378-2025</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2697,10 +2697,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>45623</v>
+        <v>46010</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2713,7 +2713,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>3.4</v>
+        <v>4.8</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2756,7 +2756,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 61217-2024</t>
+          <t>A 2535-2026</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2770,10 +2770,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45645</v>
+        <v>46037</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2786,7 +2786,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>0.8</v>
+        <v>1.6</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2829,7 +2829,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 20399-2026</t>
+          <t>A 50184-2023</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2843,10 +2843,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>46139</v>
+        <v>45208</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2859,7 +2859,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>0.9</v>
+        <v>10.8</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2902,7 +2902,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 20398-2026</t>
+          <t>A 20399-2026</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2919,7 +2919,7 @@
         <v>46139</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2932,7 +2932,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>2.4</v>
+        <v>0.9</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2975,7 +2975,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 3222-2022</t>
+          <t>A 20398-2026</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2989,10 +2989,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>44582</v>
+        <v>46139</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3005,7 +3005,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>1.8</v>
+        <v>2.4</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -3048,7 +3048,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 20898-2026</t>
+          <t>A 37245-2025</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3062,10 +3062,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>46142</v>
+        <v>45876</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3078,7 +3078,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>3.6</v>
+        <v>1.1</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -3121,7 +3121,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 3219-2022</t>
+          <t>A 20898-2026</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3135,10 +3135,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>44582</v>
+        <v>46142</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3151,7 +3151,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>0.5</v>
+        <v>3.6</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -3194,7 +3194,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 63378-2025</t>
+          <t>A 55724-2024</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3208,10 +3208,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>46010</v>
+        <v>45622</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3224,7 +3224,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>4.8</v>
+        <v>0.5</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3284,7 +3284,7 @@
         <v>45845</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3340,7 +3340,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 60755-2024</t>
+          <t>A 35955-2023</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3354,10 +3354,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45644</v>
+        <v>45148</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3370,7 +3370,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>2.1</v>
+        <v>1.1</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3413,7 +3413,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 55724-2024</t>
+          <t>A 61217-2024</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3427,10 +3427,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45622</v>
+        <v>45645</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3443,7 +3443,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3486,7 +3486,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 2535-2026</t>
+          <t>A 56002-2024</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3500,10 +3500,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>46037</v>
+        <v>45623</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3516,7 +3516,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>1.6</v>
+        <v>3.4</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3559,7 +3559,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 35955-2023</t>
+          <t>A 60728-2022</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3573,10 +3573,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45148</v>
+        <v>44913</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3589,7 +3589,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3632,7 +3632,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 60728-2022</t>
+          <t>A 3222-2022</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3646,10 +3646,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>44913</v>
+        <v>44582</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3662,7 +3662,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>1.2</v>
+        <v>1.8</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3722,7 +3722,7 @@
         <v>46244</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3800,7 +3800,7 @@
         <v>46301</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3861,7 +3861,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 37245-2025</t>
+          <t>A 60755-2024</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3875,10 +3875,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45876</v>
+        <v>45644</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3891,7 +3891,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>1.1</v>
+        <v>2.1</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3951,7 +3951,7 @@
         <v>46153</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>

--- a/Översikt EKERÖ.xlsx
+++ b/Översikt EKERÖ.xlsx
@@ -601,7 +601,7 @@
         <v>46241</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -728,7 +728,7 @@
         <v>44872</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -848,7 +848,7 @@
         <v>44974</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -963,7 +963,7 @@
         <v>45148</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1056,7 +1056,7 @@
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A 17520-2026</t>
+          <t>A 3218-2022</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1070,10 +1070,10 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>46119</v>
+        <v>44582</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1085,13 +1085,8 @@
           <t>EKERÖ</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I6" t="n">
-        <v>2.2</v>
+        <v>1.2</v>
       </c>
       <c r="J6" t="n">
         <v>1</v>
@@ -1100,36 +1095,150 @@
         <v>1</v>
       </c>
       <c r="L6" t="n">
+        <v>1</v>
+      </c>
+      <c r="M6" t="n">
+        <v>1</v>
+      </c>
+      <c r="N6" t="n">
+        <v>1</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" t="n">
         <v>3</v>
       </c>
-      <c r="M6" t="n">
-        <v>1</v>
-      </c>
-      <c r="N6" t="n">
-        <v>0</v>
-      </c>
-      <c r="O6" t="n">
-        <v>0</v>
-      </c>
-      <c r="P6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>4</v>
-      </c>
       <c r="R6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
       </c>
       <c r="T6" t="n">
+        <v>8</v>
+      </c>
+      <c r="U6" t="n">
+        <v>6</v>
+      </c>
+      <c r="V6" s="2" t="inlineStr">
+        <is>
+          <t>Bombmurkla
+Gul lammticka
+Fyrflikig jordstjärna
+Kamjordstjärna
+Blåbär</t>
+        </is>
+      </c>
+      <c r="W6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/artfynd/A 3218-2022 artfynd.xlsx", "A 3218-2022")</f>
+        <v/>
+      </c>
+      <c r="X6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor/A 3218-2022 karta.png", "A 3218-2022")</f>
+        <v/>
+      </c>
+      <c r="Y6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor_geotiff/A 3218-2022 georefererad karta.tif", "A 3218-2022")</f>
+        <v/>
+      </c>
+      <c r="AA6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomål/A 3218-2022 FSC-klagomål.docx", "A 3218-2022")</f>
+        <v/>
+      </c>
+      <c r="AB6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomålsmail/A 3218-2022 FSC-klagomål mail.docx", "A 3218-2022")</f>
+        <v/>
+      </c>
+      <c r="AC6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsyn/A 3218-2022 tillsynsbegäran.docx", "A 3218-2022")</f>
+        <v/>
+      </c>
+      <c r="AD6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsynsmail/A 3218-2022 tillsynsbegäran mail.docx", "A 3218-2022")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7" ht="15" customHeight="1">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>A 17520-2026</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D7" s="1" t="n">
+        <v>46119</v>
+      </c>
+      <c r="E7" s="1" t="n">
+        <v>46317</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>EKERÖ</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="J7" t="n">
+        <v>1</v>
+      </c>
+      <c r="K7" t="n">
+        <v>1</v>
+      </c>
+      <c r="L7" t="n">
+        <v>3</v>
+      </c>
+      <c r="M7" t="n">
+        <v>1</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>4</v>
+      </c>
+      <c r="R7" t="n">
+        <v>1</v>
+      </c>
+      <c r="S7" t="n">
         <v>5</v>
       </c>
-      <c r="U6" t="n">
-        <v>1</v>
-      </c>
-      <c r="V6" s="2" t="inlineStr">
+      <c r="T7" t="n">
+        <v>5</v>
+      </c>
+      <c r="U7" t="n">
+        <v>1</v>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
         <is>
           <t>Läderbagge
 Blekticka
@@ -1138,141 +1247,32 @@
 Gulgrön kantmusseron</t>
         </is>
       </c>
-      <c r="W6">
+      <c r="W7">
         <f>HYPERLINK("https://klasma.github.io/Logging_0125/artfynd/A 17520-2026 artfynd.xlsx", "A 17520-2026")</f>
         <v/>
       </c>
-      <c r="X6">
+      <c r="X7">
         <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor/A 17520-2026 karta.png", "A 17520-2026")</f>
         <v/>
       </c>
-      <c r="Y6">
+      <c r="Y7">
         <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor_geotiff/A 17520-2026 georefererad karta.tif", "A 17520-2026")</f>
         <v/>
       </c>
-      <c r="AA6">
+      <c r="AA7">
         <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomål/A 17520-2026 FSC-klagomål.docx", "A 17520-2026")</f>
         <v/>
       </c>
-      <c r="AB6">
+      <c r="AB7">
         <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomålsmail/A 17520-2026 FSC-klagomål mail.docx", "A 17520-2026")</f>
         <v/>
       </c>
-      <c r="AC6">
+      <c r="AC7">
         <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsyn/A 17520-2026 tillsynsbegäran.docx", "A 17520-2026")</f>
         <v/>
       </c>
-      <c r="AD6">
+      <c r="AD7">
         <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsynsmail/A 17520-2026 tillsynsbegäran mail.docx", "A 17520-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="7" ht="15" customHeight="1">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>A 3218-2022</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D7" s="1" t="n">
-        <v>44582</v>
-      </c>
-      <c r="E7" s="1" t="n">
-        <v>46316</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>EKERÖ</t>
-        </is>
-      </c>
-      <c r="I7" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="J7" t="n">
-        <v>1</v>
-      </c>
-      <c r="K7" t="n">
-        <v>1</v>
-      </c>
-      <c r="L7" t="n">
-        <v>1</v>
-      </c>
-      <c r="M7" t="n">
-        <v>1</v>
-      </c>
-      <c r="N7" t="n">
-        <v>1</v>
-      </c>
-      <c r="O7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>3</v>
-      </c>
-      <c r="R7" t="n">
-        <v>2</v>
-      </c>
-      <c r="S7" t="n">
-        <v>5</v>
-      </c>
-      <c r="T7" t="n">
-        <v>8</v>
-      </c>
-      <c r="U7" t="n">
-        <v>6</v>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>Bombmurkla
-Gul lammticka
-Fyrflikig jordstjärna
-Kamjordstjärna
-Blåbär</t>
-        </is>
-      </c>
-      <c r="W7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/artfynd/A 3218-2022 artfynd.xlsx", "A 3218-2022")</f>
-        <v/>
-      </c>
-      <c r="X7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor/A 3218-2022 karta.png", "A 3218-2022")</f>
-        <v/>
-      </c>
-      <c r="Y7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor_geotiff/A 3218-2022 georefererad karta.tif", "A 3218-2022")</f>
-        <v/>
-      </c>
-      <c r="AA7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomål/A 3218-2022 FSC-klagomål.docx", "A 3218-2022")</f>
-        <v/>
-      </c>
-      <c r="AB7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomålsmail/A 3218-2022 FSC-klagomål mail.docx", "A 3218-2022")</f>
-        <v/>
-      </c>
-      <c r="AC7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsyn/A 3218-2022 tillsynsbegäran.docx", "A 3218-2022")</f>
-        <v/>
-      </c>
-      <c r="AD7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsynsmail/A 3218-2022 tillsynsbegäran mail.docx", "A 3218-2022")</f>
         <v/>
       </c>
     </row>
@@ -1296,7 +1296,7 @@
         <v>46241</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1409,7 +1409,7 @@
         <v>44634</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1499,7 +1499,7 @@
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 13237-2023</t>
+          <t>A 49131-2025</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1513,10 +1513,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>45002</v>
+        <v>45937</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1528,25 +1528,20 @@
           <t>EKERÖ</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I10" t="n">
-        <v>9.300000000000001</v>
+        <v>0.9</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
       </c>
       <c r="K10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" t="n">
         <v>2</v>
       </c>
-      <c r="L10" t="n">
-        <v>1</v>
-      </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N10" t="n">
         <v>0</v>
@@ -1558,160 +1553,165 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S10" t="n">
         <v>3</v>
       </c>
       <c r="T10" t="n">
+        <v>3</v>
+      </c>
+      <c r="U10" t="n">
+        <v>3</v>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
+        <is>
+          <t>Jättemusseron
+Motaggsvamp
+Svartvit taggsvamp</t>
+        </is>
+      </c>
+      <c r="W10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/artfynd/A 49131-2025 artfynd.xlsx", "A 49131-2025")</f>
+        <v/>
+      </c>
+      <c r="X10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor/A 49131-2025 karta.png", "A 49131-2025")</f>
+        <v/>
+      </c>
+      <c r="Y10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor_geotiff/A 49131-2025 georefererad karta.tif", "A 49131-2025")</f>
+        <v/>
+      </c>
+      <c r="AA10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomål/A 49131-2025 FSC-klagomål.docx", "A 49131-2025")</f>
+        <v/>
+      </c>
+      <c r="AB10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomålsmail/A 49131-2025 FSC-klagomål mail.docx", "A 49131-2025")</f>
+        <v/>
+      </c>
+      <c r="AC10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsyn/A 49131-2025 tillsynsbegäran.docx", "A 49131-2025")</f>
+        <v/>
+      </c>
+      <c r="AD10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsynsmail/A 49131-2025 tillsynsbegäran mail.docx", "A 49131-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11" ht="15" customHeight="1">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>A 13237-2023</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D11" s="1" t="n">
+        <v>45002</v>
+      </c>
+      <c r="E11" s="1" t="n">
+        <v>46317</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>EKERÖ</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" t="n">
+        <v>2</v>
+      </c>
+      <c r="L11" t="n">
+        <v>1</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>1</v>
+      </c>
+      <c r="R11" t="n">
+        <v>0</v>
+      </c>
+      <c r="S11" t="n">
+        <v>3</v>
+      </c>
+      <c r="T11" t="n">
         <v>7</v>
       </c>
-      <c r="U10" t="n">
-        <v>0</v>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
+      <c r="U11" t="n">
+        <v>0</v>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
         <is>
           <t>Tallticka
 Granbarkgnagare
 Grönpyrola</t>
         </is>
       </c>
-      <c r="W10">
+      <c r="W11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0125/artfynd/A 13237-2023 artfynd.xlsx", "A 13237-2023")</f>
         <v/>
       </c>
-      <c r="X10">
+      <c r="X11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor/A 13237-2023 karta.png", "A 13237-2023")</f>
         <v/>
       </c>
-      <c r="Y10">
+      <c r="Y11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor_geotiff/A 13237-2023 georefererad karta.tif", "A 13237-2023")</f>
         <v/>
       </c>
-      <c r="AA10">
+      <c r="AA11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomål/A 13237-2023 FSC-klagomål.docx", "A 13237-2023")</f>
         <v/>
       </c>
-      <c r="AB10">
+      <c r="AB11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomålsmail/A 13237-2023 FSC-klagomål mail.docx", "A 13237-2023")</f>
         <v/>
       </c>
-      <c r="AC10">
+      <c r="AC11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsyn/A 13237-2023 tillsynsbegäran.docx", "A 13237-2023")</f>
         <v/>
       </c>
-      <c r="AD10">
+      <c r="AD11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsynsmail/A 13237-2023 tillsynsbegäran mail.docx", "A 13237-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="11" ht="15" customHeight="1">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>A 49131-2025</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D11" s="1" t="n">
-        <v>45937</v>
-      </c>
-      <c r="E11" s="1" t="n">
-        <v>46316</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>EKERÖ</t>
-        </is>
-      </c>
-      <c r="I11" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="J11" t="n">
-        <v>0</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L11" t="n">
-        <v>2</v>
-      </c>
-      <c r="M11" t="n">
-        <v>1</v>
-      </c>
-      <c r="N11" t="n">
-        <v>0</v>
-      </c>
-      <c r="O11" t="n">
-        <v>0</v>
-      </c>
-      <c r="P11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>3</v>
-      </c>
-      <c r="R11" t="n">
-        <v>1</v>
-      </c>
-      <c r="S11" t="n">
-        <v>3</v>
-      </c>
-      <c r="T11" t="n">
-        <v>3</v>
-      </c>
-      <c r="U11" t="n">
-        <v>3</v>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
-        <is>
-          <t>Jättemusseron
-Motaggsvamp
-Svartvit taggsvamp</t>
-        </is>
-      </c>
-      <c r="W11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/artfynd/A 49131-2025 artfynd.xlsx", "A 49131-2025")</f>
-        <v/>
-      </c>
-      <c r="X11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor/A 49131-2025 karta.png", "A 49131-2025")</f>
-        <v/>
-      </c>
-      <c r="Y11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor_geotiff/A 49131-2025 georefererad karta.tif", "A 49131-2025")</f>
-        <v/>
-      </c>
-      <c r="AA11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomål/A 49131-2025 FSC-klagomål.docx", "A 49131-2025")</f>
-        <v/>
-      </c>
-      <c r="AB11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomålsmail/A 49131-2025 FSC-klagomål mail.docx", "A 49131-2025")</f>
-        <v/>
-      </c>
-      <c r="AC11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsyn/A 49131-2025 tillsynsbegäran.docx", "A 49131-2025")</f>
-        <v/>
-      </c>
-      <c r="AD11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsynsmail/A 49131-2025 tillsynsbegäran mail.docx", "A 49131-2025")</f>
         <v/>
       </c>
     </row>
@@ -1735,7 +1735,7 @@
         <v>45209</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1850,7 +1850,7 @@
         <v>45170</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1956,7 +1956,7 @@
         <v>44646</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2044,7 +2044,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 3221-2022</t>
+          <t>A 1793-2025</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2058,10 +2058,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>44582</v>
+        <v>45671</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2074,13 +2074,13 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>0.5</v>
+        <v>1.7</v>
       </c>
       <c r="J15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L15" t="n">
         <v>0</v>
@@ -2107,49 +2107,49 @@
         <v>1</v>
       </c>
       <c r="T15" t="n">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="U15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Mistel</t>
         </is>
       </c>
       <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/artfynd/A 3221-2022 artfynd.xlsx", "A 3221-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/artfynd/A 1793-2025 artfynd.xlsx", "A 1793-2025")</f>
         <v/>
       </c>
       <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor/A 3221-2022 karta.png", "A 3221-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor/A 1793-2025 karta.png", "A 1793-2025")</f>
         <v/>
       </c>
       <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor_geotiff/A 3221-2022 georefererad karta.tif", "A 3221-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor_geotiff/A 1793-2025 georefererad karta.tif", "A 1793-2025")</f>
         <v/>
       </c>
       <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomål/A 3221-2022 FSC-klagomål.docx", "A 3221-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomål/A 1793-2025 FSC-klagomål.docx", "A 1793-2025")</f>
         <v/>
       </c>
       <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomålsmail/A 3221-2022 FSC-klagomål mail.docx", "A 3221-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomålsmail/A 1793-2025 FSC-klagomål mail.docx", "A 1793-2025")</f>
         <v/>
       </c>
       <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsyn/A 3221-2022 tillsynsbegäran.docx", "A 3221-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsyn/A 1793-2025 tillsynsbegäran.docx", "A 1793-2025")</f>
         <v/>
       </c>
       <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsynsmail/A 3221-2022 tillsynsbegäran mail.docx", "A 3221-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsynsmail/A 1793-2025 tillsynsbegäran mail.docx", "A 1793-2025")</f>
         <v/>
       </c>
     </row>
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 13794-2023</t>
+          <t>A 2533-2026</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2163,10 +2163,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45007</v>
+        <v>46037</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2179,16 +2179,16 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>4.8</v>
+        <v>1.4</v>
       </c>
       <c r="J16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K16" t="n">
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
         <v>0</v>
@@ -2203,7 +2203,7 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
         <v>0</v>
@@ -2219,42 +2219,42 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/artfynd/A 13794-2023 artfynd.xlsx", "A 13794-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/artfynd/A 2533-2026 artfynd.xlsx", "A 2533-2026")</f>
         <v/>
       </c>
       <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor/A 13794-2023 karta.png", "A 13794-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor/A 2533-2026 karta.png", "A 2533-2026")</f>
         <v/>
       </c>
       <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor_geotiff/A 13794-2023 georefererad karta.tif", "A 13794-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor_geotiff/A 2533-2026 georefererad karta.tif", "A 2533-2026")</f>
         <v/>
       </c>
       <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomål/A 13794-2023 FSC-klagomål.docx", "A 13794-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomål/A 2533-2026 FSC-klagomål.docx", "A 2533-2026")</f>
         <v/>
       </c>
       <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomålsmail/A 13794-2023 FSC-klagomål mail.docx", "A 13794-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomålsmail/A 2533-2026 FSC-klagomål mail.docx", "A 2533-2026")</f>
         <v/>
       </c>
       <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsyn/A 13794-2023 tillsynsbegäran.docx", "A 13794-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsyn/A 2533-2026 tillsynsbegäran.docx", "A 2533-2026")</f>
         <v/>
       </c>
       <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsynsmail/A 13794-2023 tillsynsbegäran mail.docx", "A 13794-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsynsmail/A 2533-2026 tillsynsbegäran mail.docx", "A 2533-2026")</f>
         <v/>
       </c>
     </row>
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 2533-2026</t>
+          <t>A 3221-2022</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2268,10 +2268,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>46037</v>
+        <v>44582</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2284,13 +2284,13 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>1.4</v>
+        <v>0.5</v>
       </c>
       <c r="J17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L17" t="n">
         <v>0</v>
@@ -2320,46 +2320,46 @@
         <v>1</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/artfynd/A 2533-2026 artfynd.xlsx", "A 2533-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/artfynd/A 3221-2022 artfynd.xlsx", "A 3221-2022")</f>
         <v/>
       </c>
       <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor/A 2533-2026 karta.png", "A 2533-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor/A 3221-2022 karta.png", "A 3221-2022")</f>
         <v/>
       </c>
       <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor_geotiff/A 2533-2026 georefererad karta.tif", "A 2533-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor_geotiff/A 3221-2022 georefererad karta.tif", "A 3221-2022")</f>
         <v/>
       </c>
       <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomål/A 2533-2026 FSC-klagomål.docx", "A 2533-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomål/A 3221-2022 FSC-klagomål.docx", "A 3221-2022")</f>
         <v/>
       </c>
       <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomålsmail/A 2533-2026 FSC-klagomål mail.docx", "A 2533-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomålsmail/A 3221-2022 FSC-klagomål mail.docx", "A 3221-2022")</f>
         <v/>
       </c>
       <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsyn/A 2533-2026 tillsynsbegäran.docx", "A 2533-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsyn/A 3221-2022 tillsynsbegäran.docx", "A 3221-2022")</f>
         <v/>
       </c>
       <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsynsmail/A 2533-2026 tillsynsbegäran mail.docx", "A 2533-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsynsmail/A 3221-2022 tillsynsbegäran mail.docx", "A 3221-2022")</f>
         <v/>
       </c>
     </row>
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 1793-2025</t>
+          <t>A 13794-2023</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2373,10 +2373,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45671</v>
+        <v>45007</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2389,16 +2389,16 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>1.7</v>
+        <v>4.8</v>
       </c>
       <c r="J18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K18" t="n">
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M18" t="n">
         <v>0</v>
@@ -2413,7 +2413,7 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R18" t="n">
         <v>0</v>
@@ -2422,42 +2422,42 @@
         <v>1</v>
       </c>
       <c r="T18" t="n">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="U18" t="n">
         <v>0</v>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>Mistel</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="W18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/artfynd/A 1793-2025 artfynd.xlsx", "A 1793-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/artfynd/A 13794-2023 artfynd.xlsx", "A 13794-2023")</f>
         <v/>
       </c>
       <c r="X18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor/A 1793-2025 karta.png", "A 1793-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor/A 13794-2023 karta.png", "A 13794-2023")</f>
         <v/>
       </c>
       <c r="Y18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor_geotiff/A 1793-2025 georefererad karta.tif", "A 1793-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor_geotiff/A 13794-2023 georefererad karta.tif", "A 13794-2023")</f>
         <v/>
       </c>
       <c r="AA18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomål/A 1793-2025 FSC-klagomål.docx", "A 1793-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomål/A 13794-2023 FSC-klagomål.docx", "A 13794-2023")</f>
         <v/>
       </c>
       <c r="AB18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomålsmail/A 1793-2025 FSC-klagomål mail.docx", "A 1793-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomålsmail/A 13794-2023 FSC-klagomål mail.docx", "A 13794-2023")</f>
         <v/>
       </c>
       <c r="AC18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsyn/A 1793-2025 tillsynsbegäran.docx", "A 1793-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsyn/A 13794-2023 tillsynsbegäran.docx", "A 13794-2023")</f>
         <v/>
       </c>
       <c r="AD18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsynsmail/A 1793-2025 tillsynsbegäran mail.docx", "A 1793-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsynsmail/A 13794-2023 tillsynsbegäran mail.docx", "A 13794-2023")</f>
         <v/>
       </c>
     </row>
@@ -2481,7 +2481,7 @@
         <v>44670</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2554,7 +2554,7 @@
         <v>44802</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2610,7 +2610,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 3219-2022</t>
+          <t>A 63378-2025</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2624,10 +2624,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>44582</v>
+        <v>46010</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2640,7 +2640,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>0.5</v>
+        <v>4.8</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2683,7 +2683,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 63378-2025</t>
+          <t>A 50184-2023</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2697,10 +2697,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>46010</v>
+        <v>45208</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2713,7 +2713,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>4.8</v>
+        <v>10.8</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2756,7 +2756,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 2535-2026</t>
+          <t>A 37245-2025</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2770,10 +2770,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>46037</v>
+        <v>45876</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2786,7 +2786,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>1.6</v>
+        <v>1.1</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2829,7 +2829,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 50184-2023</t>
+          <t>A 56002-2024</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2843,10 +2843,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45208</v>
+        <v>45623</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2859,7 +2859,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>10.8</v>
+        <v>3.4</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2902,7 +2902,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 20399-2026</t>
+          <t>A 2535-2026</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2916,10 +2916,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>46139</v>
+        <v>46037</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2932,7 +2932,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>0.9</v>
+        <v>1.6</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2975,7 +2975,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 20398-2026</t>
+          <t>A 61217-2024</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2989,10 +2989,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>46139</v>
+        <v>45645</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3005,7 +3005,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>2.4</v>
+        <v>0.8</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -3048,7 +3048,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 37245-2025</t>
+          <t>A 3222-2022</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3062,10 +3062,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45876</v>
+        <v>44582</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3078,7 +3078,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>1.1</v>
+        <v>1.8</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -3121,7 +3121,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 20898-2026</t>
+          <t>A 20399-2026</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3135,10 +3135,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>46142</v>
+        <v>46139</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3151,7 +3151,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>3.6</v>
+        <v>0.9</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -3194,7 +3194,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 55724-2024</t>
+          <t>A 3219-2022</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3208,10 +3208,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45622</v>
+        <v>44582</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3267,7 +3267,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 34073-2025</t>
+          <t>A 20398-2026</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3277,14 +3277,14 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45845</v>
+        <v>46139</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3297,7 +3297,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>2.9</v>
+        <v>2.4</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3340,7 +3340,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 35955-2023</t>
+          <t>A 60755-2024</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3354,10 +3354,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45148</v>
+        <v>45644</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3370,7 +3370,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>1.1</v>
+        <v>2.1</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3413,7 +3413,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 61217-2024</t>
+          <t>A 55724-2024</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3427,10 +3427,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45645</v>
+        <v>45622</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3443,7 +3443,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3486,7 +3486,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 56002-2024</t>
+          <t>A 20898-2026</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3500,10 +3500,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45623</v>
+        <v>46142</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3516,7 +3516,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3559,7 +3559,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 60728-2022</t>
+          <t>A 35955-2023</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3573,10 +3573,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>44913</v>
+        <v>45148</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3589,7 +3589,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3632,7 +3632,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 3222-2022</t>
+          <t>A 34073-2025</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3642,14 +3642,14 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>44582</v>
+        <v>45845</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3662,7 +3662,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>1.8</v>
+        <v>2.9</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3705,7 +3705,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 33154-2026</t>
+          <t>A 60728-2022</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3719,10 +3719,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>46244</v>
+        <v>44913</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3734,13 +3734,8 @@
           <t>EKERÖ</t>
         </is>
       </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I36" t="n">
-        <v>3.5</v>
+        <v>1.2</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3783,7 +3778,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 41699-2026</t>
+          <t>A 33154-2026</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3797,10 +3792,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>46301</v>
+        <v>46244</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3818,7 +3813,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>1.6</v>
+        <v>3.5</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3861,7 +3856,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 60755-2024</t>
+          <t>A 41699-2026</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3875,10 +3870,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45644</v>
+        <v>46301</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3890,8 +3885,13 @@
           <t>EKERÖ</t>
         </is>
       </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I38" t="n">
-        <v>2.1</v>
+        <v>1.6</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3951,7 +3951,7 @@
         <v>46153</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>

--- a/Översikt EKERÖ.xlsx
+++ b/Översikt EKERÖ.xlsx
@@ -601,7 +601,7 @@
         <v>46241</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -728,7 +728,7 @@
         <v>44872</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -848,7 +848,7 @@
         <v>44974</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -963,7 +963,7 @@
         <v>45148</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1056,7 +1056,7 @@
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A 3218-2022</t>
+          <t>A 17520-2026</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1070,10 +1070,10 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>44582</v>
+        <v>46119</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1085,8 +1085,13 @@
           <t>EKERÖ</t>
         </is>
       </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I6" t="n">
-        <v>1.2</v>
+        <v>2.2</v>
       </c>
       <c r="J6" t="n">
         <v>1</v>
@@ -1095,13 +1100,13 @@
         <v>1</v>
       </c>
       <c r="L6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M6" t="n">
         <v>1</v>
       </c>
       <c r="N6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1110,21 +1115,130 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="R6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
       </c>
       <c r="T6" t="n">
+        <v>5</v>
+      </c>
+      <c r="U6" t="n">
+        <v>1</v>
+      </c>
+      <c r="V6" s="2" t="inlineStr">
+        <is>
+          <t>Läderbagge
+Blekticka
+Ekticka
+Kandelabersvamp
+Gulgrön kantmusseron</t>
+        </is>
+      </c>
+      <c r="W6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/artfynd/A 17520-2026 artfynd.xlsx", "A 17520-2026")</f>
+        <v/>
+      </c>
+      <c r="X6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor/A 17520-2026 karta.png", "A 17520-2026")</f>
+        <v/>
+      </c>
+      <c r="Y6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor_geotiff/A 17520-2026 georefererad karta.tif", "A 17520-2026")</f>
+        <v/>
+      </c>
+      <c r="AA6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomål/A 17520-2026 FSC-klagomål.docx", "A 17520-2026")</f>
+        <v/>
+      </c>
+      <c r="AB6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomålsmail/A 17520-2026 FSC-klagomål mail.docx", "A 17520-2026")</f>
+        <v/>
+      </c>
+      <c r="AC6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsyn/A 17520-2026 tillsynsbegäran.docx", "A 17520-2026")</f>
+        <v/>
+      </c>
+      <c r="AD6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsynsmail/A 17520-2026 tillsynsbegäran mail.docx", "A 17520-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7" ht="15" customHeight="1">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>A 3218-2022</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D7" s="1" t="n">
+        <v>44582</v>
+      </c>
+      <c r="E7" s="1" t="n">
+        <v>46318</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>EKERÖ</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="J7" t="n">
+        <v>1</v>
+      </c>
+      <c r="K7" t="n">
+        <v>1</v>
+      </c>
+      <c r="L7" t="n">
+        <v>1</v>
+      </c>
+      <c r="M7" t="n">
+        <v>1</v>
+      </c>
+      <c r="N7" t="n">
+        <v>1</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>3</v>
+      </c>
+      <c r="R7" t="n">
+        <v>2</v>
+      </c>
+      <c r="S7" t="n">
+        <v>5</v>
+      </c>
+      <c r="T7" t="n">
         <v>8</v>
       </c>
-      <c r="U6" t="n">
+      <c r="U7" t="n">
         <v>6</v>
       </c>
-      <c r="V6" s="2" t="inlineStr">
+      <c r="V7" s="2" t="inlineStr">
         <is>
           <t>Bombmurkla
 Gul lammticka
@@ -1133,146 +1247,32 @@
 Blåbär</t>
         </is>
       </c>
-      <c r="W6">
+      <c r="W7">
         <f>HYPERLINK("https://klasma.github.io/Logging_0125/artfynd/A 3218-2022 artfynd.xlsx", "A 3218-2022")</f>
         <v/>
       </c>
-      <c r="X6">
+      <c r="X7">
         <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor/A 3218-2022 karta.png", "A 3218-2022")</f>
         <v/>
       </c>
-      <c r="Y6">
+      <c r="Y7">
         <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor_geotiff/A 3218-2022 georefererad karta.tif", "A 3218-2022")</f>
         <v/>
       </c>
-      <c r="AA6">
+      <c r="AA7">
         <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomål/A 3218-2022 FSC-klagomål.docx", "A 3218-2022")</f>
         <v/>
       </c>
-      <c r="AB6">
+      <c r="AB7">
         <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomålsmail/A 3218-2022 FSC-klagomål mail.docx", "A 3218-2022")</f>
         <v/>
       </c>
-      <c r="AC6">
+      <c r="AC7">
         <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsyn/A 3218-2022 tillsynsbegäran.docx", "A 3218-2022")</f>
         <v/>
       </c>
-      <c r="AD6">
+      <c r="AD7">
         <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsynsmail/A 3218-2022 tillsynsbegäran mail.docx", "A 3218-2022")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="7" ht="15" customHeight="1">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>A 17520-2026</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D7" s="1" t="n">
-        <v>46119</v>
-      </c>
-      <c r="E7" s="1" t="n">
-        <v>46317</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>EKERÖ</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
-      <c r="I7" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="J7" t="n">
-        <v>1</v>
-      </c>
-      <c r="K7" t="n">
-        <v>1</v>
-      </c>
-      <c r="L7" t="n">
-        <v>3</v>
-      </c>
-      <c r="M7" t="n">
-        <v>1</v>
-      </c>
-      <c r="N7" t="n">
-        <v>0</v>
-      </c>
-      <c r="O7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>4</v>
-      </c>
-      <c r="R7" t="n">
-        <v>1</v>
-      </c>
-      <c r="S7" t="n">
-        <v>5</v>
-      </c>
-      <c r="T7" t="n">
-        <v>5</v>
-      </c>
-      <c r="U7" t="n">
-        <v>1</v>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>Läderbagge
-Blekticka
-Ekticka
-Kandelabersvamp
-Gulgrön kantmusseron</t>
-        </is>
-      </c>
-      <c r="W7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/artfynd/A 17520-2026 artfynd.xlsx", "A 17520-2026")</f>
-        <v/>
-      </c>
-      <c r="X7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor/A 17520-2026 karta.png", "A 17520-2026")</f>
-        <v/>
-      </c>
-      <c r="Y7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor_geotiff/A 17520-2026 georefererad karta.tif", "A 17520-2026")</f>
-        <v/>
-      </c>
-      <c r="AA7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomål/A 17520-2026 FSC-klagomål.docx", "A 17520-2026")</f>
-        <v/>
-      </c>
-      <c r="AB7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomålsmail/A 17520-2026 FSC-klagomål mail.docx", "A 17520-2026")</f>
-        <v/>
-      </c>
-      <c r="AC7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsyn/A 17520-2026 tillsynsbegäran.docx", "A 17520-2026")</f>
-        <v/>
-      </c>
-      <c r="AD7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsynsmail/A 17520-2026 tillsynsbegäran mail.docx", "A 17520-2026")</f>
         <v/>
       </c>
     </row>
@@ -1296,7 +1296,7 @@
         <v>46241</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1409,7 +1409,7 @@
         <v>44634</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1499,7 +1499,7 @@
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 49131-2025</t>
+          <t>A 13237-2023</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1513,10 +1513,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>45937</v>
+        <v>45002</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1528,20 +1528,25 @@
           <t>EKERÖ</t>
         </is>
       </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I10" t="n">
-        <v>0.9</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N10" t="n">
         <v>0</v>
@@ -1553,165 +1558,160 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="R10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
         <v>3</v>
       </c>
       <c r="T10" t="n">
+        <v>7</v>
+      </c>
+      <c r="U10" t="n">
+        <v>0</v>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
+        <is>
+          <t>Tallticka
+Granbarkgnagare
+Grönpyrola</t>
+        </is>
+      </c>
+      <c r="W10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/artfynd/A 13237-2023 artfynd.xlsx", "A 13237-2023")</f>
+        <v/>
+      </c>
+      <c r="X10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor/A 13237-2023 karta.png", "A 13237-2023")</f>
+        <v/>
+      </c>
+      <c r="Y10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor_geotiff/A 13237-2023 georefererad karta.tif", "A 13237-2023")</f>
+        <v/>
+      </c>
+      <c r="AA10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomål/A 13237-2023 FSC-klagomål.docx", "A 13237-2023")</f>
+        <v/>
+      </c>
+      <c r="AB10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomålsmail/A 13237-2023 FSC-klagomål mail.docx", "A 13237-2023")</f>
+        <v/>
+      </c>
+      <c r="AC10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsyn/A 13237-2023 tillsynsbegäran.docx", "A 13237-2023")</f>
+        <v/>
+      </c>
+      <c r="AD10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsynsmail/A 13237-2023 tillsynsbegäran mail.docx", "A 13237-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11" ht="15" customHeight="1">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>A 49131-2025</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D11" s="1" t="n">
+        <v>45937</v>
+      </c>
+      <c r="E11" s="1" t="n">
+        <v>46318</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>EKERÖ</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" t="n">
+        <v>2</v>
+      </c>
+      <c r="M11" t="n">
+        <v>1</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" t="n">
         <v>3</v>
       </c>
-      <c r="U10" t="n">
+      <c r="R11" t="n">
+        <v>1</v>
+      </c>
+      <c r="S11" t="n">
         <v>3</v>
       </c>
-      <c r="V10" s="2" t="inlineStr">
+      <c r="T11" t="n">
+        <v>3</v>
+      </c>
+      <c r="U11" t="n">
+        <v>3</v>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
         <is>
           <t>Jättemusseron
 Motaggsvamp
 Svartvit taggsvamp</t>
         </is>
       </c>
-      <c r="W10">
+      <c r="W11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0125/artfynd/A 49131-2025 artfynd.xlsx", "A 49131-2025")</f>
         <v/>
       </c>
-      <c r="X10">
+      <c r="X11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor/A 49131-2025 karta.png", "A 49131-2025")</f>
         <v/>
       </c>
-      <c r="Y10">
+      <c r="Y11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor_geotiff/A 49131-2025 georefererad karta.tif", "A 49131-2025")</f>
         <v/>
       </c>
-      <c r="AA10">
+      <c r="AA11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomål/A 49131-2025 FSC-klagomål.docx", "A 49131-2025")</f>
         <v/>
       </c>
-      <c r="AB10">
+      <c r="AB11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomålsmail/A 49131-2025 FSC-klagomål mail.docx", "A 49131-2025")</f>
         <v/>
       </c>
-      <c r="AC10">
+      <c r="AC11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsyn/A 49131-2025 tillsynsbegäran.docx", "A 49131-2025")</f>
         <v/>
       </c>
-      <c r="AD10">
+      <c r="AD11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsynsmail/A 49131-2025 tillsynsbegäran mail.docx", "A 49131-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="11" ht="15" customHeight="1">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>A 13237-2023</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D11" s="1" t="n">
-        <v>45002</v>
-      </c>
-      <c r="E11" s="1" t="n">
-        <v>46317</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>EKERÖ</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
-      <c r="I11" t="n">
-        <v>9.300000000000001</v>
-      </c>
-      <c r="J11" t="n">
-        <v>0</v>
-      </c>
-      <c r="K11" t="n">
-        <v>2</v>
-      </c>
-      <c r="L11" t="n">
-        <v>1</v>
-      </c>
-      <c r="M11" t="n">
-        <v>0</v>
-      </c>
-      <c r="N11" t="n">
-        <v>0</v>
-      </c>
-      <c r="O11" t="n">
-        <v>0</v>
-      </c>
-      <c r="P11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>1</v>
-      </c>
-      <c r="R11" t="n">
-        <v>0</v>
-      </c>
-      <c r="S11" t="n">
-        <v>3</v>
-      </c>
-      <c r="T11" t="n">
-        <v>7</v>
-      </c>
-      <c r="U11" t="n">
-        <v>0</v>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
-        <is>
-          <t>Tallticka
-Granbarkgnagare
-Grönpyrola</t>
-        </is>
-      </c>
-      <c r="W11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/artfynd/A 13237-2023 artfynd.xlsx", "A 13237-2023")</f>
-        <v/>
-      </c>
-      <c r="X11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor/A 13237-2023 karta.png", "A 13237-2023")</f>
-        <v/>
-      </c>
-      <c r="Y11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor_geotiff/A 13237-2023 georefererad karta.tif", "A 13237-2023")</f>
-        <v/>
-      </c>
-      <c r="AA11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomål/A 13237-2023 FSC-klagomål.docx", "A 13237-2023")</f>
-        <v/>
-      </c>
-      <c r="AB11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomålsmail/A 13237-2023 FSC-klagomål mail.docx", "A 13237-2023")</f>
-        <v/>
-      </c>
-      <c r="AC11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsyn/A 13237-2023 tillsynsbegäran.docx", "A 13237-2023")</f>
-        <v/>
-      </c>
-      <c r="AD11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsynsmail/A 13237-2023 tillsynsbegäran mail.docx", "A 13237-2023")</f>
         <v/>
       </c>
     </row>
@@ -1735,7 +1735,7 @@
         <v>45209</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1850,7 +1850,7 @@
         <v>45170</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1956,7 +1956,7 @@
         <v>44646</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2044,7 +2044,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 1793-2025</t>
+          <t>A 3221-2022</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2058,10 +2058,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45671</v>
+        <v>44582</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2074,13 +2074,13 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>1.7</v>
+        <v>0.5</v>
       </c>
       <c r="J15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L15" t="n">
         <v>0</v>
@@ -2107,49 +2107,49 @@
         <v>1</v>
       </c>
       <c r="T15" t="n">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>Mistel</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/artfynd/A 1793-2025 artfynd.xlsx", "A 1793-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/artfynd/A 3221-2022 artfynd.xlsx", "A 3221-2022")</f>
         <v/>
       </c>
       <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor/A 1793-2025 karta.png", "A 1793-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor/A 3221-2022 karta.png", "A 3221-2022")</f>
         <v/>
       </c>
       <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor_geotiff/A 1793-2025 georefererad karta.tif", "A 1793-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor_geotiff/A 3221-2022 georefererad karta.tif", "A 3221-2022")</f>
         <v/>
       </c>
       <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomål/A 1793-2025 FSC-klagomål.docx", "A 1793-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomål/A 3221-2022 FSC-klagomål.docx", "A 3221-2022")</f>
         <v/>
       </c>
       <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomålsmail/A 1793-2025 FSC-klagomål mail.docx", "A 1793-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomålsmail/A 3221-2022 FSC-klagomål mail.docx", "A 3221-2022")</f>
         <v/>
       </c>
       <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsyn/A 1793-2025 tillsynsbegäran.docx", "A 1793-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsyn/A 3221-2022 tillsynsbegäran.docx", "A 3221-2022")</f>
         <v/>
       </c>
       <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsynsmail/A 1793-2025 tillsynsbegäran mail.docx", "A 1793-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsynsmail/A 3221-2022 tillsynsbegäran mail.docx", "A 3221-2022")</f>
         <v/>
       </c>
     </row>
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 2533-2026</t>
+          <t>A 13794-2023</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2163,10 +2163,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>46037</v>
+        <v>45007</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2179,16 +2179,16 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>1.4</v>
+        <v>4.8</v>
       </c>
       <c r="J16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K16" t="n">
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M16" t="n">
         <v>0</v>
@@ -2203,7 +2203,7 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R16" t="n">
         <v>0</v>
@@ -2219,42 +2219,42 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/artfynd/A 2533-2026 artfynd.xlsx", "A 2533-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/artfynd/A 13794-2023 artfynd.xlsx", "A 13794-2023")</f>
         <v/>
       </c>
       <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor/A 2533-2026 karta.png", "A 2533-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor/A 13794-2023 karta.png", "A 13794-2023")</f>
         <v/>
       </c>
       <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor_geotiff/A 2533-2026 georefererad karta.tif", "A 2533-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor_geotiff/A 13794-2023 georefererad karta.tif", "A 13794-2023")</f>
         <v/>
       </c>
       <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomål/A 2533-2026 FSC-klagomål.docx", "A 2533-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomål/A 13794-2023 FSC-klagomål.docx", "A 13794-2023")</f>
         <v/>
       </c>
       <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomålsmail/A 2533-2026 FSC-klagomål mail.docx", "A 2533-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomålsmail/A 13794-2023 FSC-klagomål mail.docx", "A 13794-2023")</f>
         <v/>
       </c>
       <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsyn/A 2533-2026 tillsynsbegäran.docx", "A 2533-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsyn/A 13794-2023 tillsynsbegäran.docx", "A 13794-2023")</f>
         <v/>
       </c>
       <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsynsmail/A 2533-2026 tillsynsbegäran mail.docx", "A 2533-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsynsmail/A 13794-2023 tillsynsbegäran mail.docx", "A 13794-2023")</f>
         <v/>
       </c>
     </row>
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 3221-2022</t>
+          <t>A 2533-2026</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2268,10 +2268,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>44582</v>
+        <v>46037</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2284,13 +2284,13 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>0.5</v>
+        <v>1.4</v>
       </c>
       <c r="J17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L17" t="n">
         <v>0</v>
@@ -2320,46 +2320,46 @@
         <v>1</v>
       </c>
       <c r="U17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/artfynd/A 3221-2022 artfynd.xlsx", "A 3221-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/artfynd/A 2533-2026 artfynd.xlsx", "A 2533-2026")</f>
         <v/>
       </c>
       <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor/A 3221-2022 karta.png", "A 3221-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor/A 2533-2026 karta.png", "A 2533-2026")</f>
         <v/>
       </c>
       <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor_geotiff/A 3221-2022 georefererad karta.tif", "A 3221-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor_geotiff/A 2533-2026 georefererad karta.tif", "A 2533-2026")</f>
         <v/>
       </c>
       <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomål/A 3221-2022 FSC-klagomål.docx", "A 3221-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomål/A 2533-2026 FSC-klagomål.docx", "A 2533-2026")</f>
         <v/>
       </c>
       <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomålsmail/A 3221-2022 FSC-klagomål mail.docx", "A 3221-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomålsmail/A 2533-2026 FSC-klagomål mail.docx", "A 2533-2026")</f>
         <v/>
       </c>
       <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsyn/A 3221-2022 tillsynsbegäran.docx", "A 3221-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsyn/A 2533-2026 tillsynsbegäran.docx", "A 2533-2026")</f>
         <v/>
       </c>
       <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsynsmail/A 3221-2022 tillsynsbegäran mail.docx", "A 3221-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsynsmail/A 2533-2026 tillsynsbegäran mail.docx", "A 2533-2026")</f>
         <v/>
       </c>
     </row>
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 13794-2023</t>
+          <t>A 1793-2025</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2373,10 +2373,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45007</v>
+        <v>45671</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2389,16 +2389,16 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>4.8</v>
+        <v>1.7</v>
       </c>
       <c r="J18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K18" t="n">
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
         <v>0</v>
@@ -2413,7 +2413,7 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
         <v>0</v>
@@ -2422,42 +2422,42 @@
         <v>1</v>
       </c>
       <c r="T18" t="n">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="U18" t="n">
         <v>0</v>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Mistel</t>
         </is>
       </c>
       <c r="W18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/artfynd/A 13794-2023 artfynd.xlsx", "A 13794-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/artfynd/A 1793-2025 artfynd.xlsx", "A 1793-2025")</f>
         <v/>
       </c>
       <c r="X18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor/A 13794-2023 karta.png", "A 13794-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor/A 1793-2025 karta.png", "A 1793-2025")</f>
         <v/>
       </c>
       <c r="Y18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor_geotiff/A 13794-2023 georefererad karta.tif", "A 13794-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor_geotiff/A 1793-2025 georefererad karta.tif", "A 1793-2025")</f>
         <v/>
       </c>
       <c r="AA18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomål/A 13794-2023 FSC-klagomål.docx", "A 13794-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomål/A 1793-2025 FSC-klagomål.docx", "A 1793-2025")</f>
         <v/>
       </c>
       <c r="AB18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomålsmail/A 13794-2023 FSC-klagomål mail.docx", "A 13794-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomålsmail/A 1793-2025 FSC-klagomål mail.docx", "A 1793-2025")</f>
         <v/>
       </c>
       <c r="AC18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsyn/A 13794-2023 tillsynsbegäran.docx", "A 13794-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsyn/A 1793-2025 tillsynsbegäran.docx", "A 1793-2025")</f>
         <v/>
       </c>
       <c r="AD18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsynsmail/A 13794-2023 tillsynsbegäran mail.docx", "A 13794-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsynsmail/A 1793-2025 tillsynsbegäran mail.docx", "A 1793-2025")</f>
         <v/>
       </c>
     </row>
@@ -2481,7 +2481,7 @@
         <v>44670</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2554,7 +2554,7 @@
         <v>44802</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2610,7 +2610,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 63378-2025</t>
+          <t>A 3219-2022</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2624,10 +2624,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>46010</v>
+        <v>44582</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2640,7 +2640,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>4.8</v>
+        <v>0.5</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2683,7 +2683,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 50184-2023</t>
+          <t>A 3222-2022</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2697,10 +2697,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>45208</v>
+        <v>44582</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2713,7 +2713,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>10.8</v>
+        <v>1.8</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2773,7 +2773,7 @@
         <v>45876</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2829,7 +2829,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 56002-2024</t>
+          <t>A 20399-2026</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2843,10 +2843,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45623</v>
+        <v>46139</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2859,7 +2859,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>3.4</v>
+        <v>0.9</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2902,7 +2902,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 2535-2026</t>
+          <t>A 20398-2026</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2916,10 +2916,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>46037</v>
+        <v>46139</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2932,7 +2932,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>1.6</v>
+        <v>2.4</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2975,7 +2975,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 61217-2024</t>
+          <t>A 20898-2026</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2989,10 +2989,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45645</v>
+        <v>46142</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3005,7 +3005,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>0.8</v>
+        <v>3.6</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -3048,7 +3048,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 3222-2022</t>
+          <t>A 63378-2025</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3062,10 +3062,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>44582</v>
+        <v>46010</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3078,7 +3078,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>1.8</v>
+        <v>4.8</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -3121,7 +3121,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 20399-2026</t>
+          <t>A 34073-2025</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3131,14 +3131,14 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>46139</v>
+        <v>45845</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3151,7 +3151,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>0.9</v>
+        <v>2.9</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -3194,7 +3194,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 3219-2022</t>
+          <t>A 60755-2024</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3208,10 +3208,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>44582</v>
+        <v>45644</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3224,7 +3224,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>0.5</v>
+        <v>2.1</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3267,7 +3267,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 20398-2026</t>
+          <t>A 2535-2026</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3281,10 +3281,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>46139</v>
+        <v>46037</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3297,7 +3297,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>2.4</v>
+        <v>1.6</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3340,7 +3340,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 60755-2024</t>
+          <t>A 50184-2023</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3354,10 +3354,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45644</v>
+        <v>45208</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3370,7 +3370,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>2.1</v>
+        <v>10.8</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3413,7 +3413,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 55724-2024</t>
+          <t>A 33154-2026</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3427,10 +3427,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45622</v>
+        <v>46244</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3442,8 +3442,13 @@
           <t>EKERÖ</t>
         </is>
       </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I32" t="n">
-        <v>0.5</v>
+        <v>3.5</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3486,7 +3491,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 20898-2026</t>
+          <t>A 55724-2024</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3500,10 +3505,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>46142</v>
+        <v>45622</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3516,7 +3521,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>3.6</v>
+        <v>0.5</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3559,7 +3564,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 35955-2023</t>
+          <t>A 41699-2026</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3573,10 +3578,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45148</v>
+        <v>46301</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3588,8 +3593,13 @@
           <t>EKERÖ</t>
         </is>
       </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I34" t="n">
-        <v>1.1</v>
+        <v>1.6</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3632,7 +3642,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 34073-2025</t>
+          <t>A 35955-2023</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3642,14 +3652,14 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45845</v>
+        <v>45148</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3662,7 +3672,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>2.9</v>
+        <v>1.1</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3705,7 +3715,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 60728-2022</t>
+          <t>A 61217-2024</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3719,10 +3729,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>44913</v>
+        <v>45645</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3735,7 +3745,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>1.2</v>
+        <v>0.8</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3778,7 +3788,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 33154-2026</t>
+          <t>A 56002-2024</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3792,10 +3802,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>46244</v>
+        <v>45623</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3807,13 +3817,8 @@
           <t>EKERÖ</t>
         </is>
       </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I37" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3856,7 +3861,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 41699-2026</t>
+          <t>A 60728-2022</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3870,10 +3875,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>46301</v>
+        <v>44913</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3885,13 +3890,8 @@
           <t>EKERÖ</t>
         </is>
       </c>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I38" t="n">
-        <v>1.6</v>
+        <v>1.2</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3951,7 +3951,7 @@
         <v>46153</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>

--- a/Översikt EKERÖ.xlsx
+++ b/Översikt EKERÖ.xlsx
@@ -601,7 +601,7 @@
         <v>46241</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -728,7 +728,7 @@
         <v>44872</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -848,7 +848,7 @@
         <v>44974</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -963,7 +963,7 @@
         <v>45148</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1073,7 +1073,7 @@
         <v>46119</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1187,7 +1187,7 @@
         <v>44582</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1296,7 +1296,7 @@
         <v>46241</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1409,7 +1409,7 @@
         <v>44634</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1499,7 +1499,7 @@
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 13237-2023</t>
+          <t>A 49131-2025</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1513,10 +1513,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>45002</v>
+        <v>45937</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1528,25 +1528,20 @@
           <t>EKERÖ</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I10" t="n">
-        <v>9.300000000000001</v>
+        <v>0.9</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
       </c>
       <c r="K10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" t="n">
         <v>2</v>
       </c>
-      <c r="L10" t="n">
-        <v>1</v>
-      </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N10" t="n">
         <v>0</v>
@@ -1558,160 +1553,165 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S10" t="n">
         <v>3</v>
       </c>
       <c r="T10" t="n">
+        <v>3</v>
+      </c>
+      <c r="U10" t="n">
+        <v>3</v>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
+        <is>
+          <t>Jättemusseron
+Motaggsvamp
+Svartvit taggsvamp</t>
+        </is>
+      </c>
+      <c r="W10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/artfynd/A 49131-2025 artfynd.xlsx", "A 49131-2025")</f>
+        <v/>
+      </c>
+      <c r="X10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor/A 49131-2025 karta.png", "A 49131-2025")</f>
+        <v/>
+      </c>
+      <c r="Y10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor_geotiff/A 49131-2025 georefererad karta.tif", "A 49131-2025")</f>
+        <v/>
+      </c>
+      <c r="AA10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomål/A 49131-2025 FSC-klagomål.docx", "A 49131-2025")</f>
+        <v/>
+      </c>
+      <c r="AB10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomålsmail/A 49131-2025 FSC-klagomål mail.docx", "A 49131-2025")</f>
+        <v/>
+      </c>
+      <c r="AC10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsyn/A 49131-2025 tillsynsbegäran.docx", "A 49131-2025")</f>
+        <v/>
+      </c>
+      <c r="AD10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsynsmail/A 49131-2025 tillsynsbegäran mail.docx", "A 49131-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11" ht="15" customHeight="1">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>A 13237-2023</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D11" s="1" t="n">
+        <v>45002</v>
+      </c>
+      <c r="E11" s="1" t="n">
+        <v>46319</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>EKERÖ</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" t="n">
+        <v>2</v>
+      </c>
+      <c r="L11" t="n">
+        <v>1</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>1</v>
+      </c>
+      <c r="R11" t="n">
+        <v>0</v>
+      </c>
+      <c r="S11" t="n">
+        <v>3</v>
+      </c>
+      <c r="T11" t="n">
         <v>7</v>
       </c>
-      <c r="U10" t="n">
-        <v>0</v>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
+      <c r="U11" t="n">
+        <v>0</v>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
         <is>
           <t>Tallticka
 Granbarkgnagare
 Grönpyrola</t>
         </is>
       </c>
-      <c r="W10">
+      <c r="W11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0125/artfynd/A 13237-2023 artfynd.xlsx", "A 13237-2023")</f>
         <v/>
       </c>
-      <c r="X10">
+      <c r="X11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor/A 13237-2023 karta.png", "A 13237-2023")</f>
         <v/>
       </c>
-      <c r="Y10">
+      <c r="Y11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor_geotiff/A 13237-2023 georefererad karta.tif", "A 13237-2023")</f>
         <v/>
       </c>
-      <c r="AA10">
+      <c r="AA11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomål/A 13237-2023 FSC-klagomål.docx", "A 13237-2023")</f>
         <v/>
       </c>
-      <c r="AB10">
+      <c r="AB11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomålsmail/A 13237-2023 FSC-klagomål mail.docx", "A 13237-2023")</f>
         <v/>
       </c>
-      <c r="AC10">
+      <c r="AC11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsyn/A 13237-2023 tillsynsbegäran.docx", "A 13237-2023")</f>
         <v/>
       </c>
-      <c r="AD10">
+      <c r="AD11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsynsmail/A 13237-2023 tillsynsbegäran mail.docx", "A 13237-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="11" ht="15" customHeight="1">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>A 49131-2025</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D11" s="1" t="n">
-        <v>45937</v>
-      </c>
-      <c r="E11" s="1" t="n">
-        <v>46318</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>EKERÖ</t>
-        </is>
-      </c>
-      <c r="I11" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="J11" t="n">
-        <v>0</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L11" t="n">
-        <v>2</v>
-      </c>
-      <c r="M11" t="n">
-        <v>1</v>
-      </c>
-      <c r="N11" t="n">
-        <v>0</v>
-      </c>
-      <c r="O11" t="n">
-        <v>0</v>
-      </c>
-      <c r="P11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>3</v>
-      </c>
-      <c r="R11" t="n">
-        <v>1</v>
-      </c>
-      <c r="S11" t="n">
-        <v>3</v>
-      </c>
-      <c r="T11" t="n">
-        <v>3</v>
-      </c>
-      <c r="U11" t="n">
-        <v>3</v>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
-        <is>
-          <t>Jättemusseron
-Motaggsvamp
-Svartvit taggsvamp</t>
-        </is>
-      </c>
-      <c r="W11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/artfynd/A 49131-2025 artfynd.xlsx", "A 49131-2025")</f>
-        <v/>
-      </c>
-      <c r="X11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor/A 49131-2025 karta.png", "A 49131-2025")</f>
-        <v/>
-      </c>
-      <c r="Y11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor_geotiff/A 49131-2025 georefererad karta.tif", "A 49131-2025")</f>
-        <v/>
-      </c>
-      <c r="AA11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomål/A 49131-2025 FSC-klagomål.docx", "A 49131-2025")</f>
-        <v/>
-      </c>
-      <c r="AB11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomålsmail/A 49131-2025 FSC-klagomål mail.docx", "A 49131-2025")</f>
-        <v/>
-      </c>
-      <c r="AC11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsyn/A 49131-2025 tillsynsbegäran.docx", "A 49131-2025")</f>
-        <v/>
-      </c>
-      <c r="AD11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsynsmail/A 49131-2025 tillsynsbegäran mail.docx", "A 49131-2025")</f>
         <v/>
       </c>
     </row>
@@ -1735,7 +1735,7 @@
         <v>45209</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1850,7 +1850,7 @@
         <v>45170</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1956,7 +1956,7 @@
         <v>44646</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2044,7 +2044,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 3221-2022</t>
+          <t>A 1793-2025</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2058,10 +2058,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>44582</v>
+        <v>45671</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2074,13 +2074,13 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>0.5</v>
+        <v>1.7</v>
       </c>
       <c r="J15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L15" t="n">
         <v>0</v>
@@ -2107,49 +2107,49 @@
         <v>1</v>
       </c>
       <c r="T15" t="n">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="U15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Mistel</t>
         </is>
       </c>
       <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/artfynd/A 3221-2022 artfynd.xlsx", "A 3221-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/artfynd/A 1793-2025 artfynd.xlsx", "A 1793-2025")</f>
         <v/>
       </c>
       <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor/A 3221-2022 karta.png", "A 3221-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor/A 1793-2025 karta.png", "A 1793-2025")</f>
         <v/>
       </c>
       <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor_geotiff/A 3221-2022 georefererad karta.tif", "A 3221-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor_geotiff/A 1793-2025 georefererad karta.tif", "A 1793-2025")</f>
         <v/>
       </c>
       <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomål/A 3221-2022 FSC-klagomål.docx", "A 3221-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomål/A 1793-2025 FSC-klagomål.docx", "A 1793-2025")</f>
         <v/>
       </c>
       <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomålsmail/A 3221-2022 FSC-klagomål mail.docx", "A 3221-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomålsmail/A 1793-2025 FSC-klagomål mail.docx", "A 1793-2025")</f>
         <v/>
       </c>
       <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsyn/A 3221-2022 tillsynsbegäran.docx", "A 3221-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsyn/A 1793-2025 tillsynsbegäran.docx", "A 1793-2025")</f>
         <v/>
       </c>
       <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsynsmail/A 3221-2022 tillsynsbegäran mail.docx", "A 3221-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsynsmail/A 1793-2025 tillsynsbegäran mail.docx", "A 1793-2025")</f>
         <v/>
       </c>
     </row>
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 13794-2023</t>
+          <t>A 2533-2026</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2163,10 +2163,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45007</v>
+        <v>46037</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2179,16 +2179,16 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>4.8</v>
+        <v>1.4</v>
       </c>
       <c r="J16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K16" t="n">
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
         <v>0</v>
@@ -2203,7 +2203,7 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
         <v>0</v>
@@ -2219,42 +2219,42 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/artfynd/A 13794-2023 artfynd.xlsx", "A 13794-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/artfynd/A 2533-2026 artfynd.xlsx", "A 2533-2026")</f>
         <v/>
       </c>
       <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor/A 13794-2023 karta.png", "A 13794-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor/A 2533-2026 karta.png", "A 2533-2026")</f>
         <v/>
       </c>
       <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor_geotiff/A 13794-2023 georefererad karta.tif", "A 13794-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor_geotiff/A 2533-2026 georefererad karta.tif", "A 2533-2026")</f>
         <v/>
       </c>
       <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomål/A 13794-2023 FSC-klagomål.docx", "A 13794-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomål/A 2533-2026 FSC-klagomål.docx", "A 2533-2026")</f>
         <v/>
       </c>
       <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomålsmail/A 13794-2023 FSC-klagomål mail.docx", "A 13794-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomålsmail/A 2533-2026 FSC-klagomål mail.docx", "A 2533-2026")</f>
         <v/>
       </c>
       <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsyn/A 13794-2023 tillsynsbegäran.docx", "A 13794-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsyn/A 2533-2026 tillsynsbegäran.docx", "A 2533-2026")</f>
         <v/>
       </c>
       <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsynsmail/A 13794-2023 tillsynsbegäran mail.docx", "A 13794-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsynsmail/A 2533-2026 tillsynsbegäran mail.docx", "A 2533-2026")</f>
         <v/>
       </c>
     </row>
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 2533-2026</t>
+          <t>A 3221-2022</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2268,10 +2268,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>46037</v>
+        <v>44582</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2284,13 +2284,13 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>1.4</v>
+        <v>0.5</v>
       </c>
       <c r="J17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L17" t="n">
         <v>0</v>
@@ -2320,46 +2320,46 @@
         <v>1</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/artfynd/A 2533-2026 artfynd.xlsx", "A 2533-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/artfynd/A 3221-2022 artfynd.xlsx", "A 3221-2022")</f>
         <v/>
       </c>
       <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor/A 2533-2026 karta.png", "A 2533-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor/A 3221-2022 karta.png", "A 3221-2022")</f>
         <v/>
       </c>
       <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor_geotiff/A 2533-2026 georefererad karta.tif", "A 2533-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor_geotiff/A 3221-2022 georefererad karta.tif", "A 3221-2022")</f>
         <v/>
       </c>
       <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomål/A 2533-2026 FSC-klagomål.docx", "A 2533-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomål/A 3221-2022 FSC-klagomål.docx", "A 3221-2022")</f>
         <v/>
       </c>
       <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomålsmail/A 2533-2026 FSC-klagomål mail.docx", "A 2533-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomålsmail/A 3221-2022 FSC-klagomål mail.docx", "A 3221-2022")</f>
         <v/>
       </c>
       <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsyn/A 2533-2026 tillsynsbegäran.docx", "A 2533-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsyn/A 3221-2022 tillsynsbegäran.docx", "A 3221-2022")</f>
         <v/>
       </c>
       <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsynsmail/A 2533-2026 tillsynsbegäran mail.docx", "A 2533-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsynsmail/A 3221-2022 tillsynsbegäran mail.docx", "A 3221-2022")</f>
         <v/>
       </c>
     </row>
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 1793-2025</t>
+          <t>A 13794-2023</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2373,10 +2373,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45671</v>
+        <v>45007</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2389,16 +2389,16 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>1.7</v>
+        <v>4.8</v>
       </c>
       <c r="J18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K18" t="n">
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M18" t="n">
         <v>0</v>
@@ -2413,7 +2413,7 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R18" t="n">
         <v>0</v>
@@ -2422,42 +2422,42 @@
         <v>1</v>
       </c>
       <c r="T18" t="n">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="U18" t="n">
         <v>0</v>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>Mistel</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="W18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/artfynd/A 1793-2025 artfynd.xlsx", "A 1793-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/artfynd/A 13794-2023 artfynd.xlsx", "A 13794-2023")</f>
         <v/>
       </c>
       <c r="X18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor/A 1793-2025 karta.png", "A 1793-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor/A 13794-2023 karta.png", "A 13794-2023")</f>
         <v/>
       </c>
       <c r="Y18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor_geotiff/A 1793-2025 georefererad karta.tif", "A 1793-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor_geotiff/A 13794-2023 georefererad karta.tif", "A 13794-2023")</f>
         <v/>
       </c>
       <c r="AA18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomål/A 1793-2025 FSC-klagomål.docx", "A 1793-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomål/A 13794-2023 FSC-klagomål.docx", "A 13794-2023")</f>
         <v/>
       </c>
       <c r="AB18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomålsmail/A 1793-2025 FSC-klagomål mail.docx", "A 1793-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomålsmail/A 13794-2023 FSC-klagomål mail.docx", "A 13794-2023")</f>
         <v/>
       </c>
       <c r="AC18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsyn/A 1793-2025 tillsynsbegäran.docx", "A 1793-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsyn/A 13794-2023 tillsynsbegäran.docx", "A 13794-2023")</f>
         <v/>
       </c>
       <c r="AD18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsynsmail/A 1793-2025 tillsynsbegäran mail.docx", "A 1793-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsynsmail/A 13794-2023 tillsynsbegäran mail.docx", "A 13794-2023")</f>
         <v/>
       </c>
     </row>
@@ -2481,7 +2481,7 @@
         <v>44670</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2554,7 +2554,7 @@
         <v>44802</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2610,7 +2610,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 3219-2022</t>
+          <t>A 60728-2022</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2624,10 +2624,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>44582</v>
+        <v>44913</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2640,7 +2640,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>0.5</v>
+        <v>1.2</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2683,7 +2683,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 3222-2022</t>
+          <t>A 34073-2025</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2693,14 +2693,14 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>44582</v>
+        <v>45845</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2713,7 +2713,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>1.8</v>
+        <v>2.9</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2756,7 +2756,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 37245-2025</t>
+          <t>A 63378-2025</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2770,10 +2770,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45876</v>
+        <v>46010</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2786,7 +2786,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>1.1</v>
+        <v>4.8</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2829,7 +2829,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 20399-2026</t>
+          <t>A 33154-2026</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2843,10 +2843,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>46139</v>
+        <v>46244</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2858,8 +2858,13 @@
           <t>EKERÖ</t>
         </is>
       </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I24" t="n">
-        <v>0.9</v>
+        <v>3.5</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2902,7 +2907,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 20398-2026</t>
+          <t>A 2535-2026</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2916,10 +2921,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>46139</v>
+        <v>46037</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2932,7 +2937,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>2.4</v>
+        <v>1.6</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2975,7 +2980,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 20898-2026</t>
+          <t>A 41699-2026</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2989,10 +2994,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>46142</v>
+        <v>46301</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3004,8 +3009,13 @@
           <t>EKERÖ</t>
         </is>
       </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I26" t="n">
-        <v>3.6</v>
+        <v>1.6</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -3048,7 +3058,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 63378-2025</t>
+          <t>A 37245-2025</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3062,10 +3072,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>46010</v>
+        <v>45876</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3078,7 +3088,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>4.8</v>
+        <v>1.1</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -3121,7 +3131,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 34073-2025</t>
+          <t>A 50184-2023</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3131,14 +3141,14 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45845</v>
+        <v>45208</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3151,7 +3161,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>2.9</v>
+        <v>10.8</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -3194,7 +3204,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 60755-2024</t>
+          <t>A 20399-2026</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3208,10 +3218,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45644</v>
+        <v>46139</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3224,7 +3234,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>2.1</v>
+        <v>0.9</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3267,7 +3277,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 2535-2026</t>
+          <t>A 20398-2026</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3281,10 +3291,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>46037</v>
+        <v>46139</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3297,7 +3307,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>1.6</v>
+        <v>2.4</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3340,7 +3350,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 50184-2023</t>
+          <t>A 20898-2026</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3354,10 +3364,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45208</v>
+        <v>46142</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3370,7 +3380,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>10.8</v>
+        <v>3.6</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3413,7 +3423,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 33154-2026</t>
+          <t>A 56002-2024</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3427,10 +3437,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>46244</v>
+        <v>45623</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3442,13 +3452,8 @@
           <t>EKERÖ</t>
         </is>
       </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I32" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3491,7 +3496,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 55724-2024</t>
+          <t>A 61217-2024</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3505,10 +3510,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45622</v>
+        <v>45645</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3521,7 +3526,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3564,7 +3569,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 41699-2026</t>
+          <t>A 3222-2022</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3578,10 +3583,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>46301</v>
+        <v>44582</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3593,13 +3598,8 @@
           <t>EKERÖ</t>
         </is>
       </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I34" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3642,7 +3642,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 35955-2023</t>
+          <t>A 3219-2022</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3656,10 +3656,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45148</v>
+        <v>44582</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3672,7 +3672,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>1.1</v>
+        <v>0.5</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3715,7 +3715,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 61217-2024</t>
+          <t>A 60755-2024</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3729,10 +3729,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45645</v>
+        <v>45644</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3745,7 +3745,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>0.8</v>
+        <v>2.1</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3788,7 +3788,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 56002-2024</t>
+          <t>A 55724-2024</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3802,10 +3802,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45623</v>
+        <v>45622</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3818,7 +3818,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>3.4</v>
+        <v>0.5</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3861,7 +3861,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 60728-2022</t>
+          <t>A 35955-2023</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3875,10 +3875,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>44913</v>
+        <v>45148</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3891,7 +3891,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3951,7 +3951,7 @@
         <v>46153</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>

--- a/Översikt EKERÖ.xlsx
+++ b/Översikt EKERÖ.xlsx
@@ -601,7 +601,7 @@
         <v>46241</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -728,7 +728,7 @@
         <v>44872</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -848,7 +848,7 @@
         <v>44974</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -963,7 +963,7 @@
         <v>45148</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1073,7 +1073,7 @@
         <v>46119</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1187,7 +1187,7 @@
         <v>44582</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1296,7 +1296,7 @@
         <v>46241</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1409,7 +1409,7 @@
         <v>44634</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1516,7 +1516,7 @@
         <v>45937</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1623,7 +1623,7 @@
         <v>45002</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1735,7 +1735,7 @@
         <v>45209</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1850,7 +1850,7 @@
         <v>45170</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1956,7 +1956,7 @@
         <v>44646</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2061,7 +2061,7 @@
         <v>45671</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2166,7 +2166,7 @@
         <v>46037</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2271,7 +2271,7 @@
         <v>44582</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2376,7 +2376,7 @@
         <v>45007</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2481,7 +2481,7 @@
         <v>44670</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2554,7 +2554,7 @@
         <v>44802</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2627,7 +2627,7 @@
         <v>44913</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2700,7 +2700,7 @@
         <v>45845</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2773,7 +2773,7 @@
         <v>46010</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2846,7 +2846,7 @@
         <v>46244</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2924,7 +2924,7 @@
         <v>46037</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2997,7 +2997,7 @@
         <v>46301</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3075,7 +3075,7 @@
         <v>45876</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3148,7 +3148,7 @@
         <v>45208</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3221,7 +3221,7 @@
         <v>46139</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3294,7 +3294,7 @@
         <v>46139</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3367,7 +3367,7 @@
         <v>46142</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3440,7 +3440,7 @@
         <v>45623</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3513,7 +3513,7 @@
         <v>45645</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3586,7 +3586,7 @@
         <v>44582</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3659,7 +3659,7 @@
         <v>44582</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3732,7 +3732,7 @@
         <v>45644</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3805,7 +3805,7 @@
         <v>45622</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3878,7 +3878,7 @@
         <v>45148</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3951,7 +3951,7 @@
         <v>46153</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>

--- a/Översikt EKERÖ.xlsx
+++ b/Översikt EKERÖ.xlsx
@@ -601,7 +601,7 @@
         <v>46241</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -728,7 +728,7 @@
         <v>44872</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -848,7 +848,7 @@
         <v>44974</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -963,7 +963,7 @@
         <v>45148</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1073,7 +1073,7 @@
         <v>46119</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1187,7 +1187,7 @@
         <v>44582</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1296,7 +1296,7 @@
         <v>46241</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1409,7 +1409,7 @@
         <v>44634</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1516,7 +1516,7 @@
         <v>45937</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1623,7 +1623,7 @@
         <v>45002</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1735,7 +1735,7 @@
         <v>45209</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1850,7 +1850,7 @@
         <v>45170</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1956,7 +1956,7 @@
         <v>44646</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2061,7 +2061,7 @@
         <v>45671</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2166,7 +2166,7 @@
         <v>46037</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2271,7 +2271,7 @@
         <v>44582</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2376,7 +2376,7 @@
         <v>45007</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2481,7 +2481,7 @@
         <v>44670</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2554,7 +2554,7 @@
         <v>44802</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2627,7 +2627,7 @@
         <v>44913</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2700,7 +2700,7 @@
         <v>45845</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2773,7 +2773,7 @@
         <v>46010</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2846,7 +2846,7 @@
         <v>46244</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2924,7 +2924,7 @@
         <v>46037</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2997,7 +2997,7 @@
         <v>46301</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3075,7 +3075,7 @@
         <v>45876</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3148,7 +3148,7 @@
         <v>45208</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3221,7 +3221,7 @@
         <v>46139</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3294,7 +3294,7 @@
         <v>46139</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3367,7 +3367,7 @@
         <v>46142</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3440,7 +3440,7 @@
         <v>45623</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3513,7 +3513,7 @@
         <v>45645</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3586,7 +3586,7 @@
         <v>44582</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3659,7 +3659,7 @@
         <v>44582</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3732,7 +3732,7 @@
         <v>45644</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3805,7 +3805,7 @@
         <v>45622</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3878,7 +3878,7 @@
         <v>45148</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3951,7 +3951,7 @@
         <v>46153</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>

--- a/Översikt EKERÖ.xlsx
+++ b/Översikt EKERÖ.xlsx
@@ -601,7 +601,7 @@
         <v>46241</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -728,7 +728,7 @@
         <v>44872</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -848,7 +848,7 @@
         <v>44974</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -963,7 +963,7 @@
         <v>45148</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1056,7 +1056,7 @@
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A 17520-2026</t>
+          <t>A 3218-2022</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1070,10 +1070,10 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>46119</v>
+        <v>44582</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1085,13 +1085,8 @@
           <t>EKERÖ</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I6" t="n">
-        <v>2.2</v>
+        <v>1.2</v>
       </c>
       <c r="J6" t="n">
         <v>1</v>
@@ -1100,36 +1095,150 @@
         <v>1</v>
       </c>
       <c r="L6" t="n">
+        <v>1</v>
+      </c>
+      <c r="M6" t="n">
+        <v>1</v>
+      </c>
+      <c r="N6" t="n">
+        <v>1</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" t="n">
         <v>3</v>
       </c>
-      <c r="M6" t="n">
-        <v>1</v>
-      </c>
-      <c r="N6" t="n">
-        <v>0</v>
-      </c>
-      <c r="O6" t="n">
-        <v>0</v>
-      </c>
-      <c r="P6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>4</v>
-      </c>
       <c r="R6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
       </c>
       <c r="T6" t="n">
+        <v>8</v>
+      </c>
+      <c r="U6" t="n">
+        <v>6</v>
+      </c>
+      <c r="V6" s="2" t="inlineStr">
+        <is>
+          <t>Bombmurkla
+Gul lammticka
+Fyrflikig jordstjärna
+Kamjordstjärna
+Blåbär</t>
+        </is>
+      </c>
+      <c r="W6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/artfynd/A 3218-2022 artfynd.xlsx", "A 3218-2022")</f>
+        <v/>
+      </c>
+      <c r="X6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor/A 3218-2022 karta.png", "A 3218-2022")</f>
+        <v/>
+      </c>
+      <c r="Y6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor_geotiff/A 3218-2022 georefererad karta.tif", "A 3218-2022")</f>
+        <v/>
+      </c>
+      <c r="AA6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomål/A 3218-2022 FSC-klagomål.docx", "A 3218-2022")</f>
+        <v/>
+      </c>
+      <c r="AB6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomålsmail/A 3218-2022 FSC-klagomål mail.docx", "A 3218-2022")</f>
+        <v/>
+      </c>
+      <c r="AC6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsyn/A 3218-2022 tillsynsbegäran.docx", "A 3218-2022")</f>
+        <v/>
+      </c>
+      <c r="AD6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsynsmail/A 3218-2022 tillsynsbegäran mail.docx", "A 3218-2022")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7" ht="15" customHeight="1">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>A 17520-2026</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D7" s="1" t="n">
+        <v>46119</v>
+      </c>
+      <c r="E7" s="1" t="n">
+        <v>46322</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>EKERÖ</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="J7" t="n">
+        <v>1</v>
+      </c>
+      <c r="K7" t="n">
+        <v>1</v>
+      </c>
+      <c r="L7" t="n">
+        <v>3</v>
+      </c>
+      <c r="M7" t="n">
+        <v>1</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>4</v>
+      </c>
+      <c r="R7" t="n">
+        <v>1</v>
+      </c>
+      <c r="S7" t="n">
         <v>5</v>
       </c>
-      <c r="U6" t="n">
-        <v>1</v>
-      </c>
-      <c r="V6" s="2" t="inlineStr">
+      <c r="T7" t="n">
+        <v>5</v>
+      </c>
+      <c r="U7" t="n">
+        <v>1</v>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
         <is>
           <t>Läderbagge
 Blekticka
@@ -1138,141 +1247,32 @@
 Gulgrön kantmusseron</t>
         </is>
       </c>
-      <c r="W6">
+      <c r="W7">
         <f>HYPERLINK("https://klasma.github.io/Logging_0125/artfynd/A 17520-2026 artfynd.xlsx", "A 17520-2026")</f>
         <v/>
       </c>
-      <c r="X6">
+      <c r="X7">
         <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor/A 17520-2026 karta.png", "A 17520-2026")</f>
         <v/>
       </c>
-      <c r="Y6">
+      <c r="Y7">
         <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor_geotiff/A 17520-2026 georefererad karta.tif", "A 17520-2026")</f>
         <v/>
       </c>
-      <c r="AA6">
+      <c r="AA7">
         <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomål/A 17520-2026 FSC-klagomål.docx", "A 17520-2026")</f>
         <v/>
       </c>
-      <c r="AB6">
+      <c r="AB7">
         <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomålsmail/A 17520-2026 FSC-klagomål mail.docx", "A 17520-2026")</f>
         <v/>
       </c>
-      <c r="AC6">
+      <c r="AC7">
         <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsyn/A 17520-2026 tillsynsbegäran.docx", "A 17520-2026")</f>
         <v/>
       </c>
-      <c r="AD6">
+      <c r="AD7">
         <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsynsmail/A 17520-2026 tillsynsbegäran mail.docx", "A 17520-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="7" ht="15" customHeight="1">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>A 3218-2022</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D7" s="1" t="n">
-        <v>44582</v>
-      </c>
-      <c r="E7" s="1" t="n">
-        <v>46321</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>EKERÖ</t>
-        </is>
-      </c>
-      <c r="I7" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="J7" t="n">
-        <v>1</v>
-      </c>
-      <c r="K7" t="n">
-        <v>1</v>
-      </c>
-      <c r="L7" t="n">
-        <v>1</v>
-      </c>
-      <c r="M7" t="n">
-        <v>1</v>
-      </c>
-      <c r="N7" t="n">
-        <v>1</v>
-      </c>
-      <c r="O7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>3</v>
-      </c>
-      <c r="R7" t="n">
-        <v>2</v>
-      </c>
-      <c r="S7" t="n">
-        <v>5</v>
-      </c>
-      <c r="T7" t="n">
-        <v>8</v>
-      </c>
-      <c r="U7" t="n">
-        <v>6</v>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>Bombmurkla
-Gul lammticka
-Fyrflikig jordstjärna
-Kamjordstjärna
-Blåbär</t>
-        </is>
-      </c>
-      <c r="W7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/artfynd/A 3218-2022 artfynd.xlsx", "A 3218-2022")</f>
-        <v/>
-      </c>
-      <c r="X7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor/A 3218-2022 karta.png", "A 3218-2022")</f>
-        <v/>
-      </c>
-      <c r="Y7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor_geotiff/A 3218-2022 georefererad karta.tif", "A 3218-2022")</f>
-        <v/>
-      </c>
-      <c r="AA7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomål/A 3218-2022 FSC-klagomål.docx", "A 3218-2022")</f>
-        <v/>
-      </c>
-      <c r="AB7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomålsmail/A 3218-2022 FSC-klagomål mail.docx", "A 3218-2022")</f>
-        <v/>
-      </c>
-      <c r="AC7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsyn/A 3218-2022 tillsynsbegäran.docx", "A 3218-2022")</f>
-        <v/>
-      </c>
-      <c r="AD7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsynsmail/A 3218-2022 tillsynsbegäran mail.docx", "A 3218-2022")</f>
         <v/>
       </c>
     </row>
@@ -1296,7 +1296,7 @@
         <v>46241</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1409,7 +1409,7 @@
         <v>44634</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1499,7 +1499,7 @@
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 49131-2025</t>
+          <t>A 13237-2023</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1513,10 +1513,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>45937</v>
+        <v>45002</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1528,20 +1528,25 @@
           <t>EKERÖ</t>
         </is>
       </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I10" t="n">
-        <v>0.9</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N10" t="n">
         <v>0</v>
@@ -1553,165 +1558,160 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="R10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
         <v>3</v>
       </c>
       <c r="T10" t="n">
+        <v>7</v>
+      </c>
+      <c r="U10" t="n">
+        <v>0</v>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
+        <is>
+          <t>Tallticka
+Granbarkgnagare
+Grönpyrola</t>
+        </is>
+      </c>
+      <c r="W10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/artfynd/A 13237-2023 artfynd.xlsx", "A 13237-2023")</f>
+        <v/>
+      </c>
+      <c r="X10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor/A 13237-2023 karta.png", "A 13237-2023")</f>
+        <v/>
+      </c>
+      <c r="Y10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor_geotiff/A 13237-2023 georefererad karta.tif", "A 13237-2023")</f>
+        <v/>
+      </c>
+      <c r="AA10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomål/A 13237-2023 FSC-klagomål.docx", "A 13237-2023")</f>
+        <v/>
+      </c>
+      <c r="AB10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomålsmail/A 13237-2023 FSC-klagomål mail.docx", "A 13237-2023")</f>
+        <v/>
+      </c>
+      <c r="AC10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsyn/A 13237-2023 tillsynsbegäran.docx", "A 13237-2023")</f>
+        <v/>
+      </c>
+      <c r="AD10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsynsmail/A 13237-2023 tillsynsbegäran mail.docx", "A 13237-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11" ht="15" customHeight="1">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>A 49131-2025</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D11" s="1" t="n">
+        <v>45937</v>
+      </c>
+      <c r="E11" s="1" t="n">
+        <v>46322</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>EKERÖ</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" t="n">
+        <v>2</v>
+      </c>
+      <c r="M11" t="n">
+        <v>1</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" t="n">
         <v>3</v>
       </c>
-      <c r="U10" t="n">
+      <c r="R11" t="n">
+        <v>1</v>
+      </c>
+      <c r="S11" t="n">
         <v>3</v>
       </c>
-      <c r="V10" s="2" t="inlineStr">
+      <c r="T11" t="n">
+        <v>3</v>
+      </c>
+      <c r="U11" t="n">
+        <v>3</v>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
         <is>
           <t>Jättemusseron
 Motaggsvamp
 Svartvit taggsvamp</t>
         </is>
       </c>
-      <c r="W10">
+      <c r="W11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0125/artfynd/A 49131-2025 artfynd.xlsx", "A 49131-2025")</f>
         <v/>
       </c>
-      <c r="X10">
+      <c r="X11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor/A 49131-2025 karta.png", "A 49131-2025")</f>
         <v/>
       </c>
-      <c r="Y10">
+      <c r="Y11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor_geotiff/A 49131-2025 georefererad karta.tif", "A 49131-2025")</f>
         <v/>
       </c>
-      <c r="AA10">
+      <c r="AA11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomål/A 49131-2025 FSC-klagomål.docx", "A 49131-2025")</f>
         <v/>
       </c>
-      <c r="AB10">
+      <c r="AB11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomålsmail/A 49131-2025 FSC-klagomål mail.docx", "A 49131-2025")</f>
         <v/>
       </c>
-      <c r="AC10">
+      <c r="AC11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsyn/A 49131-2025 tillsynsbegäran.docx", "A 49131-2025")</f>
         <v/>
       </c>
-      <c r="AD10">
+      <c r="AD11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsynsmail/A 49131-2025 tillsynsbegäran mail.docx", "A 49131-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="11" ht="15" customHeight="1">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>A 13237-2023</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D11" s="1" t="n">
-        <v>45002</v>
-      </c>
-      <c r="E11" s="1" t="n">
-        <v>46321</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>EKERÖ</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
-      <c r="I11" t="n">
-        <v>9.300000000000001</v>
-      </c>
-      <c r="J11" t="n">
-        <v>0</v>
-      </c>
-      <c r="K11" t="n">
-        <v>2</v>
-      </c>
-      <c r="L11" t="n">
-        <v>1</v>
-      </c>
-      <c r="M11" t="n">
-        <v>0</v>
-      </c>
-      <c r="N11" t="n">
-        <v>0</v>
-      </c>
-      <c r="O11" t="n">
-        <v>0</v>
-      </c>
-      <c r="P11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>1</v>
-      </c>
-      <c r="R11" t="n">
-        <v>0</v>
-      </c>
-      <c r="S11" t="n">
-        <v>3</v>
-      </c>
-      <c r="T11" t="n">
-        <v>7</v>
-      </c>
-      <c r="U11" t="n">
-        <v>0</v>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
-        <is>
-          <t>Tallticka
-Granbarkgnagare
-Grönpyrola</t>
-        </is>
-      </c>
-      <c r="W11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/artfynd/A 13237-2023 artfynd.xlsx", "A 13237-2023")</f>
-        <v/>
-      </c>
-      <c r="X11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor/A 13237-2023 karta.png", "A 13237-2023")</f>
-        <v/>
-      </c>
-      <c r="Y11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor_geotiff/A 13237-2023 georefererad karta.tif", "A 13237-2023")</f>
-        <v/>
-      </c>
-      <c r="AA11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomål/A 13237-2023 FSC-klagomål.docx", "A 13237-2023")</f>
-        <v/>
-      </c>
-      <c r="AB11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomålsmail/A 13237-2023 FSC-klagomål mail.docx", "A 13237-2023")</f>
-        <v/>
-      </c>
-      <c r="AC11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsyn/A 13237-2023 tillsynsbegäran.docx", "A 13237-2023")</f>
-        <v/>
-      </c>
-      <c r="AD11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsynsmail/A 13237-2023 tillsynsbegäran mail.docx", "A 13237-2023")</f>
         <v/>
       </c>
     </row>
@@ -1735,7 +1735,7 @@
         <v>45209</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1850,7 +1850,7 @@
         <v>45170</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1956,7 +1956,7 @@
         <v>44646</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2044,7 +2044,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 1793-2025</t>
+          <t>A 3221-2022</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2058,10 +2058,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45671</v>
+        <v>44582</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2074,13 +2074,13 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>1.7</v>
+        <v>0.5</v>
       </c>
       <c r="J15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L15" t="n">
         <v>0</v>
@@ -2107,49 +2107,49 @@
         <v>1</v>
       </c>
       <c r="T15" t="n">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>Mistel</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/artfynd/A 1793-2025 artfynd.xlsx", "A 1793-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/artfynd/A 3221-2022 artfynd.xlsx", "A 3221-2022")</f>
         <v/>
       </c>
       <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor/A 1793-2025 karta.png", "A 1793-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor/A 3221-2022 karta.png", "A 3221-2022")</f>
         <v/>
       </c>
       <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor_geotiff/A 1793-2025 georefererad karta.tif", "A 1793-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor_geotiff/A 3221-2022 georefererad karta.tif", "A 3221-2022")</f>
         <v/>
       </c>
       <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomål/A 1793-2025 FSC-klagomål.docx", "A 1793-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomål/A 3221-2022 FSC-klagomål.docx", "A 3221-2022")</f>
         <v/>
       </c>
       <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomålsmail/A 1793-2025 FSC-klagomål mail.docx", "A 1793-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomålsmail/A 3221-2022 FSC-klagomål mail.docx", "A 3221-2022")</f>
         <v/>
       </c>
       <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsyn/A 1793-2025 tillsynsbegäran.docx", "A 1793-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsyn/A 3221-2022 tillsynsbegäran.docx", "A 3221-2022")</f>
         <v/>
       </c>
       <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsynsmail/A 1793-2025 tillsynsbegäran mail.docx", "A 1793-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsynsmail/A 3221-2022 tillsynsbegäran mail.docx", "A 3221-2022")</f>
         <v/>
       </c>
     </row>
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 2533-2026</t>
+          <t>A 13794-2023</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2163,10 +2163,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>46037</v>
+        <v>45007</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2179,16 +2179,16 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>1.4</v>
+        <v>4.8</v>
       </c>
       <c r="J16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K16" t="n">
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M16" t="n">
         <v>0</v>
@@ -2203,7 +2203,7 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R16" t="n">
         <v>0</v>
@@ -2219,42 +2219,42 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/artfynd/A 2533-2026 artfynd.xlsx", "A 2533-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/artfynd/A 13794-2023 artfynd.xlsx", "A 13794-2023")</f>
         <v/>
       </c>
       <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor/A 2533-2026 karta.png", "A 2533-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor/A 13794-2023 karta.png", "A 13794-2023")</f>
         <v/>
       </c>
       <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor_geotiff/A 2533-2026 georefererad karta.tif", "A 2533-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor_geotiff/A 13794-2023 georefererad karta.tif", "A 13794-2023")</f>
         <v/>
       </c>
       <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomål/A 2533-2026 FSC-klagomål.docx", "A 2533-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomål/A 13794-2023 FSC-klagomål.docx", "A 13794-2023")</f>
         <v/>
       </c>
       <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomålsmail/A 2533-2026 FSC-klagomål mail.docx", "A 2533-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomålsmail/A 13794-2023 FSC-klagomål mail.docx", "A 13794-2023")</f>
         <v/>
       </c>
       <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsyn/A 2533-2026 tillsynsbegäran.docx", "A 2533-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsyn/A 13794-2023 tillsynsbegäran.docx", "A 13794-2023")</f>
         <v/>
       </c>
       <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsynsmail/A 2533-2026 tillsynsbegäran mail.docx", "A 2533-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsynsmail/A 13794-2023 tillsynsbegäran mail.docx", "A 13794-2023")</f>
         <v/>
       </c>
     </row>
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 3221-2022</t>
+          <t>A 1793-2025</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2268,10 +2268,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>44582</v>
+        <v>45671</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2284,13 +2284,13 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>0.5</v>
+        <v>1.7</v>
       </c>
       <c r="J17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L17" t="n">
         <v>0</v>
@@ -2317,49 +2317,49 @@
         <v>1</v>
       </c>
       <c r="T17" t="n">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="U17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Mistel</t>
         </is>
       </c>
       <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/artfynd/A 3221-2022 artfynd.xlsx", "A 3221-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/artfynd/A 1793-2025 artfynd.xlsx", "A 1793-2025")</f>
         <v/>
       </c>
       <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor/A 3221-2022 karta.png", "A 3221-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor/A 1793-2025 karta.png", "A 1793-2025")</f>
         <v/>
       </c>
       <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor_geotiff/A 3221-2022 georefererad karta.tif", "A 3221-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor_geotiff/A 1793-2025 georefererad karta.tif", "A 1793-2025")</f>
         <v/>
       </c>
       <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomål/A 3221-2022 FSC-klagomål.docx", "A 3221-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomål/A 1793-2025 FSC-klagomål.docx", "A 1793-2025")</f>
         <v/>
       </c>
       <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomålsmail/A 3221-2022 FSC-klagomål mail.docx", "A 3221-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomålsmail/A 1793-2025 FSC-klagomål mail.docx", "A 1793-2025")</f>
         <v/>
       </c>
       <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsyn/A 3221-2022 tillsynsbegäran.docx", "A 3221-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsyn/A 1793-2025 tillsynsbegäran.docx", "A 1793-2025")</f>
         <v/>
       </c>
       <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsynsmail/A 3221-2022 tillsynsbegäran mail.docx", "A 3221-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsynsmail/A 1793-2025 tillsynsbegäran mail.docx", "A 1793-2025")</f>
         <v/>
       </c>
     </row>
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 13794-2023</t>
+          <t>A 2533-2026</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2373,10 +2373,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45007</v>
+        <v>46037</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2389,16 +2389,16 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>4.8</v>
+        <v>1.4</v>
       </c>
       <c r="J18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K18" t="n">
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
         <v>0</v>
@@ -2413,7 +2413,7 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
         <v>0</v>
@@ -2429,35 +2429,35 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="W18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/artfynd/A 13794-2023 artfynd.xlsx", "A 13794-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/artfynd/A 2533-2026 artfynd.xlsx", "A 2533-2026")</f>
         <v/>
       </c>
       <c r="X18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor/A 13794-2023 karta.png", "A 13794-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor/A 2533-2026 karta.png", "A 2533-2026")</f>
         <v/>
       </c>
       <c r="Y18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor_geotiff/A 13794-2023 georefererad karta.tif", "A 13794-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor_geotiff/A 2533-2026 georefererad karta.tif", "A 2533-2026")</f>
         <v/>
       </c>
       <c r="AA18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomål/A 13794-2023 FSC-klagomål.docx", "A 13794-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomål/A 2533-2026 FSC-klagomål.docx", "A 2533-2026")</f>
         <v/>
       </c>
       <c r="AB18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomålsmail/A 13794-2023 FSC-klagomål mail.docx", "A 13794-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomålsmail/A 2533-2026 FSC-klagomål mail.docx", "A 2533-2026")</f>
         <v/>
       </c>
       <c r="AC18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsyn/A 13794-2023 tillsynsbegäran.docx", "A 13794-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsyn/A 2533-2026 tillsynsbegäran.docx", "A 2533-2026")</f>
         <v/>
       </c>
       <c r="AD18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsynsmail/A 13794-2023 tillsynsbegäran mail.docx", "A 13794-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsynsmail/A 2533-2026 tillsynsbegäran mail.docx", "A 2533-2026")</f>
         <v/>
       </c>
     </row>
@@ -2481,7 +2481,7 @@
         <v>44670</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2554,7 +2554,7 @@
         <v>44802</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2610,7 +2610,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 60728-2022</t>
+          <t>A 3219-2022</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2624,10 +2624,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>44913</v>
+        <v>44582</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2640,7 +2640,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>1.2</v>
+        <v>0.5</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2683,7 +2683,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 34073-2025</t>
+          <t>A 60755-2024</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2693,14 +2693,14 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>45845</v>
+        <v>45644</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2713,7 +2713,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>2.9</v>
+        <v>2.1</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2756,7 +2756,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 63378-2025</t>
+          <t>A 50184-2023</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2770,10 +2770,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>46010</v>
+        <v>45208</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2786,7 +2786,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>4.8</v>
+        <v>10.8</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2829,7 +2829,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 33154-2026</t>
+          <t>A 63378-2025</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2843,10 +2843,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>46244</v>
+        <v>46010</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2858,13 +2858,8 @@
           <t>EKERÖ</t>
         </is>
       </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I24" t="n">
-        <v>3.5</v>
+        <v>4.8</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2924,7 +2919,7 @@
         <v>46037</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2980,7 +2975,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 41699-2026</t>
+          <t>A 37245-2025</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2994,10 +2989,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>46301</v>
+        <v>45876</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3009,13 +3004,8 @@
           <t>EKERÖ</t>
         </is>
       </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I26" t="n">
-        <v>1.6</v>
+        <v>1.1</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -3058,7 +3048,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 37245-2025</t>
+          <t>A 55724-2024</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3072,10 +3062,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45876</v>
+        <v>45622</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3088,7 +3078,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>1.1</v>
+        <v>0.5</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -3131,7 +3121,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 50184-2023</t>
+          <t>A 35955-2023</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3145,10 +3135,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45208</v>
+        <v>45148</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3161,7 +3151,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>10.8</v>
+        <v>1.1</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -3221,7 +3211,7 @@
         <v>46139</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3277,7 +3267,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 20398-2026</t>
+          <t>A 33154-2026</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3291,10 +3281,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>46139</v>
+        <v>46244</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3306,8 +3296,13 @@
           <t>EKERÖ</t>
         </is>
       </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I30" t="n">
-        <v>2.4</v>
+        <v>3.5</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3350,7 +3345,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 20898-2026</t>
+          <t>A 61217-2024</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3364,10 +3359,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>46142</v>
+        <v>45645</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3380,7 +3375,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>3.6</v>
+        <v>0.8</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3440,7 +3435,7 @@
         <v>45623</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3496,7 +3491,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 61217-2024</t>
+          <t>A 60728-2022</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3510,10 +3505,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45645</v>
+        <v>44913</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3526,7 +3521,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>0.8</v>
+        <v>1.2</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3569,7 +3564,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 3222-2022</t>
+          <t>A 20398-2026</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3583,10 +3578,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>44582</v>
+        <v>46139</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3599,7 +3594,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>1.8</v>
+        <v>2.4</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3642,7 +3637,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 3219-2022</t>
+          <t>A 20898-2026</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3656,10 +3651,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>44582</v>
+        <v>46142</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3672,7 +3667,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>0.5</v>
+        <v>3.6</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3715,7 +3710,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 60755-2024</t>
+          <t>A 3222-2022</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3729,10 +3724,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45644</v>
+        <v>44582</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3745,7 +3740,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>2.1</v>
+        <v>1.8</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3788,7 +3783,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 55724-2024</t>
+          <t>A 34073-2025</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3798,14 +3793,14 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45622</v>
+        <v>45845</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3818,7 +3813,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>0.5</v>
+        <v>2.9</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3861,7 +3856,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 35955-2023</t>
+          <t>A 41699-2026</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3875,10 +3870,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45148</v>
+        <v>46301</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3890,8 +3885,13 @@
           <t>EKERÖ</t>
         </is>
       </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I38" t="n">
-        <v>1.1</v>
+        <v>1.6</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3951,7 +3951,7 @@
         <v>46153</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>

--- a/Översikt EKERÖ.xlsx
+++ b/Översikt EKERÖ.xlsx
@@ -601,7 +601,7 @@
         <v>46241</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -728,7 +728,7 @@
         <v>44872</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -848,7 +848,7 @@
         <v>44974</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -963,7 +963,7 @@
         <v>45148</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1073,7 +1073,7 @@
         <v>44582</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1182,7 +1182,7 @@
         <v>46119</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1296,7 +1296,7 @@
         <v>46241</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1409,7 +1409,7 @@
         <v>44634</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1499,7 +1499,7 @@
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 13237-2023</t>
+          <t>A 49131-2025</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1513,10 +1513,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>45002</v>
+        <v>45937</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1528,25 +1528,20 @@
           <t>EKERÖ</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I10" t="n">
-        <v>9.300000000000001</v>
+        <v>0.9</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
       </c>
       <c r="K10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" t="n">
         <v>2</v>
       </c>
-      <c r="L10" t="n">
-        <v>1</v>
-      </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N10" t="n">
         <v>0</v>
@@ -1558,160 +1553,165 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S10" t="n">
         <v>3</v>
       </c>
       <c r="T10" t="n">
+        <v>3</v>
+      </c>
+      <c r="U10" t="n">
+        <v>3</v>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
+        <is>
+          <t>Jättemusseron
+Motaggsvamp
+Svartvit taggsvamp</t>
+        </is>
+      </c>
+      <c r="W10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/artfynd/A 49131-2025 artfynd.xlsx", "A 49131-2025")</f>
+        <v/>
+      </c>
+      <c r="X10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor/A 49131-2025 karta.png", "A 49131-2025")</f>
+        <v/>
+      </c>
+      <c r="Y10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor_geotiff/A 49131-2025 georefererad karta.tif", "A 49131-2025")</f>
+        <v/>
+      </c>
+      <c r="AA10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomål/A 49131-2025 FSC-klagomål.docx", "A 49131-2025")</f>
+        <v/>
+      </c>
+      <c r="AB10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomålsmail/A 49131-2025 FSC-klagomål mail.docx", "A 49131-2025")</f>
+        <v/>
+      </c>
+      <c r="AC10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsyn/A 49131-2025 tillsynsbegäran.docx", "A 49131-2025")</f>
+        <v/>
+      </c>
+      <c r="AD10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsynsmail/A 49131-2025 tillsynsbegäran mail.docx", "A 49131-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11" ht="15" customHeight="1">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>A 13237-2023</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D11" s="1" t="n">
+        <v>45002</v>
+      </c>
+      <c r="E11" s="1" t="n">
+        <v>46323</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>EKERÖ</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" t="n">
+        <v>2</v>
+      </c>
+      <c r="L11" t="n">
+        <v>1</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>1</v>
+      </c>
+      <c r="R11" t="n">
+        <v>0</v>
+      </c>
+      <c r="S11" t="n">
+        <v>3</v>
+      </c>
+      <c r="T11" t="n">
         <v>7</v>
       </c>
-      <c r="U10" t="n">
-        <v>0</v>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
+      <c r="U11" t="n">
+        <v>0</v>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
         <is>
           <t>Tallticka
 Granbarkgnagare
 Grönpyrola</t>
         </is>
       </c>
-      <c r="W10">
+      <c r="W11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0125/artfynd/A 13237-2023 artfynd.xlsx", "A 13237-2023")</f>
         <v/>
       </c>
-      <c r="X10">
+      <c r="X11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor/A 13237-2023 karta.png", "A 13237-2023")</f>
         <v/>
       </c>
-      <c r="Y10">
+      <c r="Y11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor_geotiff/A 13237-2023 georefererad karta.tif", "A 13237-2023")</f>
         <v/>
       </c>
-      <c r="AA10">
+      <c r="AA11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomål/A 13237-2023 FSC-klagomål.docx", "A 13237-2023")</f>
         <v/>
       </c>
-      <c r="AB10">
+      <c r="AB11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomålsmail/A 13237-2023 FSC-klagomål mail.docx", "A 13237-2023")</f>
         <v/>
       </c>
-      <c r="AC10">
+      <c r="AC11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsyn/A 13237-2023 tillsynsbegäran.docx", "A 13237-2023")</f>
         <v/>
       </c>
-      <c r="AD10">
+      <c r="AD11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsynsmail/A 13237-2023 tillsynsbegäran mail.docx", "A 13237-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="11" ht="15" customHeight="1">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>A 49131-2025</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D11" s="1" t="n">
-        <v>45937</v>
-      </c>
-      <c r="E11" s="1" t="n">
-        <v>46322</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>EKERÖ</t>
-        </is>
-      </c>
-      <c r="I11" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="J11" t="n">
-        <v>0</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L11" t="n">
-        <v>2</v>
-      </c>
-      <c r="M11" t="n">
-        <v>1</v>
-      </c>
-      <c r="N11" t="n">
-        <v>0</v>
-      </c>
-      <c r="O11" t="n">
-        <v>0</v>
-      </c>
-      <c r="P11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>3</v>
-      </c>
-      <c r="R11" t="n">
-        <v>1</v>
-      </c>
-      <c r="S11" t="n">
-        <v>3</v>
-      </c>
-      <c r="T11" t="n">
-        <v>3</v>
-      </c>
-      <c r="U11" t="n">
-        <v>3</v>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
-        <is>
-          <t>Jättemusseron
-Motaggsvamp
-Svartvit taggsvamp</t>
-        </is>
-      </c>
-      <c r="W11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/artfynd/A 49131-2025 artfynd.xlsx", "A 49131-2025")</f>
-        <v/>
-      </c>
-      <c r="X11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor/A 49131-2025 karta.png", "A 49131-2025")</f>
-        <v/>
-      </c>
-      <c r="Y11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor_geotiff/A 49131-2025 georefererad karta.tif", "A 49131-2025")</f>
-        <v/>
-      </c>
-      <c r="AA11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomål/A 49131-2025 FSC-klagomål.docx", "A 49131-2025")</f>
-        <v/>
-      </c>
-      <c r="AB11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomålsmail/A 49131-2025 FSC-klagomål mail.docx", "A 49131-2025")</f>
-        <v/>
-      </c>
-      <c r="AC11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsyn/A 49131-2025 tillsynsbegäran.docx", "A 49131-2025")</f>
-        <v/>
-      </c>
-      <c r="AD11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsynsmail/A 49131-2025 tillsynsbegäran mail.docx", "A 49131-2025")</f>
         <v/>
       </c>
     </row>
@@ -1735,7 +1735,7 @@
         <v>45209</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1850,7 +1850,7 @@
         <v>45170</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1956,7 +1956,7 @@
         <v>44646</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2061,7 +2061,7 @@
         <v>44582</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2149,7 +2149,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 13794-2023</t>
+          <t>A 1793-2025</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2163,10 +2163,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45007</v>
+        <v>45671</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2179,16 +2179,16 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>4.8</v>
+        <v>1.7</v>
       </c>
       <c r="J16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K16" t="n">
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
         <v>0</v>
@@ -2203,7 +2203,7 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
         <v>0</v>
@@ -2212,49 +2212,49 @@
         <v>1</v>
       </c>
       <c r="T16" t="n">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="U16" t="n">
         <v>0</v>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Mistel</t>
         </is>
       </c>
       <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/artfynd/A 13794-2023 artfynd.xlsx", "A 13794-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/artfynd/A 1793-2025 artfynd.xlsx", "A 1793-2025")</f>
         <v/>
       </c>
       <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor/A 13794-2023 karta.png", "A 13794-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor/A 1793-2025 karta.png", "A 1793-2025")</f>
         <v/>
       </c>
       <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor_geotiff/A 13794-2023 georefererad karta.tif", "A 13794-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor_geotiff/A 1793-2025 georefererad karta.tif", "A 1793-2025")</f>
         <v/>
       </c>
       <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomål/A 13794-2023 FSC-klagomål.docx", "A 13794-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomål/A 1793-2025 FSC-klagomål.docx", "A 1793-2025")</f>
         <v/>
       </c>
       <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomålsmail/A 13794-2023 FSC-klagomål mail.docx", "A 13794-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomålsmail/A 1793-2025 FSC-klagomål mail.docx", "A 1793-2025")</f>
         <v/>
       </c>
       <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsyn/A 13794-2023 tillsynsbegäran.docx", "A 13794-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsyn/A 1793-2025 tillsynsbegäran.docx", "A 1793-2025")</f>
         <v/>
       </c>
       <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsynsmail/A 13794-2023 tillsynsbegäran mail.docx", "A 13794-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsynsmail/A 1793-2025 tillsynsbegäran mail.docx", "A 1793-2025")</f>
         <v/>
       </c>
     </row>
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 1793-2025</t>
+          <t>A 2533-2026</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2268,10 +2268,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45671</v>
+        <v>46037</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2284,7 +2284,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>1.7</v>
+        <v>1.4</v>
       </c>
       <c r="J17" t="n">
         <v>1</v>
@@ -2317,49 +2317,49 @@
         <v>1</v>
       </c>
       <c r="T17" t="n">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="U17" t="n">
         <v>0</v>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>Mistel</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/artfynd/A 1793-2025 artfynd.xlsx", "A 1793-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/artfynd/A 2533-2026 artfynd.xlsx", "A 2533-2026")</f>
         <v/>
       </c>
       <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor/A 1793-2025 karta.png", "A 1793-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor/A 2533-2026 karta.png", "A 2533-2026")</f>
         <v/>
       </c>
       <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor_geotiff/A 1793-2025 georefererad karta.tif", "A 1793-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor_geotiff/A 2533-2026 georefererad karta.tif", "A 2533-2026")</f>
         <v/>
       </c>
       <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomål/A 1793-2025 FSC-klagomål.docx", "A 1793-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomål/A 2533-2026 FSC-klagomål.docx", "A 2533-2026")</f>
         <v/>
       </c>
       <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomålsmail/A 1793-2025 FSC-klagomål mail.docx", "A 1793-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomålsmail/A 2533-2026 FSC-klagomål mail.docx", "A 2533-2026")</f>
         <v/>
       </c>
       <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsyn/A 1793-2025 tillsynsbegäran.docx", "A 1793-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsyn/A 2533-2026 tillsynsbegäran.docx", "A 2533-2026")</f>
         <v/>
       </c>
       <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsynsmail/A 1793-2025 tillsynsbegäran mail.docx", "A 1793-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsynsmail/A 2533-2026 tillsynsbegäran mail.docx", "A 2533-2026")</f>
         <v/>
       </c>
     </row>
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 2533-2026</t>
+          <t>A 13794-2023</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2373,10 +2373,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>46037</v>
+        <v>45007</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2389,16 +2389,16 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>1.4</v>
+        <v>4.8</v>
       </c>
       <c r="J18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K18" t="n">
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M18" t="n">
         <v>0</v>
@@ -2413,7 +2413,7 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R18" t="n">
         <v>0</v>
@@ -2429,35 +2429,35 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="W18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/artfynd/A 2533-2026 artfynd.xlsx", "A 2533-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/artfynd/A 13794-2023 artfynd.xlsx", "A 13794-2023")</f>
         <v/>
       </c>
       <c r="X18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor/A 2533-2026 karta.png", "A 2533-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor/A 13794-2023 karta.png", "A 13794-2023")</f>
         <v/>
       </c>
       <c r="Y18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor_geotiff/A 2533-2026 georefererad karta.tif", "A 2533-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor_geotiff/A 13794-2023 georefererad karta.tif", "A 13794-2023")</f>
         <v/>
       </c>
       <c r="AA18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomål/A 2533-2026 FSC-klagomål.docx", "A 2533-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomål/A 13794-2023 FSC-klagomål.docx", "A 13794-2023")</f>
         <v/>
       </c>
       <c r="AB18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomålsmail/A 2533-2026 FSC-klagomål mail.docx", "A 2533-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomålsmail/A 13794-2023 FSC-klagomål mail.docx", "A 13794-2023")</f>
         <v/>
       </c>
       <c r="AC18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsyn/A 2533-2026 tillsynsbegäran.docx", "A 2533-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsyn/A 13794-2023 tillsynsbegäran.docx", "A 13794-2023")</f>
         <v/>
       </c>
       <c r="AD18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsynsmail/A 2533-2026 tillsynsbegäran mail.docx", "A 2533-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsynsmail/A 13794-2023 tillsynsbegäran mail.docx", "A 13794-2023")</f>
         <v/>
       </c>
     </row>
@@ -2481,7 +2481,7 @@
         <v>44670</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2554,7 +2554,7 @@
         <v>44802</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2610,7 +2610,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 3219-2022</t>
+          <t>A 56002-2024</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2624,10 +2624,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>44582</v>
+        <v>45623</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2640,7 +2640,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>0.5</v>
+        <v>3.4</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2683,7 +2683,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 60755-2024</t>
+          <t>A 61217-2024</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2697,10 +2697,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>45644</v>
+        <v>45645</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2713,7 +2713,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>2.1</v>
+        <v>0.8</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2756,7 +2756,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 50184-2023</t>
+          <t>A 3222-2022</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2770,10 +2770,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45208</v>
+        <v>44582</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2786,7 +2786,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>10.8</v>
+        <v>1.8</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2829,7 +2829,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 63378-2025</t>
+          <t>A 50184-2023</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2843,10 +2843,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>46010</v>
+        <v>45208</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2859,7 +2859,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>4.8</v>
+        <v>10.8</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2902,7 +2902,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 2535-2026</t>
+          <t>A 3219-2022</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2916,10 +2916,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>46037</v>
+        <v>44582</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2932,7 +2932,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>1.6</v>
+        <v>0.5</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2975,7 +2975,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 37245-2025</t>
+          <t>A 60755-2024</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2989,10 +2989,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45876</v>
+        <v>45644</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3005,7 +3005,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>1.1</v>
+        <v>2.1</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -3048,7 +3048,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 55724-2024</t>
+          <t>A 63378-2025</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3062,10 +3062,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45622</v>
+        <v>46010</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3078,7 +3078,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>0.5</v>
+        <v>4.8</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -3121,7 +3121,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 35955-2023</t>
+          <t>A 55724-2024</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3135,10 +3135,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45148</v>
+        <v>45622</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3151,7 +3151,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>1.1</v>
+        <v>0.5</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -3194,7 +3194,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 20399-2026</t>
+          <t>A 2535-2026</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3208,10 +3208,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>46139</v>
+        <v>46037</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3224,7 +3224,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>0.9</v>
+        <v>1.6</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3267,7 +3267,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 33154-2026</t>
+          <t>A 35955-2023</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3281,10 +3281,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>46244</v>
+        <v>45148</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3296,13 +3296,8 @@
           <t>EKERÖ</t>
         </is>
       </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I30" t="n">
-        <v>3.5</v>
+        <v>1.1</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3345,7 +3340,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 61217-2024</t>
+          <t>A 33154-2026</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3359,10 +3354,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45645</v>
+        <v>46244</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3374,8 +3369,13 @@
           <t>EKERÖ</t>
         </is>
       </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I31" t="n">
-        <v>0.8</v>
+        <v>3.5</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3418,7 +3418,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 56002-2024</t>
+          <t>A 41699-2026</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3432,10 +3432,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45623</v>
+        <v>46301</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3447,8 +3447,13 @@
           <t>EKERÖ</t>
         </is>
       </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I32" t="n">
-        <v>3.4</v>
+        <v>1.6</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3508,7 +3513,7 @@
         <v>44913</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3564,7 +3569,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 20398-2026</t>
+          <t>A 20399-2026</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3581,7 +3586,7 @@
         <v>46139</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3594,7 +3599,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>2.4</v>
+        <v>0.9</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3637,7 +3642,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 20898-2026</t>
+          <t>A 20398-2026</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3651,10 +3656,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>46142</v>
+        <v>46139</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3667,7 +3672,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>3.6</v>
+        <v>2.4</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3710,7 +3715,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 3222-2022</t>
+          <t>A 20898-2026</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3724,10 +3729,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>44582</v>
+        <v>46142</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3740,7 +3745,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>1.8</v>
+        <v>3.6</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3783,7 +3788,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 34073-2025</t>
+          <t>A 37245-2025</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3793,14 +3798,14 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45845</v>
+        <v>45876</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3813,7 +3818,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>2.9</v>
+        <v>1.1</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3856,7 +3861,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 41699-2026</t>
+          <t>A 34073-2025</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3866,14 +3871,14 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>46301</v>
+        <v>45845</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3885,13 +3890,8 @@
           <t>EKERÖ</t>
         </is>
       </c>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I38" t="n">
-        <v>1.6</v>
+        <v>2.9</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3951,7 +3951,7 @@
         <v>46153</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>

--- a/Översikt EKERÖ.xlsx
+++ b/Översikt EKERÖ.xlsx
@@ -601,7 +601,7 @@
         <v>46241</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -728,7 +728,7 @@
         <v>44872</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -831,7 +831,7 @@
     <row r="4" ht="15" customHeight="1">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A 8216-2023</t>
+          <t>A 35953-2023</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -845,10 +845,10 @@
         </is>
       </c>
       <c r="D4" s="1" t="n">
-        <v>44974</v>
+        <v>45148</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -860,51 +860,161 @@
           <t>EKERÖ</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I4" t="n">
-        <v>5</v>
+        <v>2.1</v>
       </c>
       <c r="J4" t="n">
         <v>2</v>
       </c>
       <c r="K4" t="n">
+        <v>1</v>
+      </c>
+      <c r="L4" t="n">
+        <v>1</v>
+      </c>
+      <c r="M4" t="n">
+        <v>1</v>
+      </c>
+      <c r="N4" t="n">
+        <v>1</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q4" t="n">
         <v>3</v>
       </c>
-      <c r="L4" t="n">
-        <v>0</v>
-      </c>
-      <c r="M4" t="n">
-        <v>1</v>
-      </c>
-      <c r="N4" t="n">
-        <v>0</v>
-      </c>
-      <c r="O4" t="n">
-        <v>0</v>
-      </c>
-      <c r="P4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>1</v>
-      </c>
       <c r="R4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S4" t="n">
         <v>6</v>
       </c>
       <c r="T4" t="n">
+        <v>14</v>
+      </c>
+      <c r="U4" t="n">
         <v>9</v>
       </c>
-      <c r="U4" t="n">
-        <v>0</v>
-      </c>
       <c r="V4" s="2" t="inlineStr">
+        <is>
+          <t>Bombmurkla
+Gul lammticka
+Fyrflikig jordstjärna
+Kamjordstjärna
+Blåbär
+Vanlig groda</t>
+        </is>
+      </c>
+      <c r="W4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/artfynd/A 35953-2023 artfynd.xlsx", "A 35953-2023")</f>
+        <v/>
+      </c>
+      <c r="X4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor/A 35953-2023 karta.png", "A 35953-2023")</f>
+        <v/>
+      </c>
+      <c r="Y4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor_geotiff/A 35953-2023 georefererad karta.tif", "A 35953-2023")</f>
+        <v/>
+      </c>
+      <c r="AA4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomål/A 35953-2023 FSC-klagomål.docx", "A 35953-2023")</f>
+        <v/>
+      </c>
+      <c r="AB4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomålsmail/A 35953-2023 FSC-klagomål mail.docx", "A 35953-2023")</f>
+        <v/>
+      </c>
+      <c r="AC4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsyn/A 35953-2023 tillsynsbegäran.docx", "A 35953-2023")</f>
+        <v/>
+      </c>
+      <c r="AD4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsynsmail/A 35953-2023 tillsynsbegäran mail.docx", "A 35953-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5" ht="15" customHeight="1">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>A 8216-2023</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D5" s="1" t="n">
+        <v>44974</v>
+      </c>
+      <c r="E5" s="1" t="n">
+        <v>46324</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>EKERÖ</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>5</v>
+      </c>
+      <c r="J5" t="n">
+        <v>2</v>
+      </c>
+      <c r="K5" t="n">
+        <v>3</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" t="n">
+        <v>1</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>1</v>
+      </c>
+      <c r="R5" t="n">
+        <v>1</v>
+      </c>
+      <c r="S5" t="n">
+        <v>6</v>
+      </c>
+      <c r="T5" t="n">
+        <v>9</v>
+      </c>
+      <c r="U5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V5" s="2" t="inlineStr">
         <is>
           <t>Gul lammticka
 Blomkålssvamp
@@ -914,142 +1024,32 @@
 Kungsfågel</t>
         </is>
       </c>
-      <c r="W4">
+      <c r="W5">
         <f>HYPERLINK("https://klasma.github.io/Logging_0125/artfynd/A 8216-2023 artfynd.xlsx", "A 8216-2023")</f>
         <v/>
       </c>
-      <c r="X4">
+      <c r="X5">
         <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor/A 8216-2023 karta.png", "A 8216-2023")</f>
         <v/>
       </c>
-      <c r="Y4">
+      <c r="Y5">
         <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor_geotiff/A 8216-2023 georefererad karta.tif", "A 8216-2023")</f>
         <v/>
       </c>
-      <c r="AA4">
+      <c r="AA5">
         <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomål/A 8216-2023 FSC-klagomål.docx", "A 8216-2023")</f>
         <v/>
       </c>
-      <c r="AB4">
+      <c r="AB5">
         <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomålsmail/A 8216-2023 FSC-klagomål mail.docx", "A 8216-2023")</f>
         <v/>
       </c>
-      <c r="AC4">
+      <c r="AC5">
         <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsyn/A 8216-2023 tillsynsbegäran.docx", "A 8216-2023")</f>
         <v/>
       </c>
-      <c r="AD4">
+      <c r="AD5">
         <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsynsmail/A 8216-2023 tillsynsbegäran mail.docx", "A 8216-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="5" ht="15" customHeight="1">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>A 35953-2023</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D5" s="1" t="n">
-        <v>45148</v>
-      </c>
-      <c r="E5" s="1" t="n">
-        <v>46323</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>EKERÖ</t>
-        </is>
-      </c>
-      <c r="I5" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="J5" t="n">
-        <v>2</v>
-      </c>
-      <c r="K5" t="n">
-        <v>1</v>
-      </c>
-      <c r="L5" t="n">
-        <v>1</v>
-      </c>
-      <c r="M5" t="n">
-        <v>1</v>
-      </c>
-      <c r="N5" t="n">
-        <v>1</v>
-      </c>
-      <c r="O5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>3</v>
-      </c>
-      <c r="R5" t="n">
-        <v>2</v>
-      </c>
-      <c r="S5" t="n">
-        <v>6</v>
-      </c>
-      <c r="T5" t="n">
-        <v>14</v>
-      </c>
-      <c r="U5" t="n">
-        <v>9</v>
-      </c>
-      <c r="V5" s="2" t="inlineStr">
-        <is>
-          <t>Bombmurkla
-Gul lammticka
-Fyrflikig jordstjärna
-Kamjordstjärna
-Blåbär
-Vanlig groda</t>
-        </is>
-      </c>
-      <c r="W5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/artfynd/A 35953-2023 artfynd.xlsx", "A 35953-2023")</f>
-        <v/>
-      </c>
-      <c r="X5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor/A 35953-2023 karta.png", "A 35953-2023")</f>
-        <v/>
-      </c>
-      <c r="Y5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor_geotiff/A 35953-2023 georefererad karta.tif", "A 35953-2023")</f>
-        <v/>
-      </c>
-      <c r="AA5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomål/A 35953-2023 FSC-klagomål.docx", "A 35953-2023")</f>
-        <v/>
-      </c>
-      <c r="AB5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomålsmail/A 35953-2023 FSC-klagomål mail.docx", "A 35953-2023")</f>
-        <v/>
-      </c>
-      <c r="AC5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsyn/A 35953-2023 tillsynsbegäran.docx", "A 35953-2023")</f>
-        <v/>
-      </c>
-      <c r="AD5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsynsmail/A 35953-2023 tillsynsbegäran mail.docx", "A 35953-2023")</f>
         <v/>
       </c>
     </row>
@@ -1073,7 +1073,7 @@
         <v>44582</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1182,7 +1182,7 @@
         <v>46119</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1296,7 +1296,7 @@
         <v>46241</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1409,7 +1409,7 @@
         <v>44634</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1499,7 +1499,7 @@
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 49131-2025</t>
+          <t>A 13237-2023</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1513,10 +1513,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>45937</v>
+        <v>45002</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1528,20 +1528,25 @@
           <t>EKERÖ</t>
         </is>
       </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I10" t="n">
-        <v>0.9</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N10" t="n">
         <v>0</v>
@@ -1553,165 +1558,160 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="R10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
         <v>3</v>
       </c>
       <c r="T10" t="n">
+        <v>7</v>
+      </c>
+      <c r="U10" t="n">
+        <v>0</v>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
+        <is>
+          <t>Tallticka
+Granbarkgnagare
+Grönpyrola</t>
+        </is>
+      </c>
+      <c r="W10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/artfynd/A 13237-2023 artfynd.xlsx", "A 13237-2023")</f>
+        <v/>
+      </c>
+      <c r="X10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor/A 13237-2023 karta.png", "A 13237-2023")</f>
+        <v/>
+      </c>
+      <c r="Y10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor_geotiff/A 13237-2023 georefererad karta.tif", "A 13237-2023")</f>
+        <v/>
+      </c>
+      <c r="AA10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomål/A 13237-2023 FSC-klagomål.docx", "A 13237-2023")</f>
+        <v/>
+      </c>
+      <c r="AB10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomålsmail/A 13237-2023 FSC-klagomål mail.docx", "A 13237-2023")</f>
+        <v/>
+      </c>
+      <c r="AC10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsyn/A 13237-2023 tillsynsbegäran.docx", "A 13237-2023")</f>
+        <v/>
+      </c>
+      <c r="AD10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsynsmail/A 13237-2023 tillsynsbegäran mail.docx", "A 13237-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11" ht="15" customHeight="1">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>A 49131-2025</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D11" s="1" t="n">
+        <v>45937</v>
+      </c>
+      <c r="E11" s="1" t="n">
+        <v>46324</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>EKERÖ</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" t="n">
+        <v>2</v>
+      </c>
+      <c r="M11" t="n">
+        <v>1</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" t="n">
         <v>3</v>
       </c>
-      <c r="U10" t="n">
+      <c r="R11" t="n">
+        <v>1</v>
+      </c>
+      <c r="S11" t="n">
         <v>3</v>
       </c>
-      <c r="V10" s="2" t="inlineStr">
+      <c r="T11" t="n">
+        <v>3</v>
+      </c>
+      <c r="U11" t="n">
+        <v>3</v>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
         <is>
           <t>Jättemusseron
 Motaggsvamp
 Svartvit taggsvamp</t>
         </is>
       </c>
-      <c r="W10">
+      <c r="W11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0125/artfynd/A 49131-2025 artfynd.xlsx", "A 49131-2025")</f>
         <v/>
       </c>
-      <c r="X10">
+      <c r="X11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor/A 49131-2025 karta.png", "A 49131-2025")</f>
         <v/>
       </c>
-      <c r="Y10">
+      <c r="Y11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor_geotiff/A 49131-2025 georefererad karta.tif", "A 49131-2025")</f>
         <v/>
       </c>
-      <c r="AA10">
+      <c r="AA11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomål/A 49131-2025 FSC-klagomål.docx", "A 49131-2025")</f>
         <v/>
       </c>
-      <c r="AB10">
+      <c r="AB11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomålsmail/A 49131-2025 FSC-klagomål mail.docx", "A 49131-2025")</f>
         <v/>
       </c>
-      <c r="AC10">
+      <c r="AC11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsyn/A 49131-2025 tillsynsbegäran.docx", "A 49131-2025")</f>
         <v/>
       </c>
-      <c r="AD10">
+      <c r="AD11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsynsmail/A 49131-2025 tillsynsbegäran mail.docx", "A 49131-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="11" ht="15" customHeight="1">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>A 13237-2023</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D11" s="1" t="n">
-        <v>45002</v>
-      </c>
-      <c r="E11" s="1" t="n">
-        <v>46323</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>EKERÖ</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
-      <c r="I11" t="n">
-        <v>9.300000000000001</v>
-      </c>
-      <c r="J11" t="n">
-        <v>0</v>
-      </c>
-      <c r="K11" t="n">
-        <v>2</v>
-      </c>
-      <c r="L11" t="n">
-        <v>1</v>
-      </c>
-      <c r="M11" t="n">
-        <v>0</v>
-      </c>
-      <c r="N11" t="n">
-        <v>0</v>
-      </c>
-      <c r="O11" t="n">
-        <v>0</v>
-      </c>
-      <c r="P11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>1</v>
-      </c>
-      <c r="R11" t="n">
-        <v>0</v>
-      </c>
-      <c r="S11" t="n">
-        <v>3</v>
-      </c>
-      <c r="T11" t="n">
-        <v>7</v>
-      </c>
-      <c r="U11" t="n">
-        <v>0</v>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
-        <is>
-          <t>Tallticka
-Granbarkgnagare
-Grönpyrola</t>
-        </is>
-      </c>
-      <c r="W11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/artfynd/A 13237-2023 artfynd.xlsx", "A 13237-2023")</f>
-        <v/>
-      </c>
-      <c r="X11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor/A 13237-2023 karta.png", "A 13237-2023")</f>
-        <v/>
-      </c>
-      <c r="Y11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor_geotiff/A 13237-2023 georefererad karta.tif", "A 13237-2023")</f>
-        <v/>
-      </c>
-      <c r="AA11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomål/A 13237-2023 FSC-klagomål.docx", "A 13237-2023")</f>
-        <v/>
-      </c>
-      <c r="AB11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomålsmail/A 13237-2023 FSC-klagomål mail.docx", "A 13237-2023")</f>
-        <v/>
-      </c>
-      <c r="AC11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsyn/A 13237-2023 tillsynsbegäran.docx", "A 13237-2023")</f>
-        <v/>
-      </c>
-      <c r="AD11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsynsmail/A 13237-2023 tillsynsbegäran mail.docx", "A 13237-2023")</f>
         <v/>
       </c>
     </row>
@@ -1735,7 +1735,7 @@
         <v>45209</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1850,7 +1850,7 @@
         <v>45170</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1956,7 +1956,7 @@
         <v>44646</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2061,7 +2061,7 @@
         <v>44582</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2149,7 +2149,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 1793-2025</t>
+          <t>A 2533-2026</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2163,10 +2163,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45671</v>
+        <v>46037</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2179,7 +2179,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>1.7</v>
+        <v>1.4</v>
       </c>
       <c r="J16" t="n">
         <v>1</v>
@@ -2212,49 +2212,49 @@
         <v>1</v>
       </c>
       <c r="T16" t="n">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="U16" t="n">
         <v>0</v>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>Mistel</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/artfynd/A 1793-2025 artfynd.xlsx", "A 1793-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/artfynd/A 2533-2026 artfynd.xlsx", "A 2533-2026")</f>
         <v/>
       </c>
       <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor/A 1793-2025 karta.png", "A 1793-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor/A 2533-2026 karta.png", "A 2533-2026")</f>
         <v/>
       </c>
       <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor_geotiff/A 1793-2025 georefererad karta.tif", "A 1793-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor_geotiff/A 2533-2026 georefererad karta.tif", "A 2533-2026")</f>
         <v/>
       </c>
       <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomål/A 1793-2025 FSC-klagomål.docx", "A 1793-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomål/A 2533-2026 FSC-klagomål.docx", "A 2533-2026")</f>
         <v/>
       </c>
       <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomålsmail/A 1793-2025 FSC-klagomål mail.docx", "A 1793-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomålsmail/A 2533-2026 FSC-klagomål mail.docx", "A 2533-2026")</f>
         <v/>
       </c>
       <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsyn/A 1793-2025 tillsynsbegäran.docx", "A 1793-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsyn/A 2533-2026 tillsynsbegäran.docx", "A 2533-2026")</f>
         <v/>
       </c>
       <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsynsmail/A 1793-2025 tillsynsbegäran mail.docx", "A 1793-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsynsmail/A 2533-2026 tillsynsbegäran mail.docx", "A 2533-2026")</f>
         <v/>
       </c>
     </row>
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 2533-2026</t>
+          <t>A 13794-2023</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2268,10 +2268,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>46037</v>
+        <v>45007</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2284,16 +2284,16 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>1.4</v>
+        <v>4.8</v>
       </c>
       <c r="J17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K17" t="n">
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M17" t="n">
         <v>0</v>
@@ -2308,7 +2308,7 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R17" t="n">
         <v>0</v>
@@ -2324,42 +2324,42 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/artfynd/A 2533-2026 artfynd.xlsx", "A 2533-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/artfynd/A 13794-2023 artfynd.xlsx", "A 13794-2023")</f>
         <v/>
       </c>
       <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor/A 2533-2026 karta.png", "A 2533-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor/A 13794-2023 karta.png", "A 13794-2023")</f>
         <v/>
       </c>
       <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor_geotiff/A 2533-2026 georefererad karta.tif", "A 2533-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor_geotiff/A 13794-2023 georefererad karta.tif", "A 13794-2023")</f>
         <v/>
       </c>
       <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomål/A 2533-2026 FSC-klagomål.docx", "A 2533-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomål/A 13794-2023 FSC-klagomål.docx", "A 13794-2023")</f>
         <v/>
       </c>
       <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomålsmail/A 2533-2026 FSC-klagomål mail.docx", "A 2533-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomålsmail/A 13794-2023 FSC-klagomål mail.docx", "A 13794-2023")</f>
         <v/>
       </c>
       <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsyn/A 2533-2026 tillsynsbegäran.docx", "A 2533-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsyn/A 13794-2023 tillsynsbegäran.docx", "A 13794-2023")</f>
         <v/>
       </c>
       <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsynsmail/A 2533-2026 tillsynsbegäran mail.docx", "A 2533-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsynsmail/A 13794-2023 tillsynsbegäran mail.docx", "A 13794-2023")</f>
         <v/>
       </c>
     </row>
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 13794-2023</t>
+          <t>A 1793-2025</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2373,10 +2373,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45007</v>
+        <v>45671</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2389,16 +2389,16 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>4.8</v>
+        <v>1.7</v>
       </c>
       <c r="J18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K18" t="n">
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
         <v>0</v>
@@ -2413,7 +2413,7 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
         <v>0</v>
@@ -2422,42 +2422,42 @@
         <v>1</v>
       </c>
       <c r="T18" t="n">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="U18" t="n">
         <v>0</v>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Mistel</t>
         </is>
       </c>
       <c r="W18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/artfynd/A 13794-2023 artfynd.xlsx", "A 13794-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/artfynd/A 1793-2025 artfynd.xlsx", "A 1793-2025")</f>
         <v/>
       </c>
       <c r="X18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor/A 13794-2023 karta.png", "A 13794-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor/A 1793-2025 karta.png", "A 1793-2025")</f>
         <v/>
       </c>
       <c r="Y18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor_geotiff/A 13794-2023 georefererad karta.tif", "A 13794-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor_geotiff/A 1793-2025 georefererad karta.tif", "A 1793-2025")</f>
         <v/>
       </c>
       <c r="AA18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomål/A 13794-2023 FSC-klagomål.docx", "A 13794-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomål/A 1793-2025 FSC-klagomål.docx", "A 1793-2025")</f>
         <v/>
       </c>
       <c r="AB18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomålsmail/A 13794-2023 FSC-klagomål mail.docx", "A 13794-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomålsmail/A 1793-2025 FSC-klagomål mail.docx", "A 1793-2025")</f>
         <v/>
       </c>
       <c r="AC18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsyn/A 13794-2023 tillsynsbegäran.docx", "A 13794-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsyn/A 1793-2025 tillsynsbegäran.docx", "A 1793-2025")</f>
         <v/>
       </c>
       <c r="AD18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsynsmail/A 13794-2023 tillsynsbegäran mail.docx", "A 13794-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsynsmail/A 1793-2025 tillsynsbegäran mail.docx", "A 1793-2025")</f>
         <v/>
       </c>
     </row>
@@ -2481,7 +2481,7 @@
         <v>44670</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2554,7 +2554,7 @@
         <v>44802</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2610,7 +2610,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 56002-2024</t>
+          <t>A 35955-2023</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2624,10 +2624,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45623</v>
+        <v>45148</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2640,7 +2640,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>3.4</v>
+        <v>1.1</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2700,7 +2700,7 @@
         <v>45645</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2756,7 +2756,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 3222-2022</t>
+          <t>A 56002-2024</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2770,10 +2770,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>44582</v>
+        <v>45623</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2786,7 +2786,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>1.8</v>
+        <v>3.4</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2829,7 +2829,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 50184-2023</t>
+          <t>A 60728-2022</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2843,10 +2843,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45208</v>
+        <v>44913</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2859,7 +2859,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>10.8</v>
+        <v>1.2</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2919,7 +2919,7 @@
         <v>44582</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2975,7 +2975,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 60755-2024</t>
+          <t>A 3222-2022</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2989,10 +2989,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45644</v>
+        <v>44582</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3005,7 +3005,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>2.1</v>
+        <v>1.8</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -3048,7 +3048,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 63378-2025</t>
+          <t>A 37245-2025</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3062,10 +3062,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>46010</v>
+        <v>45876</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3078,7 +3078,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>4.8</v>
+        <v>1.1</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -3121,7 +3121,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 55724-2024</t>
+          <t>A 20898-2026</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3135,10 +3135,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45622</v>
+        <v>46142</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3151,7 +3151,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>0.5</v>
+        <v>3.6</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -3194,7 +3194,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 2535-2026</t>
+          <t>A 34073-2025</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3204,14 +3204,14 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>46037</v>
+        <v>45845</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3224,7 +3224,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>1.6</v>
+        <v>2.9</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3267,7 +3267,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 35955-2023</t>
+          <t>A 63378-2025</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3281,10 +3281,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45148</v>
+        <v>46010</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3297,7 +3297,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>1.1</v>
+        <v>4.8</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3340,7 +3340,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 33154-2026</t>
+          <t>A 2535-2026</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3354,10 +3354,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>46244</v>
+        <v>46037</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3369,13 +3369,8 @@
           <t>EKERÖ</t>
         </is>
       </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I31" t="n">
-        <v>3.5</v>
+        <v>1.6</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3418,7 +3413,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 41699-2026</t>
+          <t>A 60755-2024</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3432,10 +3427,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>46301</v>
+        <v>45644</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3447,13 +3442,8 @@
           <t>EKERÖ</t>
         </is>
       </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I32" t="n">
-        <v>1.6</v>
+        <v>2.1</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3496,7 +3486,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 60728-2022</t>
+          <t>A 20399-2026</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3510,10 +3500,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>44913</v>
+        <v>46139</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3526,7 +3516,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>1.2</v>
+        <v>0.9</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3569,7 +3559,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 20399-2026</t>
+          <t>A 50184-2023</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3583,10 +3573,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>46139</v>
+        <v>45208</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3599,7 +3589,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>0.9</v>
+        <v>10.8</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3642,7 +3632,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 20398-2026</t>
+          <t>A 33154-2026</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3656,10 +3646,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>46139</v>
+        <v>46244</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3671,8 +3661,13 @@
           <t>EKERÖ</t>
         </is>
       </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I35" t="n">
-        <v>2.4</v>
+        <v>3.5</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3715,7 +3710,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 20898-2026</t>
+          <t>A 20398-2026</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3729,10 +3724,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>46142</v>
+        <v>46139</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3745,7 +3740,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>3.6</v>
+        <v>2.4</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3788,7 +3783,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 37245-2025</t>
+          <t>A 41699-2026</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3802,10 +3797,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45876</v>
+        <v>46301</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3817,8 +3812,13 @@
           <t>EKERÖ</t>
         </is>
       </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I37" t="n">
-        <v>1.1</v>
+        <v>1.6</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3861,7 +3861,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 34073-2025</t>
+          <t>A 55724-2024</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3871,14 +3871,14 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45845</v>
+        <v>45622</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3891,7 +3891,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>2.9</v>
+        <v>0.5</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3951,7 +3951,7 @@
         <v>46153</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>

--- a/Översikt EKERÖ.xlsx
+++ b/Översikt EKERÖ.xlsx
@@ -601,7 +601,7 @@
         <v>46241</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -728,7 +728,7 @@
         <v>44872</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -831,7 +831,7 @@
     <row r="4" ht="15" customHeight="1">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A 35953-2023</t>
+          <t>A 8216-2023</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -845,10 +845,10 @@
         </is>
       </c>
       <c r="D4" s="1" t="n">
-        <v>45148</v>
+        <v>44974</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -860,23 +860,28 @@
           <t>EKERÖ</t>
         </is>
       </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I4" t="n">
-        <v>2.1</v>
+        <v>5</v>
       </c>
       <c r="J4" t="n">
         <v>2</v>
       </c>
       <c r="K4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
         <v>1</v>
       </c>
       <c r="N4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -885,21 +890,131 @@
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="R4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S4" t="n">
         <v>6</v>
       </c>
       <c r="T4" t="n">
+        <v>9</v>
+      </c>
+      <c r="U4" t="n">
+        <v>0</v>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
+        <is>
+          <t>Gul lammticka
+Blomkålssvamp
+Granbarkgnagare
+Thomsons trägnagare
+Blåsippa
+Kungsfågel</t>
+        </is>
+      </c>
+      <c r="W4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/artfynd/A 8216-2023 artfynd.xlsx", "A 8216-2023")</f>
+        <v/>
+      </c>
+      <c r="X4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor/A 8216-2023 karta.png", "A 8216-2023")</f>
+        <v/>
+      </c>
+      <c r="Y4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor_geotiff/A 8216-2023 georefererad karta.tif", "A 8216-2023")</f>
+        <v/>
+      </c>
+      <c r="AA4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomål/A 8216-2023 FSC-klagomål.docx", "A 8216-2023")</f>
+        <v/>
+      </c>
+      <c r="AB4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomålsmail/A 8216-2023 FSC-klagomål mail.docx", "A 8216-2023")</f>
+        <v/>
+      </c>
+      <c r="AC4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsyn/A 8216-2023 tillsynsbegäran.docx", "A 8216-2023")</f>
+        <v/>
+      </c>
+      <c r="AD4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsynsmail/A 8216-2023 tillsynsbegäran mail.docx", "A 8216-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5" ht="15" customHeight="1">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>A 35953-2023</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D5" s="1" t="n">
+        <v>45148</v>
+      </c>
+      <c r="E5" s="1" t="n">
+        <v>46326</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>EKERÖ</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="J5" t="n">
+        <v>2</v>
+      </c>
+      <c r="K5" t="n">
+        <v>1</v>
+      </c>
+      <c r="L5" t="n">
+        <v>1</v>
+      </c>
+      <c r="M5" t="n">
+        <v>1</v>
+      </c>
+      <c r="N5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>3</v>
+      </c>
+      <c r="R5" t="n">
+        <v>2</v>
+      </c>
+      <c r="S5" t="n">
+        <v>6</v>
+      </c>
+      <c r="T5" t="n">
         <v>14</v>
       </c>
-      <c r="U4" t="n">
+      <c r="U5" t="n">
         <v>9</v>
       </c>
-      <c r="V4" s="2" t="inlineStr">
+      <c r="V5" s="2" t="inlineStr">
         <is>
           <t>Bombmurkla
 Gul lammticka
@@ -909,147 +1024,32 @@
 Vanlig groda</t>
         </is>
       </c>
-      <c r="W4">
+      <c r="W5">
         <f>HYPERLINK("https://klasma.github.io/Logging_0125/artfynd/A 35953-2023 artfynd.xlsx", "A 35953-2023")</f>
         <v/>
       </c>
-      <c r="X4">
+      <c r="X5">
         <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor/A 35953-2023 karta.png", "A 35953-2023")</f>
         <v/>
       </c>
-      <c r="Y4">
+      <c r="Y5">
         <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor_geotiff/A 35953-2023 georefererad karta.tif", "A 35953-2023")</f>
         <v/>
       </c>
-      <c r="AA4">
+      <c r="AA5">
         <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomål/A 35953-2023 FSC-klagomål.docx", "A 35953-2023")</f>
         <v/>
       </c>
-      <c r="AB4">
+      <c r="AB5">
         <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomålsmail/A 35953-2023 FSC-klagomål mail.docx", "A 35953-2023")</f>
         <v/>
       </c>
-      <c r="AC4">
+      <c r="AC5">
         <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsyn/A 35953-2023 tillsynsbegäran.docx", "A 35953-2023")</f>
         <v/>
       </c>
-      <c r="AD4">
+      <c r="AD5">
         <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsynsmail/A 35953-2023 tillsynsbegäran mail.docx", "A 35953-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="5" ht="15" customHeight="1">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>A 8216-2023</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D5" s="1" t="n">
-        <v>44974</v>
-      </c>
-      <c r="E5" s="1" t="n">
-        <v>46324</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>EKERÖ</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
-      <c r="I5" t="n">
-        <v>5</v>
-      </c>
-      <c r="J5" t="n">
-        <v>2</v>
-      </c>
-      <c r="K5" t="n">
-        <v>3</v>
-      </c>
-      <c r="L5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M5" t="n">
-        <v>1</v>
-      </c>
-      <c r="N5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>1</v>
-      </c>
-      <c r="R5" t="n">
-        <v>1</v>
-      </c>
-      <c r="S5" t="n">
-        <v>6</v>
-      </c>
-      <c r="T5" t="n">
-        <v>9</v>
-      </c>
-      <c r="U5" t="n">
-        <v>0</v>
-      </c>
-      <c r="V5" s="2" t="inlineStr">
-        <is>
-          <t>Gul lammticka
-Blomkålssvamp
-Granbarkgnagare
-Thomsons trägnagare
-Blåsippa
-Kungsfågel</t>
-        </is>
-      </c>
-      <c r="W5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/artfynd/A 8216-2023 artfynd.xlsx", "A 8216-2023")</f>
-        <v/>
-      </c>
-      <c r="X5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor/A 8216-2023 karta.png", "A 8216-2023")</f>
-        <v/>
-      </c>
-      <c r="Y5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor_geotiff/A 8216-2023 georefererad karta.tif", "A 8216-2023")</f>
-        <v/>
-      </c>
-      <c r="AA5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomål/A 8216-2023 FSC-klagomål.docx", "A 8216-2023")</f>
-        <v/>
-      </c>
-      <c r="AB5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomålsmail/A 8216-2023 FSC-klagomål mail.docx", "A 8216-2023")</f>
-        <v/>
-      </c>
-      <c r="AC5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsyn/A 8216-2023 tillsynsbegäran.docx", "A 8216-2023")</f>
-        <v/>
-      </c>
-      <c r="AD5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsynsmail/A 8216-2023 tillsynsbegäran mail.docx", "A 8216-2023")</f>
         <v/>
       </c>
     </row>
@@ -1073,7 +1073,7 @@
         <v>44582</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1182,7 +1182,7 @@
         <v>46119</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1296,7 +1296,7 @@
         <v>46241</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1409,7 +1409,7 @@
         <v>44634</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1516,7 +1516,7 @@
         <v>45002</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1628,7 +1628,7 @@
         <v>45937</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1735,7 +1735,7 @@
         <v>45209</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1850,7 +1850,7 @@
         <v>45170</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1956,7 +1956,7 @@
         <v>44646</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2061,7 +2061,7 @@
         <v>44582</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2149,7 +2149,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 2533-2026</t>
+          <t>A 13794-2023</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2163,10 +2163,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>46037</v>
+        <v>45007</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2179,16 +2179,16 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>1.4</v>
+        <v>4.8</v>
       </c>
       <c r="J16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K16" t="n">
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M16" t="n">
         <v>0</v>
@@ -2203,7 +2203,7 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R16" t="n">
         <v>0</v>
@@ -2219,42 +2219,42 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/artfynd/A 2533-2026 artfynd.xlsx", "A 2533-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/artfynd/A 13794-2023 artfynd.xlsx", "A 13794-2023")</f>
         <v/>
       </c>
       <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor/A 2533-2026 karta.png", "A 2533-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor/A 13794-2023 karta.png", "A 13794-2023")</f>
         <v/>
       </c>
       <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor_geotiff/A 2533-2026 georefererad karta.tif", "A 2533-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor_geotiff/A 13794-2023 georefererad karta.tif", "A 13794-2023")</f>
         <v/>
       </c>
       <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomål/A 2533-2026 FSC-klagomål.docx", "A 2533-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomål/A 13794-2023 FSC-klagomål.docx", "A 13794-2023")</f>
         <v/>
       </c>
       <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomålsmail/A 2533-2026 FSC-klagomål mail.docx", "A 2533-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomålsmail/A 13794-2023 FSC-klagomål mail.docx", "A 13794-2023")</f>
         <v/>
       </c>
       <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsyn/A 2533-2026 tillsynsbegäran.docx", "A 2533-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsyn/A 13794-2023 tillsynsbegäran.docx", "A 13794-2023")</f>
         <v/>
       </c>
       <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsynsmail/A 2533-2026 tillsynsbegäran mail.docx", "A 2533-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsynsmail/A 13794-2023 tillsynsbegäran mail.docx", "A 13794-2023")</f>
         <v/>
       </c>
     </row>
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 13794-2023</t>
+          <t>A 2533-2026</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2268,10 +2268,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45007</v>
+        <v>46037</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2284,16 +2284,16 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>4.8</v>
+        <v>1.4</v>
       </c>
       <c r="J17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K17" t="n">
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
         <v>0</v>
@@ -2308,7 +2308,7 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
         <v>0</v>
@@ -2324,35 +2324,35 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/artfynd/A 13794-2023 artfynd.xlsx", "A 13794-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/artfynd/A 2533-2026 artfynd.xlsx", "A 2533-2026")</f>
         <v/>
       </c>
       <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor/A 13794-2023 karta.png", "A 13794-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor/A 2533-2026 karta.png", "A 2533-2026")</f>
         <v/>
       </c>
       <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor_geotiff/A 13794-2023 georefererad karta.tif", "A 13794-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/kartor_geotiff/A 2533-2026 georefererad karta.tif", "A 2533-2026")</f>
         <v/>
       </c>
       <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomål/A 13794-2023 FSC-klagomål.docx", "A 13794-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomål/A 2533-2026 FSC-klagomål.docx", "A 2533-2026")</f>
         <v/>
       </c>
       <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomålsmail/A 13794-2023 FSC-klagomål mail.docx", "A 13794-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/klagomålsmail/A 2533-2026 FSC-klagomål mail.docx", "A 2533-2026")</f>
         <v/>
       </c>
       <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsyn/A 13794-2023 tillsynsbegäran.docx", "A 13794-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsyn/A 2533-2026 tillsynsbegäran.docx", "A 2533-2026")</f>
         <v/>
       </c>
       <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsynsmail/A 13794-2023 tillsynsbegäran mail.docx", "A 13794-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0125/tillsynsmail/A 2533-2026 tillsynsbegäran mail.docx", "A 2533-2026")</f>
         <v/>
       </c>
     </row>
@@ -2376,7 +2376,7 @@
         <v>45671</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2481,7 +2481,7 @@
         <v>44670</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2554,7 +2554,7 @@
         <v>44802</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2610,7 +2610,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 35955-2023</t>
+          <t>A 3219-2022</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2624,10 +2624,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45148</v>
+        <v>44582</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2640,7 +2640,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>1.1</v>
+        <v>0.5</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2683,7 +2683,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 61217-2024</t>
+          <t>A 50184-2023</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2697,10 +2697,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>45645</v>
+        <v>45208</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2713,7 +2713,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>0.8</v>
+        <v>10.8</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2756,7 +2756,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 56002-2024</t>
+          <t>A 2535-2026</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2770,10 +2770,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45623</v>
+        <v>46037</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2786,7 +2786,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>3.4</v>
+        <v>1.6</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2829,7 +2829,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 60728-2022</t>
+          <t>A 37245-2025</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2843,10 +2843,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>44913</v>
+        <v>45876</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2859,7 +2859,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2902,7 +2902,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 3219-2022</t>
+          <t>A 55724-2024</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2916,10 +2916,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>44582</v>
+        <v>45622</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2975,7 +2975,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 3222-2022</t>
+          <t>A 63378-2025</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2989,10 +2989,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>44582</v>
+        <v>46010</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3005,7 +3005,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>1.8</v>
+        <v>4.8</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -3048,7 +3048,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 37245-2025</t>
+          <t>A 35955-2023</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3062,10 +3062,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45876</v>
+        <v>45148</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3121,7 +3121,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 20898-2026</t>
+          <t>A 61217-2024</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3135,10 +3135,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>46142</v>
+        <v>45645</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3151,7 +3151,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>3.6</v>
+        <v>0.8</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -3194,7 +3194,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 34073-2025</t>
+          <t>A 56002-2024</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3204,14 +3204,14 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45845</v>
+        <v>45623</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3224,7 +3224,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>2.9</v>
+        <v>3.4</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3267,7 +3267,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 63378-2025</t>
+          <t>A 60728-2022</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3281,10 +3281,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>46010</v>
+        <v>44913</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3297,7 +3297,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>4.8</v>
+        <v>1.2</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3340,7 +3340,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 2535-2026</t>
+          <t>A 20399-2026</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3354,10 +3354,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>46037</v>
+        <v>46139</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3370,7 +3370,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>1.6</v>
+        <v>0.9</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3413,7 +3413,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 60755-2024</t>
+          <t>A 20398-2026</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3427,10 +3427,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45644</v>
+        <v>46139</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3443,7 +3443,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>2.1</v>
+        <v>2.4</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3486,7 +3486,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 20399-2026</t>
+          <t>A 3222-2022</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3500,10 +3500,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>46139</v>
+        <v>44582</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3516,7 +3516,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>0.9</v>
+        <v>1.8</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3559,7 +3559,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 50184-2023</t>
+          <t>A 20898-2026</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3573,10 +3573,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45208</v>
+        <v>46142</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3589,7 +3589,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>10.8</v>
+        <v>3.6</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3632,7 +3632,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 33154-2026</t>
+          <t>A 34073-2025</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3642,14 +3642,14 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>46244</v>
+        <v>45845</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3661,13 +3661,8 @@
           <t>EKERÖ</t>
         </is>
       </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I35" t="n">
-        <v>3.5</v>
+        <v>2.9</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3710,7 +3705,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 20398-2026</t>
+          <t>A 60755-2024</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3724,10 +3719,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>46139</v>
+        <v>45644</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3740,7 +3735,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>2.4</v>
+        <v>2.1</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3783,7 +3778,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 41699-2026</t>
+          <t>A 33154-2026</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3797,10 +3792,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>46301</v>
+        <v>46244</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3818,7 +3813,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>1.6</v>
+        <v>3.5</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3861,7 +3856,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 55724-2024</t>
+          <t>A 41699-2026</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3875,10 +3870,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45622</v>
+        <v>46301</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3890,8 +3885,13 @@
           <t>EKERÖ</t>
         </is>
       </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I38" t="n">
-        <v>0.5</v>
+        <v>1.6</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3951,7 +3951,7 @@
         <v>46153</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
